--- a/db/A7XLK-1405-TVSeries.xlsx
+++ b/db/A7XLK-1405-TVSeries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B99EE0E5-5EB5-5643-83C2-1CDC2ADB86DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC76F14A-5B43-1845-A25C-FBEF795DE0FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="460" yWindow="600" windowWidth="39500" windowHeight="17320" xr2:uid="{BAC94C6D-C196-2D4F-A2F2-89F0A182D671}"/>
+    <workbookView xWindow="-34440" yWindow="6460" windowWidth="29840" windowHeight="17320" xr2:uid="{BAC94C6D-C196-2D4F-A2F2-89F0A182D671}"/>
   </bookViews>
   <sheets>
     <sheet name="今日電影" sheetId="1" r:id="rId1"/>
@@ -136,9 +136,6 @@
     <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-014.jpeg</t>
   </si>
   <si>
-    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-015.jpeg</t>
-  </si>
-  <si>
     <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-016.jpeg</t>
   </si>
   <si>
@@ -169,9 +166,6 @@
     <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-025.jpeg</t>
   </si>
   <si>
-    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-026.jpeg</t>
-  </si>
-  <si>
     <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-027.jpeg</t>
   </si>
   <si>
@@ -196,9 +190,6 @@
     <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-035.jpeg</t>
   </si>
   <si>
-    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-036.jpeg</t>
-  </si>
-  <si>
     <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-037.jpeg</t>
   </si>
   <si>
@@ -1104,6 +1095,18 @@
   </si>
   <si>
     <t>2020以前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-015.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-026.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-036.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1517,7 +1520,7 @@
         <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>9</v>
@@ -1540,7 +1543,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -1552,27 +1555,27 @@
         <v>2021</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H2" s="3">
         <v>9760868</v>
       </c>
       <c r="I2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
@@ -1584,13 +1587,13 @@
         <v>2021</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H3" s="3">
         <v>8844170</v>
@@ -1599,12 +1602,12 @@
         <v>23</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
@@ -1616,27 +1619,27 @@
         <v>2021</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F4" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="G4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H4" s="3">
         <v>6002697</v>
       </c>
       <c r="I4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
@@ -1648,27 +1651,27 @@
         <v>2021</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F5" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H5" s="3">
         <v>4155026</v>
       </c>
       <c r="I5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
@@ -1680,13 +1683,13 @@
         <v>2021</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H6" s="3">
         <v>2815834</v>
@@ -1695,12 +1698,12 @@
         <v>16</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
@@ -1712,13 +1715,13 @@
         <v>2021</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H7" s="3">
         <v>2454774</v>
@@ -1727,12 +1730,12 @@
         <v>24</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
@@ -1744,13 +1747,13 @@
         <v>2021</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F8" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H8" s="3">
         <v>2378245</v>
@@ -1759,7 +1762,7 @@
         <v>21</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1776,13 +1779,13 @@
         <v>2021</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H9" s="3">
         <v>2132343</v>
@@ -1791,12 +1794,12 @@
         <v>15</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
@@ -1808,13 +1811,13 @@
         <v>2021</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F10" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H10" s="3">
         <v>2059245</v>
@@ -1823,12 +1826,12 @@
         <v>20</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
@@ -1840,13 +1843,13 @@
         <v>2021</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F11" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G11" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H11" s="3">
         <v>1960230</v>
@@ -1855,12 +1858,12 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
@@ -1872,27 +1875,27 @@
         <v>2021</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F12" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="G12" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H12" s="3">
         <v>1845243</v>
       </c>
       <c r="I12" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B13" t="s">
         <v>11</v>
@@ -1904,13 +1907,13 @@
         <v>2021</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F13" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G13" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H13" s="3">
         <v>1796008</v>
@@ -1919,12 +1922,12 @@
         <v>27</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
@@ -1936,27 +1939,27 @@
         <v>2021</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F14" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="G14" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H14" s="3">
         <v>1758290</v>
       </c>
       <c r="I14" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B15" t="s">
         <v>11</v>
@@ -1968,27 +1971,27 @@
         <v>2021</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F15" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="G15" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H15" s="3">
         <v>1560320</v>
       </c>
       <c r="I15" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s">
         <v>11</v>
@@ -2000,13 +2003,13 @@
         <v>2021</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F16" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G16" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H16" s="3">
         <v>1212038</v>
@@ -2015,12 +2018,12 @@
         <v>25</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B17" t="s">
         <v>11</v>
@@ -2032,13 +2035,13 @@
         <v>2021</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F17" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G17" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H17" s="3">
         <v>1071359</v>
@@ -2047,12 +2050,12 @@
         <v>26</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B18" t="s">
         <v>11</v>
@@ -2064,13 +2067,13 @@
         <v>2021</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F18" t="s">
         <v>164</v>
       </c>
-      <c r="F18" t="s">
-        <v>167</v>
-      </c>
       <c r="G18" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H18" s="3">
         <v>1028428</v>
@@ -2079,12 +2082,12 @@
         <v>17</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B19" t="s">
         <v>11</v>
@@ -2096,10 +2099,10 @@
         <v>2021</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G19" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H19" s="3">
         <v>976802</v>
@@ -2108,12 +2111,12 @@
         <v>19</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B20" t="s">
         <v>11</v>
@@ -2125,30 +2128,30 @@
         <v>2021</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F20" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G20" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H20" s="3">
         <v>653514</v>
       </c>
       <c r="I20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B21" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C21">
         <v>2021</v>
@@ -2157,27 +2160,27 @@
         <v>2021</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F21" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="G21" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H21" s="3">
         <v>459883</v>
       </c>
       <c r="I21" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
         <v>11</v>
@@ -2189,13 +2192,13 @@
         <v>2021</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F22" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G22" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H22" s="3">
         <v>303763</v>
@@ -2204,7 +2207,7 @@
         <v>18</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -2236,12 +2239,12 @@
         <v>14</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B24" t="s">
         <v>11</v>
@@ -2253,27 +2256,27 @@
         <v>2021</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F24" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H24" s="3">
         <v>132204</v>
       </c>
       <c r="I24" t="s">
-        <v>28</v>
+        <v>289</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B25" t="s">
         <v>11</v>
@@ -2285,27 +2288,27 @@
         <v>2021</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F25" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="G25" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H25" s="3">
         <v>121479</v>
       </c>
       <c r="I25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B26" t="s">
         <v>11</v>
@@ -2317,27 +2320,27 @@
         <v>2021</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F26" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G26" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H26" s="3">
         <v>4524</v>
       </c>
       <c r="I26" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B27" t="s">
         <v>11</v>
@@ -2346,30 +2349,30 @@
         <v>2020</v>
       </c>
       <c r="D27" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F27" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G27" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H27" s="3">
         <v>7733587</v>
       </c>
       <c r="I27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B28" t="s">
         <v>11</v>
@@ -2378,30 +2381,30 @@
         <v>2020</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F28" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G28" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H28" s="3">
         <v>1218509</v>
       </c>
       <c r="I28" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B29" t="s">
         <v>11</v>
@@ -2410,30 +2413,30 @@
         <v>2020</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F29" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="G29" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H29" s="3">
         <v>613506</v>
       </c>
       <c r="I29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B30" t="s">
         <v>11</v>
@@ -2442,30 +2445,30 @@
         <v>2020</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F30" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="G30" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H30" s="3">
         <v>552739</v>
       </c>
       <c r="I30" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B31" t="s">
         <v>11</v>
@@ -2474,30 +2477,30 @@
         <v>2020</v>
       </c>
       <c r="D31" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F31" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="G31" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H31" s="3">
         <v>189629</v>
       </c>
       <c r="I31" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B32" t="s">
         <v>11</v>
@@ -2506,30 +2509,30 @@
         <v>2020</v>
       </c>
       <c r="D32" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F32" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G32" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H32" s="3">
         <v>25178</v>
       </c>
       <c r="I32" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B33" t="s">
         <v>11</v>
@@ -2538,30 +2541,30 @@
         <v>2020</v>
       </c>
       <c r="D33" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F33" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G33" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H33" s="3">
         <v>19483</v>
       </c>
       <c r="I33" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B34" t="s">
         <v>11</v>
@@ -2570,30 +2573,30 @@
         <v>2019</v>
       </c>
       <c r="D34" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F34" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="G34" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H34" s="3">
         <v>5265895</v>
       </c>
       <c r="I34" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B35" t="s">
         <v>11</v>
@@ -2602,62 +2605,62 @@
         <v>2019</v>
       </c>
       <c r="D35" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F35" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="G35" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H35" s="3">
         <v>2991300</v>
       </c>
       <c r="I35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B36" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C36">
         <v>2019</v>
       </c>
       <c r="D36" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F36" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="G36" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H36" s="3">
         <v>2563754</v>
       </c>
       <c r="I36" t="s">
-        <v>39</v>
+        <v>290</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B37" t="s">
         <v>11</v>
@@ -2666,30 +2669,30 @@
         <v>2019</v>
       </c>
       <c r="D37" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F37" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="G37" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H37" s="3">
         <v>587879</v>
       </c>
       <c r="I37" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B38" t="s">
         <v>11</v>
@@ -2698,30 +2701,30 @@
         <v>2019</v>
       </c>
       <c r="D38" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F38" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G38" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H38" s="3">
         <v>517958</v>
       </c>
       <c r="I38" t="s">
-        <v>48</v>
+        <v>291</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B39" t="s">
         <v>11</v>
@@ -2730,30 +2733,30 @@
         <v>2019</v>
       </c>
       <c r="D39" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F39" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G39" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H39" s="3">
         <v>349359</v>
       </c>
       <c r="I39" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B40" t="s">
         <v>11</v>
@@ -2762,30 +2765,30 @@
         <v>2018</v>
       </c>
       <c r="D40" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F40" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G40" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H40" s="3">
         <v>5275870</v>
       </c>
       <c r="I40" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B41" t="s">
         <v>11</v>
@@ -2794,30 +2797,30 @@
         <v>2018</v>
       </c>
       <c r="D41" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F41" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G41" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H41" s="3">
         <v>4674495</v>
       </c>
       <c r="I41" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B42" t="s">
         <v>11</v>
@@ -2826,30 +2829,30 @@
         <v>2018</v>
       </c>
       <c r="D42" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F42" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="G42" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H42" s="3">
         <v>4141267</v>
       </c>
       <c r="I42" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B43" t="s">
         <v>11</v>
@@ -2858,30 +2861,30 @@
         <v>2018</v>
       </c>
       <c r="D43" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F43" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G43" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H43" s="3">
         <v>1265188</v>
       </c>
       <c r="I43" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="J43" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B44" t="s">
         <v>11</v>
@@ -2890,30 +2893,30 @@
         <v>2018</v>
       </c>
       <c r="D44" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F44" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="G44" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H44" s="3">
         <v>1259285</v>
       </c>
       <c r="I44" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B45" t="s">
         <v>11</v>
@@ -2922,30 +2925,30 @@
         <v>2017</v>
       </c>
       <c r="D45" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F45" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G45" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H45" s="3">
         <v>617188</v>
       </c>
       <c r="I45" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B46" t="s">
         <v>11</v>
@@ -2954,30 +2957,30 @@
         <v>2017</v>
       </c>
       <c r="D46" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F46" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="G46" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H46" s="3">
         <v>290313</v>
       </c>
       <c r="I46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B47" t="s">
         <v>11</v>
@@ -2986,30 +2989,30 @@
         <v>2017</v>
       </c>
       <c r="D47" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F47" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="G47" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H47" s="3">
         <v>99365</v>
       </c>
       <c r="I47" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B48" t="s">
         <v>11</v>
@@ -3018,30 +3021,30 @@
         <v>2016</v>
       </c>
       <c r="D48" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F48" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G48" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H48" s="3">
         <v>243599</v>
       </c>
       <c r="I48" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B49" t="s">
         <v>11</v>
@@ -3050,30 +3053,30 @@
         <v>2016</v>
       </c>
       <c r="D49" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F49" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="G49" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H49" s="3">
         <v>136424</v>
       </c>
       <c r="I49" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B50" t="s">
         <v>11</v>
@@ -3082,30 +3085,30 @@
         <v>2015</v>
       </c>
       <c r="D50" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F50" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="G50" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H50" s="3">
         <v>947291</v>
       </c>
       <c r="I50" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B51" t="s">
         <v>11</v>
@@ -3114,25 +3117,25 @@
         <v>2011</v>
       </c>
       <c r="D51" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F51" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G51" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H51" s="3">
         <v>802315</v>
       </c>
       <c r="I51" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>

--- a/db/A7XLK-1405-TVSeries.xlsx
+++ b/db/A7XLK-1405-TVSeries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC76F14A-5B43-1845-A25C-FBEF795DE0FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C1520D-FF5E-E341-9B5C-16573D22E03D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34440" yWindow="6460" windowWidth="29840" windowHeight="17320" xr2:uid="{BAC94C6D-C196-2D4F-A2F2-89F0A182D671}"/>
+    <workbookView xWindow="-35900" yWindow="6400" windowWidth="29840" windowHeight="17320" xr2:uid="{BAC94C6D-C196-2D4F-A2F2-89F0A182D671}"/>
   </bookViews>
   <sheets>
     <sheet name="今日電影" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="400">
   <si>
     <t>No</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1094,10 +1094,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2020以前</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-015.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1107,6 +1103,408 @@
   </si>
   <si>
     <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-036.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>今年新戲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>歷史名劇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>028</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>琅琊榜之風起長林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>劉昊然 佟麗婭 張慧雯 孫淳 吳昊宸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/3638.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-028.jpeg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海岸村恰恰恰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>好好生活</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上游</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>叛逆者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸡毛飞上天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>贅婿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我的巴比倫戀人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>愛上特種兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我的砍價女王</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我的前半生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>傳聞中的陳芊芊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安家</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>喬家的兒女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幸福一家人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>獨孤天下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>北上廣依然相信愛情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最好的我們</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>059</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>060</t>
+  </si>
+  <si>
+    <t>061</t>
+  </si>
+  <si>
+    <t>063</t>
+  </si>
+  <si>
+    <t>064</t>
+  </si>
+  <si>
+    <t>065</t>
+  </si>
+  <si>
+    <t>066</t>
+  </si>
+  <si>
+    <t>068</t>
+  </si>
+  <si>
+    <t>069</t>
+  </si>
+  <si>
+    <t>070</t>
+  </si>
+  <si>
+    <t>073</t>
+  </si>
+  <si>
+    <t>075</t>
+  </si>
+  <si>
+    <t>076</t>
+  </si>
+  <si>
+    <t>077</t>
+  </si>
+  <si>
+    <t>078</t>
+  </si>
+  <si>
+    <t>079</t>
+  </si>
+  <si>
+    <t>080</t>
+  </si>
+  <si>
+    <t>081</t>
+  </si>
+  <si>
+    <t>082</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-059.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-060.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-061.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-063.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-064.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-065.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-066.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-069.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-073.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-075.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-076.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-078.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-079.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-080.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-081.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-082.jpeg</t>
+  </si>
+  <si>
+    <t>韓國</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>申敏兒 金宣虎 李相二 孔敏晶 金英玉 趙漢哲 印喬鎮 李鳳蓮 李世亨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/158142.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">林雨申 蔡文靜 鄒廷威 姜妍 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/160783.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王瑞昌 胡意旋 陳博豪 戚硯笛 姜卓君 譚泉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-36</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/156621.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">朱一龍 童瑤 王志文 王陽 朱珠 李強 張子賢 姚安濂 袁文康 代旭 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/150714.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>二十不惑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>關曉彤 卜冠今 李庚希 董思怡 金世佳 牛駿峯 王安宇 曹恩齊 徐紹瑛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/65029.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/137570.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>郭麒麟 宋軼 蔣依依 高曙光 海一天 尚語賢 朱珠 張若昀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>張譯 殷桃 陶澤如 張佳寧 高姝瑤 吳其江 花昆 程實 林一霆 楊洪武 閆龍飛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/121496.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-068.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鳳小岳 卜冠今 許瑋甯 周遊 王瑞昌 朱顏曼滋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/159839.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">黃景瑜 李沁 楊舒 聶子皓 姜嫄 趙荀 傅浤鳴 於躍 費鯉齊 劉曉潔 徐洪浩 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/150167.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-070.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">林更新 吳謹言 吳奇隆 王鶴潤 馬思超 宋奕星 陳希郡 艾曉琪 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/158432.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>親愛的，熱愛的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">楊紫 李現 胡一天 李鴻其 王真兒 李澤鋒 姜珮瑤 王樂君 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>41</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/29613.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>靳東 馬伊琍 袁泉 雷佳音 吳越 許娣 張齡心 鄔君梅 陳道明 梅婷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/137479.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>趙露思 丁禹兮 盛英豪 周紫馨 權沛倫 陳名豪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/58681.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-077.webp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>孫儷 羅晉 張萌 郭濤 胡可 王自健 田雷 楊皓宇 孫佳雨 張曉謙 王藝哲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>53</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/36545.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白宇 宋祖兒 毛曉彤 張晚意 周翊然 劉鈞 周放 曲哲明 侯雯元 孫安可</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/157499.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">董潔 翟天臨 李立羣 邱澤 何美璇 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/15007.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>胡冰卿 張丹峯 安以軒 徐正溪 李依曉 應昊茗 鄒廷威 黃文豪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/5355.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">朱亞文 陳妍希 張鐸 曾泳醍 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>44</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">劉昊然 譚松韻 王櫟鑫 董晴 李硯 方文強 陳夢希 劉啓恆 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/137359.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/139988.html</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1496,7 +1894,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C0AA310-9C39-A04D-BB87-9521EAB5B98C}">
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
@@ -1551,8 +1949,8 @@
       <c r="C2">
         <v>2021</v>
       </c>
-      <c r="D2">
-        <v>2021</v>
+      <c r="D2" t="s">
+        <v>291</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>230</v>
@@ -1583,8 +1981,8 @@
       <c r="C3">
         <v>2021</v>
       </c>
-      <c r="D3">
-        <v>2021</v>
+      <c r="D3" t="s">
+        <v>291</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>179</v>
@@ -1615,8 +2013,8 @@
       <c r="C4">
         <v>2021</v>
       </c>
-      <c r="D4">
-        <v>2021</v>
+      <c r="D4" t="s">
+        <v>291</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>189</v>
@@ -1639,7 +2037,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>76</v>
+        <v>321</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
@@ -1647,31 +2045,31 @@
       <c r="C5">
         <v>2021</v>
       </c>
-      <c r="D5">
-        <v>2021</v>
+      <c r="D5" t="s">
+        <v>291</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F5" t="s">
-        <v>233</v>
+        <v>366</v>
       </c>
       <c r="G5" t="s">
-        <v>113</v>
+        <v>303</v>
       </c>
       <c r="H5" s="3">
-        <v>4155026</v>
+        <v>5150111</v>
       </c>
       <c r="I5" t="s">
-        <v>41</v>
+        <v>340</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>234</v>
+        <v>368</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
@@ -1679,31 +2077,31 @@
       <c r="C6">
         <v>2021</v>
       </c>
-      <c r="D6">
-        <v>2021</v>
+      <c r="D6" t="s">
+        <v>291</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="F6" t="s">
-        <v>162</v>
+        <v>233</v>
       </c>
       <c r="G6" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="H6" s="3">
-        <v>2815834</v>
+        <v>4155026</v>
       </c>
       <c r="I6" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>163</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
@@ -1711,63 +2109,63 @@
       <c r="C7">
         <v>2021</v>
       </c>
-      <c r="D7">
-        <v>2021</v>
+      <c r="D7" t="s">
+        <v>291</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="F7" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="G7" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="H7" s="3">
-        <v>2454774</v>
+        <v>2815834</v>
       </c>
       <c r="I7" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>54</v>
+        <v>315</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>350</v>
       </c>
       <c r="C8">
         <v>2021</v>
       </c>
-      <c r="D8">
-        <v>2021</v>
+      <c r="D8" t="s">
+        <v>291</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>173</v>
+        <v>351</v>
       </c>
       <c r="F8" t="s">
-        <v>174</v>
+        <v>352</v>
       </c>
       <c r="G8" t="s">
-        <v>91</v>
+        <v>298</v>
       </c>
       <c r="H8" s="3">
-        <v>2378245</v>
+        <v>2535509</v>
       </c>
       <c r="I8" t="s">
-        <v>21</v>
+        <v>334</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>175</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
@@ -1775,31 +2173,31 @@
       <c r="C9">
         <v>2021</v>
       </c>
-      <c r="D9">
-        <v>2021</v>
+      <c r="D9" t="s">
+        <v>291</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="F9" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="G9" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="H9" s="3">
-        <v>2132343</v>
+        <v>2454774</v>
       </c>
       <c r="I9" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
@@ -1807,31 +2205,31 @@
       <c r="C10">
         <v>2021</v>
       </c>
-      <c r="D10">
-        <v>2021</v>
+      <c r="D10" t="s">
+        <v>291</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F10" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H10" s="3">
-        <v>2059245</v>
+        <v>2378245</v>
       </c>
       <c r="I10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="1" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
@@ -1839,31 +2237,31 @@
       <c r="C11">
         <v>2021</v>
       </c>
-      <c r="D11">
-        <v>2021</v>
+      <c r="D11" t="s">
+        <v>291</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="F11" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="G11" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H11" s="3">
-        <v>1960230</v>
+        <v>2132343</v>
       </c>
       <c r="I11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="1" t="s">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
@@ -1871,31 +2269,31 @@
       <c r="C12">
         <v>2021</v>
       </c>
-      <c r="D12">
-        <v>2021</v>
+      <c r="D12" t="s">
+        <v>291</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="F12" t="s">
-        <v>264</v>
+        <v>171</v>
       </c>
       <c r="G12" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="H12" s="3">
-        <v>1845243</v>
+        <v>2059245</v>
       </c>
       <c r="I12" t="s">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>265</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s">
         <v>11</v>
@@ -1903,31 +2301,31 @@
       <c r="C13">
         <v>2021</v>
       </c>
-      <c r="D13">
-        <v>2021</v>
+      <c r="D13" t="s">
+        <v>291</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="F13" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="G13" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="H13" s="3">
-        <v>1796008</v>
+        <v>1960230</v>
       </c>
       <c r="I13" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="1" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
@@ -1935,31 +2333,31 @@
       <c r="C14">
         <v>2021</v>
       </c>
-      <c r="D14">
-        <v>2021</v>
+      <c r="D14" t="s">
+        <v>291</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>282</v>
+        <v>158</v>
       </c>
       <c r="F14" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="G14" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="H14" s="3">
-        <v>1758290</v>
+        <v>1845243</v>
       </c>
       <c r="I14" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="1" t="s">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="B15" t="s">
         <v>11</v>
@@ -1967,31 +2365,31 @@
       <c r="C15">
         <v>2021</v>
       </c>
-      <c r="D15">
-        <v>2021</v>
+      <c r="D15" t="s">
+        <v>291</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="F15" t="s">
-        <v>262</v>
+        <v>190</v>
       </c>
       <c r="G15" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="H15" s="3">
-        <v>1560320</v>
+        <v>1796008</v>
       </c>
       <c r="I15" t="s">
-        <v>147</v>
+        <v>27</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>263</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="1" t="s">
-        <v>58</v>
+        <v>323</v>
       </c>
       <c r="B16" t="s">
         <v>11</v>
@@ -1999,31 +2397,31 @@
       <c r="C16">
         <v>2021</v>
       </c>
-      <c r="D16">
-        <v>2021</v>
+      <c r="D16" t="s">
+        <v>291</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="F16" t="s">
-        <v>185</v>
+        <v>372</v>
       </c>
       <c r="G16" t="s">
-        <v>95</v>
+        <v>305</v>
       </c>
       <c r="H16" s="3">
-        <v>1212038</v>
+        <v>1771888</v>
       </c>
       <c r="I16" t="s">
-        <v>25</v>
+        <v>341</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>186</v>
+        <v>373</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="1" t="s">
-        <v>59</v>
+        <v>143</v>
       </c>
       <c r="B17" t="s">
         <v>11</v>
@@ -2031,31 +2429,31 @@
       <c r="C17">
         <v>2021</v>
       </c>
-      <c r="D17">
-        <v>2021</v>
+      <c r="D17" t="s">
+        <v>291</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>158</v>
+        <v>282</v>
       </c>
       <c r="F17" t="s">
-        <v>187</v>
+        <v>281</v>
       </c>
       <c r="G17" t="s">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="H17" s="3">
-        <v>1071359</v>
+        <v>1758290</v>
       </c>
       <c r="I17" t="s">
-        <v>26</v>
+        <v>155</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>188</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="1" t="s">
-        <v>50</v>
+        <v>135</v>
       </c>
       <c r="B18" t="s">
         <v>11</v>
@@ -2063,31 +2461,31 @@
       <c r="C18">
         <v>2021</v>
       </c>
-      <c r="D18">
-        <v>2021</v>
+      <c r="D18" t="s">
+        <v>291</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="F18" t="s">
-        <v>164</v>
+        <v>262</v>
       </c>
       <c r="G18" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="H18" s="3">
-        <v>1028428</v>
+        <v>1560320</v>
       </c>
       <c r="I18" t="s">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>165</v>
+        <v>263</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B19" t="s">
         <v>11</v>
@@ -2095,28 +2493,31 @@
       <c r="C19">
         <v>2021</v>
       </c>
-      <c r="D19">
-        <v>2021</v>
+      <c r="D19" t="s">
+        <v>291</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>161</v>
+        <v>184</v>
+      </c>
+      <c r="F19" t="s">
+        <v>185</v>
       </c>
       <c r="G19" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H19" s="3">
-        <v>976802</v>
+        <v>1212038</v>
       </c>
       <c r="I19" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="B20" t="s">
         <v>11</v>
@@ -2124,63 +2525,63 @@
       <c r="C20">
         <v>2021</v>
       </c>
-      <c r="D20">
-        <v>2021</v>
+      <c r="D20" t="s">
+        <v>291</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>198</v>
+        <v>158</v>
       </c>
       <c r="F20" t="s">
-        <v>212</v>
+        <v>187</v>
       </c>
       <c r="G20" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="H20" s="3">
-        <v>653514</v>
+        <v>1071359</v>
       </c>
       <c r="I20" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>213</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="1" t="s">
-        <v>138</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>224</v>
+        <v>11</v>
       </c>
       <c r="C21">
         <v>2021</v>
       </c>
-      <c r="D21">
-        <v>2021</v>
+      <c r="D21" t="s">
+        <v>291</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>268</v>
+        <v>161</v>
       </c>
       <c r="F21" t="s">
-        <v>269</v>
+        <v>164</v>
       </c>
       <c r="G21" t="s">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="H21" s="3">
-        <v>459883</v>
+        <v>1028428</v>
       </c>
       <c r="I21" t="s">
-        <v>150</v>
+        <v>17</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>270</v>
+        <v>165</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B22" t="s">
         <v>11</v>
@@ -2188,31 +2589,28 @@
       <c r="C22">
         <v>2021</v>
       </c>
-      <c r="D22">
-        <v>2021</v>
+      <c r="D22" t="s">
+        <v>291</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F22" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="G22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H22" s="3">
-        <v>303763</v>
+        <v>976802</v>
       </c>
       <c r="I22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="1" t="s">
-        <v>6</v>
+        <v>324</v>
       </c>
       <c r="B23" t="s">
         <v>11</v>
@@ -2220,31 +2618,31 @@
       <c r="C23">
         <v>2021</v>
       </c>
-      <c r="D23">
-        <v>2021</v>
-      </c>
-      <c r="E23" s="1">
-        <v>-10</v>
+      <c r="D23" t="s">
+        <v>291</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>173</v>
       </c>
       <c r="F23" t="s">
-        <v>13</v>
+        <v>375</v>
       </c>
       <c r="G23" t="s">
-        <v>10</v>
+        <v>306</v>
       </c>
       <c r="H23" s="3">
-        <v>200612</v>
+        <v>954238</v>
       </c>
       <c r="I23" t="s">
-        <v>14</v>
+        <v>374</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>160</v>
+        <v>376</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="1" t="s">
-        <v>61</v>
+        <v>317</v>
       </c>
       <c r="B24" t="s">
         <v>11</v>
@@ -2252,31 +2650,31 @@
       <c r="C24">
         <v>2021</v>
       </c>
-      <c r="D24">
-        <v>2021</v>
+      <c r="D24" t="s">
+        <v>291</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>192</v>
+        <v>358</v>
       </c>
       <c r="F24" t="s">
-        <v>193</v>
+        <v>357</v>
       </c>
       <c r="G24" t="s">
-        <v>98</v>
+        <v>300</v>
       </c>
       <c r="H24" s="3">
-        <v>132204</v>
+        <v>795715</v>
       </c>
       <c r="I24" t="s">
-        <v>289</v>
+        <v>336</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>194</v>
+        <v>359</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="1" t="s">
-        <v>67</v>
+        <v>329</v>
       </c>
       <c r="B25" t="s">
         <v>11</v>
@@ -2284,31 +2682,31 @@
       <c r="C25">
         <v>2021</v>
       </c>
-      <c r="D25">
-        <v>2021</v>
+      <c r="D25" t="s">
+        <v>291</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="F25" t="s">
-        <v>210</v>
+        <v>389</v>
       </c>
       <c r="G25" t="s">
-        <v>104</v>
+        <v>310</v>
       </c>
       <c r="H25" s="3">
-        <v>121479</v>
+        <v>767044</v>
       </c>
       <c r="I25" t="s">
-        <v>33</v>
+        <v>345</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>211</v>
+        <v>390</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="1" t="s">
-        <v>137</v>
+        <v>68</v>
       </c>
       <c r="B26" t="s">
         <v>11</v>
@@ -2316,383 +2714,383 @@
       <c r="C26">
         <v>2021</v>
       </c>
-      <c r="D26">
-        <v>2021</v>
+      <c r="D26" t="s">
+        <v>291</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="F26" t="s">
-        <v>266</v>
+        <v>212</v>
       </c>
       <c r="G26" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="H26" s="3">
-        <v>4524</v>
+        <v>653514</v>
       </c>
       <c r="I26" t="s">
-        <v>149</v>
+        <v>34</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>267</v>
+        <v>213</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="1" t="s">
-        <v>62</v>
+        <v>138</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>224</v>
       </c>
       <c r="C27">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>195</v>
+        <v>268</v>
       </c>
       <c r="F27" t="s">
-        <v>196</v>
+        <v>269</v>
       </c>
       <c r="G27" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="H27" s="3">
-        <v>7733587</v>
+        <v>459883</v>
       </c>
       <c r="I27" t="s">
-        <v>28</v>
+        <v>150</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>197</v>
+        <v>270</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="1" t="s">
-        <v>144</v>
+        <v>318</v>
       </c>
       <c r="B28" t="s">
         <v>11</v>
       </c>
       <c r="C28">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D28" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>285</v>
+        <v>195</v>
       </c>
       <c r="F28" t="s">
-        <v>284</v>
+        <v>360</v>
       </c>
       <c r="G28" t="s">
-        <v>132</v>
+        <v>301</v>
       </c>
       <c r="H28" s="3">
-        <v>1218509</v>
+        <v>378104</v>
       </c>
       <c r="I28" t="s">
-        <v>156</v>
+        <v>337</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>286</v>
+        <v>361</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="1" t="s">
-        <v>71</v>
+        <v>316</v>
       </c>
       <c r="B29" t="s">
         <v>11</v>
       </c>
       <c r="C29">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D29" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>189</v>
+        <v>355</v>
       </c>
       <c r="F29" t="s">
-        <v>220</v>
+        <v>354</v>
       </c>
       <c r="G29" t="s">
-        <v>108</v>
+        <v>299</v>
       </c>
       <c r="H29" s="3">
-        <v>613506</v>
+        <v>377267</v>
       </c>
       <c r="I29" t="s">
-        <v>37</v>
+        <v>335</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>221</v>
+        <v>356</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="1" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="B30" t="s">
         <v>11</v>
       </c>
       <c r="C30">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D30" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="F30" t="s">
-        <v>250</v>
+        <v>168</v>
       </c>
       <c r="G30" t="s">
-        <v>249</v>
+        <v>87</v>
       </c>
       <c r="H30" s="3">
-        <v>552739</v>
+        <v>303763</v>
       </c>
       <c r="I30" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>251</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="1" t="s">
-        <v>139</v>
+        <v>6</v>
       </c>
       <c r="B31" t="s">
         <v>11</v>
       </c>
       <c r="C31">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D31" t="s">
-        <v>288</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>198</v>
+        <v>291</v>
+      </c>
+      <c r="E31" s="1">
+        <v>-10</v>
       </c>
       <c r="F31" t="s">
-        <v>271</v>
+        <v>13</v>
       </c>
       <c r="G31" t="s">
-        <v>127</v>
+        <v>10</v>
       </c>
       <c r="H31" s="3">
-        <v>189629</v>
+        <v>200612</v>
       </c>
       <c r="I31" t="s">
-        <v>151</v>
+        <v>14</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>272</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="1" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="B32" t="s">
         <v>11</v>
       </c>
       <c r="C32">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D32" t="s">
+        <v>291</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F32" t="s">
+        <v>193</v>
+      </c>
+      <c r="G32" t="s">
+        <v>98</v>
+      </c>
+      <c r="H32" s="3">
+        <v>132204</v>
+      </c>
+      <c r="I32" t="s">
         <v>288</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="F32" t="s">
-        <v>235</v>
-      </c>
-      <c r="G32" t="s">
-        <v>114</v>
-      </c>
-      <c r="H32" s="3">
-        <v>25178</v>
-      </c>
-      <c r="I32" t="s">
-        <v>42</v>
-      </c>
       <c r="J32" s="2" t="s">
-        <v>237</v>
+        <v>194</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B33" t="s">
         <v>11</v>
       </c>
       <c r="C33">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D33" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="F33" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="G33" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="H33" s="3">
-        <v>19483</v>
+        <v>121479</v>
       </c>
       <c r="I33" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="1" t="s">
-        <v>80</v>
+        <v>322</v>
       </c>
       <c r="B34" t="s">
         <v>11</v>
       </c>
       <c r="C34">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="D34" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>244</v>
+        <v>158</v>
       </c>
       <c r="F34" t="s">
-        <v>243</v>
+        <v>370</v>
       </c>
       <c r="G34" t="s">
-        <v>117</v>
+        <v>304</v>
       </c>
       <c r="H34" s="3">
-        <v>5265895</v>
+        <v>98231</v>
       </c>
       <c r="I34" t="s">
-        <v>45</v>
+        <v>369</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>245</v>
+        <v>371</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="1" t="s">
-        <v>66</v>
+        <v>137</v>
       </c>
       <c r="B35" t="s">
         <v>11</v>
       </c>
       <c r="C35">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="D35" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="F35" t="s">
-        <v>208</v>
+        <v>266</v>
       </c>
       <c r="G35" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="H35" s="3">
-        <v>2991300</v>
+        <v>4524</v>
       </c>
       <c r="I35" t="s">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>209</v>
+        <v>267</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B36" t="s">
-        <v>224</v>
+        <v>11</v>
       </c>
       <c r="C36">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D36" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>222</v>
+        <v>195</v>
       </c>
       <c r="F36" t="s">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="G36" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="H36" s="3">
-        <v>2563754</v>
+        <v>7733587</v>
       </c>
       <c r="I36" t="s">
-        <v>290</v>
+        <v>28</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="1" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="B37" t="s">
         <v>11</v>
       </c>
       <c r="C37">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D37" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="F37" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="G37" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H37" s="3">
-        <v>587879</v>
+        <v>5275870</v>
       </c>
       <c r="I37" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B38" t="s">
         <v>11</v>
@@ -2701,94 +3099,94 @@
         <v>2019</v>
       </c>
       <c r="D38" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F38" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="G38" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H38" s="3">
-        <v>517958</v>
+        <v>5265895</v>
       </c>
       <c r="I38" t="s">
-        <v>291</v>
+        <v>45</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B39" t="s">
         <v>11</v>
       </c>
       <c r="C39">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D39" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F39" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="G39" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H39" s="3">
-        <v>349359</v>
+        <v>4674495</v>
       </c>
       <c r="I39" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="1" t="s">
-        <v>83</v>
+        <v>327</v>
       </c>
       <c r="B40" t="s">
         <v>11</v>
       </c>
       <c r="C40">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="D40" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>253</v>
+        <v>158</v>
       </c>
       <c r="F40" t="s">
-        <v>252</v>
+        <v>383</v>
       </c>
       <c r="G40" t="s">
-        <v>119</v>
+        <v>308</v>
       </c>
       <c r="H40" s="3">
-        <v>5275870</v>
+        <v>4655514</v>
       </c>
       <c r="I40" t="s">
-        <v>47</v>
+        <v>344</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>254</v>
+        <v>384</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="1" t="s">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="B41" t="s">
         <v>11</v>
@@ -2797,403 +3195,1063 @@
         <v>2018</v>
       </c>
       <c r="D41" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>274</v>
+        <v>214</v>
       </c>
       <c r="F41" t="s">
-        <v>273</v>
+        <v>215</v>
       </c>
       <c r="G41" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="H41" s="3">
-        <v>4674495</v>
+        <v>4141267</v>
       </c>
       <c r="I41" t="s">
-        <v>152</v>
+        <v>35</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>275</v>
+        <v>216</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B42" t="s">
         <v>11</v>
       </c>
       <c r="C42">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D42" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="F42" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="G42" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H42" s="3">
-        <v>4141267</v>
+        <v>2991300</v>
       </c>
       <c r="I42" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="1" t="s">
-        <v>133</v>
+        <v>72</v>
       </c>
       <c r="B43" t="s">
-        <v>11</v>
+        <v>224</v>
       </c>
       <c r="C43">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D43" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>258</v>
+        <v>222</v>
       </c>
       <c r="F43" t="s">
-        <v>257</v>
+        <v>223</v>
       </c>
       <c r="G43" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="H43" s="3">
-        <v>1265188</v>
+        <v>2563754</v>
       </c>
       <c r="I43" t="s">
-        <v>145</v>
-      </c>
-      <c r="J43" t="s">
-        <v>259</v>
+        <v>289</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="1" t="s">
-        <v>84</v>
+        <v>328</v>
       </c>
       <c r="B44" t="s">
         <v>11</v>
       </c>
       <c r="C44">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="D44" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>230</v>
+        <v>387</v>
       </c>
       <c r="F44" t="s">
-        <v>255</v>
+        <v>386</v>
       </c>
       <c r="G44" t="s">
-        <v>120</v>
+        <v>309</v>
       </c>
       <c r="H44" s="3">
-        <v>1259285</v>
+        <v>2400663</v>
       </c>
       <c r="I44" t="s">
-        <v>48</v>
+        <v>385</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>256</v>
+        <v>388</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="1" t="s">
-        <v>70</v>
+        <v>325</v>
       </c>
       <c r="B45" t="s">
         <v>11</v>
       </c>
       <c r="C45">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="D45" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>217</v>
+        <v>379</v>
       </c>
       <c r="F45" t="s">
-        <v>218</v>
+        <v>378</v>
       </c>
       <c r="G45" t="s">
-        <v>107</v>
+        <v>377</v>
       </c>
       <c r="H45" s="3">
-        <v>617188</v>
+        <v>2340742</v>
       </c>
       <c r="I45" t="s">
-        <v>36</v>
+        <v>342</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>219</v>
+        <v>380</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="1" t="s">
-        <v>64</v>
+        <v>133</v>
       </c>
       <c r="B46" t="s">
         <v>11</v>
       </c>
       <c r="C46">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D46" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>202</v>
+        <v>258</v>
       </c>
       <c r="F46" t="s">
-        <v>201</v>
+        <v>257</v>
       </c>
       <c r="G46" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="H46" s="3">
-        <v>290313</v>
+        <v>1265188</v>
       </c>
       <c r="I46" t="s">
-        <v>30</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>203</v>
+        <v>145</v>
+      </c>
+      <c r="J46" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="1" t="s">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="B47" t="s">
         <v>11</v>
       </c>
       <c r="C47">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D47" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>277</v>
+        <v>230</v>
       </c>
       <c r="F47" t="s">
-        <v>276</v>
+        <v>255</v>
       </c>
       <c r="G47" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="H47" s="3">
-        <v>99365</v>
+        <v>1259285</v>
       </c>
       <c r="I47" t="s">
-        <v>153</v>
+        <v>48</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>278</v>
+        <v>256</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="1" t="s">
-        <v>65</v>
+        <v>144</v>
       </c>
       <c r="B48" t="s">
         <v>11</v>
       </c>
       <c r="C48">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="D48" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>204</v>
+        <v>285</v>
       </c>
       <c r="F48" t="s">
-        <v>205</v>
+        <v>284</v>
       </c>
       <c r="G48" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="H48" s="3">
-        <v>243599</v>
+        <v>1218509</v>
       </c>
       <c r="I48" t="s">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>206</v>
+        <v>286</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B49" t="s">
         <v>11</v>
       </c>
       <c r="C49">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D49" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="F49" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="G49" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H49" s="3">
-        <v>136424</v>
+        <v>947291</v>
       </c>
       <c r="I49" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>200</v>
+        <v>227</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B50" t="s">
         <v>11</v>
       </c>
       <c r="C50">
-        <v>2015</v>
+        <v>2011</v>
       </c>
       <c r="D50" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="F50" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="G50" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="H50" s="3">
-        <v>947291</v>
+        <v>802315</v>
       </c>
       <c r="I50" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B51" t="s">
         <v>11</v>
       </c>
       <c r="C51">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="D51" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="F51" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="G51" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="H51" s="3">
-        <v>802315</v>
+        <v>617188</v>
       </c>
       <c r="I51" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>240</v>
+        <v>219</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B52" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52">
+        <v>2020</v>
+      </c>
+      <c r="D52" t="s">
+        <v>292</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F52" t="s">
+        <v>220</v>
+      </c>
+      <c r="G52" t="s">
+        <v>108</v>
+      </c>
+      <c r="H52" s="3">
+        <v>613506</v>
+      </c>
+      <c r="I52" t="s">
+        <v>37</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B53" t="s">
+        <v>11</v>
+      </c>
+      <c r="C53">
+        <v>2019</v>
+      </c>
+      <c r="D53" t="s">
+        <v>292</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F53" t="s">
+        <v>260</v>
+      </c>
+      <c r="G53" t="s">
+        <v>122</v>
+      </c>
+      <c r="H53" s="3">
+        <v>587879</v>
+      </c>
+      <c r="I53" t="s">
+        <v>146</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B54" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54">
+        <v>2017</v>
+      </c>
+      <c r="D54" t="s">
+        <v>292</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F54" t="s">
+        <v>295</v>
+      </c>
+      <c r="G54" t="s">
+        <v>294</v>
+      </c>
+      <c r="H54" s="3">
+        <v>562667</v>
+      </c>
+      <c r="I54" t="s">
+        <v>297</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B55" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55">
+        <v>2020</v>
+      </c>
+      <c r="D55" t="s">
+        <v>292</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F55" t="s">
+        <v>250</v>
+      </c>
+      <c r="G55" t="s">
+        <v>249</v>
+      </c>
+      <c r="H55" s="3">
+        <v>552739</v>
+      </c>
+      <c r="I55" t="s">
+        <v>46</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B56" t="s">
+        <v>11</v>
+      </c>
+      <c r="C56">
+        <v>2019</v>
+      </c>
+      <c r="D56" t="s">
+        <v>292</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F56" t="s">
+        <v>246</v>
+      </c>
+      <c r="G56" t="s">
+        <v>118</v>
+      </c>
+      <c r="H56" s="3">
+        <v>517958</v>
+      </c>
+      <c r="I56" t="s">
+        <v>290</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B57" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57">
+        <v>2020</v>
+      </c>
+      <c r="D57" t="s">
+        <v>292</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F57" t="s">
+        <v>363</v>
+      </c>
+      <c r="G57" t="s">
+        <v>362</v>
+      </c>
+      <c r="H57" s="3">
+        <v>483734</v>
+      </c>
+      <c r="I57" t="s">
+        <v>338</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B58" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58">
+        <v>2018</v>
+      </c>
+      <c r="D58" t="s">
+        <v>292</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F58" t="s">
+        <v>391</v>
+      </c>
+      <c r="G58" t="s">
+        <v>311</v>
+      </c>
+      <c r="H58" s="3">
+        <v>470562</v>
+      </c>
+      <c r="I58" t="s">
+        <v>346</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B59" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59">
+        <v>2019</v>
+      </c>
+      <c r="D59" t="s">
+        <v>292</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="F59" t="s">
+        <v>279</v>
+      </c>
+      <c r="G59" t="s">
+        <v>130</v>
+      </c>
+      <c r="H59" s="3">
+        <v>349359</v>
+      </c>
+      <c r="I59" t="s">
+        <v>154</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B60" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60">
+        <v>2017</v>
+      </c>
+      <c r="D60" t="s">
+        <v>292</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="F60" t="s">
+        <v>201</v>
+      </c>
+      <c r="G60" t="s">
+        <v>101</v>
+      </c>
+      <c r="H60" s="3">
+        <v>290313</v>
+      </c>
+      <c r="I60" t="s">
+        <v>30</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B61" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61">
+        <v>2016</v>
+      </c>
+      <c r="D61" t="s">
+        <v>292</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F61" t="s">
+        <v>205</v>
+      </c>
+      <c r="G61" t="s">
+        <v>102</v>
+      </c>
+      <c r="H61" s="3">
+        <v>243599</v>
+      </c>
+      <c r="I61" t="s">
+        <v>31</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B62" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62">
+        <v>2020</v>
+      </c>
+      <c r="D62" t="s">
+        <v>292</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F62" t="s">
+        <v>271</v>
+      </c>
+      <c r="G62" t="s">
+        <v>127</v>
+      </c>
+      <c r="H62" s="3">
+        <v>189629</v>
+      </c>
+      <c r="I62" t="s">
+        <v>151</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B63" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63">
+        <v>2018</v>
+      </c>
+      <c r="D63" t="s">
+        <v>292</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F63" t="s">
+        <v>393</v>
+      </c>
+      <c r="G63" t="s">
+        <v>312</v>
+      </c>
+      <c r="H63" s="3">
+        <v>154914</v>
+      </c>
+      <c r="I63" t="s">
+        <v>347</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B64" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64">
+        <v>2017</v>
+      </c>
+      <c r="D64" t="s">
+        <v>292</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F64" t="s">
+        <v>381</v>
+      </c>
+      <c r="G64" t="s">
+        <v>307</v>
+      </c>
+      <c r="H64" s="3">
+        <v>147091</v>
+      </c>
+      <c r="I64" t="s">
+        <v>343</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B65" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65">
+        <v>2016</v>
+      </c>
+      <c r="D65" t="s">
+        <v>292</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F65" t="s">
+        <v>199</v>
+      </c>
+      <c r="G65" t="s">
+        <v>100</v>
+      </c>
+      <c r="H65" s="3">
+        <v>136424</v>
+      </c>
+      <c r="I65" t="s">
+        <v>29</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B66" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66">
+        <v>2016</v>
+      </c>
+      <c r="D66" t="s">
+        <v>292</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F66" t="s">
+        <v>397</v>
+      </c>
+      <c r="G66" t="s">
+        <v>314</v>
+      </c>
+      <c r="H66" s="3">
+        <v>136234</v>
+      </c>
+      <c r="I66" t="s">
+        <v>349</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B67" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67">
+        <v>2017</v>
+      </c>
+      <c r="D67" t="s">
+        <v>292</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="F67" t="s">
+        <v>276</v>
+      </c>
+      <c r="G67" t="s">
+        <v>129</v>
+      </c>
+      <c r="H67" s="3">
+        <v>99365</v>
+      </c>
+      <c r="I67" t="s">
+        <v>153</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B68" t="s">
+        <v>11</v>
+      </c>
+      <c r="C68">
+        <v>2017</v>
+      </c>
+      <c r="D68" t="s">
+        <v>292</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F68" t="s">
+        <v>367</v>
+      </c>
+      <c r="G68" t="s">
+        <v>302</v>
+      </c>
+      <c r="H68" s="3">
+        <v>67758</v>
+      </c>
+      <c r="I68" t="s">
+        <v>339</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B69" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69">
+        <v>2020</v>
+      </c>
+      <c r="D69" t="s">
+        <v>292</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F69" t="s">
+        <v>235</v>
+      </c>
+      <c r="G69" t="s">
+        <v>114</v>
+      </c>
+      <c r="H69" s="3">
+        <v>25178</v>
+      </c>
+      <c r="I69" t="s">
+        <v>42</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B70" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70">
+        <v>2020</v>
+      </c>
+      <c r="D70" t="s">
+        <v>292</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F70" t="s">
+        <v>228</v>
+      </c>
+      <c r="G70" t="s">
+        <v>111</v>
+      </c>
+      <c r="H70" s="3">
+        <v>19483</v>
+      </c>
+      <c r="I70" t="s">
+        <v>39</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B71" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71">
+        <v>2016</v>
+      </c>
+      <c r="D71" t="s">
+        <v>292</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="F71" t="s">
+        <v>395</v>
+      </c>
+      <c r="G71" t="s">
+        <v>313</v>
+      </c>
+      <c r="H71" s="3">
+        <v>15835</v>
+      </c>
+      <c r="I71" t="s">
+        <v>348</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>399</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J51">
-    <sortCondition descending="1" ref="C2:C51"/>
-    <sortCondition descending="1" ref="H2:H51"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J71">
+    <sortCondition ref="D2:D71"/>
+    <sortCondition descending="1" ref="H2:H71"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="J23" r:id="rId1" xr:uid="{725A3016-CC80-5F4A-B091-4E71BCFAD36B}"/>
-    <hyperlink ref="J9" r:id="rId2" xr:uid="{38F493C0-3185-604E-A3BD-AAB0EC5B83DF}"/>
-    <hyperlink ref="J6" r:id="rId3" xr:uid="{2E642780-E9D7-BF4B-9D23-FEBE51DDD0C9}"/>
-    <hyperlink ref="J18" r:id="rId4" xr:uid="{5CF6DEF3-9028-3D4C-846C-DA2618807577}"/>
-    <hyperlink ref="J22" r:id="rId5" xr:uid="{A298B622-5340-5148-820B-D468159EA5BD}"/>
-    <hyperlink ref="J19" r:id="rId6" xr:uid="{EF9BC619-52CD-2D48-BE99-80BD81A8CD54}"/>
-    <hyperlink ref="J10" r:id="rId7" xr:uid="{0002A242-754F-5A40-86A8-5F7DBBEBB9D1}"/>
-    <hyperlink ref="J8" r:id="rId8" xr:uid="{085C9D3E-4AFA-FF48-AA1A-64ECF275D4C0}"/>
-    <hyperlink ref="J11" r:id="rId9" xr:uid="{118F4CA9-C4A7-F74E-8AFF-041FB2741717}"/>
+    <hyperlink ref="J31" r:id="rId1" xr:uid="{725A3016-CC80-5F4A-B091-4E71BCFAD36B}"/>
+    <hyperlink ref="J11" r:id="rId2" xr:uid="{38F493C0-3185-604E-A3BD-AAB0EC5B83DF}"/>
+    <hyperlink ref="J7" r:id="rId3" xr:uid="{2E642780-E9D7-BF4B-9D23-FEBE51DDD0C9}"/>
+    <hyperlink ref="J21" r:id="rId4" xr:uid="{5CF6DEF3-9028-3D4C-846C-DA2618807577}"/>
+    <hyperlink ref="J30" r:id="rId5" xr:uid="{A298B622-5340-5148-820B-D468159EA5BD}"/>
+    <hyperlink ref="J22" r:id="rId6" xr:uid="{EF9BC619-52CD-2D48-BE99-80BD81A8CD54}"/>
+    <hyperlink ref="J12" r:id="rId7" xr:uid="{0002A242-754F-5A40-86A8-5F7DBBEBB9D1}"/>
+    <hyperlink ref="J10" r:id="rId8" xr:uid="{085C9D3E-4AFA-FF48-AA1A-64ECF275D4C0}"/>
+    <hyperlink ref="J13" r:id="rId9" xr:uid="{118F4CA9-C4A7-F74E-8AFF-041FB2741717}"/>
     <hyperlink ref="J3" r:id="rId10" xr:uid="{75687EB7-0A29-5C47-921B-954A17F06565}"/>
-    <hyperlink ref="J7" r:id="rId11" xr:uid="{81B8E0D0-29DD-E74A-8CE3-1464ECDB131A}"/>
-    <hyperlink ref="J16" r:id="rId12" xr:uid="{5D4D2728-3F60-EE43-86DF-EE58ADBF8432}"/>
-    <hyperlink ref="J17" r:id="rId13" xr:uid="{31C21087-E027-4542-80B2-C095CF193FA7}"/>
-    <hyperlink ref="J13" r:id="rId14" xr:uid="{36CFF13A-82D4-9642-B07B-0C3E49B5D215}"/>
-    <hyperlink ref="J24" r:id="rId15" xr:uid="{DDDE99D5-3422-6549-8393-D5FC330D45B8}"/>
-    <hyperlink ref="J27" r:id="rId16" xr:uid="{9621A5D4-6BD1-984D-9C8C-2A89CFA54CFF}"/>
-    <hyperlink ref="J49" r:id="rId17" xr:uid="{CC87EE91-DF39-EA48-9614-33030270159C}"/>
-    <hyperlink ref="J46" r:id="rId18" xr:uid="{C4E1F448-AF1B-BC43-983F-FB439266392E}"/>
-    <hyperlink ref="J48" r:id="rId19" xr:uid="{17A665F7-B807-4640-B444-16CFE27D5FDF}"/>
-    <hyperlink ref="J35" r:id="rId20" xr:uid="{244C8E1D-D3A7-9549-9D73-8F4D984A6ACD}"/>
-    <hyperlink ref="J25" r:id="rId21" xr:uid="{135AB67A-502A-8A4D-B049-40F78987A6E4}"/>
-    <hyperlink ref="J20" r:id="rId22" xr:uid="{2EBEE3F8-DF57-0E4A-9FB8-2C6B08B9453B}"/>
-    <hyperlink ref="J42" r:id="rId23" xr:uid="{50C93161-BA50-264D-9EB0-FD96B5179BD3}"/>
-    <hyperlink ref="J45" r:id="rId24" xr:uid="{EB1586AB-126F-2B4B-AB36-6A028744AF76}"/>
-    <hyperlink ref="J29" r:id="rId25" xr:uid="{7C55426F-9022-8044-ACAA-5AEC9137C037}"/>
-    <hyperlink ref="J36" r:id="rId26" xr:uid="{AD424BE3-B862-2442-B3B2-5028AF918C6F}"/>
-    <hyperlink ref="J50" r:id="rId27" xr:uid="{2183D387-1FD2-324D-A080-BF2A14B2C266}"/>
-    <hyperlink ref="J33" r:id="rId28" xr:uid="{FDBD3899-8300-BE4F-B928-93EB7382FF06}"/>
+    <hyperlink ref="J9" r:id="rId11" xr:uid="{81B8E0D0-29DD-E74A-8CE3-1464ECDB131A}"/>
+    <hyperlink ref="J19" r:id="rId12" xr:uid="{5D4D2728-3F60-EE43-86DF-EE58ADBF8432}"/>
+    <hyperlink ref="J20" r:id="rId13" xr:uid="{31C21087-E027-4542-80B2-C095CF193FA7}"/>
+    <hyperlink ref="J15" r:id="rId14" xr:uid="{36CFF13A-82D4-9642-B07B-0C3E49B5D215}"/>
+    <hyperlink ref="J32" r:id="rId15" xr:uid="{DDDE99D5-3422-6549-8393-D5FC330D45B8}"/>
+    <hyperlink ref="J36" r:id="rId16" xr:uid="{9621A5D4-6BD1-984D-9C8C-2A89CFA54CFF}"/>
+    <hyperlink ref="J65" r:id="rId17" xr:uid="{CC87EE91-DF39-EA48-9614-33030270159C}"/>
+    <hyperlink ref="J60" r:id="rId18" xr:uid="{C4E1F448-AF1B-BC43-983F-FB439266392E}"/>
+    <hyperlink ref="J61" r:id="rId19" xr:uid="{17A665F7-B807-4640-B444-16CFE27D5FDF}"/>
+    <hyperlink ref="J42" r:id="rId20" xr:uid="{244C8E1D-D3A7-9549-9D73-8F4D984A6ACD}"/>
+    <hyperlink ref="J33" r:id="rId21" xr:uid="{135AB67A-502A-8A4D-B049-40F78987A6E4}"/>
+    <hyperlink ref="J26" r:id="rId22" xr:uid="{2EBEE3F8-DF57-0E4A-9FB8-2C6B08B9453B}"/>
+    <hyperlink ref="J41" r:id="rId23" xr:uid="{50C93161-BA50-264D-9EB0-FD96B5179BD3}"/>
+    <hyperlink ref="J51" r:id="rId24" xr:uid="{EB1586AB-126F-2B4B-AB36-6A028744AF76}"/>
+    <hyperlink ref="J52" r:id="rId25" xr:uid="{7C55426F-9022-8044-ACAA-5AEC9137C037}"/>
+    <hyperlink ref="J43" r:id="rId26" xr:uid="{AD424BE3-B862-2442-B3B2-5028AF918C6F}"/>
+    <hyperlink ref="J49" r:id="rId27" xr:uid="{2183D387-1FD2-324D-A080-BF2A14B2C266}"/>
+    <hyperlink ref="J70" r:id="rId28" xr:uid="{FDBD3899-8300-BE4F-B928-93EB7382FF06}"/>
     <hyperlink ref="J2" r:id="rId29" xr:uid="{529C6D37-3C52-0C4C-8560-C27F3F7C2BCE}"/>
-    <hyperlink ref="J5" r:id="rId30" xr:uid="{D004E2AA-6899-A547-B940-4CF0A68E6AE2}"/>
-    <hyperlink ref="J32" r:id="rId31" xr:uid="{2DA721C4-AB3A-EB48-85F9-525AB6A822AB}"/>
-    <hyperlink ref="J51" r:id="rId32" xr:uid="{72A6DA76-289B-1945-8072-DAECE2441387}"/>
+    <hyperlink ref="J6" r:id="rId30" xr:uid="{D004E2AA-6899-A547-B940-4CF0A68E6AE2}"/>
+    <hyperlink ref="J69" r:id="rId31" xr:uid="{2DA721C4-AB3A-EB48-85F9-525AB6A822AB}"/>
+    <hyperlink ref="J50" r:id="rId32" xr:uid="{72A6DA76-289B-1945-8072-DAECE2441387}"/>
     <hyperlink ref="J4" r:id="rId33" xr:uid="{1ED33379-967F-8D43-85DD-BDDF4C65376C}"/>
-    <hyperlink ref="J34" r:id="rId34" xr:uid="{F704F2D4-3F11-614C-BFFC-5AA6E996A592}"/>
-    <hyperlink ref="J38" r:id="rId35" xr:uid="{5F94CB6B-2D0C-7C41-9363-23A9286E6D55}"/>
-    <hyperlink ref="J30" r:id="rId36" xr:uid="{02572C89-38D3-4B47-B603-D75FBB76E0BB}"/>
-    <hyperlink ref="J40" r:id="rId37" xr:uid="{96F331DE-1BF1-354F-9E54-FA8C80316EFB}"/>
-    <hyperlink ref="J44" r:id="rId38" xr:uid="{D40AF006-F71D-054C-BD53-C9CF18C19E2B}"/>
-    <hyperlink ref="J37" r:id="rId39" xr:uid="{D3ABB7B3-002B-9E42-A591-D3282F8D9EDC}"/>
-    <hyperlink ref="J15" r:id="rId40" xr:uid="{F2CD1548-C098-164F-AE85-0E2D85DE116F}"/>
-    <hyperlink ref="J12" r:id="rId41" xr:uid="{81094FDB-D745-024E-BD73-D63401EE9AA2}"/>
-    <hyperlink ref="J26" r:id="rId42" xr:uid="{850F5B2D-3612-1E44-A230-B654A61C2B8F}"/>
-    <hyperlink ref="J21" r:id="rId43" xr:uid="{D84F734D-746E-B841-A450-F741C1E43856}"/>
-    <hyperlink ref="J31" r:id="rId44" xr:uid="{7870E1C9-1855-634F-8B01-0A6F56E1C8EC}"/>
-    <hyperlink ref="J41" r:id="rId45" xr:uid="{74E258E9-3406-444C-9382-59C9A5DD2D28}"/>
-    <hyperlink ref="J47" r:id="rId46" xr:uid="{22AFEECC-9483-CC40-B244-DB64D5BE611A}"/>
-    <hyperlink ref="J39" r:id="rId47" xr:uid="{3F60EBBC-9A66-404C-8F8D-E0FD74919AF5}"/>
-    <hyperlink ref="J14" r:id="rId48" xr:uid="{97FC090B-C1AF-3B40-8E1E-653AF871E0B8}"/>
-    <hyperlink ref="J28" r:id="rId49" xr:uid="{24271837-2997-A04B-B1A8-30D8EAA5AABF}"/>
+    <hyperlink ref="J38" r:id="rId34" xr:uid="{F704F2D4-3F11-614C-BFFC-5AA6E996A592}"/>
+    <hyperlink ref="J56" r:id="rId35" xr:uid="{5F94CB6B-2D0C-7C41-9363-23A9286E6D55}"/>
+    <hyperlink ref="J55" r:id="rId36" xr:uid="{02572C89-38D3-4B47-B603-D75FBB76E0BB}"/>
+    <hyperlink ref="J37" r:id="rId37" xr:uid="{96F331DE-1BF1-354F-9E54-FA8C80316EFB}"/>
+    <hyperlink ref="J47" r:id="rId38" xr:uid="{D40AF006-F71D-054C-BD53-C9CF18C19E2B}"/>
+    <hyperlink ref="J53" r:id="rId39" xr:uid="{D3ABB7B3-002B-9E42-A591-D3282F8D9EDC}"/>
+    <hyperlink ref="J18" r:id="rId40" xr:uid="{F2CD1548-C098-164F-AE85-0E2D85DE116F}"/>
+    <hyperlink ref="J14" r:id="rId41" xr:uid="{81094FDB-D745-024E-BD73-D63401EE9AA2}"/>
+    <hyperlink ref="J35" r:id="rId42" xr:uid="{850F5B2D-3612-1E44-A230-B654A61C2B8F}"/>
+    <hyperlink ref="J27" r:id="rId43" xr:uid="{D84F734D-746E-B841-A450-F741C1E43856}"/>
+    <hyperlink ref="J62" r:id="rId44" xr:uid="{7870E1C9-1855-634F-8B01-0A6F56E1C8EC}"/>
+    <hyperlink ref="J39" r:id="rId45" xr:uid="{74E258E9-3406-444C-9382-59C9A5DD2D28}"/>
+    <hyperlink ref="J67" r:id="rId46" xr:uid="{22AFEECC-9483-CC40-B244-DB64D5BE611A}"/>
+    <hyperlink ref="J59" r:id="rId47" xr:uid="{3F60EBBC-9A66-404C-8F8D-E0FD74919AF5}"/>
+    <hyperlink ref="J17" r:id="rId48" xr:uid="{97FC090B-C1AF-3B40-8E1E-653AF871E0B8}"/>
+    <hyperlink ref="J48" r:id="rId49" xr:uid="{24271837-2997-A04B-B1A8-30D8EAA5AABF}"/>
+    <hyperlink ref="J54" r:id="rId50" xr:uid="{C6FE7874-DE1E-8744-8F7F-A7266A282BC7}"/>
+    <hyperlink ref="J8" r:id="rId51" xr:uid="{45D4B454-64FD-E043-9E1E-D98B915DA3C4}"/>
+    <hyperlink ref="J29" r:id="rId52" xr:uid="{592E8301-AD04-6A43-BE2C-DF1DCF4D0C8C}"/>
+    <hyperlink ref="J24" r:id="rId53" xr:uid="{AFFE99AD-C3BD-7D47-ADD2-0033AB1BD297}"/>
+    <hyperlink ref="J28" r:id="rId54" xr:uid="{10637FCE-769F-EF46-AFAF-F312278F1225}"/>
+    <hyperlink ref="J57" r:id="rId55" xr:uid="{1E8D6F6E-5279-684F-9870-749B17340F35}"/>
+    <hyperlink ref="J68" r:id="rId56" xr:uid="{C19F506D-023C-1247-BE6A-C23960198C51}"/>
+    <hyperlink ref="J5" r:id="rId57" xr:uid="{3E64B722-3690-B44C-ABC4-059D3B71C8D7}"/>
+    <hyperlink ref="J34" r:id="rId58" xr:uid="{50C3436F-19AF-D74F-8E0A-E9F0AEF4EF7F}"/>
+    <hyperlink ref="J16" r:id="rId59" xr:uid="{A5BBD32C-6F92-A842-A00C-8F17A0710E00}"/>
+    <hyperlink ref="J23" r:id="rId60" xr:uid="{117A81C3-427C-DF49-BA81-BE00A024107F}"/>
+    <hyperlink ref="J45" r:id="rId61" xr:uid="{5E89FA9C-5C01-5342-876F-D8B51FE4E2B8}"/>
+    <hyperlink ref="J64" r:id="rId62" xr:uid="{AE06ADB0-CCC6-5E4F-AA64-084B6EC4EDA5}"/>
+    <hyperlink ref="J40" r:id="rId63" xr:uid="{C1BBF821-4DC8-5347-B6F0-96939C529BA4}"/>
+    <hyperlink ref="J44" r:id="rId64" xr:uid="{990812EE-4D67-A148-8354-137377C29D95}"/>
+    <hyperlink ref="J25" r:id="rId65" xr:uid="{9C8D9D49-3342-1D45-9490-372911350A58}"/>
+    <hyperlink ref="J58" r:id="rId66" xr:uid="{EFDE2707-AAFE-A445-930B-DB05A658CF11}"/>
+    <hyperlink ref="J63" r:id="rId67" xr:uid="{C4CFA4B9-7F0C-2D48-848B-F4855312250F}"/>
+    <hyperlink ref="J66" r:id="rId68" xr:uid="{2C92D437-B811-BA4F-A7A0-ECBD7F90C3E8}"/>
+    <hyperlink ref="J71" r:id="rId69" xr:uid="{1DA360B3-3EEC-0B4A-92B2-F41887D4DA99}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-1405-TVSeries.xlsx
+++ b/db/A7XLK-1405-TVSeries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C1520D-FF5E-E341-9B5C-16573D22E03D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{213C4D98-FD67-1A44-A6A6-4A04F10875B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-35900" yWindow="6400" windowWidth="29840" windowHeight="17320" xr2:uid="{BAC94C6D-C196-2D4F-A2F2-89F0A182D671}"/>
   </bookViews>

--- a/db/A7XLK-1405-TVSeries.xlsx
+++ b/db/A7XLK-1405-TVSeries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{213C4D98-FD67-1A44-A6A6-4A04F10875B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77893EFA-796B-7543-9B94-FD664008DF8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35900" yWindow="6400" windowWidth="29840" windowHeight="17320" xr2:uid="{BAC94C6D-C196-2D4F-A2F2-89F0A182D671}"/>
+    <workbookView xWindow="4500" yWindow="2600" windowWidth="29840" windowHeight="17320" xr2:uid="{BAC94C6D-C196-2D4F-A2F2-89F0A182D671}"/>
   </bookViews>
   <sheets>
     <sheet name="今日電影" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="464">
   <si>
     <t>No</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1505,6 +1505,242 @@
   </si>
   <si>
     <t>https://gimy.app/vod/139988.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Score2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-101.jpeg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-102.jpeg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-103.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-104.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-105.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-106.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-107.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-108.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-109.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-110.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-111.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-112.jpeg</t>
+  </si>
+  <si>
+    <t>山河令</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>張哲瀚 龔俊 周也 馬聞遠 孫浠倫 金樂 柯乃予 王若麟 郭家豪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/121877.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>楊羽 大牛 張梓豫 張平 章濤 邢鼕鼕 邵莊 安寧 黎偉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/126777.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我在他鄉挺好的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>城市的邊緣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>周雨彤 任素汐 孫千 白宇帆 馬思超 代雲帆 金靖 泰樂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/155492.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你好，對方辯友2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">吳佳怡 翟子路 魯照華 米咪 王澤軒 柯穎 陳澤 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/119606.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>理想之城</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>孫儷 趙又廷 於和偉 陳明昊 高葉 李傳纓 張澍 李洪濤 趙君</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/157153.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>變成你的那一天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">張新成 梁潔 趙志偉 王薇 周士原 蘇勳倫 安戈 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/151403.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>突如其來的假期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>闞清子 陳若軒 倪虹潔 劉美含 朱嘉琦 張磊 傅首爾 劉名楷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/155360.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玫瑰行者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林鵬 鄭業成 李子峯 王志剛 金楷傑 蔡蝶 魏健隆 霄宇 羅康</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/157115.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>掃黑風暴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>孫紅雷 張藝興 劉奕君 吳越 王志飛 劉之冰 吳曉亮 江疏影</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>28</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/156984.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>理智派生活</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">秦嵐 王鶴棣 李宗翰 潘虹 陳鵬萬里 康亢 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/124388.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雲南蟲谷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>潘粵明 張雨綺 姜超</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/158230.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雙鏡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">張楠 孫伊涵 方安娜 劉智揚 周大爲 何奉天 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/157161.html</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1512,8 +1748,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="#,##0_ "/>
+    <numFmt numFmtId="177" formatCode="#,##0.0_ "/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1566,7 +1803,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1577,6 +1814,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1894,7 +2134,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C0AA310-9C39-A04D-BB87-9521EAB5B98C}">
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:K83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
@@ -1903,11 +2143,12 @@
     <col min="6" max="6" width="40.83203125" customWidth="1"/>
     <col min="7" max="7" width="32.33203125" customWidth="1"/>
     <col min="8" max="8" width="13.5" style="3" customWidth="1"/>
-    <col min="9" max="9" width="50.6640625" customWidth="1"/>
-    <col min="10" max="10" width="43.83203125" customWidth="1"/>
+    <col min="9" max="9" width="13.5" style="4" customWidth="1"/>
+    <col min="10" max="10" width="50.6640625" customWidth="1"/>
+    <col min="11" max="11" width="43.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1932,14 +2173,17 @@
       <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="J1" t="s">
         <v>1</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>75</v>
       </c>
@@ -1964,14 +2208,14 @@
       <c r="H2" s="3">
         <v>9760868</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>40</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>56</v>
       </c>
@@ -1996,14 +2240,17 @@
       <c r="H3" s="3">
         <v>8844170</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="4">
+        <v>7</v>
+      </c>
+      <c r="J3" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>79</v>
       </c>
@@ -2028,14 +2275,14 @@
       <c r="H4" s="3">
         <v>6002697</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>44</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
         <v>321</v>
       </c>
@@ -2060,14 +2307,14 @@
       <c r="H5" s="3">
         <v>5150111</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>340</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
         <v>76</v>
       </c>
@@ -2092,14 +2339,17 @@
       <c r="H6" s="3">
         <v>4155026</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="4">
+        <v>8.1</v>
+      </c>
+      <c r="J6" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
         <v>49</v>
       </c>
@@ -2124,14 +2374,14 @@
       <c r="H7" s="3">
         <v>2815834</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
         <v>315</v>
       </c>
@@ -2156,14 +2406,14 @@
       <c r="H8" s="3">
         <v>2535509</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>334</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
         <v>57</v>
       </c>
@@ -2188,14 +2438,14 @@
       <c r="H9" s="3">
         <v>2454774</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>24</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="K9" s="2" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
         <v>54</v>
       </c>
@@ -2220,14 +2470,14 @@
       <c r="H10" s="3">
         <v>2378245</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="K10" s="2" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
@@ -2252,14 +2502,14 @@
       <c r="H11" s="3">
         <v>2132343</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>15</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="K11" s="2" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
         <v>53</v>
       </c>
@@ -2284,14 +2534,14 @@
       <c r="H12" s="3">
         <v>2059245</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>20</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="K12" s="2" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:11">
       <c r="A13" s="1" t="s">
         <v>55</v>
       </c>
@@ -2316,14 +2566,14 @@
       <c r="H13" s="3">
         <v>1960230</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>22</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="K13" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:11">
       <c r="A14" s="1" t="s">
         <v>136</v>
       </c>
@@ -2348,14 +2598,14 @@
       <c r="H14" s="3">
         <v>1845243</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>148</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="K14" s="2" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:11">
       <c r="A15" s="1" t="s">
         <v>60</v>
       </c>
@@ -2380,14 +2630,14 @@
       <c r="H15" s="3">
         <v>1796008</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>27</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="K15" s="2" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:11">
       <c r="A16" s="1" t="s">
         <v>323</v>
       </c>
@@ -2412,14 +2662,14 @@
       <c r="H16" s="3">
         <v>1771888</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>341</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="K16" s="2" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:11">
       <c r="A17" s="1" t="s">
         <v>143</v>
       </c>
@@ -2444,14 +2694,14 @@
       <c r="H17" s="3">
         <v>1758290</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>155</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="K17" s="2" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:11">
       <c r="A18" s="1" t="s">
         <v>135</v>
       </c>
@@ -2476,14 +2726,14 @@
       <c r="H18" s="3">
         <v>1560320</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>147</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="K18" s="2" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:11">
       <c r="A19" s="1" t="s">
         <v>58</v>
       </c>
@@ -2508,14 +2758,14 @@
       <c r="H19" s="3">
         <v>1212038</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>25</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="K19" s="2" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:11">
       <c r="A20" s="1" t="s">
         <v>59</v>
       </c>
@@ -2540,14 +2790,17 @@
       <c r="H20" s="3">
         <v>1071359</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20" s="4">
+        <v>7.1</v>
+      </c>
+      <c r="J20" t="s">
         <v>26</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="K20" s="2" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:11">
       <c r="A21" s="1" t="s">
         <v>50</v>
       </c>
@@ -2572,14 +2825,17 @@
       <c r="H21" s="3">
         <v>1028428</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21" s="4">
+        <v>7.1</v>
+      </c>
+      <c r="J21" t="s">
         <v>17</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="K21" s="2" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:11">
       <c r="A22" s="1" t="s">
         <v>52</v>
       </c>
@@ -2601,14 +2857,14 @@
       <c r="H22" s="3">
         <v>976802</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>19</v>
       </c>
-      <c r="J22" s="2" t="s">
+      <c r="K22" s="2" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:11">
       <c r="A23" s="1" t="s">
         <v>324</v>
       </c>
@@ -2633,14 +2889,14 @@
       <c r="H23" s="3">
         <v>954238</v>
       </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>374</v>
       </c>
-      <c r="J23" s="2" t="s">
+      <c r="K23" s="2" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:11">
       <c r="A24" s="1" t="s">
         <v>317</v>
       </c>
@@ -2665,14 +2921,14 @@
       <c r="H24" s="3">
         <v>795715</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>336</v>
       </c>
-      <c r="J24" s="2" t="s">
+      <c r="K24" s="2" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:11">
       <c r="A25" s="1" t="s">
         <v>329</v>
       </c>
@@ -2697,14 +2953,17 @@
       <c r="H25" s="3">
         <v>767044</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I25" s="4">
+        <v>7.8</v>
+      </c>
+      <c r="J25" t="s">
         <v>345</v>
       </c>
-      <c r="J25" s="2" t="s">
+      <c r="K25" s="2" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:11">
       <c r="A26" s="1" t="s">
         <v>68</v>
       </c>
@@ -2729,14 +2988,14 @@
       <c r="H26" s="3">
         <v>653514</v>
       </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>34</v>
       </c>
-      <c r="J26" s="2" t="s">
+      <c r="K26" s="2" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:11">
       <c r="A27" s="1" t="s">
         <v>138</v>
       </c>
@@ -2761,14 +3020,14 @@
       <c r="H27" s="3">
         <v>459883</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>150</v>
       </c>
-      <c r="J27" s="2" t="s">
+      <c r="K27" s="2" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:11">
       <c r="A28" s="1" t="s">
         <v>318</v>
       </c>
@@ -2793,14 +3052,17 @@
       <c r="H28" s="3">
         <v>378104</v>
       </c>
-      <c r="I28" t="s">
+      <c r="I28" s="4">
+        <v>7.8</v>
+      </c>
+      <c r="J28" t="s">
         <v>337</v>
       </c>
-      <c r="J28" s="2" t="s">
+      <c r="K28" s="2" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:11">
       <c r="A29" s="1" t="s">
         <v>316</v>
       </c>
@@ -2825,14 +3087,14 @@
       <c r="H29" s="3">
         <v>377267</v>
       </c>
-      <c r="I29" t="s">
+      <c r="J29" t="s">
         <v>335</v>
       </c>
-      <c r="J29" s="2" t="s">
+      <c r="K29" s="2" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:11">
       <c r="A30" s="1" t="s">
         <v>51</v>
       </c>
@@ -2857,14 +3119,14 @@
       <c r="H30" s="3">
         <v>303763</v>
       </c>
-      <c r="I30" t="s">
+      <c r="J30" t="s">
         <v>18</v>
       </c>
-      <c r="J30" s="2" t="s">
+      <c r="K30" s="2" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:11">
       <c r="A31" s="1" t="s">
         <v>6</v>
       </c>
@@ -2889,14 +3151,14 @@
       <c r="H31" s="3">
         <v>200612</v>
       </c>
-      <c r="I31" t="s">
+      <c r="J31" t="s">
         <v>14</v>
       </c>
-      <c r="J31" s="2" t="s">
+      <c r="K31" s="2" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:11">
       <c r="A32" s="1" t="s">
         <v>61</v>
       </c>
@@ -2921,14 +3183,14 @@
       <c r="H32" s="3">
         <v>132204</v>
       </c>
-      <c r="I32" t="s">
+      <c r="J32" t="s">
         <v>288</v>
       </c>
-      <c r="J32" s="2" t="s">
+      <c r="K32" s="2" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:11">
       <c r="A33" s="1" t="s">
         <v>67</v>
       </c>
@@ -2953,14 +3215,14 @@
       <c r="H33" s="3">
         <v>121479</v>
       </c>
-      <c r="I33" t="s">
+      <c r="J33" t="s">
         <v>33</v>
       </c>
-      <c r="J33" s="2" t="s">
+      <c r="K33" s="2" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:11">
       <c r="A34" s="1" t="s">
         <v>322</v>
       </c>
@@ -2985,14 +3247,14 @@
       <c r="H34" s="3">
         <v>98231</v>
       </c>
-      <c r="I34" t="s">
+      <c r="J34" t="s">
         <v>369</v>
       </c>
-      <c r="J34" s="2" t="s">
+      <c r="K34" s="2" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:11">
       <c r="A35" s="1" t="s">
         <v>137</v>
       </c>
@@ -3017,14 +3279,14 @@
       <c r="H35" s="3">
         <v>4524</v>
       </c>
-      <c r="I35" t="s">
+      <c r="J35" t="s">
         <v>149</v>
       </c>
-      <c r="J35" s="2" t="s">
+      <c r="K35" s="2" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:11">
       <c r="A36" s="1" t="s">
         <v>62</v>
       </c>
@@ -3049,14 +3311,14 @@
       <c r="H36" s="3">
         <v>7733587</v>
       </c>
-      <c r="I36" t="s">
+      <c r="J36" t="s">
         <v>28</v>
       </c>
-      <c r="J36" s="2" t="s">
+      <c r="K36" s="2" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:11">
       <c r="A37" s="1" t="s">
         <v>83</v>
       </c>
@@ -3081,14 +3343,14 @@
       <c r="H37" s="3">
         <v>5275870</v>
       </c>
-      <c r="I37" t="s">
+      <c r="J37" t="s">
         <v>47</v>
       </c>
-      <c r="J37" s="2" t="s">
+      <c r="K37" s="2" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:11">
       <c r="A38" s="1" t="s">
         <v>80</v>
       </c>
@@ -3113,14 +3375,14 @@
       <c r="H38" s="3">
         <v>5265895</v>
       </c>
-      <c r="I38" t="s">
+      <c r="J38" t="s">
         <v>45</v>
       </c>
-      <c r="J38" s="2" t="s">
+      <c r="K38" s="2" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:11">
       <c r="A39" s="1" t="s">
         <v>140</v>
       </c>
@@ -3145,14 +3407,14 @@
       <c r="H39" s="3">
         <v>4674495</v>
       </c>
-      <c r="I39" t="s">
+      <c r="J39" t="s">
         <v>152</v>
       </c>
-      <c r="J39" s="2" t="s">
+      <c r="K39" s="2" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:11">
       <c r="A40" s="1" t="s">
         <v>327</v>
       </c>
@@ -3177,14 +3439,14 @@
       <c r="H40" s="3">
         <v>4655514</v>
       </c>
-      <c r="I40" t="s">
+      <c r="J40" t="s">
         <v>344</v>
       </c>
-      <c r="J40" s="2" t="s">
+      <c r="K40" s="2" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:11">
       <c r="A41" s="1" t="s">
         <v>69</v>
       </c>
@@ -3209,14 +3471,14 @@
       <c r="H41" s="3">
         <v>4141267</v>
       </c>
-      <c r="I41" t="s">
+      <c r="J41" t="s">
         <v>35</v>
       </c>
-      <c r="J41" s="2" t="s">
+      <c r="K41" s="2" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:11">
       <c r="A42" s="1" t="s">
         <v>66</v>
       </c>
@@ -3241,14 +3503,14 @@
       <c r="H42" s="3">
         <v>2991300</v>
       </c>
-      <c r="I42" t="s">
+      <c r="J42" t="s">
         <v>32</v>
       </c>
-      <c r="J42" s="2" t="s">
+      <c r="K42" s="2" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:11">
       <c r="A43" s="1" t="s">
         <v>72</v>
       </c>
@@ -3273,14 +3535,14 @@
       <c r="H43" s="3">
         <v>2563754</v>
       </c>
-      <c r="I43" t="s">
+      <c r="J43" t="s">
         <v>289</v>
       </c>
-      <c r="J43" s="2" t="s">
+      <c r="K43" s="2" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:11">
       <c r="A44" s="1" t="s">
         <v>328</v>
       </c>
@@ -3305,14 +3567,14 @@
       <c r="H44" s="3">
         <v>2400663</v>
       </c>
-      <c r="I44" t="s">
+      <c r="J44" t="s">
         <v>385</v>
       </c>
-      <c r="J44" s="2" t="s">
+      <c r="K44" s="2" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:11">
       <c r="A45" s="1" t="s">
         <v>325</v>
       </c>
@@ -3337,14 +3599,14 @@
       <c r="H45" s="3">
         <v>2340742</v>
       </c>
-      <c r="I45" t="s">
+      <c r="J45" t="s">
         <v>342</v>
       </c>
-      <c r="J45" s="2" t="s">
+      <c r="K45" s="2" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:11">
       <c r="A46" s="1" t="s">
         <v>133</v>
       </c>
@@ -3369,14 +3631,14 @@
       <c r="H46" s="3">
         <v>1265188</v>
       </c>
-      <c r="I46" t="s">
+      <c r="J46" t="s">
         <v>145</v>
       </c>
-      <c r="J46" t="s">
+      <c r="K46" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:11">
       <c r="A47" s="1" t="s">
         <v>84</v>
       </c>
@@ -3401,14 +3663,14 @@
       <c r="H47" s="3">
         <v>1259285</v>
       </c>
-      <c r="I47" t="s">
+      <c r="J47" t="s">
         <v>48</v>
       </c>
-      <c r="J47" s="2" t="s">
+      <c r="K47" s="2" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:11">
       <c r="A48" s="1" t="s">
         <v>144</v>
       </c>
@@ -3433,14 +3695,14 @@
       <c r="H48" s="3">
         <v>1218509</v>
       </c>
-      <c r="I48" t="s">
+      <c r="J48" t="s">
         <v>156</v>
       </c>
-      <c r="J48" s="2" t="s">
+      <c r="K48" s="2" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:11">
       <c r="A49" s="1" t="s">
         <v>73</v>
       </c>
@@ -3465,14 +3727,14 @@
       <c r="H49" s="3">
         <v>947291</v>
       </c>
-      <c r="I49" t="s">
+      <c r="J49" t="s">
         <v>38</v>
       </c>
-      <c r="J49" s="2" t="s">
+      <c r="K49" s="2" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:11">
       <c r="A50" s="1" t="s">
         <v>78</v>
       </c>
@@ -3497,14 +3759,14 @@
       <c r="H50" s="3">
         <v>802315</v>
       </c>
-      <c r="I50" t="s">
+      <c r="J50" t="s">
         <v>43</v>
       </c>
-      <c r="J50" s="2" t="s">
+      <c r="K50" s="2" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:11">
       <c r="A51" s="1" t="s">
         <v>70</v>
       </c>
@@ -3529,14 +3791,14 @@
       <c r="H51" s="3">
         <v>617188</v>
       </c>
-      <c r="I51" t="s">
+      <c r="J51" t="s">
         <v>36</v>
       </c>
-      <c r="J51" s="2" t="s">
+      <c r="K51" s="2" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:11">
       <c r="A52" s="1" t="s">
         <v>71</v>
       </c>
@@ -3561,14 +3823,14 @@
       <c r="H52" s="3">
         <v>613506</v>
       </c>
-      <c r="I52" t="s">
+      <c r="J52" t="s">
         <v>37</v>
       </c>
-      <c r="J52" s="2" t="s">
+      <c r="K52" s="2" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:11">
       <c r="A53" s="1" t="s">
         <v>134</v>
       </c>
@@ -3593,14 +3855,14 @@
       <c r="H53" s="3">
         <v>587879</v>
       </c>
-      <c r="I53" t="s">
+      <c r="J53" t="s">
         <v>146</v>
       </c>
-      <c r="J53" s="2" t="s">
+      <c r="K53" s="2" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:11">
       <c r="A54" s="1" t="s">
         <v>293</v>
       </c>
@@ -3625,14 +3887,14 @@
       <c r="H54" s="3">
         <v>562667</v>
       </c>
-      <c r="I54" t="s">
+      <c r="J54" t="s">
         <v>297</v>
       </c>
-      <c r="J54" s="2" t="s">
+      <c r="K54" s="2" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:11">
       <c r="A55" s="1" t="s">
         <v>82</v>
       </c>
@@ -3657,14 +3919,14 @@
       <c r="H55" s="3">
         <v>552739</v>
       </c>
-      <c r="I55" t="s">
+      <c r="J55" t="s">
         <v>46</v>
       </c>
-      <c r="J55" s="2" t="s">
+      <c r="K55" s="2" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:11">
       <c r="A56" s="1" t="s">
         <v>81</v>
       </c>
@@ -3689,14 +3951,14 @@
       <c r="H56" s="3">
         <v>517958</v>
       </c>
-      <c r="I56" t="s">
+      <c r="J56" t="s">
         <v>290</v>
       </c>
-      <c r="J56" s="2" t="s">
+      <c r="K56" s="2" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:11">
       <c r="A57" s="1" t="s">
         <v>319</v>
       </c>
@@ -3721,14 +3983,14 @@
       <c r="H57" s="3">
         <v>483734</v>
       </c>
-      <c r="I57" t="s">
+      <c r="J57" t="s">
         <v>338</v>
       </c>
-      <c r="J57" s="2" t="s">
+      <c r="K57" s="2" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:11">
       <c r="A58" s="1" t="s">
         <v>330</v>
       </c>
@@ -3753,14 +4015,14 @@
       <c r="H58" s="3">
         <v>470562</v>
       </c>
-      <c r="I58" t="s">
+      <c r="J58" t="s">
         <v>346</v>
       </c>
-      <c r="J58" s="2" t="s">
+      <c r="K58" s="2" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:11">
       <c r="A59" s="1" t="s">
         <v>142</v>
       </c>
@@ -3785,14 +4047,14 @@
       <c r="H59" s="3">
         <v>349359</v>
       </c>
-      <c r="I59" t="s">
+      <c r="J59" t="s">
         <v>154</v>
       </c>
-      <c r="J59" s="2" t="s">
+      <c r="K59" s="2" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:11">
       <c r="A60" s="1" t="s">
         <v>64</v>
       </c>
@@ -3817,14 +4079,14 @@
       <c r="H60" s="3">
         <v>290313</v>
       </c>
-      <c r="I60" t="s">
+      <c r="J60" t="s">
         <v>30</v>
       </c>
-      <c r="J60" s="2" t="s">
+      <c r="K60" s="2" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:11">
       <c r="A61" s="1" t="s">
         <v>65</v>
       </c>
@@ -3849,14 +4111,14 @@
       <c r="H61" s="3">
         <v>243599</v>
       </c>
-      <c r="I61" t="s">
+      <c r="J61" t="s">
         <v>31</v>
       </c>
-      <c r="J61" s="2" t="s">
+      <c r="K61" s="2" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:11">
       <c r="A62" s="1" t="s">
         <v>139</v>
       </c>
@@ -3881,14 +4143,14 @@
       <c r="H62" s="3">
         <v>189629</v>
       </c>
-      <c r="I62" t="s">
+      <c r="J62" t="s">
         <v>151</v>
       </c>
-      <c r="J62" s="2" t="s">
+      <c r="K62" s="2" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:11">
       <c r="A63" s="1" t="s">
         <v>331</v>
       </c>
@@ -3913,14 +4175,14 @@
       <c r="H63" s="3">
         <v>154914</v>
       </c>
-      <c r="I63" t="s">
+      <c r="J63" t="s">
         <v>347</v>
       </c>
-      <c r="J63" s="2" t="s">
+      <c r="K63" s="2" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:11">
       <c r="A64" s="1" t="s">
         <v>326</v>
       </c>
@@ -3945,14 +4207,14 @@
       <c r="H64" s="3">
         <v>147091</v>
       </c>
-      <c r="I64" t="s">
+      <c r="J64" t="s">
         <v>343</v>
       </c>
-      <c r="J64" s="2" t="s">
+      <c r="K64" s="2" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:11">
       <c r="A65" s="1" t="s">
         <v>63</v>
       </c>
@@ -3977,14 +4239,14 @@
       <c r="H65" s="3">
         <v>136424</v>
       </c>
-      <c r="I65" t="s">
+      <c r="J65" t="s">
         <v>29</v>
       </c>
-      <c r="J65" s="2" t="s">
+      <c r="K65" s="2" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:11">
       <c r="A66" s="1" t="s">
         <v>333</v>
       </c>
@@ -4009,14 +4271,14 @@
       <c r="H66" s="3">
         <v>136234</v>
       </c>
-      <c r="I66" t="s">
+      <c r="J66" t="s">
         <v>349</v>
       </c>
-      <c r="J66" s="2" t="s">
+      <c r="K66" s="2" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:11">
       <c r="A67" s="1" t="s">
         <v>141</v>
       </c>
@@ -4041,14 +4303,14 @@
       <c r="H67" s="3">
         <v>99365</v>
       </c>
-      <c r="I67" t="s">
+      <c r="J67" t="s">
         <v>153</v>
       </c>
-      <c r="J67" s="2" t="s">
+      <c r="K67" s="2" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:11">
       <c r="A68" s="1" t="s">
         <v>320</v>
       </c>
@@ -4073,14 +4335,14 @@
       <c r="H68" s="3">
         <v>67758</v>
       </c>
-      <c r="I68" t="s">
+      <c r="J68" t="s">
         <v>339</v>
       </c>
-      <c r="J68" s="2" t="s">
+      <c r="K68" s="2" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:11">
       <c r="A69" s="1" t="s">
         <v>77</v>
       </c>
@@ -4105,14 +4367,14 @@
       <c r="H69" s="3">
         <v>25178</v>
       </c>
-      <c r="I69" t="s">
+      <c r="J69" t="s">
         <v>42</v>
       </c>
-      <c r="J69" s="2" t="s">
+      <c r="K69" s="2" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:11">
       <c r="A70" s="1" t="s">
         <v>74</v>
       </c>
@@ -4137,14 +4399,14 @@
       <c r="H70" s="3">
         <v>19483</v>
       </c>
-      <c r="I70" t="s">
+      <c r="J70" t="s">
         <v>39</v>
       </c>
-      <c r="J70" s="2" t="s">
+      <c r="K70" s="2" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:11">
       <c r="A71" s="1" t="s">
         <v>332</v>
       </c>
@@ -4169,89 +4431,521 @@
       <c r="H71" s="3">
         <v>15835</v>
       </c>
-      <c r="I71" t="s">
+      <c r="J71" t="s">
         <v>348</v>
       </c>
-      <c r="J71" s="2" t="s">
+      <c r="K71" s="2" t="s">
         <v>399</v>
       </c>
     </row>
+    <row r="72" spans="1:11">
+      <c r="A72" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B72" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72">
+        <v>2021</v>
+      </c>
+      <c r="D72" t="s">
+        <v>291</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F72" t="s">
+        <v>426</v>
+      </c>
+      <c r="G72" t="s">
+        <v>425</v>
+      </c>
+      <c r="H72" s="3">
+        <v>3164608</v>
+      </c>
+      <c r="I72" s="4">
+        <v>8.6</v>
+      </c>
+      <c r="J72" t="s">
+        <v>413</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73">
+        <v>2021</v>
+      </c>
+      <c r="D73" t="s">
+        <v>291</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F73" t="s">
+        <v>428</v>
+      </c>
+      <c r="G73" t="s">
+        <v>431</v>
+      </c>
+      <c r="H73" s="3">
+        <v>52300</v>
+      </c>
+      <c r="I73" s="4">
+        <v>8.5</v>
+      </c>
+      <c r="J73" t="s">
+        <v>414</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B74" t="s">
+        <v>11</v>
+      </c>
+      <c r="C74">
+        <v>2021</v>
+      </c>
+      <c r="D74" t="s">
+        <v>291</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="F74" t="s">
+        <v>432</v>
+      </c>
+      <c r="G74" t="s">
+        <v>430</v>
+      </c>
+      <c r="H74" s="3">
+        <v>489413</v>
+      </c>
+      <c r="I74" s="4">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="J74" t="s">
+        <v>415</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B75" t="s">
+        <v>11</v>
+      </c>
+      <c r="C75">
+        <v>2021</v>
+      </c>
+      <c r="D75" t="s">
+        <v>291</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F75" t="s">
+        <v>436</v>
+      </c>
+      <c r="G75" t="s">
+        <v>435</v>
+      </c>
+      <c r="H75" s="3">
+        <v>95136</v>
+      </c>
+      <c r="I75" s="4">
+        <v>7.9</v>
+      </c>
+      <c r="J75" t="s">
+        <v>416</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="A76" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B76" t="s">
+        <v>11</v>
+      </c>
+      <c r="C76">
+        <v>2021</v>
+      </c>
+      <c r="D76" t="s">
+        <v>291</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F76" t="s">
+        <v>439</v>
+      </c>
+      <c r="G76" t="s">
+        <v>438</v>
+      </c>
+      <c r="H76" s="3">
+        <v>2330511</v>
+      </c>
+      <c r="I76" s="4">
+        <v>7.6</v>
+      </c>
+      <c r="J76" t="s">
+        <v>417</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B77" t="s">
+        <v>11</v>
+      </c>
+      <c r="C77">
+        <v>2021</v>
+      </c>
+      <c r="D77" t="s">
+        <v>291</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F77" t="s">
+        <v>442</v>
+      </c>
+      <c r="G77" t="s">
+        <v>441</v>
+      </c>
+      <c r="H77" s="3">
+        <v>548641</v>
+      </c>
+      <c r="I77" s="4">
+        <v>7.6</v>
+      </c>
+      <c r="J77" t="s">
+        <v>418</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B78" t="s">
+        <v>11</v>
+      </c>
+      <c r="C78">
+        <v>2021</v>
+      </c>
+      <c r="D78" t="s">
+        <v>291</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="F78" t="s">
+        <v>445</v>
+      </c>
+      <c r="G78" t="s">
+        <v>444</v>
+      </c>
+      <c r="H78" s="3">
+        <v>52113</v>
+      </c>
+      <c r="I78" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="J78" t="s">
+        <v>419</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
+      <c r="A79" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B79" t="s">
+        <v>11</v>
+      </c>
+      <c r="C79">
+        <v>2021</v>
+      </c>
+      <c r="D79" t="s">
+        <v>291</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F79" t="s">
+        <v>448</v>
+      </c>
+      <c r="G79" t="s">
+        <v>447</v>
+      </c>
+      <c r="H79" s="3">
+        <v>134785</v>
+      </c>
+      <c r="I79" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="J79" t="s">
+        <v>420</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B80" t="s">
+        <v>11</v>
+      </c>
+      <c r="C80">
+        <v>2021</v>
+      </c>
+      <c r="D80" t="s">
+        <v>291</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="F80" t="s">
+        <v>451</v>
+      </c>
+      <c r="G80" t="s">
+        <v>450</v>
+      </c>
+      <c r="H80" s="3">
+        <v>1278633</v>
+      </c>
+      <c r="I80" s="4">
+        <v>7.3</v>
+      </c>
+      <c r="J80" t="s">
+        <v>421</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B81" t="s">
+        <v>11</v>
+      </c>
+      <c r="C81">
+        <v>2021</v>
+      </c>
+      <c r="D81" t="s">
+        <v>291</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="F81" t="s">
+        <v>455</v>
+      </c>
+      <c r="G81" t="s">
+        <v>454</v>
+      </c>
+      <c r="H81" s="3">
+        <v>2043804</v>
+      </c>
+      <c r="I81" s="4">
+        <v>7.2</v>
+      </c>
+      <c r="J81" t="s">
+        <v>422</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="A82" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B82" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82">
+        <v>2021</v>
+      </c>
+      <c r="D82" t="s">
+        <v>291</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F82" t="s">
+        <v>458</v>
+      </c>
+      <c r="G82" t="s">
+        <v>457</v>
+      </c>
+      <c r="H82" s="3">
+        <v>785247</v>
+      </c>
+      <c r="I82" s="4">
+        <v>7</v>
+      </c>
+      <c r="J82" t="s">
+        <v>423</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B83" t="s">
+        <v>11</v>
+      </c>
+      <c r="C83">
+        <v>2021</v>
+      </c>
+      <c r="D83" t="s">
+        <v>291</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="F83" t="s">
+        <v>462</v>
+      </c>
+      <c r="G83" t="s">
+        <v>461</v>
+      </c>
+      <c r="H83" s="3">
+        <v>89338</v>
+      </c>
+      <c r="I83" s="4">
+        <v>7</v>
+      </c>
+      <c r="J83" t="s">
+        <v>424</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>463</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J71">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K71">
     <sortCondition ref="D2:D71"/>
     <sortCondition descending="1" ref="H2:H71"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="J31" r:id="rId1" xr:uid="{725A3016-CC80-5F4A-B091-4E71BCFAD36B}"/>
-    <hyperlink ref="J11" r:id="rId2" xr:uid="{38F493C0-3185-604E-A3BD-AAB0EC5B83DF}"/>
-    <hyperlink ref="J7" r:id="rId3" xr:uid="{2E642780-E9D7-BF4B-9D23-FEBE51DDD0C9}"/>
-    <hyperlink ref="J21" r:id="rId4" xr:uid="{5CF6DEF3-9028-3D4C-846C-DA2618807577}"/>
-    <hyperlink ref="J30" r:id="rId5" xr:uid="{A298B622-5340-5148-820B-D468159EA5BD}"/>
-    <hyperlink ref="J22" r:id="rId6" xr:uid="{EF9BC619-52CD-2D48-BE99-80BD81A8CD54}"/>
-    <hyperlink ref="J12" r:id="rId7" xr:uid="{0002A242-754F-5A40-86A8-5F7DBBEBB9D1}"/>
-    <hyperlink ref="J10" r:id="rId8" xr:uid="{085C9D3E-4AFA-FF48-AA1A-64ECF275D4C0}"/>
-    <hyperlink ref="J13" r:id="rId9" xr:uid="{118F4CA9-C4A7-F74E-8AFF-041FB2741717}"/>
-    <hyperlink ref="J3" r:id="rId10" xr:uid="{75687EB7-0A29-5C47-921B-954A17F06565}"/>
-    <hyperlink ref="J9" r:id="rId11" xr:uid="{81B8E0D0-29DD-E74A-8CE3-1464ECDB131A}"/>
-    <hyperlink ref="J19" r:id="rId12" xr:uid="{5D4D2728-3F60-EE43-86DF-EE58ADBF8432}"/>
-    <hyperlink ref="J20" r:id="rId13" xr:uid="{31C21087-E027-4542-80B2-C095CF193FA7}"/>
-    <hyperlink ref="J15" r:id="rId14" xr:uid="{36CFF13A-82D4-9642-B07B-0C3E49B5D215}"/>
-    <hyperlink ref="J32" r:id="rId15" xr:uid="{DDDE99D5-3422-6549-8393-D5FC330D45B8}"/>
-    <hyperlink ref="J36" r:id="rId16" xr:uid="{9621A5D4-6BD1-984D-9C8C-2A89CFA54CFF}"/>
-    <hyperlink ref="J65" r:id="rId17" xr:uid="{CC87EE91-DF39-EA48-9614-33030270159C}"/>
-    <hyperlink ref="J60" r:id="rId18" xr:uid="{C4E1F448-AF1B-BC43-983F-FB439266392E}"/>
-    <hyperlink ref="J61" r:id="rId19" xr:uid="{17A665F7-B807-4640-B444-16CFE27D5FDF}"/>
-    <hyperlink ref="J42" r:id="rId20" xr:uid="{244C8E1D-D3A7-9549-9D73-8F4D984A6ACD}"/>
-    <hyperlink ref="J33" r:id="rId21" xr:uid="{135AB67A-502A-8A4D-B049-40F78987A6E4}"/>
-    <hyperlink ref="J26" r:id="rId22" xr:uid="{2EBEE3F8-DF57-0E4A-9FB8-2C6B08B9453B}"/>
-    <hyperlink ref="J41" r:id="rId23" xr:uid="{50C93161-BA50-264D-9EB0-FD96B5179BD3}"/>
-    <hyperlink ref="J51" r:id="rId24" xr:uid="{EB1586AB-126F-2B4B-AB36-6A028744AF76}"/>
-    <hyperlink ref="J52" r:id="rId25" xr:uid="{7C55426F-9022-8044-ACAA-5AEC9137C037}"/>
-    <hyperlink ref="J43" r:id="rId26" xr:uid="{AD424BE3-B862-2442-B3B2-5028AF918C6F}"/>
-    <hyperlink ref="J49" r:id="rId27" xr:uid="{2183D387-1FD2-324D-A080-BF2A14B2C266}"/>
-    <hyperlink ref="J70" r:id="rId28" xr:uid="{FDBD3899-8300-BE4F-B928-93EB7382FF06}"/>
-    <hyperlink ref="J2" r:id="rId29" xr:uid="{529C6D37-3C52-0C4C-8560-C27F3F7C2BCE}"/>
-    <hyperlink ref="J6" r:id="rId30" xr:uid="{D004E2AA-6899-A547-B940-4CF0A68E6AE2}"/>
-    <hyperlink ref="J69" r:id="rId31" xr:uid="{2DA721C4-AB3A-EB48-85F9-525AB6A822AB}"/>
-    <hyperlink ref="J50" r:id="rId32" xr:uid="{72A6DA76-289B-1945-8072-DAECE2441387}"/>
-    <hyperlink ref="J4" r:id="rId33" xr:uid="{1ED33379-967F-8D43-85DD-BDDF4C65376C}"/>
-    <hyperlink ref="J38" r:id="rId34" xr:uid="{F704F2D4-3F11-614C-BFFC-5AA6E996A592}"/>
-    <hyperlink ref="J56" r:id="rId35" xr:uid="{5F94CB6B-2D0C-7C41-9363-23A9286E6D55}"/>
-    <hyperlink ref="J55" r:id="rId36" xr:uid="{02572C89-38D3-4B47-B603-D75FBB76E0BB}"/>
-    <hyperlink ref="J37" r:id="rId37" xr:uid="{96F331DE-1BF1-354F-9E54-FA8C80316EFB}"/>
-    <hyperlink ref="J47" r:id="rId38" xr:uid="{D40AF006-F71D-054C-BD53-C9CF18C19E2B}"/>
-    <hyperlink ref="J53" r:id="rId39" xr:uid="{D3ABB7B3-002B-9E42-A591-D3282F8D9EDC}"/>
-    <hyperlink ref="J18" r:id="rId40" xr:uid="{F2CD1548-C098-164F-AE85-0E2D85DE116F}"/>
-    <hyperlink ref="J14" r:id="rId41" xr:uid="{81094FDB-D745-024E-BD73-D63401EE9AA2}"/>
-    <hyperlink ref="J35" r:id="rId42" xr:uid="{850F5B2D-3612-1E44-A230-B654A61C2B8F}"/>
-    <hyperlink ref="J27" r:id="rId43" xr:uid="{D84F734D-746E-B841-A450-F741C1E43856}"/>
-    <hyperlink ref="J62" r:id="rId44" xr:uid="{7870E1C9-1855-634F-8B01-0A6F56E1C8EC}"/>
-    <hyperlink ref="J39" r:id="rId45" xr:uid="{74E258E9-3406-444C-9382-59C9A5DD2D28}"/>
-    <hyperlink ref="J67" r:id="rId46" xr:uid="{22AFEECC-9483-CC40-B244-DB64D5BE611A}"/>
-    <hyperlink ref="J59" r:id="rId47" xr:uid="{3F60EBBC-9A66-404C-8F8D-E0FD74919AF5}"/>
-    <hyperlink ref="J17" r:id="rId48" xr:uid="{97FC090B-C1AF-3B40-8E1E-653AF871E0B8}"/>
-    <hyperlink ref="J48" r:id="rId49" xr:uid="{24271837-2997-A04B-B1A8-30D8EAA5AABF}"/>
-    <hyperlink ref="J54" r:id="rId50" xr:uid="{C6FE7874-DE1E-8744-8F7F-A7266A282BC7}"/>
-    <hyperlink ref="J8" r:id="rId51" xr:uid="{45D4B454-64FD-E043-9E1E-D98B915DA3C4}"/>
-    <hyperlink ref="J29" r:id="rId52" xr:uid="{592E8301-AD04-6A43-BE2C-DF1DCF4D0C8C}"/>
-    <hyperlink ref="J24" r:id="rId53" xr:uid="{AFFE99AD-C3BD-7D47-ADD2-0033AB1BD297}"/>
-    <hyperlink ref="J28" r:id="rId54" xr:uid="{10637FCE-769F-EF46-AFAF-F312278F1225}"/>
-    <hyperlink ref="J57" r:id="rId55" xr:uid="{1E8D6F6E-5279-684F-9870-749B17340F35}"/>
-    <hyperlink ref="J68" r:id="rId56" xr:uid="{C19F506D-023C-1247-BE6A-C23960198C51}"/>
-    <hyperlink ref="J5" r:id="rId57" xr:uid="{3E64B722-3690-B44C-ABC4-059D3B71C8D7}"/>
-    <hyperlink ref="J34" r:id="rId58" xr:uid="{50C3436F-19AF-D74F-8E0A-E9F0AEF4EF7F}"/>
-    <hyperlink ref="J16" r:id="rId59" xr:uid="{A5BBD32C-6F92-A842-A00C-8F17A0710E00}"/>
-    <hyperlink ref="J23" r:id="rId60" xr:uid="{117A81C3-427C-DF49-BA81-BE00A024107F}"/>
-    <hyperlink ref="J45" r:id="rId61" xr:uid="{5E89FA9C-5C01-5342-876F-D8B51FE4E2B8}"/>
-    <hyperlink ref="J64" r:id="rId62" xr:uid="{AE06ADB0-CCC6-5E4F-AA64-084B6EC4EDA5}"/>
-    <hyperlink ref="J40" r:id="rId63" xr:uid="{C1BBF821-4DC8-5347-B6F0-96939C529BA4}"/>
-    <hyperlink ref="J44" r:id="rId64" xr:uid="{990812EE-4D67-A148-8354-137377C29D95}"/>
-    <hyperlink ref="J25" r:id="rId65" xr:uid="{9C8D9D49-3342-1D45-9490-372911350A58}"/>
-    <hyperlink ref="J58" r:id="rId66" xr:uid="{EFDE2707-AAFE-A445-930B-DB05A658CF11}"/>
-    <hyperlink ref="J63" r:id="rId67" xr:uid="{C4CFA4B9-7F0C-2D48-848B-F4855312250F}"/>
-    <hyperlink ref="J66" r:id="rId68" xr:uid="{2C92D437-B811-BA4F-A7A0-ECBD7F90C3E8}"/>
-    <hyperlink ref="J71" r:id="rId69" xr:uid="{1DA360B3-3EEC-0B4A-92B2-F41887D4DA99}"/>
+    <hyperlink ref="K31" r:id="rId1" xr:uid="{725A3016-CC80-5F4A-B091-4E71BCFAD36B}"/>
+    <hyperlink ref="K11" r:id="rId2" xr:uid="{38F493C0-3185-604E-A3BD-AAB0EC5B83DF}"/>
+    <hyperlink ref="K7" r:id="rId3" xr:uid="{2E642780-E9D7-BF4B-9D23-FEBE51DDD0C9}"/>
+    <hyperlink ref="K21" r:id="rId4" xr:uid="{5CF6DEF3-9028-3D4C-846C-DA2618807577}"/>
+    <hyperlink ref="K30" r:id="rId5" xr:uid="{A298B622-5340-5148-820B-D468159EA5BD}"/>
+    <hyperlink ref="K22" r:id="rId6" xr:uid="{EF9BC619-52CD-2D48-BE99-80BD81A8CD54}"/>
+    <hyperlink ref="K12" r:id="rId7" xr:uid="{0002A242-754F-5A40-86A8-5F7DBBEBB9D1}"/>
+    <hyperlink ref="K10" r:id="rId8" xr:uid="{085C9D3E-4AFA-FF48-AA1A-64ECF275D4C0}"/>
+    <hyperlink ref="K13" r:id="rId9" xr:uid="{118F4CA9-C4A7-F74E-8AFF-041FB2741717}"/>
+    <hyperlink ref="K3" r:id="rId10" xr:uid="{75687EB7-0A29-5C47-921B-954A17F06565}"/>
+    <hyperlink ref="K9" r:id="rId11" xr:uid="{81B8E0D0-29DD-E74A-8CE3-1464ECDB131A}"/>
+    <hyperlink ref="K19" r:id="rId12" xr:uid="{5D4D2728-3F60-EE43-86DF-EE58ADBF8432}"/>
+    <hyperlink ref="K20" r:id="rId13" xr:uid="{31C21087-E027-4542-80B2-C095CF193FA7}"/>
+    <hyperlink ref="K15" r:id="rId14" xr:uid="{36CFF13A-82D4-9642-B07B-0C3E49B5D215}"/>
+    <hyperlink ref="K32" r:id="rId15" xr:uid="{DDDE99D5-3422-6549-8393-D5FC330D45B8}"/>
+    <hyperlink ref="K36" r:id="rId16" xr:uid="{9621A5D4-6BD1-984D-9C8C-2A89CFA54CFF}"/>
+    <hyperlink ref="K65" r:id="rId17" xr:uid="{CC87EE91-DF39-EA48-9614-33030270159C}"/>
+    <hyperlink ref="K60" r:id="rId18" xr:uid="{C4E1F448-AF1B-BC43-983F-FB439266392E}"/>
+    <hyperlink ref="K61" r:id="rId19" xr:uid="{17A665F7-B807-4640-B444-16CFE27D5FDF}"/>
+    <hyperlink ref="K42" r:id="rId20" xr:uid="{244C8E1D-D3A7-9549-9D73-8F4D984A6ACD}"/>
+    <hyperlink ref="K33" r:id="rId21" xr:uid="{135AB67A-502A-8A4D-B049-40F78987A6E4}"/>
+    <hyperlink ref="K26" r:id="rId22" xr:uid="{2EBEE3F8-DF57-0E4A-9FB8-2C6B08B9453B}"/>
+    <hyperlink ref="K41" r:id="rId23" xr:uid="{50C93161-BA50-264D-9EB0-FD96B5179BD3}"/>
+    <hyperlink ref="K51" r:id="rId24" xr:uid="{EB1586AB-126F-2B4B-AB36-6A028744AF76}"/>
+    <hyperlink ref="K52" r:id="rId25" xr:uid="{7C55426F-9022-8044-ACAA-5AEC9137C037}"/>
+    <hyperlink ref="K43" r:id="rId26" xr:uid="{AD424BE3-B862-2442-B3B2-5028AF918C6F}"/>
+    <hyperlink ref="K49" r:id="rId27" xr:uid="{2183D387-1FD2-324D-A080-BF2A14B2C266}"/>
+    <hyperlink ref="K70" r:id="rId28" xr:uid="{FDBD3899-8300-BE4F-B928-93EB7382FF06}"/>
+    <hyperlink ref="K2" r:id="rId29" xr:uid="{529C6D37-3C52-0C4C-8560-C27F3F7C2BCE}"/>
+    <hyperlink ref="K6" r:id="rId30" xr:uid="{D004E2AA-6899-A547-B940-4CF0A68E6AE2}"/>
+    <hyperlink ref="K69" r:id="rId31" xr:uid="{2DA721C4-AB3A-EB48-85F9-525AB6A822AB}"/>
+    <hyperlink ref="K50" r:id="rId32" xr:uid="{72A6DA76-289B-1945-8072-DAECE2441387}"/>
+    <hyperlink ref="K4" r:id="rId33" xr:uid="{1ED33379-967F-8D43-85DD-BDDF4C65376C}"/>
+    <hyperlink ref="K38" r:id="rId34" xr:uid="{F704F2D4-3F11-614C-BFFC-5AA6E996A592}"/>
+    <hyperlink ref="K56" r:id="rId35" xr:uid="{5F94CB6B-2D0C-7C41-9363-23A9286E6D55}"/>
+    <hyperlink ref="K55" r:id="rId36" xr:uid="{02572C89-38D3-4B47-B603-D75FBB76E0BB}"/>
+    <hyperlink ref="K37" r:id="rId37" xr:uid="{96F331DE-1BF1-354F-9E54-FA8C80316EFB}"/>
+    <hyperlink ref="K47" r:id="rId38" xr:uid="{D40AF006-F71D-054C-BD53-C9CF18C19E2B}"/>
+    <hyperlink ref="K53" r:id="rId39" xr:uid="{D3ABB7B3-002B-9E42-A591-D3282F8D9EDC}"/>
+    <hyperlink ref="K18" r:id="rId40" xr:uid="{F2CD1548-C098-164F-AE85-0E2D85DE116F}"/>
+    <hyperlink ref="K14" r:id="rId41" xr:uid="{81094FDB-D745-024E-BD73-D63401EE9AA2}"/>
+    <hyperlink ref="K35" r:id="rId42" xr:uid="{850F5B2D-3612-1E44-A230-B654A61C2B8F}"/>
+    <hyperlink ref="K27" r:id="rId43" xr:uid="{D84F734D-746E-B841-A450-F741C1E43856}"/>
+    <hyperlink ref="K62" r:id="rId44" xr:uid="{7870E1C9-1855-634F-8B01-0A6F56E1C8EC}"/>
+    <hyperlink ref="K39" r:id="rId45" xr:uid="{74E258E9-3406-444C-9382-59C9A5DD2D28}"/>
+    <hyperlink ref="K67" r:id="rId46" xr:uid="{22AFEECC-9483-CC40-B244-DB64D5BE611A}"/>
+    <hyperlink ref="K59" r:id="rId47" xr:uid="{3F60EBBC-9A66-404C-8F8D-E0FD74919AF5}"/>
+    <hyperlink ref="K17" r:id="rId48" xr:uid="{97FC090B-C1AF-3B40-8E1E-653AF871E0B8}"/>
+    <hyperlink ref="K48" r:id="rId49" xr:uid="{24271837-2997-A04B-B1A8-30D8EAA5AABF}"/>
+    <hyperlink ref="K54" r:id="rId50" xr:uid="{C6FE7874-DE1E-8744-8F7F-A7266A282BC7}"/>
+    <hyperlink ref="K8" r:id="rId51" xr:uid="{45D4B454-64FD-E043-9E1E-D98B915DA3C4}"/>
+    <hyperlink ref="K29" r:id="rId52" xr:uid="{592E8301-AD04-6A43-BE2C-DF1DCF4D0C8C}"/>
+    <hyperlink ref="K24" r:id="rId53" xr:uid="{AFFE99AD-C3BD-7D47-ADD2-0033AB1BD297}"/>
+    <hyperlink ref="K28" r:id="rId54" xr:uid="{10637FCE-769F-EF46-AFAF-F312278F1225}"/>
+    <hyperlink ref="K57" r:id="rId55" xr:uid="{1E8D6F6E-5279-684F-9870-749B17340F35}"/>
+    <hyperlink ref="K68" r:id="rId56" xr:uid="{C19F506D-023C-1247-BE6A-C23960198C51}"/>
+    <hyperlink ref="K5" r:id="rId57" xr:uid="{3E64B722-3690-B44C-ABC4-059D3B71C8D7}"/>
+    <hyperlink ref="K34" r:id="rId58" xr:uid="{50C3436F-19AF-D74F-8E0A-E9F0AEF4EF7F}"/>
+    <hyperlink ref="K16" r:id="rId59" xr:uid="{A5BBD32C-6F92-A842-A00C-8F17A0710E00}"/>
+    <hyperlink ref="K23" r:id="rId60" xr:uid="{117A81C3-427C-DF49-BA81-BE00A024107F}"/>
+    <hyperlink ref="K45" r:id="rId61" xr:uid="{5E89FA9C-5C01-5342-876F-D8B51FE4E2B8}"/>
+    <hyperlink ref="K64" r:id="rId62" xr:uid="{AE06ADB0-CCC6-5E4F-AA64-084B6EC4EDA5}"/>
+    <hyperlink ref="K40" r:id="rId63" xr:uid="{C1BBF821-4DC8-5347-B6F0-96939C529BA4}"/>
+    <hyperlink ref="K44" r:id="rId64" xr:uid="{990812EE-4D67-A148-8354-137377C29D95}"/>
+    <hyperlink ref="K25" r:id="rId65" xr:uid="{9C8D9D49-3342-1D45-9490-372911350A58}"/>
+    <hyperlink ref="K58" r:id="rId66" xr:uid="{EFDE2707-AAFE-A445-930B-DB05A658CF11}"/>
+    <hyperlink ref="K63" r:id="rId67" xr:uid="{C4CFA4B9-7F0C-2D48-848B-F4855312250F}"/>
+    <hyperlink ref="K66" r:id="rId68" xr:uid="{2C92D437-B811-BA4F-A7A0-ECBD7F90C3E8}"/>
+    <hyperlink ref="K71" r:id="rId69" xr:uid="{1DA360B3-3EEC-0B4A-92B2-F41887D4DA99}"/>
+    <hyperlink ref="K72" r:id="rId70" xr:uid="{53707DD5-6AE9-244D-BE8B-768805F672D6}"/>
+    <hyperlink ref="K73" r:id="rId71" xr:uid="{36EBDC68-249C-1C48-AAF4-2B47231ACC4B}"/>
+    <hyperlink ref="K74" r:id="rId72" xr:uid="{A1D0B6A6-8992-754F-A034-0A1E7D5B9BCB}"/>
+    <hyperlink ref="K75" r:id="rId73" xr:uid="{A089F750-0C9E-6945-9649-FC6752762842}"/>
+    <hyperlink ref="K76" r:id="rId74" xr:uid="{DB5E5AED-5451-EE4B-9408-E80763135A0D}"/>
+    <hyperlink ref="K77" r:id="rId75" xr:uid="{54790613-574F-C04B-943E-7BC43E9CE3FE}"/>
+    <hyperlink ref="K78" r:id="rId76" xr:uid="{04799654-C848-244D-A1F9-FAA86321A73F}"/>
+    <hyperlink ref="K79" r:id="rId77" xr:uid="{0EB41F51-36DD-AA40-AA97-D6366DF2ACBF}"/>
+    <hyperlink ref="K80" r:id="rId78" xr:uid="{7DFC2710-EE37-1F4C-A14D-E4C357A34AC5}"/>
+    <hyperlink ref="K81" r:id="rId79" xr:uid="{F62AC8D7-0E4C-8D4A-A393-61AF8AC0EB46}"/>
+    <hyperlink ref="K82" r:id="rId80" xr:uid="{EE4CEA07-2929-A846-98F2-C6C1968C5BD7}"/>
+    <hyperlink ref="K83" r:id="rId81" xr:uid="{0B614C9A-CC57-2C4A-9102-DE5C3F305979}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-1405-TVSeries.xlsx
+++ b/db/A7XLK-1405-TVSeries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77893EFA-796B-7543-9B94-FD664008DF8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78834634-124F-F94F-BEB4-89D6C9D1A97F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4500" yWindow="2600" windowWidth="29840" windowHeight="17320" xr2:uid="{BAC94C6D-C196-2D4F-A2F2-89F0A182D671}"/>
   </bookViews>
@@ -2351,7 +2351,7 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>49</v>
+        <v>401</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
@@ -2363,30 +2363,33 @@
         <v>291</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="F7" t="s">
-        <v>162</v>
+        <v>426</v>
       </c>
       <c r="G7" t="s">
-        <v>86</v>
+        <v>425</v>
       </c>
       <c r="H7" s="3">
-        <v>2815834</v>
+        <v>3164608</v>
+      </c>
+      <c r="I7" s="4">
+        <v>8.6</v>
       </c>
       <c r="J7" t="s">
-        <v>16</v>
+        <v>413</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>163</v>
+        <v>427</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>315</v>
+        <v>49</v>
       </c>
       <c r="B8" t="s">
-        <v>350</v>
+        <v>11</v>
       </c>
       <c r="C8">
         <v>2021</v>
@@ -2395,30 +2398,30 @@
         <v>291</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>351</v>
+        <v>161</v>
       </c>
       <c r="F8" t="s">
-        <v>352</v>
+        <v>162</v>
       </c>
       <c r="G8" t="s">
-        <v>298</v>
+        <v>86</v>
       </c>
       <c r="H8" s="3">
-        <v>2535509</v>
+        <v>2815834</v>
       </c>
       <c r="J8" t="s">
-        <v>334</v>
+        <v>16</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>353</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>57</v>
+        <v>315</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>350</v>
       </c>
       <c r="C9">
         <v>2021</v>
@@ -2427,27 +2430,27 @@
         <v>291</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>173</v>
+        <v>351</v>
       </c>
       <c r="F9" t="s">
-        <v>182</v>
+        <v>352</v>
       </c>
       <c r="G9" t="s">
-        <v>94</v>
+        <v>298</v>
       </c>
       <c r="H9" s="3">
-        <v>2454774</v>
+        <v>2535509</v>
       </c>
       <c r="J9" t="s">
-        <v>24</v>
+        <v>334</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>183</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
@@ -2462,24 +2465,24 @@
         <v>173</v>
       </c>
       <c r="F10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="G10" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H10" s="3">
-        <v>2378245</v>
+        <v>2454774</v>
       </c>
       <c r="J10" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
@@ -2491,27 +2494,27 @@
         <v>291</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="F11" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="G11" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H11" s="3">
-        <v>2132343</v>
+        <v>2378245</v>
       </c>
       <c r="J11" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
-        <v>53</v>
+        <v>405</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
@@ -2523,27 +2526,30 @@
         <v>291</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F12" t="s">
-        <v>171</v>
+        <v>439</v>
       </c>
       <c r="G12" t="s">
-        <v>90</v>
+        <v>438</v>
       </c>
       <c r="H12" s="3">
-        <v>2059245</v>
+        <v>2330511</v>
+      </c>
+      <c r="I12" s="4">
+        <v>7.6</v>
       </c>
       <c r="J12" t="s">
-        <v>20</v>
+        <v>417</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>172</v>
+        <v>440</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
         <v>11</v>
@@ -2555,27 +2561,27 @@
         <v>291</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="F13" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="G13" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H13" s="3">
-        <v>1960230</v>
+        <v>2132343</v>
       </c>
       <c r="J13" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1" t="s">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
@@ -2587,27 +2593,27 @@
         <v>291</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="F14" t="s">
-        <v>264</v>
+        <v>171</v>
       </c>
       <c r="G14" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="H14" s="3">
-        <v>1845243</v>
+        <v>2059245</v>
       </c>
       <c r="J14" t="s">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>265</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1" t="s">
-        <v>60</v>
+        <v>410</v>
       </c>
       <c r="B15" t="s">
         <v>11</v>
@@ -2619,27 +2625,30 @@
         <v>291</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>189</v>
+        <v>285</v>
       </c>
       <c r="F15" t="s">
-        <v>190</v>
+        <v>455</v>
       </c>
       <c r="G15" t="s">
-        <v>97</v>
+        <v>454</v>
       </c>
       <c r="H15" s="3">
-        <v>1796008</v>
+        <v>2043804</v>
+      </c>
+      <c r="I15" s="4">
+        <v>7.2</v>
       </c>
       <c r="J15" t="s">
-        <v>27</v>
+        <v>422</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>191</v>
+        <v>456</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="1" t="s">
-        <v>323</v>
+        <v>55</v>
       </c>
       <c r="B16" t="s">
         <v>11</v>
@@ -2651,27 +2660,27 @@
         <v>291</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F16" t="s">
-        <v>372</v>
+        <v>177</v>
       </c>
       <c r="G16" t="s">
-        <v>305</v>
+        <v>92</v>
       </c>
       <c r="H16" s="3">
-        <v>1771888</v>
+        <v>1960230</v>
       </c>
       <c r="J16" t="s">
-        <v>341</v>
+        <v>22</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>373</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="1" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B17" t="s">
         <v>11</v>
@@ -2683,27 +2692,27 @@
         <v>291</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>282</v>
+        <v>158</v>
       </c>
       <c r="F17" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="G17" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="H17" s="3">
-        <v>1758290</v>
+        <v>1845243</v>
       </c>
       <c r="J17" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="1" t="s">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="B18" t="s">
         <v>11</v>
@@ -2715,27 +2724,27 @@
         <v>291</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="F18" t="s">
-        <v>262</v>
+        <v>190</v>
       </c>
       <c r="G18" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="H18" s="3">
-        <v>1560320</v>
+        <v>1796008</v>
       </c>
       <c r="J18" t="s">
-        <v>147</v>
+        <v>27</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>263</v>
+        <v>191</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="1" t="s">
-        <v>58</v>
+        <v>323</v>
       </c>
       <c r="B19" t="s">
         <v>11</v>
@@ -2747,27 +2756,27 @@
         <v>291</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="F19" t="s">
-        <v>185</v>
+        <v>372</v>
       </c>
       <c r="G19" t="s">
-        <v>95</v>
+        <v>305</v>
       </c>
       <c r="H19" s="3">
-        <v>1212038</v>
+        <v>1771888</v>
       </c>
       <c r="J19" t="s">
-        <v>25</v>
+        <v>341</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>186</v>
+        <v>373</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="1" t="s">
-        <v>59</v>
+        <v>143</v>
       </c>
       <c r="B20" t="s">
         <v>11</v>
@@ -2779,30 +2788,27 @@
         <v>291</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>158</v>
+        <v>282</v>
       </c>
       <c r="F20" t="s">
-        <v>187</v>
+        <v>281</v>
       </c>
       <c r="G20" t="s">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="H20" s="3">
-        <v>1071359</v>
-      </c>
-      <c r="I20" s="4">
-        <v>7.1</v>
+        <v>1758290</v>
       </c>
       <c r="J20" t="s">
-        <v>26</v>
+        <v>155</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>188</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="1" t="s">
-        <v>50</v>
+        <v>135</v>
       </c>
       <c r="B21" t="s">
         <v>11</v>
@@ -2814,30 +2820,27 @@
         <v>291</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="F21" t="s">
-        <v>164</v>
+        <v>262</v>
       </c>
       <c r="G21" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="H21" s="3">
-        <v>1028428</v>
-      </c>
-      <c r="I21" s="4">
-        <v>7.1</v>
+        <v>1560320</v>
       </c>
       <c r="J21" t="s">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>165</v>
+        <v>263</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>409</v>
       </c>
       <c r="B22" t="s">
         <v>11</v>
@@ -2849,24 +2852,30 @@
         <v>291</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>161</v>
+        <v>452</v>
+      </c>
+      <c r="F22" t="s">
+        <v>451</v>
       </c>
       <c r="G22" t="s">
-        <v>89</v>
+        <v>450</v>
       </c>
       <c r="H22" s="3">
-        <v>976802</v>
+        <v>1278633</v>
+      </c>
+      <c r="I22" s="4">
+        <v>7.3</v>
       </c>
       <c r="J22" t="s">
-        <v>19</v>
+        <v>421</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>169</v>
+        <v>453</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="1" t="s">
-        <v>324</v>
+        <v>58</v>
       </c>
       <c r="B23" t="s">
         <v>11</v>
@@ -2878,27 +2887,27 @@
         <v>291</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="F23" t="s">
-        <v>375</v>
+        <v>185</v>
       </c>
       <c r="G23" t="s">
-        <v>306</v>
+        <v>95</v>
       </c>
       <c r="H23" s="3">
-        <v>954238</v>
+        <v>1212038</v>
       </c>
       <c r="J23" t="s">
-        <v>374</v>
+        <v>25</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>376</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="1" t="s">
-        <v>317</v>
+        <v>59</v>
       </c>
       <c r="B24" t="s">
         <v>11</v>
@@ -2910,27 +2919,30 @@
         <v>291</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>358</v>
+        <v>158</v>
       </c>
       <c r="F24" t="s">
-        <v>357</v>
+        <v>187</v>
       </c>
       <c r="G24" t="s">
-        <v>300</v>
+        <v>96</v>
       </c>
       <c r="H24" s="3">
-        <v>795715</v>
+        <v>1071359</v>
+      </c>
+      <c r="I24" s="4">
+        <v>7.1</v>
       </c>
       <c r="J24" t="s">
-        <v>336</v>
+        <v>26</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>359</v>
+        <v>188</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="1" t="s">
-        <v>329</v>
+        <v>50</v>
       </c>
       <c r="B25" t="s">
         <v>11</v>
@@ -2942,30 +2954,30 @@
         <v>291</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="F25" t="s">
-        <v>389</v>
+        <v>164</v>
       </c>
       <c r="G25" t="s">
-        <v>310</v>
+        <v>88</v>
       </c>
       <c r="H25" s="3">
-        <v>767044</v>
+        <v>1028428</v>
       </c>
       <c r="I25" s="4">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
       <c r="J25" t="s">
-        <v>345</v>
+        <v>17</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>390</v>
+        <v>165</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="1" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="B26" t="s">
         <v>11</v>
@@ -2977,30 +2989,27 @@
         <v>291</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="F26" t="s">
-        <v>212</v>
+        <v>161</v>
       </c>
       <c r="G26" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="H26" s="3">
-        <v>653514</v>
+        <v>976802</v>
       </c>
       <c r="J26" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>213</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="1" t="s">
-        <v>138</v>
+        <v>324</v>
       </c>
       <c r="B27" t="s">
-        <v>224</v>
+        <v>11</v>
       </c>
       <c r="C27">
         <v>2021</v>
@@ -3009,27 +3018,27 @@
         <v>291</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>268</v>
+        <v>173</v>
       </c>
       <c r="F27" t="s">
-        <v>269</v>
+        <v>375</v>
       </c>
       <c r="G27" t="s">
-        <v>126</v>
+        <v>306</v>
       </c>
       <c r="H27" s="3">
-        <v>459883</v>
+        <v>954238</v>
       </c>
       <c r="J27" t="s">
-        <v>150</v>
+        <v>374</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>270</v>
+        <v>376</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B28" t="s">
         <v>11</v>
@@ -3041,30 +3050,27 @@
         <v>291</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>195</v>
+        <v>358</v>
       </c>
       <c r="F28" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="G28" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H28" s="3">
-        <v>378104</v>
-      </c>
-      <c r="I28" s="4">
-        <v>7.8</v>
+        <v>795715</v>
       </c>
       <c r="J28" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="1" t="s">
-        <v>316</v>
+        <v>411</v>
       </c>
       <c r="B29" t="s">
         <v>11</v>
@@ -3076,27 +3082,30 @@
         <v>291</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>355</v>
+        <v>459</v>
       </c>
       <c r="F29" t="s">
-        <v>354</v>
+        <v>458</v>
       </c>
       <c r="G29" t="s">
-        <v>299</v>
+        <v>457</v>
       </c>
       <c r="H29" s="3">
-        <v>377267</v>
+        <v>785247</v>
+      </c>
+      <c r="I29" s="4">
+        <v>7</v>
       </c>
       <c r="J29" t="s">
-        <v>335</v>
+        <v>423</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>356</v>
+        <v>460</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="1" t="s">
-        <v>51</v>
+        <v>329</v>
       </c>
       <c r="B30" t="s">
         <v>11</v>
@@ -3108,27 +3117,30 @@
         <v>291</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F30" t="s">
-        <v>168</v>
+        <v>389</v>
       </c>
       <c r="G30" t="s">
-        <v>87</v>
+        <v>310</v>
       </c>
       <c r="H30" s="3">
-        <v>303763</v>
+        <v>767044</v>
+      </c>
+      <c r="I30" s="4">
+        <v>7.8</v>
       </c>
       <c r="J30" t="s">
-        <v>18</v>
+        <v>345</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>166</v>
+        <v>390</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="1" t="s">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="B31" t="s">
         <v>11</v>
@@ -3139,28 +3151,28 @@
       <c r="D31" t="s">
         <v>291</v>
       </c>
-      <c r="E31" s="1">
-        <v>-10</v>
+      <c r="E31" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="F31" t="s">
-        <v>13</v>
+        <v>212</v>
       </c>
       <c r="G31" t="s">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="H31" s="3">
-        <v>200612</v>
+        <v>653514</v>
       </c>
       <c r="J31" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>160</v>
+        <v>213</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="1" t="s">
-        <v>61</v>
+        <v>406</v>
       </c>
       <c r="B32" t="s">
         <v>11</v>
@@ -3172,27 +3184,30 @@
         <v>291</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="F32" t="s">
-        <v>193</v>
+        <v>442</v>
       </c>
       <c r="G32" t="s">
-        <v>98</v>
+        <v>441</v>
       </c>
       <c r="H32" s="3">
-        <v>132204</v>
+        <v>548641</v>
+      </c>
+      <c r="I32" s="4">
+        <v>7.6</v>
       </c>
       <c r="J32" t="s">
-        <v>288</v>
+        <v>418</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>194</v>
+        <v>443</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="1" t="s">
-        <v>67</v>
+        <v>403</v>
       </c>
       <c r="B33" t="s">
         <v>11</v>
@@ -3204,30 +3219,33 @@
         <v>291</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>195</v>
+        <v>433</v>
       </c>
       <c r="F33" t="s">
-        <v>210</v>
+        <v>432</v>
       </c>
       <c r="G33" t="s">
-        <v>104</v>
+        <v>430</v>
       </c>
       <c r="H33" s="3">
-        <v>121479</v>
+        <v>489413</v>
+      </c>
+      <c r="I33" s="4">
+        <v>8.1999999999999993</v>
       </c>
       <c r="J33" t="s">
-        <v>33</v>
+        <v>415</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>211</v>
+        <v>434</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="1" t="s">
-        <v>322</v>
+        <v>138</v>
       </c>
       <c r="B34" t="s">
-        <v>11</v>
+        <v>224</v>
       </c>
       <c r="C34">
         <v>2021</v>
@@ -3236,27 +3254,27 @@
         <v>291</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>158</v>
+        <v>268</v>
       </c>
       <c r="F34" t="s">
-        <v>370</v>
+        <v>269</v>
       </c>
       <c r="G34" t="s">
-        <v>304</v>
+        <v>126</v>
       </c>
       <c r="H34" s="3">
-        <v>98231</v>
+        <v>459883</v>
       </c>
       <c r="J34" t="s">
-        <v>369</v>
+        <v>150</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>371</v>
+        <v>270</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="1" t="s">
-        <v>137</v>
+        <v>318</v>
       </c>
       <c r="B35" t="s">
         <v>11</v>
@@ -3268,411 +3286,429 @@
         <v>291</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="F35" t="s">
-        <v>266</v>
+        <v>360</v>
       </c>
       <c r="G35" t="s">
-        <v>125</v>
+        <v>301</v>
       </c>
       <c r="H35" s="3">
-        <v>4524</v>
+        <v>378104</v>
+      </c>
+      <c r="I35" s="4">
+        <v>7.8</v>
       </c>
       <c r="J35" t="s">
-        <v>149</v>
+        <v>337</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>267</v>
+        <v>361</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="1" t="s">
-        <v>62</v>
+        <v>316</v>
       </c>
       <c r="B36" t="s">
         <v>11</v>
       </c>
       <c r="C36">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D36" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>195</v>
+        <v>355</v>
       </c>
       <c r="F36" t="s">
-        <v>196</v>
+        <v>354</v>
       </c>
       <c r="G36" t="s">
-        <v>99</v>
+        <v>299</v>
       </c>
       <c r="H36" s="3">
-        <v>7733587</v>
+        <v>377267</v>
       </c>
       <c r="J36" t="s">
-        <v>28</v>
+        <v>335</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>197</v>
+        <v>356</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="1" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="B37" t="s">
         <v>11</v>
       </c>
       <c r="C37">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="D37" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>253</v>
+        <v>167</v>
       </c>
       <c r="F37" t="s">
-        <v>252</v>
+        <v>168</v>
       </c>
       <c r="G37" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="H37" s="3">
-        <v>5275870</v>
+        <v>303763</v>
       </c>
       <c r="J37" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>254</v>
+        <v>166</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="1" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="B38" t="s">
         <v>11</v>
       </c>
       <c r="C38">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="D38" t="s">
-        <v>292</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>244</v>
+        <v>291</v>
+      </c>
+      <c r="E38" s="1">
+        <v>-10</v>
       </c>
       <c r="F38" t="s">
-        <v>243</v>
+        <v>13</v>
       </c>
       <c r="G38" t="s">
-        <v>117</v>
+        <v>10</v>
       </c>
       <c r="H38" s="3">
-        <v>5265895</v>
+        <v>200612</v>
       </c>
       <c r="J38" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>245</v>
+        <v>160</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="1" t="s">
-        <v>140</v>
+        <v>408</v>
       </c>
       <c r="B39" t="s">
         <v>11</v>
       </c>
       <c r="C39">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="D39" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>274</v>
+        <v>158</v>
       </c>
       <c r="F39" t="s">
-        <v>273</v>
+        <v>448</v>
       </c>
       <c r="G39" t="s">
-        <v>128</v>
+        <v>447</v>
       </c>
       <c r="H39" s="3">
-        <v>4674495</v>
+        <v>134785</v>
+      </c>
+      <c r="I39" s="4">
+        <v>7.5</v>
       </c>
       <c r="J39" t="s">
-        <v>152</v>
+        <v>420</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>275</v>
+        <v>449</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="1" t="s">
-        <v>327</v>
+        <v>61</v>
       </c>
       <c r="B40" t="s">
         <v>11</v>
       </c>
       <c r="C40">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D40" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="F40" t="s">
-        <v>383</v>
+        <v>193</v>
       </c>
       <c r="G40" t="s">
-        <v>308</v>
+        <v>98</v>
       </c>
       <c r="H40" s="3">
-        <v>4655514</v>
+        <v>132204</v>
       </c>
       <c r="J40" t="s">
-        <v>344</v>
+        <v>288</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>384</v>
+        <v>194</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B41" t="s">
         <v>11</v>
       </c>
       <c r="C41">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="D41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="F41" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="G41" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H41" s="3">
-        <v>4141267</v>
+        <v>121479</v>
       </c>
       <c r="J41" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="1" t="s">
-        <v>66</v>
+        <v>322</v>
       </c>
       <c r="B42" t="s">
         <v>11</v>
       </c>
       <c r="C42">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="D42" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>207</v>
+        <v>158</v>
       </c>
       <c r="F42" t="s">
-        <v>208</v>
+        <v>370</v>
       </c>
       <c r="G42" t="s">
-        <v>103</v>
+        <v>304</v>
       </c>
       <c r="H42" s="3">
-        <v>2991300</v>
+        <v>98231</v>
       </c>
       <c r="J42" t="s">
-        <v>32</v>
+        <v>369</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>209</v>
+        <v>371</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="1" t="s">
-        <v>72</v>
+        <v>404</v>
       </c>
       <c r="B43" t="s">
-        <v>224</v>
+        <v>11</v>
       </c>
       <c r="C43">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="D43" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>222</v>
+        <v>161</v>
       </c>
       <c r="F43" t="s">
-        <v>223</v>
+        <v>436</v>
       </c>
       <c r="G43" t="s">
-        <v>109</v>
+        <v>435</v>
       </c>
       <c r="H43" s="3">
-        <v>2563754</v>
+        <v>95136</v>
+      </c>
+      <c r="I43" s="4">
+        <v>7.9</v>
       </c>
       <c r="J43" t="s">
-        <v>289</v>
+        <v>416</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>225</v>
+        <v>437</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="1" t="s">
-        <v>328</v>
+        <v>412</v>
       </c>
       <c r="B44" t="s">
         <v>11</v>
       </c>
       <c r="C44">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D44" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>387</v>
+        <v>433</v>
       </c>
       <c r="F44" t="s">
-        <v>386</v>
+        <v>462</v>
       </c>
       <c r="G44" t="s">
-        <v>309</v>
+        <v>461</v>
       </c>
       <c r="H44" s="3">
-        <v>2400663</v>
+        <v>89338</v>
+      </c>
+      <c r="I44" s="4">
+        <v>7</v>
       </c>
       <c r="J44" t="s">
-        <v>385</v>
+        <v>424</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>388</v>
+        <v>463</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="1" t="s">
-        <v>325</v>
+        <v>402</v>
       </c>
       <c r="B45" t="s">
         <v>11</v>
       </c>
       <c r="C45">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="D45" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>379</v>
+        <v>161</v>
       </c>
       <c r="F45" t="s">
-        <v>378</v>
+        <v>428</v>
       </c>
       <c r="G45" t="s">
-        <v>377</v>
+        <v>431</v>
       </c>
       <c r="H45" s="3">
-        <v>2340742</v>
+        <v>52300</v>
+      </c>
+      <c r="I45" s="4">
+        <v>8.5</v>
       </c>
       <c r="J45" t="s">
-        <v>342</v>
+        <v>414</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>380</v>
+        <v>429</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="1" t="s">
-        <v>133</v>
+        <v>407</v>
       </c>
       <c r="B46" t="s">
         <v>11</v>
       </c>
       <c r="C46">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="D46" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>258</v>
+        <v>433</v>
       </c>
       <c r="F46" t="s">
-        <v>257</v>
+        <v>445</v>
       </c>
       <c r="G46" t="s">
-        <v>121</v>
+        <v>444</v>
       </c>
       <c r="H46" s="3">
-        <v>1265188</v>
+        <v>52113</v>
+      </c>
+      <c r="I46" s="4">
+        <v>7.5</v>
       </c>
       <c r="J46" t="s">
-        <v>145</v>
-      </c>
-      <c r="K46" t="s">
-        <v>259</v>
+        <v>419</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="1" t="s">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="B47" t="s">
         <v>11</v>
       </c>
       <c r="C47">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="D47" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>230</v>
+        <v>179</v>
       </c>
       <c r="F47" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="G47" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H47" s="3">
-        <v>1259285</v>
+        <v>4524</v>
       </c>
       <c r="J47" t="s">
-        <v>48</v>
+        <v>149</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="1" t="s">
-        <v>144</v>
+        <v>62</v>
       </c>
       <c r="B48" t="s">
         <v>11</v>
@@ -3684,123 +3720,123 @@
         <v>292</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>285</v>
+        <v>195</v>
       </c>
       <c r="F48" t="s">
-        <v>284</v>
+        <v>196</v>
       </c>
       <c r="G48" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="H48" s="3">
-        <v>1218509</v>
+        <v>7733587</v>
       </c>
       <c r="J48" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>286</v>
+        <v>197</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B49" t="s">
         <v>11</v>
       </c>
       <c r="C49">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="D49" t="s">
         <v>292</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>204</v>
+        <v>253</v>
       </c>
       <c r="F49" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="G49" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H49" s="3">
-        <v>947291</v>
+        <v>5275870</v>
       </c>
       <c r="J49" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>227</v>
+        <v>254</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B50" t="s">
         <v>11</v>
       </c>
       <c r="C50">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="D50" t="s">
         <v>292</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="F50" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="G50" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H50" s="3">
-        <v>802315</v>
+        <v>5265895</v>
       </c>
       <c r="J50" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="1" t="s">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="B51" t="s">
         <v>11</v>
       </c>
       <c r="C51">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D51" t="s">
         <v>292</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>217</v>
+        <v>274</v>
       </c>
       <c r="F51" t="s">
-        <v>218</v>
+        <v>273</v>
       </c>
       <c r="G51" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="H51" s="3">
-        <v>617188</v>
+        <v>4674495</v>
       </c>
       <c r="J51" t="s">
-        <v>36</v>
+        <v>152</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>219</v>
+        <v>275</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="1" t="s">
-        <v>71</v>
+        <v>327</v>
       </c>
       <c r="B52" t="s">
         <v>11</v>
@@ -3812,65 +3848,65 @@
         <v>292</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>189</v>
+        <v>158</v>
       </c>
       <c r="F52" t="s">
-        <v>220</v>
+        <v>383</v>
       </c>
       <c r="G52" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="H52" s="3">
-        <v>613506</v>
+        <v>4655514</v>
       </c>
       <c r="J52" t="s">
-        <v>37</v>
+        <v>344</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>221</v>
+        <v>384</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="1" t="s">
-        <v>134</v>
+        <v>69</v>
       </c>
       <c r="B53" t="s">
         <v>11</v>
       </c>
       <c r="C53">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D53" t="s">
         <v>292</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>247</v>
+        <v>214</v>
       </c>
       <c r="F53" t="s">
-        <v>260</v>
+        <v>215</v>
       </c>
       <c r="G53" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="H53" s="3">
-        <v>587879</v>
+        <v>4141267</v>
       </c>
       <c r="J53" t="s">
-        <v>146</v>
+        <v>35</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>261</v>
+        <v>216</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="1" t="s">
-        <v>293</v>
+        <v>66</v>
       </c>
       <c r="B54" t="s">
         <v>11</v>
       </c>
       <c r="C54">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="D54" t="s">
         <v>292</v>
@@ -3879,120 +3915,120 @@
         <v>207</v>
       </c>
       <c r="F54" t="s">
-        <v>295</v>
+        <v>208</v>
       </c>
       <c r="G54" t="s">
-        <v>294</v>
+        <v>103</v>
       </c>
       <c r="H54" s="3">
-        <v>562667</v>
+        <v>2991300</v>
       </c>
       <c r="J54" t="s">
-        <v>297</v>
+        <v>32</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>296</v>
+        <v>209</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="1" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B55" t="s">
-        <v>11</v>
+        <v>224</v>
       </c>
       <c r="C55">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D55" t="s">
         <v>292</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="F55" t="s">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="G55" t="s">
-        <v>249</v>
+        <v>109</v>
       </c>
       <c r="H55" s="3">
-        <v>552739</v>
+        <v>2563754</v>
       </c>
       <c r="J55" t="s">
-        <v>46</v>
+        <v>289</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="1" t="s">
-        <v>81</v>
+        <v>328</v>
       </c>
       <c r="B56" t="s">
         <v>11</v>
       </c>
       <c r="C56">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D56" t="s">
         <v>292</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>247</v>
+        <v>387</v>
       </c>
       <c r="F56" t="s">
-        <v>246</v>
+        <v>386</v>
       </c>
       <c r="G56" t="s">
-        <v>118</v>
+        <v>309</v>
       </c>
       <c r="H56" s="3">
-        <v>517958</v>
+        <v>2400663</v>
       </c>
       <c r="J56" t="s">
-        <v>290</v>
+        <v>385</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>248</v>
+        <v>388</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="1" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B57" t="s">
         <v>11</v>
       </c>
       <c r="C57">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D57" t="s">
         <v>292</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>198</v>
+        <v>379</v>
       </c>
       <c r="F57" t="s">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="G57" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="H57" s="3">
-        <v>483734</v>
+        <v>2340742</v>
       </c>
       <c r="J57" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>364</v>
+        <v>380</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" s="1" t="s">
-        <v>330</v>
+        <v>133</v>
       </c>
       <c r="B58" t="s">
         <v>11</v>
@@ -4004,97 +4040,97 @@
         <v>292</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>207</v>
+        <v>258</v>
       </c>
       <c r="F58" t="s">
-        <v>391</v>
+        <v>257</v>
       </c>
       <c r="G58" t="s">
-        <v>311</v>
+        <v>121</v>
       </c>
       <c r="H58" s="3">
-        <v>470562</v>
+        <v>1265188</v>
       </c>
       <c r="J58" t="s">
-        <v>346</v>
-      </c>
-      <c r="K58" s="2" t="s">
-        <v>392</v>
+        <v>145</v>
+      </c>
+      <c r="K58" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" s="1" t="s">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="B59" t="s">
         <v>11</v>
       </c>
       <c r="C59">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D59" t="s">
         <v>292</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>277</v>
+        <v>230</v>
       </c>
       <c r="F59" t="s">
-        <v>279</v>
+        <v>255</v>
       </c>
       <c r="G59" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="H59" s="3">
-        <v>349359</v>
+        <v>1259285</v>
       </c>
       <c r="J59" t="s">
-        <v>154</v>
+        <v>48</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>280</v>
+        <v>256</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" s="1" t="s">
-        <v>64</v>
+        <v>144</v>
       </c>
       <c r="B60" t="s">
         <v>11</v>
       </c>
       <c r="C60">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="D60" t="s">
         <v>292</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>202</v>
+        <v>285</v>
       </c>
       <c r="F60" t="s">
-        <v>201</v>
+        <v>284</v>
       </c>
       <c r="G60" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="H60" s="3">
-        <v>290313</v>
+        <v>1218509</v>
       </c>
       <c r="J60" t="s">
-        <v>30</v>
+        <v>156</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>203</v>
+        <v>286</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" s="1" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B61" t="s">
         <v>11</v>
       </c>
       <c r="C61">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D61" t="s">
         <v>292</v>
@@ -4103,222 +4139,222 @@
         <v>204</v>
       </c>
       <c r="F61" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="G61" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="H61" s="3">
-        <v>243599</v>
+        <v>947291</v>
       </c>
       <c r="J61" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" s="1" t="s">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="B62" t="s">
         <v>11</v>
       </c>
       <c r="C62">
-        <v>2020</v>
+        <v>2011</v>
       </c>
       <c r="D62" t="s">
         <v>292</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
       <c r="F62" t="s">
-        <v>271</v>
+        <v>238</v>
       </c>
       <c r="G62" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="H62" s="3">
-        <v>189629</v>
+        <v>802315</v>
       </c>
       <c r="J62" t="s">
-        <v>151</v>
+        <v>43</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>272</v>
+        <v>240</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="1" t="s">
-        <v>331</v>
+        <v>70</v>
       </c>
       <c r="B63" t="s">
         <v>11</v>
       </c>
       <c r="C63">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D63" t="s">
         <v>292</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>247</v>
+        <v>217</v>
       </c>
       <c r="F63" t="s">
-        <v>393</v>
+        <v>218</v>
       </c>
       <c r="G63" t="s">
-        <v>312</v>
+        <v>107</v>
       </c>
       <c r="H63" s="3">
-        <v>154914</v>
+        <v>617188</v>
       </c>
       <c r="J63" t="s">
-        <v>347</v>
+        <v>36</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>394</v>
+        <v>219</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" s="1" t="s">
-        <v>326</v>
+        <v>71</v>
       </c>
       <c r="B64" t="s">
         <v>11</v>
       </c>
       <c r="C64">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="D64" t="s">
         <v>292</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="F64" t="s">
-        <v>381</v>
+        <v>220</v>
       </c>
       <c r="G64" t="s">
-        <v>307</v>
+        <v>108</v>
       </c>
       <c r="H64" s="3">
-        <v>147091</v>
+        <v>613506</v>
       </c>
       <c r="J64" t="s">
-        <v>343</v>
+        <v>37</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>382</v>
+        <v>221</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="A65" s="1" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="B65" t="s">
         <v>11</v>
       </c>
       <c r="C65">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="D65" t="s">
         <v>292</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>198</v>
+        <v>247</v>
       </c>
       <c r="F65" t="s">
-        <v>199</v>
+        <v>260</v>
       </c>
       <c r="G65" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="H65" s="3">
-        <v>136424</v>
+        <v>587879</v>
       </c>
       <c r="J65" t="s">
-        <v>29</v>
+        <v>146</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>200</v>
+        <v>261</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="1" t="s">
-        <v>333</v>
+        <v>293</v>
       </c>
       <c r="B66" t="s">
         <v>11</v>
       </c>
       <c r="C66">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D66" t="s">
         <v>292</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>158</v>
+        <v>207</v>
       </c>
       <c r="F66" t="s">
-        <v>397</v>
+        <v>295</v>
       </c>
       <c r="G66" t="s">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="H66" s="3">
-        <v>136234</v>
+        <v>562667</v>
       </c>
       <c r="J66" t="s">
-        <v>349</v>
+        <v>297</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>398</v>
+        <v>296</v>
       </c>
     </row>
     <row r="67" spans="1:11">
       <c r="A67" s="1" t="s">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="B67" t="s">
         <v>11</v>
       </c>
       <c r="C67">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="D67" t="s">
         <v>292</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>277</v>
+        <v>195</v>
       </c>
       <c r="F67" t="s">
-        <v>276</v>
+        <v>250</v>
       </c>
       <c r="G67" t="s">
-        <v>129</v>
+        <v>249</v>
       </c>
       <c r="H67" s="3">
-        <v>99365</v>
+        <v>552739</v>
       </c>
       <c r="J67" t="s">
-        <v>153</v>
+        <v>46</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="1" t="s">
-        <v>320</v>
+        <v>81</v>
       </c>
       <c r="B68" t="s">
         <v>11</v>
       </c>
       <c r="C68">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="D68" t="s">
         <v>292</v>
@@ -4327,24 +4363,24 @@
         <v>247</v>
       </c>
       <c r="F68" t="s">
-        <v>367</v>
+        <v>246</v>
       </c>
       <c r="G68" t="s">
-        <v>302</v>
+        <v>118</v>
       </c>
       <c r="H68" s="3">
-        <v>67758</v>
+        <v>517958</v>
       </c>
       <c r="J68" t="s">
-        <v>339</v>
+        <v>290</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>365</v>
+        <v>248</v>
       </c>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" s="1" t="s">
-        <v>77</v>
+        <v>319</v>
       </c>
       <c r="B69" t="s">
         <v>11</v>
@@ -4356,596 +4392,560 @@
         <v>292</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>236</v>
+        <v>198</v>
       </c>
       <c r="F69" t="s">
-        <v>235</v>
+        <v>363</v>
       </c>
       <c r="G69" t="s">
-        <v>114</v>
+        <v>362</v>
       </c>
       <c r="H69" s="3">
-        <v>25178</v>
+        <v>483734</v>
       </c>
       <c r="J69" t="s">
-        <v>42</v>
+        <v>338</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>237</v>
+        <v>364</v>
       </c>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" s="1" t="s">
-        <v>74</v>
+        <v>330</v>
       </c>
       <c r="B70" t="s">
         <v>11</v>
       </c>
       <c r="C70">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="D70" t="s">
         <v>292</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>173</v>
+        <v>207</v>
       </c>
       <c r="F70" t="s">
-        <v>228</v>
+        <v>391</v>
       </c>
       <c r="G70" t="s">
-        <v>111</v>
+        <v>311</v>
       </c>
       <c r="H70" s="3">
-        <v>19483</v>
+        <v>470562</v>
       </c>
       <c r="J70" t="s">
-        <v>39</v>
+        <v>346</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>229</v>
+        <v>392</v>
       </c>
     </row>
     <row r="71" spans="1:11">
       <c r="A71" s="1" t="s">
-        <v>332</v>
+        <v>142</v>
       </c>
       <c r="B71" t="s">
         <v>11</v>
       </c>
       <c r="C71">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="D71" t="s">
         <v>292</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>396</v>
+        <v>277</v>
       </c>
       <c r="F71" t="s">
-        <v>395</v>
+        <v>279</v>
       </c>
       <c r="G71" t="s">
-        <v>313</v>
+        <v>130</v>
       </c>
       <c r="H71" s="3">
-        <v>15835</v>
+        <v>349359</v>
       </c>
       <c r="J71" t="s">
-        <v>348</v>
+        <v>154</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>399</v>
+        <v>280</v>
       </c>
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="1" t="s">
-        <v>401</v>
+        <v>64</v>
       </c>
       <c r="B72" t="s">
         <v>11</v>
       </c>
       <c r="C72">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="D72" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>170</v>
+        <v>202</v>
       </c>
       <c r="F72" t="s">
-        <v>426</v>
+        <v>201</v>
       </c>
       <c r="G72" t="s">
-        <v>425</v>
+        <v>101</v>
       </c>
       <c r="H72" s="3">
-        <v>3164608</v>
-      </c>
-      <c r="I72" s="4">
-        <v>8.6</v>
+        <v>290313</v>
       </c>
       <c r="J72" t="s">
-        <v>413</v>
+        <v>30</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>427</v>
+        <v>203</v>
       </c>
     </row>
     <row r="73" spans="1:11">
       <c r="A73" s="1" t="s">
-        <v>402</v>
+        <v>65</v>
       </c>
       <c r="B73" t="s">
         <v>11</v>
       </c>
       <c r="C73">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="D73" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>161</v>
+        <v>204</v>
       </c>
       <c r="F73" t="s">
-        <v>428</v>
+        <v>205</v>
       </c>
       <c r="G73" t="s">
-        <v>431</v>
+        <v>102</v>
       </c>
       <c r="H73" s="3">
-        <v>52300</v>
-      </c>
-      <c r="I73" s="4">
-        <v>8.5</v>
+        <v>243599</v>
       </c>
       <c r="J73" t="s">
-        <v>414</v>
+        <v>31</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>429</v>
+        <v>206</v>
       </c>
     </row>
     <row r="74" spans="1:11">
       <c r="A74" s="1" t="s">
-        <v>403</v>
+        <v>139</v>
       </c>
       <c r="B74" t="s">
         <v>11</v>
       </c>
       <c r="C74">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="D74" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>433</v>
+        <v>198</v>
       </c>
       <c r="F74" t="s">
-        <v>432</v>
+        <v>271</v>
       </c>
       <c r="G74" t="s">
-        <v>430</v>
+        <v>127</v>
       </c>
       <c r="H74" s="3">
-        <v>489413</v>
-      </c>
-      <c r="I74" s="4">
-        <v>8.1999999999999993</v>
+        <v>189629</v>
       </c>
       <c r="J74" t="s">
-        <v>415</v>
+        <v>151</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>434</v>
+        <v>272</v>
       </c>
     </row>
     <row r="75" spans="1:11">
       <c r="A75" s="1" t="s">
-        <v>404</v>
+        <v>331</v>
       </c>
       <c r="B75" t="s">
         <v>11</v>
       </c>
       <c r="C75">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="D75" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>161</v>
+        <v>247</v>
       </c>
       <c r="F75" t="s">
-        <v>436</v>
+        <v>393</v>
       </c>
       <c r="G75" t="s">
-        <v>435</v>
+        <v>312</v>
       </c>
       <c r="H75" s="3">
-        <v>95136</v>
-      </c>
-      <c r="I75" s="4">
-        <v>7.9</v>
+        <v>154914</v>
       </c>
       <c r="J75" t="s">
-        <v>416</v>
+        <v>347</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>437</v>
+        <v>394</v>
       </c>
     </row>
     <row r="76" spans="1:11">
       <c r="A76" s="1" t="s">
-        <v>405</v>
+        <v>326</v>
       </c>
       <c r="B76" t="s">
         <v>11</v>
       </c>
       <c r="C76">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="D76" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>173</v>
       </c>
       <c r="F76" t="s">
-        <v>439</v>
+        <v>381</v>
       </c>
       <c r="G76" t="s">
-        <v>438</v>
+        <v>307</v>
       </c>
       <c r="H76" s="3">
-        <v>2330511</v>
-      </c>
-      <c r="I76" s="4">
-        <v>7.6</v>
+        <v>147091</v>
       </c>
       <c r="J76" t="s">
-        <v>417</v>
+        <v>343</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>440</v>
+        <v>382</v>
       </c>
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="1" t="s">
-        <v>406</v>
+        <v>63</v>
       </c>
       <c r="B77" t="s">
         <v>11</v>
       </c>
       <c r="C77">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="D77" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="F77" t="s">
-        <v>442</v>
+        <v>199</v>
       </c>
       <c r="G77" t="s">
-        <v>441</v>
+        <v>100</v>
       </c>
       <c r="H77" s="3">
-        <v>548641</v>
-      </c>
-      <c r="I77" s="4">
-        <v>7.6</v>
+        <v>136424</v>
       </c>
       <c r="J77" t="s">
-        <v>418</v>
+        <v>29</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>443</v>
+        <v>200</v>
       </c>
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="1" t="s">
-        <v>407</v>
+        <v>333</v>
       </c>
       <c r="B78" t="s">
         <v>11</v>
       </c>
       <c r="C78">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="D78" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>433</v>
+        <v>158</v>
       </c>
       <c r="F78" t="s">
-        <v>445</v>
+        <v>397</v>
       </c>
       <c r="G78" t="s">
-        <v>444</v>
+        <v>314</v>
       </c>
       <c r="H78" s="3">
-        <v>52113</v>
-      </c>
-      <c r="I78" s="4">
-        <v>7.5</v>
+        <v>136234</v>
       </c>
       <c r="J78" t="s">
-        <v>419</v>
+        <v>349</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>446</v>
+        <v>398</v>
       </c>
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="1" t="s">
-        <v>408</v>
+        <v>141</v>
       </c>
       <c r="B79" t="s">
         <v>11</v>
       </c>
       <c r="C79">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="D79" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>158</v>
+        <v>277</v>
       </c>
       <c r="F79" t="s">
-        <v>448</v>
+        <v>276</v>
       </c>
       <c r="G79" t="s">
-        <v>447</v>
+        <v>129</v>
       </c>
       <c r="H79" s="3">
-        <v>134785</v>
-      </c>
-      <c r="I79" s="4">
-        <v>7.5</v>
+        <v>99365</v>
       </c>
       <c r="J79" t="s">
-        <v>420</v>
+        <v>153</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>449</v>
+        <v>278</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="1" t="s">
-        <v>409</v>
+        <v>320</v>
       </c>
       <c r="B80" t="s">
         <v>11</v>
       </c>
       <c r="C80">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="D80" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>452</v>
+        <v>247</v>
       </c>
       <c r="F80" t="s">
-        <v>451</v>
+        <v>367</v>
       </c>
       <c r="G80" t="s">
-        <v>450</v>
+        <v>302</v>
       </c>
       <c r="H80" s="3">
-        <v>1278633</v>
-      </c>
-      <c r="I80" s="4">
-        <v>7.3</v>
+        <v>67758</v>
       </c>
       <c r="J80" t="s">
-        <v>421</v>
+        <v>339</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>453</v>
+        <v>365</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="A81" s="1" t="s">
-        <v>410</v>
+        <v>77</v>
       </c>
       <c r="B81" t="s">
         <v>11</v>
       </c>
       <c r="C81">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="D81" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>285</v>
+        <v>236</v>
       </c>
       <c r="F81" t="s">
-        <v>455</v>
+        <v>235</v>
       </c>
       <c r="G81" t="s">
-        <v>454</v>
+        <v>114</v>
       </c>
       <c r="H81" s="3">
-        <v>2043804</v>
-      </c>
-      <c r="I81" s="4">
-        <v>7.2</v>
+        <v>25178</v>
       </c>
       <c r="J81" t="s">
-        <v>422</v>
+        <v>42</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>456</v>
+        <v>237</v>
       </c>
     </row>
     <row r="82" spans="1:11">
       <c r="A82" s="1" t="s">
-        <v>411</v>
+        <v>74</v>
       </c>
       <c r="B82" t="s">
         <v>11</v>
       </c>
       <c r="C82">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="D82" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>459</v>
+        <v>173</v>
       </c>
       <c r="F82" t="s">
-        <v>458</v>
+        <v>228</v>
       </c>
       <c r="G82" t="s">
-        <v>457</v>
+        <v>111</v>
       </c>
       <c r="H82" s="3">
-        <v>785247</v>
-      </c>
-      <c r="I82" s="4">
-        <v>7</v>
+        <v>19483</v>
       </c>
       <c r="J82" t="s">
-        <v>423</v>
+        <v>39</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>460</v>
+        <v>229</v>
       </c>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="1" t="s">
-        <v>412</v>
+        <v>332</v>
       </c>
       <c r="B83" t="s">
         <v>11</v>
       </c>
       <c r="C83">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="D83" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>433</v>
+        <v>396</v>
       </c>
       <c r="F83" t="s">
-        <v>462</v>
+        <v>395</v>
       </c>
       <c r="G83" t="s">
-        <v>461</v>
+        <v>313</v>
       </c>
       <c r="H83" s="3">
-        <v>89338</v>
-      </c>
-      <c r="I83" s="4">
-        <v>7</v>
+        <v>15835</v>
       </c>
       <c r="J83" t="s">
-        <v>424</v>
+        <v>348</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>463</v>
+        <v>399</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K71">
-    <sortCondition ref="D2:D71"/>
-    <sortCondition descending="1" ref="H2:H71"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K83">
+    <sortCondition ref="D2:D83"/>
+    <sortCondition descending="1" ref="H2:H83"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="K31" r:id="rId1" xr:uid="{725A3016-CC80-5F4A-B091-4E71BCFAD36B}"/>
-    <hyperlink ref="K11" r:id="rId2" xr:uid="{38F493C0-3185-604E-A3BD-AAB0EC5B83DF}"/>
-    <hyperlink ref="K7" r:id="rId3" xr:uid="{2E642780-E9D7-BF4B-9D23-FEBE51DDD0C9}"/>
-    <hyperlink ref="K21" r:id="rId4" xr:uid="{5CF6DEF3-9028-3D4C-846C-DA2618807577}"/>
-    <hyperlink ref="K30" r:id="rId5" xr:uid="{A298B622-5340-5148-820B-D468159EA5BD}"/>
-    <hyperlink ref="K22" r:id="rId6" xr:uid="{EF9BC619-52CD-2D48-BE99-80BD81A8CD54}"/>
-    <hyperlink ref="K12" r:id="rId7" xr:uid="{0002A242-754F-5A40-86A8-5F7DBBEBB9D1}"/>
-    <hyperlink ref="K10" r:id="rId8" xr:uid="{085C9D3E-4AFA-FF48-AA1A-64ECF275D4C0}"/>
-    <hyperlink ref="K13" r:id="rId9" xr:uid="{118F4CA9-C4A7-F74E-8AFF-041FB2741717}"/>
+    <hyperlink ref="K38" r:id="rId1" xr:uid="{725A3016-CC80-5F4A-B091-4E71BCFAD36B}"/>
+    <hyperlink ref="K13" r:id="rId2" xr:uid="{38F493C0-3185-604E-A3BD-AAB0EC5B83DF}"/>
+    <hyperlink ref="K8" r:id="rId3" xr:uid="{2E642780-E9D7-BF4B-9D23-FEBE51DDD0C9}"/>
+    <hyperlink ref="K25" r:id="rId4" xr:uid="{5CF6DEF3-9028-3D4C-846C-DA2618807577}"/>
+    <hyperlink ref="K37" r:id="rId5" xr:uid="{A298B622-5340-5148-820B-D468159EA5BD}"/>
+    <hyperlink ref="K26" r:id="rId6" xr:uid="{EF9BC619-52CD-2D48-BE99-80BD81A8CD54}"/>
+    <hyperlink ref="K14" r:id="rId7" xr:uid="{0002A242-754F-5A40-86A8-5F7DBBEBB9D1}"/>
+    <hyperlink ref="K11" r:id="rId8" xr:uid="{085C9D3E-4AFA-FF48-AA1A-64ECF275D4C0}"/>
+    <hyperlink ref="K16" r:id="rId9" xr:uid="{118F4CA9-C4A7-F74E-8AFF-041FB2741717}"/>
     <hyperlink ref="K3" r:id="rId10" xr:uid="{75687EB7-0A29-5C47-921B-954A17F06565}"/>
-    <hyperlink ref="K9" r:id="rId11" xr:uid="{81B8E0D0-29DD-E74A-8CE3-1464ECDB131A}"/>
-    <hyperlink ref="K19" r:id="rId12" xr:uid="{5D4D2728-3F60-EE43-86DF-EE58ADBF8432}"/>
-    <hyperlink ref="K20" r:id="rId13" xr:uid="{31C21087-E027-4542-80B2-C095CF193FA7}"/>
-    <hyperlink ref="K15" r:id="rId14" xr:uid="{36CFF13A-82D4-9642-B07B-0C3E49B5D215}"/>
-    <hyperlink ref="K32" r:id="rId15" xr:uid="{DDDE99D5-3422-6549-8393-D5FC330D45B8}"/>
-    <hyperlink ref="K36" r:id="rId16" xr:uid="{9621A5D4-6BD1-984D-9C8C-2A89CFA54CFF}"/>
-    <hyperlink ref="K65" r:id="rId17" xr:uid="{CC87EE91-DF39-EA48-9614-33030270159C}"/>
-    <hyperlink ref="K60" r:id="rId18" xr:uid="{C4E1F448-AF1B-BC43-983F-FB439266392E}"/>
-    <hyperlink ref="K61" r:id="rId19" xr:uid="{17A665F7-B807-4640-B444-16CFE27D5FDF}"/>
-    <hyperlink ref="K42" r:id="rId20" xr:uid="{244C8E1D-D3A7-9549-9D73-8F4D984A6ACD}"/>
-    <hyperlink ref="K33" r:id="rId21" xr:uid="{135AB67A-502A-8A4D-B049-40F78987A6E4}"/>
-    <hyperlink ref="K26" r:id="rId22" xr:uid="{2EBEE3F8-DF57-0E4A-9FB8-2C6B08B9453B}"/>
-    <hyperlink ref="K41" r:id="rId23" xr:uid="{50C93161-BA50-264D-9EB0-FD96B5179BD3}"/>
-    <hyperlink ref="K51" r:id="rId24" xr:uid="{EB1586AB-126F-2B4B-AB36-6A028744AF76}"/>
-    <hyperlink ref="K52" r:id="rId25" xr:uid="{7C55426F-9022-8044-ACAA-5AEC9137C037}"/>
-    <hyperlink ref="K43" r:id="rId26" xr:uid="{AD424BE3-B862-2442-B3B2-5028AF918C6F}"/>
-    <hyperlink ref="K49" r:id="rId27" xr:uid="{2183D387-1FD2-324D-A080-BF2A14B2C266}"/>
-    <hyperlink ref="K70" r:id="rId28" xr:uid="{FDBD3899-8300-BE4F-B928-93EB7382FF06}"/>
+    <hyperlink ref="K10" r:id="rId11" xr:uid="{81B8E0D0-29DD-E74A-8CE3-1464ECDB131A}"/>
+    <hyperlink ref="K23" r:id="rId12" xr:uid="{5D4D2728-3F60-EE43-86DF-EE58ADBF8432}"/>
+    <hyperlink ref="K24" r:id="rId13" xr:uid="{31C21087-E027-4542-80B2-C095CF193FA7}"/>
+    <hyperlink ref="K18" r:id="rId14" xr:uid="{36CFF13A-82D4-9642-B07B-0C3E49B5D215}"/>
+    <hyperlink ref="K40" r:id="rId15" xr:uid="{DDDE99D5-3422-6549-8393-D5FC330D45B8}"/>
+    <hyperlink ref="K48" r:id="rId16" xr:uid="{9621A5D4-6BD1-984D-9C8C-2A89CFA54CFF}"/>
+    <hyperlink ref="K77" r:id="rId17" xr:uid="{CC87EE91-DF39-EA48-9614-33030270159C}"/>
+    <hyperlink ref="K72" r:id="rId18" xr:uid="{C4E1F448-AF1B-BC43-983F-FB439266392E}"/>
+    <hyperlink ref="K73" r:id="rId19" xr:uid="{17A665F7-B807-4640-B444-16CFE27D5FDF}"/>
+    <hyperlink ref="K54" r:id="rId20" xr:uid="{244C8E1D-D3A7-9549-9D73-8F4D984A6ACD}"/>
+    <hyperlink ref="K41" r:id="rId21" xr:uid="{135AB67A-502A-8A4D-B049-40F78987A6E4}"/>
+    <hyperlink ref="K31" r:id="rId22" xr:uid="{2EBEE3F8-DF57-0E4A-9FB8-2C6B08B9453B}"/>
+    <hyperlink ref="K53" r:id="rId23" xr:uid="{50C93161-BA50-264D-9EB0-FD96B5179BD3}"/>
+    <hyperlink ref="K63" r:id="rId24" xr:uid="{EB1586AB-126F-2B4B-AB36-6A028744AF76}"/>
+    <hyperlink ref="K64" r:id="rId25" xr:uid="{7C55426F-9022-8044-ACAA-5AEC9137C037}"/>
+    <hyperlink ref="K55" r:id="rId26" xr:uid="{AD424BE3-B862-2442-B3B2-5028AF918C6F}"/>
+    <hyperlink ref="K61" r:id="rId27" xr:uid="{2183D387-1FD2-324D-A080-BF2A14B2C266}"/>
+    <hyperlink ref="K82" r:id="rId28" xr:uid="{FDBD3899-8300-BE4F-B928-93EB7382FF06}"/>
     <hyperlink ref="K2" r:id="rId29" xr:uid="{529C6D37-3C52-0C4C-8560-C27F3F7C2BCE}"/>
     <hyperlink ref="K6" r:id="rId30" xr:uid="{D004E2AA-6899-A547-B940-4CF0A68E6AE2}"/>
-    <hyperlink ref="K69" r:id="rId31" xr:uid="{2DA721C4-AB3A-EB48-85F9-525AB6A822AB}"/>
-    <hyperlink ref="K50" r:id="rId32" xr:uid="{72A6DA76-289B-1945-8072-DAECE2441387}"/>
+    <hyperlink ref="K81" r:id="rId31" xr:uid="{2DA721C4-AB3A-EB48-85F9-525AB6A822AB}"/>
+    <hyperlink ref="K62" r:id="rId32" xr:uid="{72A6DA76-289B-1945-8072-DAECE2441387}"/>
     <hyperlink ref="K4" r:id="rId33" xr:uid="{1ED33379-967F-8D43-85DD-BDDF4C65376C}"/>
-    <hyperlink ref="K38" r:id="rId34" xr:uid="{F704F2D4-3F11-614C-BFFC-5AA6E996A592}"/>
-    <hyperlink ref="K56" r:id="rId35" xr:uid="{5F94CB6B-2D0C-7C41-9363-23A9286E6D55}"/>
-    <hyperlink ref="K55" r:id="rId36" xr:uid="{02572C89-38D3-4B47-B603-D75FBB76E0BB}"/>
-    <hyperlink ref="K37" r:id="rId37" xr:uid="{96F331DE-1BF1-354F-9E54-FA8C80316EFB}"/>
-    <hyperlink ref="K47" r:id="rId38" xr:uid="{D40AF006-F71D-054C-BD53-C9CF18C19E2B}"/>
-    <hyperlink ref="K53" r:id="rId39" xr:uid="{D3ABB7B3-002B-9E42-A591-D3282F8D9EDC}"/>
-    <hyperlink ref="K18" r:id="rId40" xr:uid="{F2CD1548-C098-164F-AE85-0E2D85DE116F}"/>
-    <hyperlink ref="K14" r:id="rId41" xr:uid="{81094FDB-D745-024E-BD73-D63401EE9AA2}"/>
-    <hyperlink ref="K35" r:id="rId42" xr:uid="{850F5B2D-3612-1E44-A230-B654A61C2B8F}"/>
-    <hyperlink ref="K27" r:id="rId43" xr:uid="{D84F734D-746E-B841-A450-F741C1E43856}"/>
-    <hyperlink ref="K62" r:id="rId44" xr:uid="{7870E1C9-1855-634F-8B01-0A6F56E1C8EC}"/>
-    <hyperlink ref="K39" r:id="rId45" xr:uid="{74E258E9-3406-444C-9382-59C9A5DD2D28}"/>
-    <hyperlink ref="K67" r:id="rId46" xr:uid="{22AFEECC-9483-CC40-B244-DB64D5BE611A}"/>
-    <hyperlink ref="K59" r:id="rId47" xr:uid="{3F60EBBC-9A66-404C-8F8D-E0FD74919AF5}"/>
-    <hyperlink ref="K17" r:id="rId48" xr:uid="{97FC090B-C1AF-3B40-8E1E-653AF871E0B8}"/>
-    <hyperlink ref="K48" r:id="rId49" xr:uid="{24271837-2997-A04B-B1A8-30D8EAA5AABF}"/>
-    <hyperlink ref="K54" r:id="rId50" xr:uid="{C6FE7874-DE1E-8744-8F7F-A7266A282BC7}"/>
-    <hyperlink ref="K8" r:id="rId51" xr:uid="{45D4B454-64FD-E043-9E1E-D98B915DA3C4}"/>
-    <hyperlink ref="K29" r:id="rId52" xr:uid="{592E8301-AD04-6A43-BE2C-DF1DCF4D0C8C}"/>
-    <hyperlink ref="K24" r:id="rId53" xr:uid="{AFFE99AD-C3BD-7D47-ADD2-0033AB1BD297}"/>
-    <hyperlink ref="K28" r:id="rId54" xr:uid="{10637FCE-769F-EF46-AFAF-F312278F1225}"/>
-    <hyperlink ref="K57" r:id="rId55" xr:uid="{1E8D6F6E-5279-684F-9870-749B17340F35}"/>
-    <hyperlink ref="K68" r:id="rId56" xr:uid="{C19F506D-023C-1247-BE6A-C23960198C51}"/>
+    <hyperlink ref="K50" r:id="rId34" xr:uid="{F704F2D4-3F11-614C-BFFC-5AA6E996A592}"/>
+    <hyperlink ref="K68" r:id="rId35" xr:uid="{5F94CB6B-2D0C-7C41-9363-23A9286E6D55}"/>
+    <hyperlink ref="K67" r:id="rId36" xr:uid="{02572C89-38D3-4B47-B603-D75FBB76E0BB}"/>
+    <hyperlink ref="K49" r:id="rId37" xr:uid="{96F331DE-1BF1-354F-9E54-FA8C80316EFB}"/>
+    <hyperlink ref="K59" r:id="rId38" xr:uid="{D40AF006-F71D-054C-BD53-C9CF18C19E2B}"/>
+    <hyperlink ref="K65" r:id="rId39" xr:uid="{D3ABB7B3-002B-9E42-A591-D3282F8D9EDC}"/>
+    <hyperlink ref="K21" r:id="rId40" xr:uid="{F2CD1548-C098-164F-AE85-0E2D85DE116F}"/>
+    <hyperlink ref="K17" r:id="rId41" xr:uid="{81094FDB-D745-024E-BD73-D63401EE9AA2}"/>
+    <hyperlink ref="K47" r:id="rId42" xr:uid="{850F5B2D-3612-1E44-A230-B654A61C2B8F}"/>
+    <hyperlink ref="K34" r:id="rId43" xr:uid="{D84F734D-746E-B841-A450-F741C1E43856}"/>
+    <hyperlink ref="K74" r:id="rId44" xr:uid="{7870E1C9-1855-634F-8B01-0A6F56E1C8EC}"/>
+    <hyperlink ref="K51" r:id="rId45" xr:uid="{74E258E9-3406-444C-9382-59C9A5DD2D28}"/>
+    <hyperlink ref="K79" r:id="rId46" xr:uid="{22AFEECC-9483-CC40-B244-DB64D5BE611A}"/>
+    <hyperlink ref="K71" r:id="rId47" xr:uid="{3F60EBBC-9A66-404C-8F8D-E0FD74919AF5}"/>
+    <hyperlink ref="K20" r:id="rId48" xr:uid="{97FC090B-C1AF-3B40-8E1E-653AF871E0B8}"/>
+    <hyperlink ref="K60" r:id="rId49" xr:uid="{24271837-2997-A04B-B1A8-30D8EAA5AABF}"/>
+    <hyperlink ref="K66" r:id="rId50" xr:uid="{C6FE7874-DE1E-8744-8F7F-A7266A282BC7}"/>
+    <hyperlink ref="K9" r:id="rId51" xr:uid="{45D4B454-64FD-E043-9E1E-D98B915DA3C4}"/>
+    <hyperlink ref="K36" r:id="rId52" xr:uid="{592E8301-AD04-6A43-BE2C-DF1DCF4D0C8C}"/>
+    <hyperlink ref="K28" r:id="rId53" xr:uid="{AFFE99AD-C3BD-7D47-ADD2-0033AB1BD297}"/>
+    <hyperlink ref="K35" r:id="rId54" xr:uid="{10637FCE-769F-EF46-AFAF-F312278F1225}"/>
+    <hyperlink ref="K69" r:id="rId55" xr:uid="{1E8D6F6E-5279-684F-9870-749B17340F35}"/>
+    <hyperlink ref="K80" r:id="rId56" xr:uid="{C19F506D-023C-1247-BE6A-C23960198C51}"/>
     <hyperlink ref="K5" r:id="rId57" xr:uid="{3E64B722-3690-B44C-ABC4-059D3B71C8D7}"/>
-    <hyperlink ref="K34" r:id="rId58" xr:uid="{50C3436F-19AF-D74F-8E0A-E9F0AEF4EF7F}"/>
-    <hyperlink ref="K16" r:id="rId59" xr:uid="{A5BBD32C-6F92-A842-A00C-8F17A0710E00}"/>
-    <hyperlink ref="K23" r:id="rId60" xr:uid="{117A81C3-427C-DF49-BA81-BE00A024107F}"/>
-    <hyperlink ref="K45" r:id="rId61" xr:uid="{5E89FA9C-5C01-5342-876F-D8B51FE4E2B8}"/>
-    <hyperlink ref="K64" r:id="rId62" xr:uid="{AE06ADB0-CCC6-5E4F-AA64-084B6EC4EDA5}"/>
-    <hyperlink ref="K40" r:id="rId63" xr:uid="{C1BBF821-4DC8-5347-B6F0-96939C529BA4}"/>
-    <hyperlink ref="K44" r:id="rId64" xr:uid="{990812EE-4D67-A148-8354-137377C29D95}"/>
-    <hyperlink ref="K25" r:id="rId65" xr:uid="{9C8D9D49-3342-1D45-9490-372911350A58}"/>
-    <hyperlink ref="K58" r:id="rId66" xr:uid="{EFDE2707-AAFE-A445-930B-DB05A658CF11}"/>
-    <hyperlink ref="K63" r:id="rId67" xr:uid="{C4CFA4B9-7F0C-2D48-848B-F4855312250F}"/>
-    <hyperlink ref="K66" r:id="rId68" xr:uid="{2C92D437-B811-BA4F-A7A0-ECBD7F90C3E8}"/>
-    <hyperlink ref="K71" r:id="rId69" xr:uid="{1DA360B3-3EEC-0B4A-92B2-F41887D4DA99}"/>
-    <hyperlink ref="K72" r:id="rId70" xr:uid="{53707DD5-6AE9-244D-BE8B-768805F672D6}"/>
-    <hyperlink ref="K73" r:id="rId71" xr:uid="{36EBDC68-249C-1C48-AAF4-2B47231ACC4B}"/>
-    <hyperlink ref="K74" r:id="rId72" xr:uid="{A1D0B6A6-8992-754F-A034-0A1E7D5B9BCB}"/>
-    <hyperlink ref="K75" r:id="rId73" xr:uid="{A089F750-0C9E-6945-9649-FC6752762842}"/>
-    <hyperlink ref="K76" r:id="rId74" xr:uid="{DB5E5AED-5451-EE4B-9408-E80763135A0D}"/>
-    <hyperlink ref="K77" r:id="rId75" xr:uid="{54790613-574F-C04B-943E-7BC43E9CE3FE}"/>
-    <hyperlink ref="K78" r:id="rId76" xr:uid="{04799654-C848-244D-A1F9-FAA86321A73F}"/>
-    <hyperlink ref="K79" r:id="rId77" xr:uid="{0EB41F51-36DD-AA40-AA97-D6366DF2ACBF}"/>
-    <hyperlink ref="K80" r:id="rId78" xr:uid="{7DFC2710-EE37-1F4C-A14D-E4C357A34AC5}"/>
-    <hyperlink ref="K81" r:id="rId79" xr:uid="{F62AC8D7-0E4C-8D4A-A393-61AF8AC0EB46}"/>
-    <hyperlink ref="K82" r:id="rId80" xr:uid="{EE4CEA07-2929-A846-98F2-C6C1968C5BD7}"/>
-    <hyperlink ref="K83" r:id="rId81" xr:uid="{0B614C9A-CC57-2C4A-9102-DE5C3F305979}"/>
+    <hyperlink ref="K42" r:id="rId58" xr:uid="{50C3436F-19AF-D74F-8E0A-E9F0AEF4EF7F}"/>
+    <hyperlink ref="K19" r:id="rId59" xr:uid="{A5BBD32C-6F92-A842-A00C-8F17A0710E00}"/>
+    <hyperlink ref="K27" r:id="rId60" xr:uid="{117A81C3-427C-DF49-BA81-BE00A024107F}"/>
+    <hyperlink ref="K57" r:id="rId61" xr:uid="{5E89FA9C-5C01-5342-876F-D8B51FE4E2B8}"/>
+    <hyperlink ref="K76" r:id="rId62" xr:uid="{AE06ADB0-CCC6-5E4F-AA64-084B6EC4EDA5}"/>
+    <hyperlink ref="K52" r:id="rId63" xr:uid="{C1BBF821-4DC8-5347-B6F0-96939C529BA4}"/>
+    <hyperlink ref="K56" r:id="rId64" xr:uid="{990812EE-4D67-A148-8354-137377C29D95}"/>
+    <hyperlink ref="K30" r:id="rId65" xr:uid="{9C8D9D49-3342-1D45-9490-372911350A58}"/>
+    <hyperlink ref="K70" r:id="rId66" xr:uid="{EFDE2707-AAFE-A445-930B-DB05A658CF11}"/>
+    <hyperlink ref="K75" r:id="rId67" xr:uid="{C4CFA4B9-7F0C-2D48-848B-F4855312250F}"/>
+    <hyperlink ref="K78" r:id="rId68" xr:uid="{2C92D437-B811-BA4F-A7A0-ECBD7F90C3E8}"/>
+    <hyperlink ref="K83" r:id="rId69" xr:uid="{1DA360B3-3EEC-0B4A-92B2-F41887D4DA99}"/>
+    <hyperlink ref="K7" r:id="rId70" xr:uid="{53707DD5-6AE9-244D-BE8B-768805F672D6}"/>
+    <hyperlink ref="K45" r:id="rId71" xr:uid="{36EBDC68-249C-1C48-AAF4-2B47231ACC4B}"/>
+    <hyperlink ref="K33" r:id="rId72" xr:uid="{A1D0B6A6-8992-754F-A034-0A1E7D5B9BCB}"/>
+    <hyperlink ref="K43" r:id="rId73" xr:uid="{A089F750-0C9E-6945-9649-FC6752762842}"/>
+    <hyperlink ref="K12" r:id="rId74" xr:uid="{DB5E5AED-5451-EE4B-9408-E80763135A0D}"/>
+    <hyperlink ref="K32" r:id="rId75" xr:uid="{54790613-574F-C04B-943E-7BC43E9CE3FE}"/>
+    <hyperlink ref="K46" r:id="rId76" xr:uid="{04799654-C848-244D-A1F9-FAA86321A73F}"/>
+    <hyperlink ref="K39" r:id="rId77" xr:uid="{0EB41F51-36DD-AA40-AA97-D6366DF2ACBF}"/>
+    <hyperlink ref="K22" r:id="rId78" xr:uid="{7DFC2710-EE37-1F4C-A14D-E4C357A34AC5}"/>
+    <hyperlink ref="K15" r:id="rId79" xr:uid="{F62AC8D7-0E4C-8D4A-A393-61AF8AC0EB46}"/>
+    <hyperlink ref="K29" r:id="rId80" xr:uid="{EE4CEA07-2929-A846-98F2-C6C1968C5BD7}"/>
+    <hyperlink ref="K44" r:id="rId81" xr:uid="{0B614C9A-CC57-2C4A-9102-DE5C3F305979}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-1405-TVSeries.xlsx
+++ b/db/A7XLK-1405-TVSeries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78834634-124F-F94F-BEB4-89D6C9D1A97F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBF20A5-2F0E-1B4F-83D1-568110CDCEC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4500" yWindow="2600" windowWidth="29840" windowHeight="17320" xr2:uid="{BAC94C6D-C196-2D4F-A2F2-89F0A182D671}"/>
   </bookViews>
@@ -2185,7 +2185,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>75</v>
+        <v>401</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -2197,27 +2197,30 @@
         <v>291</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>230</v>
+        <v>170</v>
       </c>
       <c r="F2" t="s">
-        <v>231</v>
+        <v>426</v>
       </c>
       <c r="G2" t="s">
-        <v>112</v>
+        <v>425</v>
       </c>
       <c r="H2" s="3">
-        <v>9760868</v>
+        <v>3164608</v>
+      </c>
+      <c r="I2" s="4">
+        <v>8.6</v>
       </c>
       <c r="J2" t="s">
-        <v>40</v>
+        <v>413</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>232</v>
+        <v>427</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>56</v>
+        <v>402</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
@@ -2229,30 +2232,30 @@
         <v>291</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="F3" t="s">
-        <v>180</v>
+        <v>428</v>
       </c>
       <c r="G3" t="s">
-        <v>93</v>
+        <v>431</v>
       </c>
       <c r="H3" s="3">
-        <v>8844170</v>
+        <v>52300</v>
       </c>
       <c r="I3" s="4">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="J3" t="s">
-        <v>23</v>
+        <v>414</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>181</v>
+        <v>429</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>79</v>
+        <v>403</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
@@ -2264,27 +2267,30 @@
         <v>291</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>189</v>
+        <v>433</v>
       </c>
       <c r="F4" t="s">
-        <v>241</v>
+        <v>432</v>
       </c>
       <c r="G4" t="s">
-        <v>116</v>
+        <v>430</v>
       </c>
       <c r="H4" s="3">
-        <v>6002697</v>
+        <v>489413</v>
+      </c>
+      <c r="I4" s="4">
+        <v>8.1999999999999993</v>
       </c>
       <c r="J4" t="s">
-        <v>44</v>
+        <v>415</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>242</v>
+        <v>434</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>321</v>
+        <v>76</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
@@ -2299,24 +2305,27 @@
         <v>170</v>
       </c>
       <c r="F5" t="s">
-        <v>366</v>
+        <v>233</v>
       </c>
       <c r="G5" t="s">
-        <v>303</v>
+        <v>113</v>
       </c>
       <c r="H5" s="3">
-        <v>5150111</v>
+        <v>4155026</v>
+      </c>
+      <c r="I5" s="4">
+        <v>8.1</v>
       </c>
       <c r="J5" t="s">
-        <v>340</v>
+        <v>41</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>368</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>76</v>
+        <v>404</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
@@ -2328,30 +2337,30 @@
         <v>291</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="F6" t="s">
-        <v>233</v>
+        <v>436</v>
       </c>
       <c r="G6" t="s">
-        <v>113</v>
+        <v>435</v>
       </c>
       <c r="H6" s="3">
-        <v>4155026</v>
+        <v>95136</v>
       </c>
       <c r="I6" s="4">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J6" t="s">
-        <v>41</v>
+        <v>416</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>234</v>
+        <v>437</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>401</v>
+        <v>329</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
@@ -2366,27 +2375,27 @@
         <v>170</v>
       </c>
       <c r="F7" t="s">
-        <v>426</v>
+        <v>389</v>
       </c>
       <c r="G7" t="s">
-        <v>425</v>
+        <v>310</v>
       </c>
       <c r="H7" s="3">
-        <v>3164608</v>
+        <v>767044</v>
       </c>
       <c r="I7" s="4">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="J7" t="s">
-        <v>413</v>
+        <v>345</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>427</v>
+        <v>390</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>49</v>
+        <v>318</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
@@ -2398,30 +2407,33 @@
         <v>291</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="F8" t="s">
-        <v>162</v>
+        <v>360</v>
       </c>
       <c r="G8" t="s">
-        <v>86</v>
+        <v>301</v>
       </c>
       <c r="H8" s="3">
-        <v>2815834</v>
+        <v>378104</v>
+      </c>
+      <c r="I8" s="4">
+        <v>7.8</v>
       </c>
       <c r="J8" t="s">
-        <v>16</v>
+        <v>337</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>163</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>315</v>
+        <v>405</v>
       </c>
       <c r="B9" t="s">
-        <v>350</v>
+        <v>11</v>
       </c>
       <c r="C9">
         <v>2021</v>
@@ -2430,27 +2442,30 @@
         <v>291</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>351</v>
+        <v>173</v>
       </c>
       <c r="F9" t="s">
-        <v>352</v>
+        <v>439</v>
       </c>
       <c r="G9" t="s">
-        <v>298</v>
+        <v>438</v>
       </c>
       <c r="H9" s="3">
-        <v>2535509</v>
+        <v>2330511</v>
+      </c>
+      <c r="I9" s="4">
+        <v>7.6</v>
       </c>
       <c r="J9" t="s">
-        <v>334</v>
+        <v>417</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>353</v>
+        <v>440</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
-        <v>57</v>
+        <v>406</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
@@ -2462,27 +2477,30 @@
         <v>291</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>173</v>
+        <v>222</v>
       </c>
       <c r="F10" t="s">
-        <v>182</v>
+        <v>442</v>
       </c>
       <c r="G10" t="s">
-        <v>94</v>
+        <v>441</v>
       </c>
       <c r="H10" s="3">
-        <v>2454774</v>
+        <v>548641</v>
+      </c>
+      <c r="I10" s="4">
+        <v>7.6</v>
       </c>
       <c r="J10" t="s">
-        <v>24</v>
+        <v>418</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>183</v>
+        <v>443</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
-        <v>54</v>
+        <v>408</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
@@ -2494,27 +2512,30 @@
         <v>291</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="F11" t="s">
-        <v>174</v>
+        <v>448</v>
       </c>
       <c r="G11" t="s">
-        <v>91</v>
+        <v>447</v>
       </c>
       <c r="H11" s="3">
-        <v>2378245</v>
+        <v>134785</v>
+      </c>
+      <c r="I11" s="4">
+        <v>7.5</v>
       </c>
       <c r="J11" t="s">
-        <v>21</v>
+        <v>420</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>175</v>
+        <v>449</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
@@ -2526,30 +2547,30 @@
         <v>291</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>173</v>
+        <v>433</v>
       </c>
       <c r="F12" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="G12" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="H12" s="3">
-        <v>2330511</v>
+        <v>52113</v>
       </c>
       <c r="I12" s="4">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J12" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1" t="s">
-        <v>7</v>
+        <v>409</v>
       </c>
       <c r="B13" t="s">
         <v>11</v>
@@ -2561,27 +2582,30 @@
         <v>291</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>158</v>
+        <v>452</v>
       </c>
       <c r="F13" t="s">
-        <v>157</v>
+        <v>451</v>
       </c>
       <c r="G13" t="s">
-        <v>85</v>
+        <v>450</v>
       </c>
       <c r="H13" s="3">
-        <v>2132343</v>
+        <v>1278633</v>
+      </c>
+      <c r="I13" s="4">
+        <v>7.3</v>
       </c>
       <c r="J13" t="s">
-        <v>15</v>
+        <v>421</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>159</v>
+        <v>453</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1" t="s">
-        <v>53</v>
+        <v>410</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
@@ -2593,27 +2617,30 @@
         <v>291</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>170</v>
+        <v>285</v>
       </c>
       <c r="F14" t="s">
-        <v>171</v>
+        <v>455</v>
       </c>
       <c r="G14" t="s">
-        <v>90</v>
+        <v>454</v>
       </c>
       <c r="H14" s="3">
-        <v>2059245</v>
+        <v>2043804</v>
+      </c>
+      <c r="I14" s="4">
+        <v>7.2</v>
       </c>
       <c r="J14" t="s">
-        <v>20</v>
+        <v>422</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>172</v>
+        <v>456</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1" t="s">
-        <v>410</v>
+        <v>59</v>
       </c>
       <c r="B15" t="s">
         <v>11</v>
@@ -2625,30 +2652,30 @@
         <v>291</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>285</v>
+        <v>158</v>
       </c>
       <c r="F15" t="s">
-        <v>455</v>
+        <v>187</v>
       </c>
       <c r="G15" t="s">
-        <v>454</v>
+        <v>96</v>
       </c>
       <c r="H15" s="3">
-        <v>2043804</v>
+        <v>1071359</v>
       </c>
       <c r="I15" s="4">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J15" t="s">
-        <v>422</v>
+        <v>26</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>456</v>
+        <v>188</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B16" t="s">
         <v>11</v>
@@ -2660,27 +2687,30 @@
         <v>291</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="F16" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="G16" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H16" s="3">
-        <v>1960230</v>
+        <v>1028428</v>
+      </c>
+      <c r="I16" s="4">
+        <v>7.1</v>
       </c>
       <c r="J16" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="1" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="B17" t="s">
         <v>11</v>
@@ -2692,27 +2722,30 @@
         <v>291</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="F17" t="s">
-        <v>264</v>
+        <v>180</v>
       </c>
       <c r="G17" t="s">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="H17" s="3">
-        <v>1845243</v>
+        <v>8844170</v>
+      </c>
+      <c r="I17" s="4">
+        <v>7</v>
       </c>
       <c r="J17" t="s">
-        <v>148</v>
+        <v>23</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>265</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="1" t="s">
-        <v>60</v>
+        <v>411</v>
       </c>
       <c r="B18" t="s">
         <v>11</v>
@@ -2724,27 +2757,30 @@
         <v>291</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>189</v>
+        <v>459</v>
       </c>
       <c r="F18" t="s">
-        <v>190</v>
+        <v>458</v>
       </c>
       <c r="G18" t="s">
-        <v>97</v>
+        <v>457</v>
       </c>
       <c r="H18" s="3">
-        <v>1796008</v>
+        <v>785247</v>
+      </c>
+      <c r="I18" s="4">
+        <v>7</v>
       </c>
       <c r="J18" t="s">
-        <v>27</v>
+        <v>423</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>191</v>
+        <v>460</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="1" t="s">
-        <v>323</v>
+        <v>412</v>
       </c>
       <c r="B19" t="s">
         <v>11</v>
@@ -2756,27 +2792,30 @@
         <v>291</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>173</v>
+        <v>433</v>
       </c>
       <c r="F19" t="s">
-        <v>372</v>
+        <v>462</v>
       </c>
       <c r="G19" t="s">
-        <v>305</v>
+        <v>461</v>
       </c>
       <c r="H19" s="3">
-        <v>1771888</v>
+        <v>89338</v>
+      </c>
+      <c r="I19" s="4">
+        <v>7</v>
       </c>
       <c r="J19" t="s">
-        <v>341</v>
+        <v>424</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>373</v>
+        <v>463</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="1" t="s">
-        <v>143</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
         <v>11</v>
@@ -2788,27 +2827,27 @@
         <v>291</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>282</v>
+        <v>230</v>
       </c>
       <c r="F20" t="s">
-        <v>281</v>
+        <v>231</v>
       </c>
       <c r="G20" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="H20" s="3">
-        <v>1758290</v>
+        <v>9760868</v>
       </c>
       <c r="J20" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>283</v>
+        <v>232</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="1" t="s">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="B21" t="s">
         <v>11</v>
@@ -2820,27 +2859,27 @@
         <v>291</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="F21" t="s">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="G21" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="H21" s="3">
-        <v>1560320</v>
+        <v>6002697</v>
       </c>
       <c r="J21" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="1" t="s">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="B22" t="s">
         <v>11</v>
@@ -2852,30 +2891,27 @@
         <v>291</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>452</v>
+        <v>170</v>
       </c>
       <c r="F22" t="s">
-        <v>451</v>
+        <v>366</v>
       </c>
       <c r="G22" t="s">
-        <v>450</v>
+        <v>303</v>
       </c>
       <c r="H22" s="3">
-        <v>1278633</v>
-      </c>
-      <c r="I22" s="4">
-        <v>7.3</v>
+        <v>5150111</v>
       </c>
       <c r="J22" t="s">
-        <v>421</v>
+        <v>340</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>453</v>
+        <v>368</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B23" t="s">
         <v>11</v>
@@ -2887,30 +2923,30 @@
         <v>291</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="F23" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="G23" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H23" s="3">
-        <v>1212038</v>
+        <v>2815834</v>
       </c>
       <c r="J23" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="1" t="s">
-        <v>59</v>
+        <v>315</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>350</v>
       </c>
       <c r="C24">
         <v>2021</v>
@@ -2919,30 +2955,27 @@
         <v>291</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>158</v>
+        <v>351</v>
       </c>
       <c r="F24" t="s">
-        <v>187</v>
+        <v>352</v>
       </c>
       <c r="G24" t="s">
-        <v>96</v>
+        <v>298</v>
       </c>
       <c r="H24" s="3">
-        <v>1071359</v>
-      </c>
-      <c r="I24" s="4">
-        <v>7.1</v>
+        <v>2535509</v>
       </c>
       <c r="J24" t="s">
-        <v>26</v>
+        <v>334</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>188</v>
+        <v>353</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="1" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B25" t="s">
         <v>11</v>
@@ -2954,30 +2987,27 @@
         <v>291</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="F25" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="G25" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H25" s="3">
-        <v>1028428</v>
-      </c>
-      <c r="I25" s="4">
-        <v>7.1</v>
+        <v>2454774</v>
       </c>
       <c r="J25" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B26" t="s">
         <v>11</v>
@@ -2989,24 +3019,27 @@
         <v>291</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>161</v>
+        <v>173</v>
+      </c>
+      <c r="F26" t="s">
+        <v>174</v>
       </c>
       <c r="G26" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H26" s="3">
-        <v>976802</v>
+        <v>2378245</v>
       </c>
       <c r="J26" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="1" t="s">
-        <v>324</v>
+        <v>7</v>
       </c>
       <c r="B27" t="s">
         <v>11</v>
@@ -3018,27 +3051,27 @@
         <v>291</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="F27" t="s">
-        <v>375</v>
+        <v>157</v>
       </c>
       <c r="G27" t="s">
-        <v>306</v>
+        <v>85</v>
       </c>
       <c r="H27" s="3">
-        <v>954238</v>
+        <v>2132343</v>
       </c>
       <c r="J27" t="s">
-        <v>374</v>
+        <v>15</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>376</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="1" t="s">
-        <v>317</v>
+        <v>53</v>
       </c>
       <c r="B28" t="s">
         <v>11</v>
@@ -3050,27 +3083,27 @@
         <v>291</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>358</v>
+        <v>170</v>
       </c>
       <c r="F28" t="s">
-        <v>357</v>
+        <v>171</v>
       </c>
       <c r="G28" t="s">
-        <v>300</v>
+        <v>90</v>
       </c>
       <c r="H28" s="3">
-        <v>795715</v>
+        <v>2059245</v>
       </c>
       <c r="J28" t="s">
-        <v>336</v>
+        <v>20</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>359</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="1" t="s">
-        <v>411</v>
+        <v>55</v>
       </c>
       <c r="B29" t="s">
         <v>11</v>
@@ -3082,30 +3115,27 @@
         <v>291</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>459</v>
+        <v>176</v>
       </c>
       <c r="F29" t="s">
-        <v>458</v>
+        <v>177</v>
       </c>
       <c r="G29" t="s">
-        <v>457</v>
+        <v>92</v>
       </c>
       <c r="H29" s="3">
-        <v>785247</v>
-      </c>
-      <c r="I29" s="4">
-        <v>7</v>
+        <v>1960230</v>
       </c>
       <c r="J29" t="s">
-        <v>423</v>
+        <v>22</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>460</v>
+        <v>178</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="1" t="s">
-        <v>329</v>
+        <v>136</v>
       </c>
       <c r="B30" t="s">
         <v>11</v>
@@ -3117,30 +3147,27 @@
         <v>291</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="F30" t="s">
-        <v>389</v>
+        <v>264</v>
       </c>
       <c r="G30" t="s">
-        <v>310</v>
+        <v>124</v>
       </c>
       <c r="H30" s="3">
-        <v>767044</v>
-      </c>
-      <c r="I30" s="4">
-        <v>7.8</v>
+        <v>1845243</v>
       </c>
       <c r="J30" t="s">
-        <v>345</v>
+        <v>148</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>390</v>
+        <v>265</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B31" t="s">
         <v>11</v>
@@ -3152,27 +3179,27 @@
         <v>291</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="F31" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="G31" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H31" s="3">
-        <v>653514</v>
+        <v>1796008</v>
       </c>
       <c r="J31" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="1" t="s">
-        <v>406</v>
+        <v>323</v>
       </c>
       <c r="B32" t="s">
         <v>11</v>
@@ -3184,30 +3211,27 @@
         <v>291</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>222</v>
+        <v>173</v>
       </c>
       <c r="F32" t="s">
-        <v>442</v>
+        <v>372</v>
       </c>
       <c r="G32" t="s">
-        <v>441</v>
+        <v>305</v>
       </c>
       <c r="H32" s="3">
-        <v>548641</v>
-      </c>
-      <c r="I32" s="4">
-        <v>7.6</v>
+        <v>1771888</v>
       </c>
       <c r="J32" t="s">
-        <v>418</v>
+        <v>341</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>443</v>
+        <v>373</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="1" t="s">
-        <v>403</v>
+        <v>143</v>
       </c>
       <c r="B33" t="s">
         <v>11</v>
@@ -3219,33 +3243,30 @@
         <v>291</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>433</v>
+        <v>282</v>
       </c>
       <c r="F33" t="s">
-        <v>432</v>
+        <v>281</v>
       </c>
       <c r="G33" t="s">
-        <v>430</v>
+        <v>131</v>
       </c>
       <c r="H33" s="3">
-        <v>489413</v>
-      </c>
-      <c r="I33" s="4">
-        <v>8.1999999999999993</v>
+        <v>1758290</v>
       </c>
       <c r="J33" t="s">
-        <v>415</v>
+        <v>155</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>434</v>
+        <v>283</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B34" t="s">
-        <v>224</v>
+        <v>11</v>
       </c>
       <c r="C34">
         <v>2021</v>
@@ -3254,27 +3275,27 @@
         <v>291</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>268</v>
+        <v>167</v>
       </c>
       <c r="F34" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="G34" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H34" s="3">
-        <v>459883</v>
+        <v>1560320</v>
       </c>
       <c r="J34" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="1" t="s">
-        <v>318</v>
+        <v>58</v>
       </c>
       <c r="B35" t="s">
         <v>11</v>
@@ -3286,30 +3307,27 @@
         <v>291</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="F35" t="s">
-        <v>360</v>
+        <v>185</v>
       </c>
       <c r="G35" t="s">
-        <v>301</v>
+        <v>95</v>
       </c>
       <c r="H35" s="3">
-        <v>378104</v>
-      </c>
-      <c r="I35" s="4">
-        <v>7.8</v>
+        <v>1212038</v>
       </c>
       <c r="J35" t="s">
-        <v>337</v>
+        <v>25</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>361</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="1" t="s">
-        <v>316</v>
+        <v>52</v>
       </c>
       <c r="B36" t="s">
         <v>11</v>
@@ -3321,27 +3339,24 @@
         <v>291</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="F36" t="s">
-        <v>354</v>
+        <v>161</v>
       </c>
       <c r="G36" t="s">
-        <v>299</v>
+        <v>89</v>
       </c>
       <c r="H36" s="3">
-        <v>377267</v>
+        <v>976802</v>
       </c>
       <c r="J36" t="s">
-        <v>335</v>
+        <v>19</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>356</v>
+        <v>169</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="1" t="s">
-        <v>51</v>
+        <v>324</v>
       </c>
       <c r="B37" t="s">
         <v>11</v>
@@ -3353,27 +3368,27 @@
         <v>291</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="F37" t="s">
-        <v>168</v>
+        <v>375</v>
       </c>
       <c r="G37" t="s">
-        <v>87</v>
+        <v>306</v>
       </c>
       <c r="H37" s="3">
-        <v>303763</v>
+        <v>954238</v>
       </c>
       <c r="J37" t="s">
-        <v>18</v>
+        <v>374</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>166</v>
+        <v>376</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="1" t="s">
-        <v>6</v>
+        <v>317</v>
       </c>
       <c r="B38" t="s">
         <v>11</v>
@@ -3384,28 +3399,28 @@
       <c r="D38" t="s">
         <v>291</v>
       </c>
-      <c r="E38" s="1">
-        <v>-10</v>
+      <c r="E38" s="1" t="s">
+        <v>358</v>
       </c>
       <c r="F38" t="s">
-        <v>13</v>
+        <v>357</v>
       </c>
       <c r="G38" t="s">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="H38" s="3">
-        <v>200612</v>
+        <v>795715</v>
       </c>
       <c r="J38" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>160</v>
+        <v>359</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="1" t="s">
-        <v>408</v>
+        <v>68</v>
       </c>
       <c r="B39" t="s">
         <v>11</v>
@@ -3417,33 +3432,30 @@
         <v>291</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>158</v>
+        <v>198</v>
       </c>
       <c r="F39" t="s">
-        <v>448</v>
+        <v>212</v>
       </c>
       <c r="G39" t="s">
-        <v>447</v>
+        <v>105</v>
       </c>
       <c r="H39" s="3">
-        <v>134785</v>
-      </c>
-      <c r="I39" s="4">
-        <v>7.5</v>
+        <v>653514</v>
       </c>
       <c r="J39" t="s">
-        <v>420</v>
+        <v>34</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>449</v>
+        <v>213</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="1" t="s">
-        <v>61</v>
+        <v>138</v>
       </c>
       <c r="B40" t="s">
-        <v>11</v>
+        <v>224</v>
       </c>
       <c r="C40">
         <v>2021</v>
@@ -3452,27 +3464,27 @@
         <v>291</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>192</v>
+        <v>268</v>
       </c>
       <c r="F40" t="s">
-        <v>193</v>
+        <v>269</v>
       </c>
       <c r="G40" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="H40" s="3">
-        <v>132204</v>
+        <v>459883</v>
       </c>
       <c r="J40" t="s">
-        <v>288</v>
+        <v>150</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>194</v>
+        <v>270</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="1" t="s">
-        <v>67</v>
+        <v>316</v>
       </c>
       <c r="B41" t="s">
         <v>11</v>
@@ -3484,27 +3496,27 @@
         <v>291</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>195</v>
+        <v>355</v>
       </c>
       <c r="F41" t="s">
-        <v>210</v>
+        <v>354</v>
       </c>
       <c r="G41" t="s">
-        <v>104</v>
+        <v>299</v>
       </c>
       <c r="H41" s="3">
-        <v>121479</v>
+        <v>377267</v>
       </c>
       <c r="J41" t="s">
-        <v>33</v>
+        <v>335</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>211</v>
+        <v>356</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="1" t="s">
-        <v>322</v>
+        <v>51</v>
       </c>
       <c r="B42" t="s">
         <v>11</v>
@@ -3516,27 +3528,27 @@
         <v>291</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="F42" t="s">
-        <v>370</v>
+        <v>168</v>
       </c>
       <c r="G42" t="s">
-        <v>304</v>
+        <v>87</v>
       </c>
       <c r="H42" s="3">
-        <v>98231</v>
+        <v>303763</v>
       </c>
       <c r="J42" t="s">
-        <v>369</v>
+        <v>18</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>371</v>
+        <v>166</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="1" t="s">
-        <v>404</v>
+        <v>6</v>
       </c>
       <c r="B43" t="s">
         <v>11</v>
@@ -3547,31 +3559,28 @@
       <c r="D43" t="s">
         <v>291</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>161</v>
+      <c r="E43" s="1">
+        <v>-10</v>
       </c>
       <c r="F43" t="s">
-        <v>436</v>
+        <v>13</v>
       </c>
       <c r="G43" t="s">
-        <v>435</v>
+        <v>10</v>
       </c>
       <c r="H43" s="3">
-        <v>95136</v>
-      </c>
-      <c r="I43" s="4">
-        <v>7.9</v>
+        <v>200612</v>
       </c>
       <c r="J43" t="s">
-        <v>416</v>
+        <v>14</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>437</v>
+        <v>160</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="1" t="s">
-        <v>412</v>
+        <v>61</v>
       </c>
       <c r="B44" t="s">
         <v>11</v>
@@ -3583,30 +3592,27 @@
         <v>291</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>433</v>
+        <v>192</v>
       </c>
       <c r="F44" t="s">
-        <v>462</v>
+        <v>193</v>
       </c>
       <c r="G44" t="s">
-        <v>461</v>
+        <v>98</v>
       </c>
       <c r="H44" s="3">
-        <v>89338</v>
-      </c>
-      <c r="I44" s="4">
-        <v>7</v>
+        <v>132204</v>
       </c>
       <c r="J44" t="s">
-        <v>424</v>
+        <v>288</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>463</v>
+        <v>194</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="1" t="s">
-        <v>402</v>
+        <v>67</v>
       </c>
       <c r="B45" t="s">
         <v>11</v>
@@ -3618,30 +3624,27 @@
         <v>291</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="F45" t="s">
-        <v>428</v>
+        <v>210</v>
       </c>
       <c r="G45" t="s">
-        <v>431</v>
+        <v>104</v>
       </c>
       <c r="H45" s="3">
-        <v>52300</v>
-      </c>
-      <c r="I45" s="4">
-        <v>8.5</v>
+        <v>121479</v>
       </c>
       <c r="J45" t="s">
-        <v>414</v>
+        <v>33</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>429</v>
+        <v>211</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="1" t="s">
-        <v>407</v>
+        <v>322</v>
       </c>
       <c r="B46" t="s">
         <v>11</v>
@@ -3653,25 +3656,22 @@
         <v>291</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>433</v>
+        <v>158</v>
       </c>
       <c r="F46" t="s">
-        <v>445</v>
+        <v>370</v>
       </c>
       <c r="G46" t="s">
-        <v>444</v>
+        <v>304</v>
       </c>
       <c r="H46" s="3">
-        <v>52113</v>
-      </c>
-      <c r="I46" s="4">
-        <v>7.5</v>
+        <v>98231</v>
       </c>
       <c r="J46" t="s">
-        <v>419</v>
+        <v>369</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>446</v>
+        <v>371</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -4861,91 +4861,92 @@
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K83">
     <sortCondition ref="D2:D83"/>
+    <sortCondition descending="1" ref="I2:I83"/>
     <sortCondition descending="1" ref="H2:H83"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="K38" r:id="rId1" xr:uid="{725A3016-CC80-5F4A-B091-4E71BCFAD36B}"/>
-    <hyperlink ref="K13" r:id="rId2" xr:uid="{38F493C0-3185-604E-A3BD-AAB0EC5B83DF}"/>
-    <hyperlink ref="K8" r:id="rId3" xr:uid="{2E642780-E9D7-BF4B-9D23-FEBE51DDD0C9}"/>
-    <hyperlink ref="K25" r:id="rId4" xr:uid="{5CF6DEF3-9028-3D4C-846C-DA2618807577}"/>
-    <hyperlink ref="K37" r:id="rId5" xr:uid="{A298B622-5340-5148-820B-D468159EA5BD}"/>
-    <hyperlink ref="K26" r:id="rId6" xr:uid="{EF9BC619-52CD-2D48-BE99-80BD81A8CD54}"/>
-    <hyperlink ref="K14" r:id="rId7" xr:uid="{0002A242-754F-5A40-86A8-5F7DBBEBB9D1}"/>
-    <hyperlink ref="K11" r:id="rId8" xr:uid="{085C9D3E-4AFA-FF48-AA1A-64ECF275D4C0}"/>
-    <hyperlink ref="K16" r:id="rId9" xr:uid="{118F4CA9-C4A7-F74E-8AFF-041FB2741717}"/>
-    <hyperlink ref="K3" r:id="rId10" xr:uid="{75687EB7-0A29-5C47-921B-954A17F06565}"/>
-    <hyperlink ref="K10" r:id="rId11" xr:uid="{81B8E0D0-29DD-E74A-8CE3-1464ECDB131A}"/>
-    <hyperlink ref="K23" r:id="rId12" xr:uid="{5D4D2728-3F60-EE43-86DF-EE58ADBF8432}"/>
-    <hyperlink ref="K24" r:id="rId13" xr:uid="{31C21087-E027-4542-80B2-C095CF193FA7}"/>
-    <hyperlink ref="K18" r:id="rId14" xr:uid="{36CFF13A-82D4-9642-B07B-0C3E49B5D215}"/>
-    <hyperlink ref="K40" r:id="rId15" xr:uid="{DDDE99D5-3422-6549-8393-D5FC330D45B8}"/>
+    <hyperlink ref="K43" r:id="rId1" xr:uid="{725A3016-CC80-5F4A-B091-4E71BCFAD36B}"/>
+    <hyperlink ref="K27" r:id="rId2" xr:uid="{38F493C0-3185-604E-A3BD-AAB0EC5B83DF}"/>
+    <hyperlink ref="K23" r:id="rId3" xr:uid="{2E642780-E9D7-BF4B-9D23-FEBE51DDD0C9}"/>
+    <hyperlink ref="K16" r:id="rId4" xr:uid="{5CF6DEF3-9028-3D4C-846C-DA2618807577}"/>
+    <hyperlink ref="K42" r:id="rId5" xr:uid="{A298B622-5340-5148-820B-D468159EA5BD}"/>
+    <hyperlink ref="K36" r:id="rId6" xr:uid="{EF9BC619-52CD-2D48-BE99-80BD81A8CD54}"/>
+    <hyperlink ref="K28" r:id="rId7" xr:uid="{0002A242-754F-5A40-86A8-5F7DBBEBB9D1}"/>
+    <hyperlink ref="K26" r:id="rId8" xr:uid="{085C9D3E-4AFA-FF48-AA1A-64ECF275D4C0}"/>
+    <hyperlink ref="K29" r:id="rId9" xr:uid="{118F4CA9-C4A7-F74E-8AFF-041FB2741717}"/>
+    <hyperlink ref="K17" r:id="rId10" xr:uid="{75687EB7-0A29-5C47-921B-954A17F06565}"/>
+    <hyperlink ref="K25" r:id="rId11" xr:uid="{81B8E0D0-29DD-E74A-8CE3-1464ECDB131A}"/>
+    <hyperlink ref="K35" r:id="rId12" xr:uid="{5D4D2728-3F60-EE43-86DF-EE58ADBF8432}"/>
+    <hyperlink ref="K15" r:id="rId13" xr:uid="{31C21087-E027-4542-80B2-C095CF193FA7}"/>
+    <hyperlink ref="K31" r:id="rId14" xr:uid="{36CFF13A-82D4-9642-B07B-0C3E49B5D215}"/>
+    <hyperlink ref="K44" r:id="rId15" xr:uid="{DDDE99D5-3422-6549-8393-D5FC330D45B8}"/>
     <hyperlink ref="K48" r:id="rId16" xr:uid="{9621A5D4-6BD1-984D-9C8C-2A89CFA54CFF}"/>
     <hyperlink ref="K77" r:id="rId17" xr:uid="{CC87EE91-DF39-EA48-9614-33030270159C}"/>
     <hyperlink ref="K72" r:id="rId18" xr:uid="{C4E1F448-AF1B-BC43-983F-FB439266392E}"/>
     <hyperlink ref="K73" r:id="rId19" xr:uid="{17A665F7-B807-4640-B444-16CFE27D5FDF}"/>
     <hyperlink ref="K54" r:id="rId20" xr:uid="{244C8E1D-D3A7-9549-9D73-8F4D984A6ACD}"/>
-    <hyperlink ref="K41" r:id="rId21" xr:uid="{135AB67A-502A-8A4D-B049-40F78987A6E4}"/>
-    <hyperlink ref="K31" r:id="rId22" xr:uid="{2EBEE3F8-DF57-0E4A-9FB8-2C6B08B9453B}"/>
+    <hyperlink ref="K45" r:id="rId21" xr:uid="{135AB67A-502A-8A4D-B049-40F78987A6E4}"/>
+    <hyperlink ref="K39" r:id="rId22" xr:uid="{2EBEE3F8-DF57-0E4A-9FB8-2C6B08B9453B}"/>
     <hyperlink ref="K53" r:id="rId23" xr:uid="{50C93161-BA50-264D-9EB0-FD96B5179BD3}"/>
     <hyperlink ref="K63" r:id="rId24" xr:uid="{EB1586AB-126F-2B4B-AB36-6A028744AF76}"/>
     <hyperlink ref="K64" r:id="rId25" xr:uid="{7C55426F-9022-8044-ACAA-5AEC9137C037}"/>
     <hyperlink ref="K55" r:id="rId26" xr:uid="{AD424BE3-B862-2442-B3B2-5028AF918C6F}"/>
     <hyperlink ref="K61" r:id="rId27" xr:uid="{2183D387-1FD2-324D-A080-BF2A14B2C266}"/>
     <hyperlink ref="K82" r:id="rId28" xr:uid="{FDBD3899-8300-BE4F-B928-93EB7382FF06}"/>
-    <hyperlink ref="K2" r:id="rId29" xr:uid="{529C6D37-3C52-0C4C-8560-C27F3F7C2BCE}"/>
-    <hyperlink ref="K6" r:id="rId30" xr:uid="{D004E2AA-6899-A547-B940-4CF0A68E6AE2}"/>
+    <hyperlink ref="K20" r:id="rId29" xr:uid="{529C6D37-3C52-0C4C-8560-C27F3F7C2BCE}"/>
+    <hyperlink ref="K5" r:id="rId30" xr:uid="{D004E2AA-6899-A547-B940-4CF0A68E6AE2}"/>
     <hyperlink ref="K81" r:id="rId31" xr:uid="{2DA721C4-AB3A-EB48-85F9-525AB6A822AB}"/>
     <hyperlink ref="K62" r:id="rId32" xr:uid="{72A6DA76-289B-1945-8072-DAECE2441387}"/>
-    <hyperlink ref="K4" r:id="rId33" xr:uid="{1ED33379-967F-8D43-85DD-BDDF4C65376C}"/>
+    <hyperlink ref="K21" r:id="rId33" xr:uid="{1ED33379-967F-8D43-85DD-BDDF4C65376C}"/>
     <hyperlink ref="K50" r:id="rId34" xr:uid="{F704F2D4-3F11-614C-BFFC-5AA6E996A592}"/>
     <hyperlink ref="K68" r:id="rId35" xr:uid="{5F94CB6B-2D0C-7C41-9363-23A9286E6D55}"/>
     <hyperlink ref="K67" r:id="rId36" xr:uid="{02572C89-38D3-4B47-B603-D75FBB76E0BB}"/>
     <hyperlink ref="K49" r:id="rId37" xr:uid="{96F331DE-1BF1-354F-9E54-FA8C80316EFB}"/>
     <hyperlink ref="K59" r:id="rId38" xr:uid="{D40AF006-F71D-054C-BD53-C9CF18C19E2B}"/>
     <hyperlink ref="K65" r:id="rId39" xr:uid="{D3ABB7B3-002B-9E42-A591-D3282F8D9EDC}"/>
-    <hyperlink ref="K21" r:id="rId40" xr:uid="{F2CD1548-C098-164F-AE85-0E2D85DE116F}"/>
-    <hyperlink ref="K17" r:id="rId41" xr:uid="{81094FDB-D745-024E-BD73-D63401EE9AA2}"/>
+    <hyperlink ref="K34" r:id="rId40" xr:uid="{F2CD1548-C098-164F-AE85-0E2D85DE116F}"/>
+    <hyperlink ref="K30" r:id="rId41" xr:uid="{81094FDB-D745-024E-BD73-D63401EE9AA2}"/>
     <hyperlink ref="K47" r:id="rId42" xr:uid="{850F5B2D-3612-1E44-A230-B654A61C2B8F}"/>
-    <hyperlink ref="K34" r:id="rId43" xr:uid="{D84F734D-746E-B841-A450-F741C1E43856}"/>
+    <hyperlink ref="K40" r:id="rId43" xr:uid="{D84F734D-746E-B841-A450-F741C1E43856}"/>
     <hyperlink ref="K74" r:id="rId44" xr:uid="{7870E1C9-1855-634F-8B01-0A6F56E1C8EC}"/>
     <hyperlink ref="K51" r:id="rId45" xr:uid="{74E258E9-3406-444C-9382-59C9A5DD2D28}"/>
     <hyperlink ref="K79" r:id="rId46" xr:uid="{22AFEECC-9483-CC40-B244-DB64D5BE611A}"/>
     <hyperlink ref="K71" r:id="rId47" xr:uid="{3F60EBBC-9A66-404C-8F8D-E0FD74919AF5}"/>
-    <hyperlink ref="K20" r:id="rId48" xr:uid="{97FC090B-C1AF-3B40-8E1E-653AF871E0B8}"/>
+    <hyperlink ref="K33" r:id="rId48" xr:uid="{97FC090B-C1AF-3B40-8E1E-653AF871E0B8}"/>
     <hyperlink ref="K60" r:id="rId49" xr:uid="{24271837-2997-A04B-B1A8-30D8EAA5AABF}"/>
     <hyperlink ref="K66" r:id="rId50" xr:uid="{C6FE7874-DE1E-8744-8F7F-A7266A282BC7}"/>
-    <hyperlink ref="K9" r:id="rId51" xr:uid="{45D4B454-64FD-E043-9E1E-D98B915DA3C4}"/>
-    <hyperlink ref="K36" r:id="rId52" xr:uid="{592E8301-AD04-6A43-BE2C-DF1DCF4D0C8C}"/>
-    <hyperlink ref="K28" r:id="rId53" xr:uid="{AFFE99AD-C3BD-7D47-ADD2-0033AB1BD297}"/>
-    <hyperlink ref="K35" r:id="rId54" xr:uid="{10637FCE-769F-EF46-AFAF-F312278F1225}"/>
+    <hyperlink ref="K24" r:id="rId51" xr:uid="{45D4B454-64FD-E043-9E1E-D98B915DA3C4}"/>
+    <hyperlink ref="K41" r:id="rId52" xr:uid="{592E8301-AD04-6A43-BE2C-DF1DCF4D0C8C}"/>
+    <hyperlink ref="K38" r:id="rId53" xr:uid="{AFFE99AD-C3BD-7D47-ADD2-0033AB1BD297}"/>
+    <hyperlink ref="K8" r:id="rId54" xr:uid="{10637FCE-769F-EF46-AFAF-F312278F1225}"/>
     <hyperlink ref="K69" r:id="rId55" xr:uid="{1E8D6F6E-5279-684F-9870-749B17340F35}"/>
     <hyperlink ref="K80" r:id="rId56" xr:uid="{C19F506D-023C-1247-BE6A-C23960198C51}"/>
-    <hyperlink ref="K5" r:id="rId57" xr:uid="{3E64B722-3690-B44C-ABC4-059D3B71C8D7}"/>
-    <hyperlink ref="K42" r:id="rId58" xr:uid="{50C3436F-19AF-D74F-8E0A-E9F0AEF4EF7F}"/>
-    <hyperlink ref="K19" r:id="rId59" xr:uid="{A5BBD32C-6F92-A842-A00C-8F17A0710E00}"/>
-    <hyperlink ref="K27" r:id="rId60" xr:uid="{117A81C3-427C-DF49-BA81-BE00A024107F}"/>
+    <hyperlink ref="K22" r:id="rId57" xr:uid="{3E64B722-3690-B44C-ABC4-059D3B71C8D7}"/>
+    <hyperlink ref="K46" r:id="rId58" xr:uid="{50C3436F-19AF-D74F-8E0A-E9F0AEF4EF7F}"/>
+    <hyperlink ref="K32" r:id="rId59" xr:uid="{A5BBD32C-6F92-A842-A00C-8F17A0710E00}"/>
+    <hyperlink ref="K37" r:id="rId60" xr:uid="{117A81C3-427C-DF49-BA81-BE00A024107F}"/>
     <hyperlink ref="K57" r:id="rId61" xr:uid="{5E89FA9C-5C01-5342-876F-D8B51FE4E2B8}"/>
     <hyperlink ref="K76" r:id="rId62" xr:uid="{AE06ADB0-CCC6-5E4F-AA64-084B6EC4EDA5}"/>
     <hyperlink ref="K52" r:id="rId63" xr:uid="{C1BBF821-4DC8-5347-B6F0-96939C529BA4}"/>
     <hyperlink ref="K56" r:id="rId64" xr:uid="{990812EE-4D67-A148-8354-137377C29D95}"/>
-    <hyperlink ref="K30" r:id="rId65" xr:uid="{9C8D9D49-3342-1D45-9490-372911350A58}"/>
+    <hyperlink ref="K7" r:id="rId65" xr:uid="{9C8D9D49-3342-1D45-9490-372911350A58}"/>
     <hyperlink ref="K70" r:id="rId66" xr:uid="{EFDE2707-AAFE-A445-930B-DB05A658CF11}"/>
     <hyperlink ref="K75" r:id="rId67" xr:uid="{C4CFA4B9-7F0C-2D48-848B-F4855312250F}"/>
     <hyperlink ref="K78" r:id="rId68" xr:uid="{2C92D437-B811-BA4F-A7A0-ECBD7F90C3E8}"/>
     <hyperlink ref="K83" r:id="rId69" xr:uid="{1DA360B3-3EEC-0B4A-92B2-F41887D4DA99}"/>
-    <hyperlink ref="K7" r:id="rId70" xr:uid="{53707DD5-6AE9-244D-BE8B-768805F672D6}"/>
-    <hyperlink ref="K45" r:id="rId71" xr:uid="{36EBDC68-249C-1C48-AAF4-2B47231ACC4B}"/>
-    <hyperlink ref="K33" r:id="rId72" xr:uid="{A1D0B6A6-8992-754F-A034-0A1E7D5B9BCB}"/>
-    <hyperlink ref="K43" r:id="rId73" xr:uid="{A089F750-0C9E-6945-9649-FC6752762842}"/>
-    <hyperlink ref="K12" r:id="rId74" xr:uid="{DB5E5AED-5451-EE4B-9408-E80763135A0D}"/>
-    <hyperlink ref="K32" r:id="rId75" xr:uid="{54790613-574F-C04B-943E-7BC43E9CE3FE}"/>
-    <hyperlink ref="K46" r:id="rId76" xr:uid="{04799654-C848-244D-A1F9-FAA86321A73F}"/>
-    <hyperlink ref="K39" r:id="rId77" xr:uid="{0EB41F51-36DD-AA40-AA97-D6366DF2ACBF}"/>
-    <hyperlink ref="K22" r:id="rId78" xr:uid="{7DFC2710-EE37-1F4C-A14D-E4C357A34AC5}"/>
-    <hyperlink ref="K15" r:id="rId79" xr:uid="{F62AC8D7-0E4C-8D4A-A393-61AF8AC0EB46}"/>
-    <hyperlink ref="K29" r:id="rId80" xr:uid="{EE4CEA07-2929-A846-98F2-C6C1968C5BD7}"/>
-    <hyperlink ref="K44" r:id="rId81" xr:uid="{0B614C9A-CC57-2C4A-9102-DE5C3F305979}"/>
+    <hyperlink ref="K2" r:id="rId70" xr:uid="{53707DD5-6AE9-244D-BE8B-768805F672D6}"/>
+    <hyperlink ref="K3" r:id="rId71" xr:uid="{36EBDC68-249C-1C48-AAF4-2B47231ACC4B}"/>
+    <hyperlink ref="K4" r:id="rId72" xr:uid="{A1D0B6A6-8992-754F-A034-0A1E7D5B9BCB}"/>
+    <hyperlink ref="K6" r:id="rId73" xr:uid="{A089F750-0C9E-6945-9649-FC6752762842}"/>
+    <hyperlink ref="K9" r:id="rId74" xr:uid="{DB5E5AED-5451-EE4B-9408-E80763135A0D}"/>
+    <hyperlink ref="K10" r:id="rId75" xr:uid="{54790613-574F-C04B-943E-7BC43E9CE3FE}"/>
+    <hyperlink ref="K12" r:id="rId76" xr:uid="{04799654-C848-244D-A1F9-FAA86321A73F}"/>
+    <hyperlink ref="K11" r:id="rId77" xr:uid="{0EB41F51-36DD-AA40-AA97-D6366DF2ACBF}"/>
+    <hyperlink ref="K13" r:id="rId78" xr:uid="{7DFC2710-EE37-1F4C-A14D-E4C357A34AC5}"/>
+    <hyperlink ref="K14" r:id="rId79" xr:uid="{F62AC8D7-0E4C-8D4A-A393-61AF8AC0EB46}"/>
+    <hyperlink ref="K18" r:id="rId80" xr:uid="{EE4CEA07-2929-A846-98F2-C6C1968C5BD7}"/>
+    <hyperlink ref="K19" r:id="rId81" xr:uid="{0B614C9A-CC57-2C4A-9102-DE5C3F305979}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-1405-TVSeries.xlsx
+++ b/db/A7XLK-1405-TVSeries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBF20A5-2F0E-1B4F-83D1-568110CDCEC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E45AA334-6141-9B47-BF10-C3A682ADB524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4500" yWindow="2600" windowWidth="29840" windowHeight="17320" xr2:uid="{BAC94C6D-C196-2D4F-A2F2-89F0A182D671}"/>
+    <workbookView xWindow="380" yWindow="1860" windowWidth="38780" windowHeight="17320" xr2:uid="{BAC94C6D-C196-2D4F-A2F2-89F0A182D671}"/>
   </bookViews>
   <sheets>
     <sheet name="今日電影" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="533">
   <si>
     <t>No</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1741,6 +1741,272 @@
   </si>
   <si>
     <t>https://gimy.app/vod/157161.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A:10/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A:11/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A:14/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A:17/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A:18/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A:20/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A:01/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A:02/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A:03/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A:05/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A:06/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A:07/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A:09/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A:08/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A:19/20, C:01/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A:12/20, C:02/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>121</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>122</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>A:13/20, C:04/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一不小心撿到愛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-122.jpeg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-123.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-124.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-125.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-126.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-127.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-121.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>趙露思 劉特 周峻緯 漆培鑫 李沐宸 劉胤君 張研 賀鵬 宗元圓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/148938.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C:05/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烏鴉小姐與蜥蜴先生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任嘉倫 邢菲 劉芮麟 趙奕歡 駿聲 葛施敏 範湉湉 宣璐 樊治欣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/126501.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C:06/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C:07/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A:04/20, C:08/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A:15/20, C:09/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C:10/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A:16/20, C:11/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我的時代，你的時代</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>胡一天 李一桐 李明德 許樂驍 王安宇 龐瀚辰 王可如 李現 楊紫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>38</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C:12/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/120939.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>原來你是這樣的顧先生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳靖可 嚴智超 郭耘奇 朱丹妮 辛瑞琪 丁嘉文 鍾偉倫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/124287.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C:13/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C:14/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>月光變奏曲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虞書欣 丁禹兮 楊仕澤 馬吟吟 王汀 葉筱瑋 秦沛 朱泳騰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/148939.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C:16/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C:17/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暗戀橘生淮南</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/131503.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">朱顏曼滋 趙順然 沈雨 張亦馳 夢秦 陳泇文 張哲浩 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C:18/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你微笑時很美</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/151793.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>許凱 程瀟 翟瀟聞 姚弛 周翊然 肖凱中 靈超 王若珊 米熱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C:19/20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2134,21 +2400,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C0AA310-9C39-A04D-BB87-9521EAB5B98C}">
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:L90"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
     <col min="2" max="4" width="11.83203125" customWidth="1"/>
     <col min="5" max="5" width="11.83203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="40.83203125" customWidth="1"/>
-    <col min="7" max="7" width="32.33203125" customWidth="1"/>
+    <col min="6" max="6" width="40.6640625" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
     <col min="8" max="8" width="13.5" style="3" customWidth="1"/>
     <col min="9" max="9" width="13.5" style="4" customWidth="1"/>
-    <col min="10" max="10" width="50.6640625" customWidth="1"/>
-    <col min="11" max="11" width="43.83203125" customWidth="1"/>
+    <col min="10" max="10" width="68" style="4" customWidth="1"/>
+    <col min="11" max="11" width="50.6640625" customWidth="1"/>
+    <col min="12" max="12" width="43.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2176,14 +2443,17 @@
       <c r="I1" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="K1" t="s">
         <v>1</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>401</v>
       </c>
@@ -2211,14 +2481,17 @@
       <c r="I2" s="4">
         <v>8.6</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="K2" t="s">
         <v>413</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>402</v>
       </c>
@@ -2246,14 +2519,17 @@
       <c r="I3" s="4">
         <v>8.5</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="K3" t="s">
         <v>414</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
         <v>403</v>
       </c>
@@ -2281,14 +2557,17 @@
       <c r="I4" s="4">
         <v>8.1999999999999993</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="K4" t="s">
         <v>415</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
         <v>76</v>
       </c>
@@ -2316,14 +2595,17 @@
       <c r="I5" s="4">
         <v>8.1</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="K5" t="s">
         <v>41</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
         <v>404</v>
       </c>
@@ -2351,14 +2633,17 @@
       <c r="I6" s="4">
         <v>7.9</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="K6" t="s">
         <v>416</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
         <v>329</v>
       </c>
@@ -2386,14 +2671,17 @@
       <c r="I7" s="4">
         <v>7.8</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="K7" t="s">
         <v>345</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
         <v>318</v>
       </c>
@@ -2421,14 +2709,17 @@
       <c r="I8" s="4">
         <v>7.8</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="K8" t="s">
         <v>337</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="L8" s="2" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
         <v>405</v>
       </c>
@@ -2456,14 +2747,17 @@
       <c r="I9" s="4">
         <v>7.6</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="K9" t="s">
         <v>417</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="L9" s="2" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
         <v>406</v>
       </c>
@@ -2491,16 +2785,19 @@
       <c r="I10" s="4">
         <v>7.6</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="K10" t="s">
         <v>418</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="L10" s="2" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
@@ -2512,30 +2809,33 @@
         <v>291</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>158</v>
+        <v>433</v>
       </c>
       <c r="F11" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="G11" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="H11" s="3">
-        <v>134785</v>
+        <v>52113</v>
       </c>
       <c r="I11" s="4">
         <v>7.5</v>
       </c>
-      <c r="J11" t="s">
-        <v>420</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="J11" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="K11" t="s">
+        <v>419</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
@@ -2547,30 +2847,33 @@
         <v>291</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>433</v>
+        <v>158</v>
       </c>
       <c r="F12" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="G12" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="H12" s="3">
-        <v>52113</v>
+        <v>134785</v>
       </c>
       <c r="I12" s="4">
         <v>7.5</v>
       </c>
-      <c r="J12" t="s">
-        <v>419</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="J12" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="K12" t="s">
+        <v>420</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="1" t="s">
-        <v>409</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
         <v>11</v>
@@ -2582,30 +2885,33 @@
         <v>291</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>452</v>
+        <v>158</v>
       </c>
       <c r="F13" t="s">
-        <v>451</v>
+        <v>157</v>
       </c>
       <c r="G13" t="s">
-        <v>450</v>
+        <v>85</v>
       </c>
       <c r="H13" s="3">
-        <v>1278633</v>
+        <v>2132343</v>
       </c>
       <c r="I13" s="4">
-        <v>7.3</v>
-      </c>
-      <c r="J13" t="s">
-        <v>421</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+        <v>7.4</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="K13" t="s">
+        <v>15</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="1" t="s">
-        <v>410</v>
+        <v>57</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
@@ -2617,30 +2923,33 @@
         <v>291</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>285</v>
+        <v>173</v>
       </c>
       <c r="F14" t="s">
-        <v>455</v>
+        <v>182</v>
       </c>
       <c r="G14" t="s">
-        <v>454</v>
+        <v>94</v>
       </c>
       <c r="H14" s="3">
-        <v>2043804</v>
+        <v>2454774</v>
       </c>
       <c r="I14" s="4">
-        <v>7.2</v>
-      </c>
-      <c r="J14" t="s">
-        <v>422</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+        <v>7.4</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="K14" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="1" t="s">
-        <v>59</v>
+        <v>409</v>
       </c>
       <c r="B15" t="s">
         <v>11</v>
@@ -2652,30 +2961,33 @@
         <v>291</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>158</v>
+        <v>452</v>
       </c>
       <c r="F15" t="s">
-        <v>187</v>
+        <v>451</v>
       </c>
       <c r="G15" t="s">
-        <v>96</v>
+        <v>450</v>
       </c>
       <c r="H15" s="3">
-        <v>1071359</v>
+        <v>1278633</v>
       </c>
       <c r="I15" s="4">
-        <v>7.1</v>
-      </c>
-      <c r="J15" t="s">
-        <v>26</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+        <v>7.3</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="K15" t="s">
+        <v>421</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="1" t="s">
-        <v>50</v>
+        <v>410</v>
       </c>
       <c r="B16" t="s">
         <v>11</v>
@@ -2687,30 +2999,33 @@
         <v>291</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>161</v>
+        <v>285</v>
       </c>
       <c r="F16" t="s">
-        <v>164</v>
+        <v>455</v>
       </c>
       <c r="G16" t="s">
-        <v>88</v>
+        <v>454</v>
       </c>
       <c r="H16" s="3">
-        <v>1028428</v>
+        <v>2043804</v>
       </c>
       <c r="I16" s="4">
-        <v>7.1</v>
-      </c>
-      <c r="J16" t="s">
-        <v>17</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+        <v>7.2</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="K16" t="s">
+        <v>422</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B17" t="s">
         <v>11</v>
@@ -2722,30 +3037,33 @@
         <v>291</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="F17" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="G17" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="H17" s="3">
-        <v>8844170</v>
+        <v>1028428</v>
       </c>
       <c r="I17" s="4">
-        <v>7</v>
-      </c>
-      <c r="J17" t="s">
-        <v>23</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+        <v>7.1</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="K17" t="s">
+        <v>17</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" s="1" t="s">
-        <v>411</v>
+        <v>59</v>
       </c>
       <c r="B18" t="s">
         <v>11</v>
@@ -2757,30 +3075,33 @@
         <v>291</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>459</v>
+        <v>158</v>
       </c>
       <c r="F18" t="s">
-        <v>458</v>
+        <v>187</v>
       </c>
       <c r="G18" t="s">
-        <v>457</v>
+        <v>96</v>
       </c>
       <c r="H18" s="3">
-        <v>785247</v>
+        <v>1071359</v>
       </c>
       <c r="I18" s="4">
-        <v>7</v>
-      </c>
-      <c r="J18" t="s">
-        <v>423</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+        <v>7.1</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="K18" t="s">
+        <v>26</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B19" t="s">
         <v>11</v>
@@ -2792,30 +3113,33 @@
         <v>291</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>433</v>
+        <v>459</v>
       </c>
       <c r="F19" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="G19" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="H19" s="3">
-        <v>89338</v>
+        <v>785247</v>
       </c>
       <c r="I19" s="4">
         <v>7</v>
       </c>
-      <c r="J19" t="s">
-        <v>424</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="J19" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="K19" t="s">
+        <v>423</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" s="1" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="B20" t="s">
         <v>11</v>
@@ -2827,27 +3151,33 @@
         <v>291</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>230</v>
+        <v>179</v>
       </c>
       <c r="F20" t="s">
-        <v>231</v>
+        <v>180</v>
       </c>
       <c r="G20" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="H20" s="3">
-        <v>9760868</v>
-      </c>
-      <c r="J20" t="s">
-        <v>40</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+        <v>8844170</v>
+      </c>
+      <c r="I20" s="4">
+        <v>7</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="K20" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" s="1" t="s">
-        <v>79</v>
+        <v>412</v>
       </c>
       <c r="B21" t="s">
         <v>11</v>
@@ -2859,27 +3189,33 @@
         <v>291</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>189</v>
+        <v>433</v>
       </c>
       <c r="F21" t="s">
-        <v>241</v>
+        <v>462</v>
       </c>
       <c r="G21" t="s">
-        <v>116</v>
+        <v>461</v>
       </c>
       <c r="H21" s="3">
-        <v>6002697</v>
-      </c>
-      <c r="J21" t="s">
-        <v>44</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+        <v>89338</v>
+      </c>
+      <c r="I21" s="4">
+        <v>7</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="K21" t="s">
+        <v>424</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" s="1" t="s">
-        <v>321</v>
+        <v>481</v>
       </c>
       <c r="B22" t="s">
         <v>11</v>
@@ -2891,27 +3227,30 @@
         <v>291</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="F22" t="s">
-        <v>366</v>
+        <v>497</v>
       </c>
       <c r="G22" t="s">
-        <v>303</v>
+        <v>489</v>
       </c>
       <c r="H22" s="3">
-        <v>5150111</v>
-      </c>
-      <c r="J22" t="s">
-        <v>340</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+        <v>1967351</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="K22" t="s">
+        <v>496</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23" s="1" t="s">
-        <v>49</v>
+        <v>482</v>
       </c>
       <c r="B23" t="s">
         <v>11</v>
@@ -2923,30 +3262,33 @@
         <v>291</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="F23" t="s">
-        <v>162</v>
+        <v>501</v>
       </c>
       <c r="G23" t="s">
-        <v>86</v>
+        <v>500</v>
       </c>
       <c r="H23" s="3">
-        <v>2815834</v>
-      </c>
-      <c r="J23" t="s">
-        <v>16</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+        <v>1724953</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="K23" t="s">
+        <v>490</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24" s="1" t="s">
-        <v>315</v>
+        <v>79</v>
       </c>
       <c r="B24" t="s">
-        <v>350</v>
+        <v>11</v>
       </c>
       <c r="C24">
         <v>2021</v>
@@ -2955,27 +3297,30 @@
         <v>291</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>351</v>
+        <v>189</v>
       </c>
       <c r="F24" t="s">
-        <v>352</v>
+        <v>241</v>
       </c>
       <c r="G24" t="s">
-        <v>298</v>
+        <v>116</v>
       </c>
       <c r="H24" s="3">
-        <v>2535509</v>
-      </c>
-      <c r="J24" t="s">
-        <v>334</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+        <v>6002697</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="K24" t="s">
+        <v>44</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25" s="1" t="s">
-        <v>57</v>
+        <v>323</v>
       </c>
       <c r="B25" t="s">
         <v>11</v>
@@ -2990,24 +3335,27 @@
         <v>173</v>
       </c>
       <c r="F25" t="s">
-        <v>182</v>
+        <v>372</v>
       </c>
       <c r="G25" t="s">
-        <v>94</v>
+        <v>305</v>
       </c>
       <c r="H25" s="3">
-        <v>2454774</v>
-      </c>
-      <c r="J25" t="s">
-        <v>24</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+        <v>1771888</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="K25" t="s">
+        <v>341</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26" s="1" t="s">
-        <v>54</v>
+        <v>483</v>
       </c>
       <c r="B26" t="s">
         <v>11</v>
@@ -3019,27 +3367,30 @@
         <v>291</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>173</v>
+        <v>511</v>
       </c>
       <c r="F26" t="s">
-        <v>174</v>
+        <v>510</v>
       </c>
       <c r="G26" t="s">
-        <v>91</v>
+        <v>509</v>
       </c>
       <c r="H26" s="3">
-        <v>2378245</v>
-      </c>
-      <c r="J26" t="s">
-        <v>21</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+        <v>1646706</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="K26" t="s">
+        <v>491</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27" s="1" t="s">
-        <v>7</v>
+        <v>484</v>
       </c>
       <c r="B27" t="s">
         <v>11</v>
@@ -3051,27 +3402,30 @@
         <v>291</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>158</v>
+        <v>516</v>
       </c>
       <c r="F27" t="s">
-        <v>157</v>
+        <v>515</v>
       </c>
       <c r="G27" t="s">
-        <v>85</v>
+        <v>514</v>
       </c>
       <c r="H27" s="3">
-        <v>2132343</v>
-      </c>
-      <c r="J27" t="s">
-        <v>15</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+        <v>1138386</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="K27" t="s">
+        <v>492</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
       <c r="A28" s="1" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="B28" t="s">
         <v>11</v>
@@ -3083,27 +3437,30 @@
         <v>291</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F28" t="s">
-        <v>171</v>
+        <v>262</v>
       </c>
       <c r="G28" t="s">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="H28" s="3">
-        <v>2059245</v>
-      </c>
-      <c r="J28" t="s">
-        <v>20</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
+        <v>1560320</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="K28" t="s">
+        <v>147</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29" s="1" t="s">
-        <v>55</v>
+        <v>485</v>
       </c>
       <c r="B29" t="s">
         <v>11</v>
@@ -3115,27 +3472,30 @@
         <v>291</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="F29" t="s">
-        <v>177</v>
+        <v>521</v>
       </c>
       <c r="G29" t="s">
-        <v>92</v>
+        <v>520</v>
       </c>
       <c r="H29" s="3">
-        <v>1960230</v>
-      </c>
-      <c r="J29" t="s">
-        <v>22</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
+        <v>2140583</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="K29" t="s">
+        <v>493</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30" s="1" t="s">
-        <v>136</v>
+        <v>60</v>
       </c>
       <c r="B30" t="s">
         <v>11</v>
@@ -3147,27 +3507,30 @@
         <v>291</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="F30" t="s">
-        <v>264</v>
+        <v>190</v>
       </c>
       <c r="G30" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="H30" s="3">
-        <v>1845243</v>
-      </c>
-      <c r="J30" t="s">
-        <v>148</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+        <v>1796008</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="K30" t="s">
+        <v>27</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31" s="1" t="s">
-        <v>60</v>
+        <v>486</v>
       </c>
       <c r="B31" t="s">
         <v>11</v>
@@ -3179,27 +3542,30 @@
         <v>291</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="F31" t="s">
-        <v>190</v>
+        <v>527</v>
       </c>
       <c r="G31" t="s">
-        <v>97</v>
+        <v>525</v>
       </c>
       <c r="H31" s="3">
-        <v>1796008</v>
-      </c>
-      <c r="J31" t="s">
-        <v>27</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+        <v>6319</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="K31" t="s">
+        <v>494</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32" s="1" t="s">
-        <v>323</v>
+        <v>487</v>
       </c>
       <c r="B32" t="s">
         <v>11</v>
@@ -3211,27 +3577,30 @@
         <v>291</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="F32" t="s">
-        <v>372</v>
+        <v>531</v>
       </c>
       <c r="G32" t="s">
-        <v>305</v>
+        <v>529</v>
       </c>
       <c r="H32" s="3">
-        <v>1771888</v>
-      </c>
-      <c r="J32" t="s">
-        <v>341</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
+        <v>3326331</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="K32" t="s">
+        <v>495</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
       <c r="A33" s="1" t="s">
-        <v>143</v>
+        <v>75</v>
       </c>
       <c r="B33" t="s">
         <v>11</v>
@@ -3243,27 +3612,27 @@
         <v>291</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>282</v>
+        <v>230</v>
       </c>
       <c r="F33" t="s">
-        <v>281</v>
+        <v>231</v>
       </c>
       <c r="G33" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="H33" s="3">
-        <v>1758290</v>
-      </c>
-      <c r="J33" t="s">
-        <v>155</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
+        <v>9760868</v>
+      </c>
+      <c r="K33" t="s">
+        <v>40</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
       <c r="A34" s="1" t="s">
-        <v>135</v>
+        <v>321</v>
       </c>
       <c r="B34" t="s">
         <v>11</v>
@@ -3275,27 +3644,27 @@
         <v>291</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F34" t="s">
-        <v>262</v>
+        <v>366</v>
       </c>
       <c r="G34" t="s">
-        <v>123</v>
+        <v>303</v>
       </c>
       <c r="H34" s="3">
-        <v>1560320</v>
-      </c>
-      <c r="J34" t="s">
-        <v>147</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
+        <v>5150111</v>
+      </c>
+      <c r="K34" t="s">
+        <v>340</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
       <c r="A35" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B35" t="s">
         <v>11</v>
@@ -3307,30 +3676,30 @@
         <v>291</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="F35" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="G35" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H35" s="3">
-        <v>1212038</v>
-      </c>
-      <c r="J35" t="s">
-        <v>25</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
+        <v>2815834</v>
+      </c>
+      <c r="K35" t="s">
+        <v>16</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
       <c r="A36" s="1" t="s">
-        <v>52</v>
+        <v>315</v>
       </c>
       <c r="B36" t="s">
-        <v>11</v>
+        <v>350</v>
       </c>
       <c r="C36">
         <v>2021</v>
@@ -3339,24 +3708,27 @@
         <v>291</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>161</v>
+        <v>351</v>
+      </c>
+      <c r="F36" t="s">
+        <v>352</v>
       </c>
       <c r="G36" t="s">
-        <v>89</v>
+        <v>298</v>
       </c>
       <c r="H36" s="3">
-        <v>976802</v>
-      </c>
-      <c r="J36" t="s">
-        <v>19</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
+        <v>2535509</v>
+      </c>
+      <c r="K36" t="s">
+        <v>334</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
       <c r="A37" s="1" t="s">
-        <v>324</v>
+        <v>54</v>
       </c>
       <c r="B37" t="s">
         <v>11</v>
@@ -3371,24 +3743,24 @@
         <v>173</v>
       </c>
       <c r="F37" t="s">
-        <v>375</v>
+        <v>174</v>
       </c>
       <c r="G37" t="s">
-        <v>306</v>
+        <v>91</v>
       </c>
       <c r="H37" s="3">
-        <v>954238</v>
-      </c>
-      <c r="J37" t="s">
-        <v>374</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
+        <v>2378245</v>
+      </c>
+      <c r="K37" t="s">
+        <v>21</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
       <c r="A38" s="1" t="s">
-        <v>317</v>
+        <v>53</v>
       </c>
       <c r="B38" t="s">
         <v>11</v>
@@ -3400,27 +3772,27 @@
         <v>291</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>358</v>
+        <v>170</v>
       </c>
       <c r="F38" t="s">
-        <v>357</v>
+        <v>171</v>
       </c>
       <c r="G38" t="s">
-        <v>300</v>
+        <v>90</v>
       </c>
       <c r="H38" s="3">
-        <v>795715</v>
-      </c>
-      <c r="J38" t="s">
-        <v>336</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11">
+        <v>2059245</v>
+      </c>
+      <c r="K38" t="s">
+        <v>20</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
       <c r="A39" s="1" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="B39" t="s">
         <v>11</v>
@@ -3432,30 +3804,30 @@
         <v>291</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="F39" t="s">
-        <v>212</v>
+        <v>177</v>
       </c>
       <c r="G39" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="H39" s="3">
-        <v>653514</v>
-      </c>
-      <c r="J39" t="s">
-        <v>34</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
+        <v>1960230</v>
+      </c>
+      <c r="K39" t="s">
+        <v>22</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
       <c r="A40" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B40" t="s">
-        <v>224</v>
+        <v>11</v>
       </c>
       <c r="C40">
         <v>2021</v>
@@ -3464,27 +3836,27 @@
         <v>291</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>268</v>
+        <v>158</v>
       </c>
       <c r="F40" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="G40" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H40" s="3">
-        <v>459883</v>
-      </c>
-      <c r="J40" t="s">
-        <v>150</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
+        <v>1845243</v>
+      </c>
+      <c r="K40" t="s">
+        <v>148</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
       <c r="A41" s="1" t="s">
-        <v>316</v>
+        <v>143</v>
       </c>
       <c r="B41" t="s">
         <v>11</v>
@@ -3496,27 +3868,27 @@
         <v>291</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>355</v>
+        <v>282</v>
       </c>
       <c r="F41" t="s">
-        <v>354</v>
+        <v>281</v>
       </c>
       <c r="G41" t="s">
-        <v>299</v>
+        <v>131</v>
       </c>
       <c r="H41" s="3">
-        <v>377267</v>
-      </c>
-      <c r="J41" t="s">
-        <v>335</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11">
+        <v>1758290</v>
+      </c>
+      <c r="K41" t="s">
+        <v>155</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
       <c r="A42" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B42" t="s">
         <v>11</v>
@@ -3528,27 +3900,27 @@
         <v>291</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="F42" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="G42" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H42" s="3">
-        <v>303763</v>
-      </c>
-      <c r="J42" t="s">
-        <v>18</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
+        <v>1212038</v>
+      </c>
+      <c r="K42" t="s">
+        <v>25</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
       <c r="A43" s="1" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="B43" t="s">
         <v>11</v>
@@ -3559,28 +3931,25 @@
       <c r="D43" t="s">
         <v>291</v>
       </c>
-      <c r="E43" s="1">
-        <v>-10</v>
-      </c>
-      <c r="F43" t="s">
-        <v>13</v>
+      <c r="E43" s="1" t="s">
+        <v>161</v>
       </c>
       <c r="G43" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="H43" s="3">
-        <v>200612</v>
-      </c>
-      <c r="J43" t="s">
-        <v>14</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
+        <v>976802</v>
+      </c>
+      <c r="K43" t="s">
+        <v>19</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
       <c r="A44" s="1" t="s">
-        <v>61</v>
+        <v>324</v>
       </c>
       <c r="B44" t="s">
         <v>11</v>
@@ -3592,27 +3961,27 @@
         <v>291</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="F44" t="s">
-        <v>193</v>
+        <v>375</v>
       </c>
       <c r="G44" t="s">
-        <v>98</v>
+        <v>306</v>
       </c>
       <c r="H44" s="3">
-        <v>132204</v>
-      </c>
-      <c r="J44" t="s">
-        <v>288</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
+        <v>954238</v>
+      </c>
+      <c r="K44" t="s">
+        <v>374</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
       <c r="A45" s="1" t="s">
-        <v>67</v>
+        <v>317</v>
       </c>
       <c r="B45" t="s">
         <v>11</v>
@@ -3624,27 +3993,27 @@
         <v>291</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>195</v>
+        <v>358</v>
       </c>
       <c r="F45" t="s">
-        <v>210</v>
+        <v>357</v>
       </c>
       <c r="G45" t="s">
-        <v>104</v>
+        <v>300</v>
       </c>
       <c r="H45" s="3">
-        <v>121479</v>
-      </c>
-      <c r="J45" t="s">
-        <v>33</v>
-      </c>
-      <c r="K45" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11">
+        <v>795715</v>
+      </c>
+      <c r="K45" t="s">
+        <v>336</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
       <c r="A46" s="1" t="s">
-        <v>322</v>
+        <v>68</v>
       </c>
       <c r="B46" t="s">
         <v>11</v>
@@ -3656,30 +4025,30 @@
         <v>291</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>158</v>
+        <v>198</v>
       </c>
       <c r="F46" t="s">
-        <v>370</v>
+        <v>212</v>
       </c>
       <c r="G46" t="s">
-        <v>304</v>
+        <v>105</v>
       </c>
       <c r="H46" s="3">
-        <v>98231</v>
-      </c>
-      <c r="J46" t="s">
-        <v>369</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11">
+        <v>653514</v>
+      </c>
+      <c r="K46" t="s">
+        <v>34</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
       <c r="A47" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B47" t="s">
-        <v>11</v>
+        <v>224</v>
       </c>
       <c r="C47">
         <v>2021</v>
@@ -3688,315 +4057,315 @@
         <v>291</v>
       </c>
       <c r="E47" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="F47" t="s">
+        <v>269</v>
+      </c>
+      <c r="G47" t="s">
+        <v>126</v>
+      </c>
+      <c r="H47" s="3">
+        <v>459883</v>
+      </c>
+      <c r="K47" t="s">
+        <v>150</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="A48" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B48" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48">
+        <v>2021</v>
+      </c>
+      <c r="D48" t="s">
+        <v>291</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="F48" t="s">
+        <v>354</v>
+      </c>
+      <c r="G48" t="s">
+        <v>299</v>
+      </c>
+      <c r="H48" s="3">
+        <v>377267</v>
+      </c>
+      <c r="K48" t="s">
+        <v>335</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B49" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49">
+        <v>2021</v>
+      </c>
+      <c r="D49" t="s">
+        <v>291</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F49" t="s">
+        <v>168</v>
+      </c>
+      <c r="G49" t="s">
+        <v>87</v>
+      </c>
+      <c r="H49" s="3">
+        <v>303763</v>
+      </c>
+      <c r="K49" t="s">
+        <v>18</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B50" t="s">
+        <v>11</v>
+      </c>
+      <c r="C50">
+        <v>2021</v>
+      </c>
+      <c r="D50" t="s">
+        <v>291</v>
+      </c>
+      <c r="E50" s="1">
+        <v>-10</v>
+      </c>
+      <c r="F50" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50" t="s">
+        <v>10</v>
+      </c>
+      <c r="H50" s="3">
+        <v>200612</v>
+      </c>
+      <c r="K50" t="s">
+        <v>14</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51">
+        <v>2021</v>
+      </c>
+      <c r="D51" t="s">
+        <v>291</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F51" t="s">
+        <v>193</v>
+      </c>
+      <c r="G51" t="s">
+        <v>98</v>
+      </c>
+      <c r="H51" s="3">
+        <v>132204</v>
+      </c>
+      <c r="K51" t="s">
+        <v>288</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B52" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52">
+        <v>2021</v>
+      </c>
+      <c r="D52" t="s">
+        <v>291</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F52" t="s">
+        <v>210</v>
+      </c>
+      <c r="G52" t="s">
+        <v>104</v>
+      </c>
+      <c r="H52" s="3">
+        <v>121479</v>
+      </c>
+      <c r="K52" t="s">
+        <v>33</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B53" t="s">
+        <v>11</v>
+      </c>
+      <c r="C53">
+        <v>2021</v>
+      </c>
+      <c r="D53" t="s">
+        <v>291</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F53" t="s">
+        <v>370</v>
+      </c>
+      <c r="G53" t="s">
+        <v>304</v>
+      </c>
+      <c r="H53" s="3">
+        <v>98231</v>
+      </c>
+      <c r="K53" t="s">
+        <v>369</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
+      <c r="A54" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B54" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54">
+        <v>2021</v>
+      </c>
+      <c r="D54" t="s">
+        <v>291</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F54" t="s">
         <v>266</v>
       </c>
-      <c r="G47" t="s">
+      <c r="G54" t="s">
         <v>125</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H54" s="3">
         <v>4524</v>
       </c>
-      <c r="J47" t="s">
+      <c r="K54" t="s">
         <v>149</v>
       </c>
-      <c r="K47" s="2" t="s">
+      <c r="L54" s="2" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
-      <c r="A48" s="1" t="s">
+    <row r="55" spans="1:12">
+      <c r="A55" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B48" t="s">
-        <v>11</v>
-      </c>
-      <c r="C48">
+      <c r="B55" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55">
         <v>2020</v>
-      </c>
-      <c r="D48" t="s">
-        <v>292</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="F48" t="s">
-        <v>196</v>
-      </c>
-      <c r="G48" t="s">
-        <v>99</v>
-      </c>
-      <c r="H48" s="3">
-        <v>7733587</v>
-      </c>
-      <c r="J48" t="s">
-        <v>28</v>
-      </c>
-      <c r="K48" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11">
-      <c r="A49" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B49" t="s">
-        <v>11</v>
-      </c>
-      <c r="C49">
-        <v>2018</v>
-      </c>
-      <c r="D49" t="s">
-        <v>292</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="F49" t="s">
-        <v>252</v>
-      </c>
-      <c r="G49" t="s">
-        <v>119</v>
-      </c>
-      <c r="H49" s="3">
-        <v>5275870</v>
-      </c>
-      <c r="J49" t="s">
-        <v>47</v>
-      </c>
-      <c r="K49" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
-      <c r="A50" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B50" t="s">
-        <v>11</v>
-      </c>
-      <c r="C50">
-        <v>2019</v>
-      </c>
-      <c r="D50" t="s">
-        <v>292</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="F50" t="s">
-        <v>243</v>
-      </c>
-      <c r="G50" t="s">
-        <v>117</v>
-      </c>
-      <c r="H50" s="3">
-        <v>5265895</v>
-      </c>
-      <c r="J50" t="s">
-        <v>45</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11">
-      <c r="A51" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B51" t="s">
-        <v>11</v>
-      </c>
-      <c r="C51">
-        <v>2018</v>
-      </c>
-      <c r="D51" t="s">
-        <v>292</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="F51" t="s">
-        <v>273</v>
-      </c>
-      <c r="G51" t="s">
-        <v>128</v>
-      </c>
-      <c r="H51" s="3">
-        <v>4674495</v>
-      </c>
-      <c r="J51" t="s">
-        <v>152</v>
-      </c>
-      <c r="K51" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11">
-      <c r="A52" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="B52" t="s">
-        <v>11</v>
-      </c>
-      <c r="C52">
-        <v>2020</v>
-      </c>
-      <c r="D52" t="s">
-        <v>292</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="F52" t="s">
-        <v>383</v>
-      </c>
-      <c r="G52" t="s">
-        <v>308</v>
-      </c>
-      <c r="H52" s="3">
-        <v>4655514</v>
-      </c>
-      <c r="J52" t="s">
-        <v>344</v>
-      </c>
-      <c r="K52" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11">
-      <c r="A53" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B53" t="s">
-        <v>11</v>
-      </c>
-      <c r="C53">
-        <v>2018</v>
-      </c>
-      <c r="D53" t="s">
-        <v>292</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="F53" t="s">
-        <v>215</v>
-      </c>
-      <c r="G53" t="s">
-        <v>106</v>
-      </c>
-      <c r="H53" s="3">
-        <v>4141267</v>
-      </c>
-      <c r="J53" t="s">
-        <v>35</v>
-      </c>
-      <c r="K53" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11">
-      <c r="A54" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B54" t="s">
-        <v>11</v>
-      </c>
-      <c r="C54">
-        <v>2019</v>
-      </c>
-      <c r="D54" t="s">
-        <v>292</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="F54" t="s">
-        <v>208</v>
-      </c>
-      <c r="G54" t="s">
-        <v>103</v>
-      </c>
-      <c r="H54" s="3">
-        <v>2991300</v>
-      </c>
-      <c r="J54" t="s">
-        <v>32</v>
-      </c>
-      <c r="K54" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11">
-      <c r="A55" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B55" t="s">
-        <v>224</v>
-      </c>
-      <c r="C55">
-        <v>2019</v>
       </c>
       <c r="D55" t="s">
         <v>292</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>222</v>
+        <v>195</v>
       </c>
       <c r="F55" t="s">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="G55" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="H55" s="3">
-        <v>2563754</v>
-      </c>
-      <c r="J55" t="s">
-        <v>289</v>
-      </c>
-      <c r="K55" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11">
+        <v>7733587</v>
+      </c>
+      <c r="K55" t="s">
+        <v>28</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
       <c r="A56" s="1" t="s">
-        <v>328</v>
+        <v>83</v>
       </c>
       <c r="B56" t="s">
         <v>11</v>
       </c>
       <c r="C56">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="D56" t="s">
         <v>292</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>387</v>
+        <v>253</v>
       </c>
       <c r="F56" t="s">
-        <v>386</v>
+        <v>252</v>
       </c>
       <c r="G56" t="s">
-        <v>309</v>
+        <v>119</v>
       </c>
       <c r="H56" s="3">
-        <v>2400663</v>
-      </c>
-      <c r="J56" t="s">
-        <v>385</v>
-      </c>
-      <c r="K56" s="2" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11">
+        <v>5275870</v>
+      </c>
+      <c r="K56" t="s">
+        <v>47</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
       <c r="A57" s="1" t="s">
-        <v>325</v>
+        <v>80</v>
       </c>
       <c r="B57" t="s">
         <v>11</v>
@@ -4008,27 +4377,27 @@
         <v>292</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>379</v>
+        <v>244</v>
       </c>
       <c r="F57" t="s">
-        <v>378</v>
+        <v>243</v>
       </c>
       <c r="G57" t="s">
-        <v>377</v>
+        <v>117</v>
       </c>
       <c r="H57" s="3">
-        <v>2340742</v>
-      </c>
-      <c r="J57" t="s">
-        <v>342</v>
-      </c>
-      <c r="K57" s="2" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11">
+        <v>5265895</v>
+      </c>
+      <c r="K57" t="s">
+        <v>45</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12">
       <c r="A58" s="1" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B58" t="s">
         <v>11</v>
@@ -4040,283 +4409,283 @@
         <v>292</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="F58" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="G58" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="H58" s="3">
-        <v>1265188</v>
-      </c>
-      <c r="J58" t="s">
-        <v>145</v>
+        <v>4674495</v>
       </c>
       <c r="K58" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11">
+        <v>152</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12">
       <c r="A59" s="1" t="s">
-        <v>84</v>
+        <v>327</v>
       </c>
       <c r="B59" t="s">
         <v>11</v>
       </c>
       <c r="C59">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="D59" t="s">
         <v>292</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>230</v>
+        <v>158</v>
       </c>
       <c r="F59" t="s">
-        <v>255</v>
+        <v>383</v>
       </c>
       <c r="G59" t="s">
-        <v>120</v>
+        <v>308</v>
       </c>
       <c r="H59" s="3">
-        <v>1259285</v>
-      </c>
-      <c r="J59" t="s">
-        <v>48</v>
-      </c>
-      <c r="K59" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11">
+        <v>4655514</v>
+      </c>
+      <c r="K59" t="s">
+        <v>344</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12">
       <c r="A60" s="1" t="s">
-        <v>144</v>
+        <v>69</v>
       </c>
       <c r="B60" t="s">
         <v>11</v>
       </c>
       <c r="C60">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="D60" t="s">
         <v>292</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>285</v>
+        <v>214</v>
       </c>
       <c r="F60" t="s">
-        <v>284</v>
+        <v>215</v>
       </c>
       <c r="G60" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="H60" s="3">
-        <v>1218509</v>
-      </c>
-      <c r="J60" t="s">
-        <v>156</v>
-      </c>
-      <c r="K60" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11">
+        <v>4141267</v>
+      </c>
+      <c r="K60" t="s">
+        <v>35</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12">
       <c r="A61" s="1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B61" t="s">
         <v>11</v>
       </c>
       <c r="C61">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="D61" t="s">
         <v>292</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F61" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="G61" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="H61" s="3">
-        <v>947291</v>
-      </c>
-      <c r="J61" t="s">
-        <v>38</v>
-      </c>
-      <c r="K61" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11">
+        <v>2991300</v>
+      </c>
+      <c r="K61" t="s">
+        <v>32</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12">
       <c r="A62" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B62" t="s">
-        <v>11</v>
+        <v>224</v>
       </c>
       <c r="C62">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="D62" t="s">
         <v>292</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="F62" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="G62" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="H62" s="3">
-        <v>802315</v>
-      </c>
-      <c r="J62" t="s">
-        <v>43</v>
-      </c>
-      <c r="K62" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11">
+        <v>2563754</v>
+      </c>
+      <c r="K62" t="s">
+        <v>289</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12">
       <c r="A63" s="1" t="s">
-        <v>70</v>
+        <v>328</v>
       </c>
       <c r="B63" t="s">
         <v>11</v>
       </c>
       <c r="C63">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="D63" t="s">
         <v>292</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>217</v>
+        <v>387</v>
       </c>
       <c r="F63" t="s">
-        <v>218</v>
+        <v>386</v>
       </c>
       <c r="G63" t="s">
-        <v>107</v>
+        <v>309</v>
       </c>
       <c r="H63" s="3">
-        <v>617188</v>
-      </c>
-      <c r="J63" t="s">
-        <v>36</v>
-      </c>
-      <c r="K63" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11">
+        <v>2400663</v>
+      </c>
+      <c r="K63" t="s">
+        <v>385</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12">
       <c r="A64" s="1" t="s">
-        <v>71</v>
+        <v>325</v>
       </c>
       <c r="B64" t="s">
         <v>11</v>
       </c>
       <c r="C64">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D64" t="s">
         <v>292</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>189</v>
+        <v>379</v>
       </c>
       <c r="F64" t="s">
-        <v>220</v>
+        <v>378</v>
       </c>
       <c r="G64" t="s">
-        <v>108</v>
+        <v>377</v>
       </c>
       <c r="H64" s="3">
-        <v>613506</v>
-      </c>
-      <c r="J64" t="s">
-        <v>37</v>
-      </c>
-      <c r="K64" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11">
+        <v>2340742</v>
+      </c>
+      <c r="K64" t="s">
+        <v>342</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12">
       <c r="A65" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B65" t="s">
         <v>11</v>
       </c>
       <c r="C65">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D65" t="s">
         <v>292</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="F65" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G65" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H65" s="3">
-        <v>587879</v>
-      </c>
-      <c r="J65" t="s">
-        <v>146</v>
-      </c>
-      <c r="K65" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11">
+        <v>1265188</v>
+      </c>
+      <c r="K65" t="s">
+        <v>145</v>
+      </c>
+      <c r="L65" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12">
       <c r="A66" s="1" t="s">
-        <v>293</v>
+        <v>84</v>
       </c>
       <c r="B66" t="s">
         <v>11</v>
       </c>
       <c r="C66">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D66" t="s">
         <v>292</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="F66" t="s">
-        <v>295</v>
+        <v>255</v>
       </c>
       <c r="G66" t="s">
-        <v>294</v>
+        <v>120</v>
       </c>
       <c r="H66" s="3">
-        <v>562667</v>
-      </c>
-      <c r="J66" t="s">
-        <v>297</v>
-      </c>
-      <c r="K66" s="2" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11">
+        <v>1259285</v>
+      </c>
+      <c r="K66" t="s">
+        <v>48</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12">
       <c r="A67" s="1" t="s">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="B67" t="s">
         <v>11</v>
@@ -4328,219 +4697,219 @@
         <v>292</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>195</v>
+        <v>285</v>
       </c>
       <c r="F67" t="s">
-        <v>250</v>
+        <v>284</v>
       </c>
       <c r="G67" t="s">
-        <v>249</v>
+        <v>132</v>
       </c>
       <c r="H67" s="3">
-        <v>552739</v>
-      </c>
-      <c r="J67" t="s">
-        <v>46</v>
-      </c>
-      <c r="K67" s="2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11">
+        <v>1218509</v>
+      </c>
+      <c r="K67" t="s">
+        <v>156</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12">
       <c r="A68" s="1" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B68" t="s">
         <v>11</v>
       </c>
       <c r="C68">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="D68" t="s">
         <v>292</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
       <c r="F68" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="G68" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="H68" s="3">
-        <v>517958</v>
-      </c>
-      <c r="J68" t="s">
-        <v>290</v>
-      </c>
-      <c r="K68" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11">
+        <v>947291</v>
+      </c>
+      <c r="K68" t="s">
+        <v>38</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12">
       <c r="A69" s="1" t="s">
-        <v>319</v>
+        <v>78</v>
       </c>
       <c r="B69" t="s">
         <v>11</v>
       </c>
       <c r="C69">
-        <v>2020</v>
+        <v>2011</v>
       </c>
       <c r="D69" t="s">
         <v>292</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
       <c r="F69" t="s">
-        <v>363</v>
+        <v>238</v>
       </c>
       <c r="G69" t="s">
-        <v>362</v>
+        <v>115</v>
       </c>
       <c r="H69" s="3">
-        <v>483734</v>
-      </c>
-      <c r="J69" t="s">
-        <v>338</v>
-      </c>
-      <c r="K69" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11">
+        <v>802315</v>
+      </c>
+      <c r="K69" t="s">
+        <v>43</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12">
       <c r="A70" s="1" t="s">
-        <v>330</v>
+        <v>70</v>
       </c>
       <c r="B70" t="s">
         <v>11</v>
       </c>
       <c r="C70">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D70" t="s">
         <v>292</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="F70" t="s">
-        <v>391</v>
+        <v>218</v>
       </c>
       <c r="G70" t="s">
-        <v>311</v>
+        <v>107</v>
       </c>
       <c r="H70" s="3">
-        <v>470562</v>
-      </c>
-      <c r="J70" t="s">
-        <v>346</v>
-      </c>
-      <c r="K70" s="2" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11">
+        <v>617188</v>
+      </c>
+      <c r="K70" t="s">
+        <v>36</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12">
       <c r="A71" s="1" t="s">
-        <v>142</v>
+        <v>71</v>
       </c>
       <c r="B71" t="s">
         <v>11</v>
       </c>
       <c r="C71">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D71" t="s">
         <v>292</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>277</v>
+        <v>189</v>
       </c>
       <c r="F71" t="s">
-        <v>279</v>
+        <v>220</v>
       </c>
       <c r="G71" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="H71" s="3">
-        <v>349359</v>
-      </c>
-      <c r="J71" t="s">
-        <v>154</v>
-      </c>
-      <c r="K71" s="2" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11">
+        <v>613506</v>
+      </c>
+      <c r="K71" t="s">
+        <v>37</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12">
       <c r="A72" s="1" t="s">
-        <v>64</v>
+        <v>134</v>
       </c>
       <c r="B72" t="s">
         <v>11</v>
       </c>
       <c r="C72">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="D72" t="s">
         <v>292</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>202</v>
+        <v>247</v>
       </c>
       <c r="F72" t="s">
-        <v>201</v>
+        <v>260</v>
       </c>
       <c r="G72" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="H72" s="3">
-        <v>290313</v>
-      </c>
-      <c r="J72" t="s">
-        <v>30</v>
-      </c>
-      <c r="K72" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11">
+        <v>587879</v>
+      </c>
+      <c r="K72" t="s">
+        <v>146</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12">
       <c r="A73" s="1" t="s">
-        <v>65</v>
+        <v>293</v>
       </c>
       <c r="B73" t="s">
         <v>11</v>
       </c>
       <c r="C73">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D73" t="s">
         <v>292</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F73" t="s">
-        <v>205</v>
+        <v>295</v>
       </c>
       <c r="G73" t="s">
-        <v>102</v>
+        <v>294</v>
       </c>
       <c r="H73" s="3">
-        <v>243599</v>
-      </c>
-      <c r="J73" t="s">
-        <v>31</v>
-      </c>
-      <c r="K73" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11">
+        <v>562667</v>
+      </c>
+      <c r="K73" t="s">
+        <v>297</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12">
       <c r="A74" s="1" t="s">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="B74" t="s">
         <v>11</v>
@@ -4552,33 +4921,33 @@
         <v>292</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F74" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="G74" t="s">
-        <v>127</v>
+        <v>249</v>
       </c>
       <c r="H74" s="3">
-        <v>189629</v>
-      </c>
-      <c r="J74" t="s">
-        <v>151</v>
-      </c>
-      <c r="K74" s="2" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11">
+        <v>552739</v>
+      </c>
+      <c r="K74" t="s">
+        <v>46</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12">
       <c r="A75" s="1" t="s">
-        <v>331</v>
+        <v>81</v>
       </c>
       <c r="B75" t="s">
         <v>11</v>
       </c>
       <c r="C75">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D75" t="s">
         <v>292</v>
@@ -4587,120 +4956,120 @@
         <v>247</v>
       </c>
       <c r="F75" t="s">
-        <v>393</v>
+        <v>246</v>
       </c>
       <c r="G75" t="s">
-        <v>312</v>
+        <v>118</v>
       </c>
       <c r="H75" s="3">
-        <v>154914</v>
-      </c>
-      <c r="J75" t="s">
-        <v>347</v>
-      </c>
-      <c r="K75" s="2" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11">
+        <v>517958</v>
+      </c>
+      <c r="K75" t="s">
+        <v>290</v>
+      </c>
+      <c r="L75" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12">
       <c r="A76" s="1" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B76" t="s">
         <v>11</v>
       </c>
       <c r="C76">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="D76" t="s">
         <v>292</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="F76" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="G76" t="s">
-        <v>307</v>
+        <v>362</v>
       </c>
       <c r="H76" s="3">
-        <v>147091</v>
-      </c>
-      <c r="J76" t="s">
-        <v>343</v>
-      </c>
-      <c r="K76" s="2" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11">
+        <v>483734</v>
+      </c>
+      <c r="K76" t="s">
+        <v>338</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12">
       <c r="A77" s="1" t="s">
-        <v>63</v>
+        <v>330</v>
       </c>
       <c r="B77" t="s">
         <v>11</v>
       </c>
       <c r="C77">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="D77" t="s">
         <v>292</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="F77" t="s">
-        <v>199</v>
+        <v>391</v>
       </c>
       <c r="G77" t="s">
-        <v>100</v>
+        <v>311</v>
       </c>
       <c r="H77" s="3">
-        <v>136424</v>
-      </c>
-      <c r="J77" t="s">
-        <v>29</v>
-      </c>
-      <c r="K77" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11">
+        <v>470562</v>
+      </c>
+      <c r="K77" t="s">
+        <v>346</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12">
       <c r="A78" s="1" t="s">
-        <v>333</v>
+        <v>142</v>
       </c>
       <c r="B78" t="s">
         <v>11</v>
       </c>
       <c r="C78">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="D78" t="s">
         <v>292</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>158</v>
+        <v>277</v>
       </c>
       <c r="F78" t="s">
-        <v>397</v>
+        <v>279</v>
       </c>
       <c r="G78" t="s">
-        <v>314</v>
+        <v>130</v>
       </c>
       <c r="H78" s="3">
-        <v>136234</v>
-      </c>
-      <c r="J78" t="s">
-        <v>349</v>
-      </c>
-      <c r="K78" s="2" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11">
+        <v>349359</v>
+      </c>
+      <c r="K78" t="s">
+        <v>154</v>
+      </c>
+      <c r="L78" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12">
       <c r="A79" s="1" t="s">
-        <v>141</v>
+        <v>64</v>
       </c>
       <c r="B79" t="s">
         <v>11</v>
@@ -4712,59 +5081,59 @@
         <v>292</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>277</v>
+        <v>202</v>
       </c>
       <c r="F79" t="s">
-        <v>276</v>
+        <v>201</v>
       </c>
       <c r="G79" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="H79" s="3">
-        <v>99365</v>
-      </c>
-      <c r="J79" t="s">
-        <v>153</v>
-      </c>
-      <c r="K79" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11">
+        <v>290313</v>
+      </c>
+      <c r="K79" t="s">
+        <v>30</v>
+      </c>
+      <c r="L79" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12">
       <c r="A80" s="1" t="s">
-        <v>320</v>
+        <v>65</v>
       </c>
       <c r="B80" t="s">
         <v>11</v>
       </c>
       <c r="C80">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D80" t="s">
         <v>292</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
       <c r="F80" t="s">
-        <v>367</v>
+        <v>205</v>
       </c>
       <c r="G80" t="s">
-        <v>302</v>
+        <v>102</v>
       </c>
       <c r="H80" s="3">
-        <v>67758</v>
-      </c>
-      <c r="J80" t="s">
-        <v>339</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11">
+        <v>243599</v>
+      </c>
+      <c r="K80" t="s">
+        <v>31</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12">
       <c r="A81" s="1" t="s">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="B81" t="s">
         <v>11</v>
@@ -4776,177 +5145,408 @@
         <v>292</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>236</v>
+        <v>198</v>
       </c>
       <c r="F81" t="s">
-        <v>235</v>
+        <v>271</v>
       </c>
       <c r="G81" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="H81" s="3">
-        <v>25178</v>
-      </c>
-      <c r="J81" t="s">
-        <v>42</v>
-      </c>
-      <c r="K81" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11">
+        <v>189629</v>
+      </c>
+      <c r="K81" t="s">
+        <v>151</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12">
       <c r="A82" s="1" t="s">
-        <v>74</v>
+        <v>331</v>
       </c>
       <c r="B82" t="s">
         <v>11</v>
       </c>
       <c r="C82">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="D82" t="s">
         <v>292</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>173</v>
+        <v>247</v>
       </c>
       <c r="F82" t="s">
-        <v>228</v>
+        <v>393</v>
       </c>
       <c r="G82" t="s">
-        <v>111</v>
+        <v>312</v>
       </c>
       <c r="H82" s="3">
-        <v>19483</v>
-      </c>
-      <c r="J82" t="s">
-        <v>39</v>
-      </c>
-      <c r="K82" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11">
+        <v>154914</v>
+      </c>
+      <c r="K82" t="s">
+        <v>347</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12">
       <c r="A83" s="1" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="B83" t="s">
         <v>11</v>
       </c>
       <c r="C83">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D83" t="s">
         <v>292</v>
       </c>
       <c r="E83" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F83" t="s">
+        <v>381</v>
+      </c>
+      <c r="G83" t="s">
+        <v>307</v>
+      </c>
+      <c r="H83" s="3">
+        <v>147091</v>
+      </c>
+      <c r="K83" t="s">
+        <v>343</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12">
+      <c r="A84" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B84" t="s">
+        <v>11</v>
+      </c>
+      <c r="C84">
+        <v>2016</v>
+      </c>
+      <c r="D84" t="s">
+        <v>292</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F84" t="s">
+        <v>199</v>
+      </c>
+      <c r="G84" t="s">
+        <v>100</v>
+      </c>
+      <c r="H84" s="3">
+        <v>136424</v>
+      </c>
+      <c r="K84" t="s">
+        <v>29</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12">
+      <c r="A85" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B85" t="s">
+        <v>11</v>
+      </c>
+      <c r="C85">
+        <v>2016</v>
+      </c>
+      <c r="D85" t="s">
+        <v>292</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F85" t="s">
+        <v>397</v>
+      </c>
+      <c r="G85" t="s">
+        <v>314</v>
+      </c>
+      <c r="H85" s="3">
+        <v>136234</v>
+      </c>
+      <c r="K85" t="s">
+        <v>349</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12">
+      <c r="A86" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B86" t="s">
+        <v>11</v>
+      </c>
+      <c r="C86">
+        <v>2017</v>
+      </c>
+      <c r="D86" t="s">
+        <v>292</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="F86" t="s">
+        <v>276</v>
+      </c>
+      <c r="G86" t="s">
+        <v>129</v>
+      </c>
+      <c r="H86" s="3">
+        <v>99365</v>
+      </c>
+      <c r="K86" t="s">
+        <v>153</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12">
+      <c r="A87" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B87" t="s">
+        <v>11</v>
+      </c>
+      <c r="C87">
+        <v>2017</v>
+      </c>
+      <c r="D87" t="s">
+        <v>292</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F87" t="s">
+        <v>367</v>
+      </c>
+      <c r="G87" t="s">
+        <v>302</v>
+      </c>
+      <c r="H87" s="3">
+        <v>67758</v>
+      </c>
+      <c r="K87" t="s">
+        <v>339</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12">
+      <c r="A88" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B88" t="s">
+        <v>11</v>
+      </c>
+      <c r="C88">
+        <v>2020</v>
+      </c>
+      <c r="D88" t="s">
+        <v>292</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F88" t="s">
+        <v>235</v>
+      </c>
+      <c r="G88" t="s">
+        <v>114</v>
+      </c>
+      <c r="H88" s="3">
+        <v>25178</v>
+      </c>
+      <c r="K88" t="s">
+        <v>42</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12">
+      <c r="A89" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B89" t="s">
+        <v>11</v>
+      </c>
+      <c r="C89">
+        <v>2020</v>
+      </c>
+      <c r="D89" t="s">
+        <v>292</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F89" t="s">
+        <v>228</v>
+      </c>
+      <c r="G89" t="s">
+        <v>111</v>
+      </c>
+      <c r="H89" s="3">
+        <v>19483</v>
+      </c>
+      <c r="K89" t="s">
+        <v>39</v>
+      </c>
+      <c r="L89" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12">
+      <c r="A90" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B90" t="s">
+        <v>11</v>
+      </c>
+      <c r="C90">
+        <v>2016</v>
+      </c>
+      <c r="D90" t="s">
+        <v>292</v>
+      </c>
+      <c r="E90" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="F83" t="s">
+      <c r="F90" t="s">
         <v>395</v>
       </c>
-      <c r="G83" t="s">
+      <c r="G90" t="s">
         <v>313</v>
       </c>
-      <c r="H83" s="3">
+      <c r="H90" s="3">
         <v>15835</v>
       </c>
-      <c r="J83" t="s">
+      <c r="K90" t="s">
         <v>348</v>
       </c>
-      <c r="K83" s="2" t="s">
+      <c r="L90" s="2" t="s">
         <v>399</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K83">
-    <sortCondition ref="D2:D83"/>
-    <sortCondition descending="1" ref="I2:I83"/>
-    <sortCondition descending="1" ref="H2:H83"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L90">
+    <sortCondition ref="D2:D90"/>
+    <sortCondition ref="J2:J90"/>
+    <sortCondition descending="1" ref="H2:H90"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="K43" r:id="rId1" xr:uid="{725A3016-CC80-5F4A-B091-4E71BCFAD36B}"/>
-    <hyperlink ref="K27" r:id="rId2" xr:uid="{38F493C0-3185-604E-A3BD-AAB0EC5B83DF}"/>
-    <hyperlink ref="K23" r:id="rId3" xr:uid="{2E642780-E9D7-BF4B-9D23-FEBE51DDD0C9}"/>
-    <hyperlink ref="K16" r:id="rId4" xr:uid="{5CF6DEF3-9028-3D4C-846C-DA2618807577}"/>
-    <hyperlink ref="K42" r:id="rId5" xr:uid="{A298B622-5340-5148-820B-D468159EA5BD}"/>
-    <hyperlink ref="K36" r:id="rId6" xr:uid="{EF9BC619-52CD-2D48-BE99-80BD81A8CD54}"/>
-    <hyperlink ref="K28" r:id="rId7" xr:uid="{0002A242-754F-5A40-86A8-5F7DBBEBB9D1}"/>
-    <hyperlink ref="K26" r:id="rId8" xr:uid="{085C9D3E-4AFA-FF48-AA1A-64ECF275D4C0}"/>
-    <hyperlink ref="K29" r:id="rId9" xr:uid="{118F4CA9-C4A7-F74E-8AFF-041FB2741717}"/>
-    <hyperlink ref="K17" r:id="rId10" xr:uid="{75687EB7-0A29-5C47-921B-954A17F06565}"/>
-    <hyperlink ref="K25" r:id="rId11" xr:uid="{81B8E0D0-29DD-E74A-8CE3-1464ECDB131A}"/>
-    <hyperlink ref="K35" r:id="rId12" xr:uid="{5D4D2728-3F60-EE43-86DF-EE58ADBF8432}"/>
-    <hyperlink ref="K15" r:id="rId13" xr:uid="{31C21087-E027-4542-80B2-C095CF193FA7}"/>
-    <hyperlink ref="K31" r:id="rId14" xr:uid="{36CFF13A-82D4-9642-B07B-0C3E49B5D215}"/>
-    <hyperlink ref="K44" r:id="rId15" xr:uid="{DDDE99D5-3422-6549-8393-D5FC330D45B8}"/>
-    <hyperlink ref="K48" r:id="rId16" xr:uid="{9621A5D4-6BD1-984D-9C8C-2A89CFA54CFF}"/>
-    <hyperlink ref="K77" r:id="rId17" xr:uid="{CC87EE91-DF39-EA48-9614-33030270159C}"/>
-    <hyperlink ref="K72" r:id="rId18" xr:uid="{C4E1F448-AF1B-BC43-983F-FB439266392E}"/>
-    <hyperlink ref="K73" r:id="rId19" xr:uid="{17A665F7-B807-4640-B444-16CFE27D5FDF}"/>
-    <hyperlink ref="K54" r:id="rId20" xr:uid="{244C8E1D-D3A7-9549-9D73-8F4D984A6ACD}"/>
-    <hyperlink ref="K45" r:id="rId21" xr:uid="{135AB67A-502A-8A4D-B049-40F78987A6E4}"/>
-    <hyperlink ref="K39" r:id="rId22" xr:uid="{2EBEE3F8-DF57-0E4A-9FB8-2C6B08B9453B}"/>
-    <hyperlink ref="K53" r:id="rId23" xr:uid="{50C93161-BA50-264D-9EB0-FD96B5179BD3}"/>
-    <hyperlink ref="K63" r:id="rId24" xr:uid="{EB1586AB-126F-2B4B-AB36-6A028744AF76}"/>
-    <hyperlink ref="K64" r:id="rId25" xr:uid="{7C55426F-9022-8044-ACAA-5AEC9137C037}"/>
-    <hyperlink ref="K55" r:id="rId26" xr:uid="{AD424BE3-B862-2442-B3B2-5028AF918C6F}"/>
-    <hyperlink ref="K61" r:id="rId27" xr:uid="{2183D387-1FD2-324D-A080-BF2A14B2C266}"/>
-    <hyperlink ref="K82" r:id="rId28" xr:uid="{FDBD3899-8300-BE4F-B928-93EB7382FF06}"/>
-    <hyperlink ref="K20" r:id="rId29" xr:uid="{529C6D37-3C52-0C4C-8560-C27F3F7C2BCE}"/>
-    <hyperlink ref="K5" r:id="rId30" xr:uid="{D004E2AA-6899-A547-B940-4CF0A68E6AE2}"/>
-    <hyperlink ref="K81" r:id="rId31" xr:uid="{2DA721C4-AB3A-EB48-85F9-525AB6A822AB}"/>
-    <hyperlink ref="K62" r:id="rId32" xr:uid="{72A6DA76-289B-1945-8072-DAECE2441387}"/>
-    <hyperlink ref="K21" r:id="rId33" xr:uid="{1ED33379-967F-8D43-85DD-BDDF4C65376C}"/>
-    <hyperlink ref="K50" r:id="rId34" xr:uid="{F704F2D4-3F11-614C-BFFC-5AA6E996A592}"/>
-    <hyperlink ref="K68" r:id="rId35" xr:uid="{5F94CB6B-2D0C-7C41-9363-23A9286E6D55}"/>
-    <hyperlink ref="K67" r:id="rId36" xr:uid="{02572C89-38D3-4B47-B603-D75FBB76E0BB}"/>
-    <hyperlink ref="K49" r:id="rId37" xr:uid="{96F331DE-1BF1-354F-9E54-FA8C80316EFB}"/>
-    <hyperlink ref="K59" r:id="rId38" xr:uid="{D40AF006-F71D-054C-BD53-C9CF18C19E2B}"/>
-    <hyperlink ref="K65" r:id="rId39" xr:uid="{D3ABB7B3-002B-9E42-A591-D3282F8D9EDC}"/>
-    <hyperlink ref="K34" r:id="rId40" xr:uid="{F2CD1548-C098-164F-AE85-0E2D85DE116F}"/>
-    <hyperlink ref="K30" r:id="rId41" xr:uid="{81094FDB-D745-024E-BD73-D63401EE9AA2}"/>
-    <hyperlink ref="K47" r:id="rId42" xr:uid="{850F5B2D-3612-1E44-A230-B654A61C2B8F}"/>
-    <hyperlink ref="K40" r:id="rId43" xr:uid="{D84F734D-746E-B841-A450-F741C1E43856}"/>
-    <hyperlink ref="K74" r:id="rId44" xr:uid="{7870E1C9-1855-634F-8B01-0A6F56E1C8EC}"/>
-    <hyperlink ref="K51" r:id="rId45" xr:uid="{74E258E9-3406-444C-9382-59C9A5DD2D28}"/>
-    <hyperlink ref="K79" r:id="rId46" xr:uid="{22AFEECC-9483-CC40-B244-DB64D5BE611A}"/>
-    <hyperlink ref="K71" r:id="rId47" xr:uid="{3F60EBBC-9A66-404C-8F8D-E0FD74919AF5}"/>
-    <hyperlink ref="K33" r:id="rId48" xr:uid="{97FC090B-C1AF-3B40-8E1E-653AF871E0B8}"/>
-    <hyperlink ref="K60" r:id="rId49" xr:uid="{24271837-2997-A04B-B1A8-30D8EAA5AABF}"/>
-    <hyperlink ref="K66" r:id="rId50" xr:uid="{C6FE7874-DE1E-8744-8F7F-A7266A282BC7}"/>
-    <hyperlink ref="K24" r:id="rId51" xr:uid="{45D4B454-64FD-E043-9E1E-D98B915DA3C4}"/>
-    <hyperlink ref="K41" r:id="rId52" xr:uid="{592E8301-AD04-6A43-BE2C-DF1DCF4D0C8C}"/>
-    <hyperlink ref="K38" r:id="rId53" xr:uid="{AFFE99AD-C3BD-7D47-ADD2-0033AB1BD297}"/>
-    <hyperlink ref="K8" r:id="rId54" xr:uid="{10637FCE-769F-EF46-AFAF-F312278F1225}"/>
-    <hyperlink ref="K69" r:id="rId55" xr:uid="{1E8D6F6E-5279-684F-9870-749B17340F35}"/>
-    <hyperlink ref="K80" r:id="rId56" xr:uid="{C19F506D-023C-1247-BE6A-C23960198C51}"/>
-    <hyperlink ref="K22" r:id="rId57" xr:uid="{3E64B722-3690-B44C-ABC4-059D3B71C8D7}"/>
-    <hyperlink ref="K46" r:id="rId58" xr:uid="{50C3436F-19AF-D74F-8E0A-E9F0AEF4EF7F}"/>
-    <hyperlink ref="K32" r:id="rId59" xr:uid="{A5BBD32C-6F92-A842-A00C-8F17A0710E00}"/>
-    <hyperlink ref="K37" r:id="rId60" xr:uid="{117A81C3-427C-DF49-BA81-BE00A024107F}"/>
-    <hyperlink ref="K57" r:id="rId61" xr:uid="{5E89FA9C-5C01-5342-876F-D8B51FE4E2B8}"/>
-    <hyperlink ref="K76" r:id="rId62" xr:uid="{AE06ADB0-CCC6-5E4F-AA64-084B6EC4EDA5}"/>
-    <hyperlink ref="K52" r:id="rId63" xr:uid="{C1BBF821-4DC8-5347-B6F0-96939C529BA4}"/>
-    <hyperlink ref="K56" r:id="rId64" xr:uid="{990812EE-4D67-A148-8354-137377C29D95}"/>
-    <hyperlink ref="K7" r:id="rId65" xr:uid="{9C8D9D49-3342-1D45-9490-372911350A58}"/>
-    <hyperlink ref="K70" r:id="rId66" xr:uid="{EFDE2707-AAFE-A445-930B-DB05A658CF11}"/>
-    <hyperlink ref="K75" r:id="rId67" xr:uid="{C4CFA4B9-7F0C-2D48-848B-F4855312250F}"/>
-    <hyperlink ref="K78" r:id="rId68" xr:uid="{2C92D437-B811-BA4F-A7A0-ECBD7F90C3E8}"/>
-    <hyperlink ref="K83" r:id="rId69" xr:uid="{1DA360B3-3EEC-0B4A-92B2-F41887D4DA99}"/>
-    <hyperlink ref="K2" r:id="rId70" xr:uid="{53707DD5-6AE9-244D-BE8B-768805F672D6}"/>
-    <hyperlink ref="K3" r:id="rId71" xr:uid="{36EBDC68-249C-1C48-AAF4-2B47231ACC4B}"/>
-    <hyperlink ref="K4" r:id="rId72" xr:uid="{A1D0B6A6-8992-754F-A034-0A1E7D5B9BCB}"/>
-    <hyperlink ref="K6" r:id="rId73" xr:uid="{A089F750-0C9E-6945-9649-FC6752762842}"/>
-    <hyperlink ref="K9" r:id="rId74" xr:uid="{DB5E5AED-5451-EE4B-9408-E80763135A0D}"/>
-    <hyperlink ref="K10" r:id="rId75" xr:uid="{54790613-574F-C04B-943E-7BC43E9CE3FE}"/>
-    <hyperlink ref="K12" r:id="rId76" xr:uid="{04799654-C848-244D-A1F9-FAA86321A73F}"/>
-    <hyperlink ref="K11" r:id="rId77" xr:uid="{0EB41F51-36DD-AA40-AA97-D6366DF2ACBF}"/>
-    <hyperlink ref="K13" r:id="rId78" xr:uid="{7DFC2710-EE37-1F4C-A14D-E4C357A34AC5}"/>
-    <hyperlink ref="K14" r:id="rId79" xr:uid="{F62AC8D7-0E4C-8D4A-A393-61AF8AC0EB46}"/>
-    <hyperlink ref="K18" r:id="rId80" xr:uid="{EE4CEA07-2929-A846-98F2-C6C1968C5BD7}"/>
-    <hyperlink ref="K19" r:id="rId81" xr:uid="{0B614C9A-CC57-2C4A-9102-DE5C3F305979}"/>
+    <hyperlink ref="L50" r:id="rId1" xr:uid="{725A3016-CC80-5F4A-B091-4E71BCFAD36B}"/>
+    <hyperlink ref="L13" r:id="rId2" xr:uid="{38F493C0-3185-604E-A3BD-AAB0EC5B83DF}"/>
+    <hyperlink ref="L35" r:id="rId3" xr:uid="{2E642780-E9D7-BF4B-9D23-FEBE51DDD0C9}"/>
+    <hyperlink ref="L17" r:id="rId4" xr:uid="{5CF6DEF3-9028-3D4C-846C-DA2618807577}"/>
+    <hyperlink ref="L49" r:id="rId5" xr:uid="{A298B622-5340-5148-820B-D468159EA5BD}"/>
+    <hyperlink ref="L43" r:id="rId6" xr:uid="{EF9BC619-52CD-2D48-BE99-80BD81A8CD54}"/>
+    <hyperlink ref="L38" r:id="rId7" xr:uid="{0002A242-754F-5A40-86A8-5F7DBBEBB9D1}"/>
+    <hyperlink ref="L37" r:id="rId8" xr:uid="{085C9D3E-4AFA-FF48-AA1A-64ECF275D4C0}"/>
+    <hyperlink ref="L39" r:id="rId9" xr:uid="{118F4CA9-C4A7-F74E-8AFF-041FB2741717}"/>
+    <hyperlink ref="L20" r:id="rId10" xr:uid="{75687EB7-0A29-5C47-921B-954A17F06565}"/>
+    <hyperlink ref="L14" r:id="rId11" xr:uid="{81B8E0D0-29DD-E74A-8CE3-1464ECDB131A}"/>
+    <hyperlink ref="L42" r:id="rId12" xr:uid="{5D4D2728-3F60-EE43-86DF-EE58ADBF8432}"/>
+    <hyperlink ref="L18" r:id="rId13" xr:uid="{31C21087-E027-4542-80B2-C095CF193FA7}"/>
+    <hyperlink ref="L30" r:id="rId14" xr:uid="{36CFF13A-82D4-9642-B07B-0C3E49B5D215}"/>
+    <hyperlink ref="L51" r:id="rId15" xr:uid="{DDDE99D5-3422-6549-8393-D5FC330D45B8}"/>
+    <hyperlink ref="L55" r:id="rId16" xr:uid="{9621A5D4-6BD1-984D-9C8C-2A89CFA54CFF}"/>
+    <hyperlink ref="L84" r:id="rId17" xr:uid="{CC87EE91-DF39-EA48-9614-33030270159C}"/>
+    <hyperlink ref="L79" r:id="rId18" xr:uid="{C4E1F448-AF1B-BC43-983F-FB439266392E}"/>
+    <hyperlink ref="L80" r:id="rId19" xr:uid="{17A665F7-B807-4640-B444-16CFE27D5FDF}"/>
+    <hyperlink ref="L61" r:id="rId20" xr:uid="{244C8E1D-D3A7-9549-9D73-8F4D984A6ACD}"/>
+    <hyperlink ref="L52" r:id="rId21" xr:uid="{135AB67A-502A-8A4D-B049-40F78987A6E4}"/>
+    <hyperlink ref="L46" r:id="rId22" xr:uid="{2EBEE3F8-DF57-0E4A-9FB8-2C6B08B9453B}"/>
+    <hyperlink ref="L60" r:id="rId23" xr:uid="{50C93161-BA50-264D-9EB0-FD96B5179BD3}"/>
+    <hyperlink ref="L70" r:id="rId24" xr:uid="{EB1586AB-126F-2B4B-AB36-6A028744AF76}"/>
+    <hyperlink ref="L71" r:id="rId25" xr:uid="{7C55426F-9022-8044-ACAA-5AEC9137C037}"/>
+    <hyperlink ref="L62" r:id="rId26" xr:uid="{AD424BE3-B862-2442-B3B2-5028AF918C6F}"/>
+    <hyperlink ref="L68" r:id="rId27" xr:uid="{2183D387-1FD2-324D-A080-BF2A14B2C266}"/>
+    <hyperlink ref="L89" r:id="rId28" xr:uid="{FDBD3899-8300-BE4F-B928-93EB7382FF06}"/>
+    <hyperlink ref="L33" r:id="rId29" xr:uid="{529C6D37-3C52-0C4C-8560-C27F3F7C2BCE}"/>
+    <hyperlink ref="L5" r:id="rId30" xr:uid="{D004E2AA-6899-A547-B940-4CF0A68E6AE2}"/>
+    <hyperlink ref="L88" r:id="rId31" xr:uid="{2DA721C4-AB3A-EB48-85F9-525AB6A822AB}"/>
+    <hyperlink ref="L69" r:id="rId32" xr:uid="{72A6DA76-289B-1945-8072-DAECE2441387}"/>
+    <hyperlink ref="L24" r:id="rId33" xr:uid="{1ED33379-967F-8D43-85DD-BDDF4C65376C}"/>
+    <hyperlink ref="L57" r:id="rId34" xr:uid="{F704F2D4-3F11-614C-BFFC-5AA6E996A592}"/>
+    <hyperlink ref="L75" r:id="rId35" xr:uid="{5F94CB6B-2D0C-7C41-9363-23A9286E6D55}"/>
+    <hyperlink ref="L74" r:id="rId36" xr:uid="{02572C89-38D3-4B47-B603-D75FBB76E0BB}"/>
+    <hyperlink ref="L56" r:id="rId37" xr:uid="{96F331DE-1BF1-354F-9E54-FA8C80316EFB}"/>
+    <hyperlink ref="L66" r:id="rId38" xr:uid="{D40AF006-F71D-054C-BD53-C9CF18C19E2B}"/>
+    <hyperlink ref="L72" r:id="rId39" xr:uid="{D3ABB7B3-002B-9E42-A591-D3282F8D9EDC}"/>
+    <hyperlink ref="L28" r:id="rId40" xr:uid="{F2CD1548-C098-164F-AE85-0E2D85DE116F}"/>
+    <hyperlink ref="L40" r:id="rId41" xr:uid="{81094FDB-D745-024E-BD73-D63401EE9AA2}"/>
+    <hyperlink ref="L54" r:id="rId42" xr:uid="{850F5B2D-3612-1E44-A230-B654A61C2B8F}"/>
+    <hyperlink ref="L47" r:id="rId43" xr:uid="{D84F734D-746E-B841-A450-F741C1E43856}"/>
+    <hyperlink ref="L81" r:id="rId44" xr:uid="{7870E1C9-1855-634F-8B01-0A6F56E1C8EC}"/>
+    <hyperlink ref="L58" r:id="rId45" xr:uid="{74E258E9-3406-444C-9382-59C9A5DD2D28}"/>
+    <hyperlink ref="L86" r:id="rId46" xr:uid="{22AFEECC-9483-CC40-B244-DB64D5BE611A}"/>
+    <hyperlink ref="L78" r:id="rId47" xr:uid="{3F60EBBC-9A66-404C-8F8D-E0FD74919AF5}"/>
+    <hyperlink ref="L41" r:id="rId48" xr:uid="{97FC090B-C1AF-3B40-8E1E-653AF871E0B8}"/>
+    <hyperlink ref="L67" r:id="rId49" xr:uid="{24271837-2997-A04B-B1A8-30D8EAA5AABF}"/>
+    <hyperlink ref="L73" r:id="rId50" xr:uid="{C6FE7874-DE1E-8744-8F7F-A7266A282BC7}"/>
+    <hyperlink ref="L36" r:id="rId51" xr:uid="{45D4B454-64FD-E043-9E1E-D98B915DA3C4}"/>
+    <hyperlink ref="L48" r:id="rId52" xr:uid="{592E8301-AD04-6A43-BE2C-DF1DCF4D0C8C}"/>
+    <hyperlink ref="L45" r:id="rId53" xr:uid="{AFFE99AD-C3BD-7D47-ADD2-0033AB1BD297}"/>
+    <hyperlink ref="L8" r:id="rId54" xr:uid="{10637FCE-769F-EF46-AFAF-F312278F1225}"/>
+    <hyperlink ref="L76" r:id="rId55" xr:uid="{1E8D6F6E-5279-684F-9870-749B17340F35}"/>
+    <hyperlink ref="L87" r:id="rId56" xr:uid="{C19F506D-023C-1247-BE6A-C23960198C51}"/>
+    <hyperlink ref="L34" r:id="rId57" xr:uid="{3E64B722-3690-B44C-ABC4-059D3B71C8D7}"/>
+    <hyperlink ref="L53" r:id="rId58" xr:uid="{50C3436F-19AF-D74F-8E0A-E9F0AEF4EF7F}"/>
+    <hyperlink ref="L25" r:id="rId59" xr:uid="{A5BBD32C-6F92-A842-A00C-8F17A0710E00}"/>
+    <hyperlink ref="L44" r:id="rId60" xr:uid="{117A81C3-427C-DF49-BA81-BE00A024107F}"/>
+    <hyperlink ref="L64" r:id="rId61" xr:uid="{5E89FA9C-5C01-5342-876F-D8B51FE4E2B8}"/>
+    <hyperlink ref="L83" r:id="rId62" xr:uid="{AE06ADB0-CCC6-5E4F-AA64-084B6EC4EDA5}"/>
+    <hyperlink ref="L59" r:id="rId63" xr:uid="{C1BBF821-4DC8-5347-B6F0-96939C529BA4}"/>
+    <hyperlink ref="L63" r:id="rId64" xr:uid="{990812EE-4D67-A148-8354-137377C29D95}"/>
+    <hyperlink ref="L7" r:id="rId65" xr:uid="{9C8D9D49-3342-1D45-9490-372911350A58}"/>
+    <hyperlink ref="L77" r:id="rId66" xr:uid="{EFDE2707-AAFE-A445-930B-DB05A658CF11}"/>
+    <hyperlink ref="L82" r:id="rId67" xr:uid="{C4CFA4B9-7F0C-2D48-848B-F4855312250F}"/>
+    <hyperlink ref="L85" r:id="rId68" xr:uid="{2C92D437-B811-BA4F-A7A0-ECBD7F90C3E8}"/>
+    <hyperlink ref="L90" r:id="rId69" xr:uid="{1DA360B3-3EEC-0B4A-92B2-F41887D4DA99}"/>
+    <hyperlink ref="L2" r:id="rId70" xr:uid="{53707DD5-6AE9-244D-BE8B-768805F672D6}"/>
+    <hyperlink ref="L3" r:id="rId71" xr:uid="{36EBDC68-249C-1C48-AAF4-2B47231ACC4B}"/>
+    <hyperlink ref="L4" r:id="rId72" xr:uid="{A1D0B6A6-8992-754F-A034-0A1E7D5B9BCB}"/>
+    <hyperlink ref="L6" r:id="rId73" xr:uid="{A089F750-0C9E-6945-9649-FC6752762842}"/>
+    <hyperlink ref="L9" r:id="rId74" xr:uid="{DB5E5AED-5451-EE4B-9408-E80763135A0D}"/>
+    <hyperlink ref="L10" r:id="rId75" xr:uid="{54790613-574F-C04B-943E-7BC43E9CE3FE}"/>
+    <hyperlink ref="L11" r:id="rId76" xr:uid="{04799654-C848-244D-A1F9-FAA86321A73F}"/>
+    <hyperlink ref="L12" r:id="rId77" xr:uid="{0EB41F51-36DD-AA40-AA97-D6366DF2ACBF}"/>
+    <hyperlink ref="L15" r:id="rId78" xr:uid="{7DFC2710-EE37-1F4C-A14D-E4C357A34AC5}"/>
+    <hyperlink ref="L16" r:id="rId79" xr:uid="{F62AC8D7-0E4C-8D4A-A393-61AF8AC0EB46}"/>
+    <hyperlink ref="L19" r:id="rId80" xr:uid="{EE4CEA07-2929-A846-98F2-C6C1968C5BD7}"/>
+    <hyperlink ref="L21" r:id="rId81" xr:uid="{0B614C9A-CC57-2C4A-9102-DE5C3F305979}"/>
+    <hyperlink ref="L22" r:id="rId82" xr:uid="{0E055B84-9754-294D-BAD4-527D9AAD8D7D}"/>
+    <hyperlink ref="L23" r:id="rId83" xr:uid="{4D6B94BB-74D1-384A-BF13-D058A0D388F1}"/>
+    <hyperlink ref="L26" r:id="rId84" xr:uid="{6BBF5FFF-5E47-624E-BA4D-0A56088710A7}"/>
+    <hyperlink ref="L27" r:id="rId85" xr:uid="{8DF044C4-A8AA-3D4B-ABD7-19CFCC462FBC}"/>
+    <hyperlink ref="L29" r:id="rId86" xr:uid="{E7621B53-08FB-B74A-A424-0441D515E519}"/>
+    <hyperlink ref="L31" r:id="rId87" xr:uid="{5A433509-4F2A-A14A-A833-86760759B3D9}"/>
+    <hyperlink ref="L32" r:id="rId88" xr:uid="{BB2B37DA-456D-874A-BDF1-8CD5A80F949B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-1405-TVSeries.xlsx
+++ b/db/A7XLK-1405-TVSeries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF23295D-D98A-C64D-B014-38D287D320E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223CC60A-646C-504F-B674-14FAF85DC82F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-360" yWindow="6360" windowWidth="38780" windowHeight="17320" xr2:uid="{BAC94C6D-C196-2D4F-A2F2-89F0A182D671}"/>
+    <workbookView xWindow="0" yWindow="5720" windowWidth="38780" windowHeight="17320" activeTab="1" xr2:uid="{BAC94C6D-C196-2D4F-A2F2-89F0A182D671}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="181029"/>
   <pivotCaches>
-    <pivotCache cacheId="22" r:id="rId3"/>
+    <pivotCache cacheId="23" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1857,9 +1857,6 @@
     <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-124.jpeg</t>
   </si>
   <si>
-    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-125.jpeg</t>
-  </si>
-  <si>
     <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-126.jpeg</t>
   </si>
   <si>
@@ -2279,6 +2276,10 @@
   </si>
   <si>
     <t>最大 - DescriptionC</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-125.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -8281,7 +8282,336 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B5774F1F-8CC6-0140-BB44-59355F1C8F00}" name="樞紐分析表3" cacheId="22" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6DD823C2-4304-DD47-B4EE-A412207DD9D7}" name="樞紐分析表1" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+  <location ref="A4:B56" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="15">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
+      <items count="90">
+        <item x="20"/>
+        <item x="33"/>
+        <item x="74"/>
+        <item x="53"/>
+        <item x="43"/>
+        <item x="79"/>
+        <item x="84"/>
+        <item x="0"/>
+        <item x="72"/>
+        <item x="27"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="48"/>
+        <item x="15"/>
+        <item x="44"/>
+        <item x="46"/>
+        <item x="56"/>
+        <item x="61"/>
+        <item x="4"/>
+        <item x="12"/>
+        <item x="18"/>
+        <item x="30"/>
+        <item x="35"/>
+        <item x="2"/>
+        <item x="26"/>
+        <item x="51"/>
+        <item x="81"/>
+        <item x="42"/>
+        <item x="24"/>
+        <item x="40"/>
+        <item x="77"/>
+        <item x="11"/>
+        <item x="75"/>
+        <item x="54"/>
+        <item x="73"/>
+        <item x="10"/>
+        <item x="58"/>
+        <item x="64"/>
+        <item x="31"/>
+        <item x="6"/>
+        <item x="1"/>
+        <item x="9"/>
+        <item x="28"/>
+        <item x="39"/>
+        <item x="63"/>
+        <item x="25"/>
+        <item x="16"/>
+        <item x="52"/>
+        <item x="34"/>
+        <item x="21"/>
+        <item x="3"/>
+        <item x="13"/>
+        <item x="66"/>
+        <item x="71"/>
+        <item x="14"/>
+        <item x="7"/>
+        <item x="49"/>
+        <item x="59"/>
+        <item x="5"/>
+        <item x="83"/>
+        <item x="41"/>
+        <item x="17"/>
+        <item x="57"/>
+        <item x="60"/>
+        <item x="23"/>
+        <item x="38"/>
+        <item x="29"/>
+        <item x="68"/>
+        <item x="36"/>
+        <item x="86"/>
+        <item x="67"/>
+        <item x="37"/>
+        <item x="55"/>
+        <item x="69"/>
+        <item x="80"/>
+        <item x="62"/>
+        <item x="47"/>
+        <item x="22"/>
+        <item x="70"/>
+        <item x="78"/>
+        <item x="32"/>
+        <item x="19"/>
+        <item x="65"/>
+        <item x="50"/>
+        <item x="76"/>
+        <item x="82"/>
+        <item x="45"/>
+        <item x="8"/>
+        <item x="85"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="176" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="52">
+    <i>
+      <x v="47"/>
+    </i>
+    <i>
+      <x v="66"/>
+    </i>
+    <i>
+      <x v="41"/>
+    </i>
+    <i>
+      <x v="40"/>
+    </i>
+    <i>
+      <x v="81"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="83"/>
+    </i>
+    <i>
+      <x v="56"/>
+    </i>
+    <i>
+      <x v="35"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="76"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="39"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="87"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="58"/>
+    </i>
+    <i>
+      <x v="61"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="60"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="46"/>
+    </i>
+    <i>
+      <x v="45"/>
+    </i>
+    <i>
+      <x v="29"/>
+    </i>
+    <i>
+      <x v="51"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="49"/>
+    </i>
+    <i>
+      <x v="43"/>
+    </i>
+    <i>
+      <x v="64"/>
+    </i>
+    <i>
+      <x v="42"/>
+    </i>
+    <i>
+      <x v="65"/>
+    </i>
+    <i>
+      <x v="71"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="54"/>
+    </i>
+    <i>
+      <x v="68"/>
+    </i>
+    <i>
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="55"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="50"/>
+    </i>
+    <i>
+      <x v="80"/>
+    </i>
+    <i>
+      <x v="77"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="38"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="4" hier="-1"/>
+    <pageField fld="2" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="平均值 - Score" fld="8" subtotal="average" baseField="0" baseItem="0" numFmtId="176"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B5774F1F-8CC6-0140-BB44-59355F1C8F00}" name="樞紐分析表3" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="B98:D116" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -8641,8 +8971,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5EDD2423-2942-7940-B018-804ACE898FE2}" name="樞紐分析表2" cacheId="22" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5EDD2423-2942-7940-B018-804ACE898FE2}" name="樞紐分析表2" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="B66:D87" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -9108,335 +9438,6 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6DD823C2-4304-DD47-B4EE-A412207DD9D7}" name="樞紐分析表1" cacheId="22" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
-  <location ref="A4:B56" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="15">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="ascending">
-      <items count="90">
-        <item x="20"/>
-        <item x="33"/>
-        <item x="74"/>
-        <item x="53"/>
-        <item x="43"/>
-        <item x="79"/>
-        <item x="84"/>
-        <item x="0"/>
-        <item x="72"/>
-        <item x="27"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="48"/>
-        <item x="15"/>
-        <item x="44"/>
-        <item x="46"/>
-        <item x="56"/>
-        <item x="61"/>
-        <item x="4"/>
-        <item x="12"/>
-        <item x="18"/>
-        <item x="30"/>
-        <item x="35"/>
-        <item x="2"/>
-        <item x="26"/>
-        <item x="51"/>
-        <item x="81"/>
-        <item x="42"/>
-        <item x="24"/>
-        <item x="40"/>
-        <item x="77"/>
-        <item x="11"/>
-        <item x="75"/>
-        <item x="54"/>
-        <item x="73"/>
-        <item x="10"/>
-        <item x="58"/>
-        <item x="64"/>
-        <item x="31"/>
-        <item x="6"/>
-        <item x="1"/>
-        <item x="9"/>
-        <item x="28"/>
-        <item x="39"/>
-        <item x="63"/>
-        <item x="25"/>
-        <item x="16"/>
-        <item x="52"/>
-        <item x="34"/>
-        <item x="21"/>
-        <item x="3"/>
-        <item x="13"/>
-        <item x="66"/>
-        <item x="71"/>
-        <item x="14"/>
-        <item x="7"/>
-        <item x="49"/>
-        <item x="59"/>
-        <item x="5"/>
-        <item x="83"/>
-        <item x="41"/>
-        <item x="17"/>
-        <item x="57"/>
-        <item x="60"/>
-        <item x="23"/>
-        <item x="38"/>
-        <item x="29"/>
-        <item x="68"/>
-        <item x="36"/>
-        <item x="86"/>
-        <item x="67"/>
-        <item x="37"/>
-        <item x="55"/>
-        <item x="69"/>
-        <item x="80"/>
-        <item x="62"/>
-        <item x="47"/>
-        <item x="22"/>
-        <item x="70"/>
-        <item x="78"/>
-        <item x="32"/>
-        <item x="19"/>
-        <item x="65"/>
-        <item x="50"/>
-        <item x="76"/>
-        <item x="82"/>
-        <item x="45"/>
-        <item x="8"/>
-        <item x="85"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField dataField="1" numFmtId="176" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="7"/>
-  </rowFields>
-  <rowItems count="52">
-    <i>
-      <x v="47"/>
-    </i>
-    <i>
-      <x v="66"/>
-    </i>
-    <i>
-      <x v="41"/>
-    </i>
-    <i>
-      <x v="40"/>
-    </i>
-    <i>
-      <x v="81"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="25"/>
-    </i>
-    <i>
-      <x v="83"/>
-    </i>
-    <i>
-      <x v="56"/>
-    </i>
-    <i>
-      <x v="35"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="76"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="39"/>
-    </i>
-    <i>
-      <x v="23"/>
-    </i>
-    <i>
-      <x v="87"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="58"/>
-    </i>
-    <i>
-      <x v="61"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="27"/>
-    </i>
-    <i>
-      <x v="60"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="46"/>
-    </i>
-    <i>
-      <x v="45"/>
-    </i>
-    <i>
-      <x v="29"/>
-    </i>
-    <i>
-      <x v="51"/>
-    </i>
-    <i>
-      <x v="24"/>
-    </i>
-    <i>
-      <x v="28"/>
-    </i>
-    <i>
-      <x v="49"/>
-    </i>
-    <i>
-      <x v="43"/>
-    </i>
-    <i>
-      <x v="64"/>
-    </i>
-    <i>
-      <x v="42"/>
-    </i>
-    <i>
-      <x v="65"/>
-    </i>
-    <i>
-      <x v="71"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="54"/>
-    </i>
-    <i>
-      <x v="68"/>
-    </i>
-    <i>
-      <x v="31"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="55"/>
-    </i>
-    <i>
-      <x v="22"/>
-    </i>
-    <i>
-      <x v="19"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="21"/>
-    </i>
-    <i>
-      <x v="50"/>
-    </i>
-    <i>
-      <x v="80"/>
-    </i>
-    <i>
-      <x v="77"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i>
-      <x v="38"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="4" hier="-1"/>
-    <pageField fld="2" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="平均值 - Score" fld="8" subtotal="average" baseField="0" baseItem="0" numFmtId="176"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
   <a:themeElements>
@@ -9747,31 +9748,31 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="5" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="B2" t="s">
         <v>589</v>
-      </c>
-      <c r="B2" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="5" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B4" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="6" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B5" s="3">
         <v>4524</v>
@@ -9779,7 +9780,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="6" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B6" s="3">
         <v>6319</v>
@@ -9787,7 +9788,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="6" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B7" s="3">
         <v>52113</v>
@@ -9795,7 +9796,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="6" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B8" s="3">
         <v>52300</v>
@@ -9803,7 +9804,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="6" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B9" s="3">
         <v>89338</v>
@@ -9811,7 +9812,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="6" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B10" s="3">
         <v>95136</v>
@@ -9819,7 +9820,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B11" s="3">
         <v>98231</v>
@@ -9827,7 +9828,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B12" s="3">
         <v>121479</v>
@@ -9835,7 +9836,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="6" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B13" s="3">
         <v>132204</v>
@@ -9843,7 +9844,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="6" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B14" s="3">
         <v>134785</v>
@@ -9851,7 +9852,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="6" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B15" s="3">
         <v>200612</v>
@@ -9859,7 +9860,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="6" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B16" s="3">
         <v>303763</v>
@@ -9867,7 +9868,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="6" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B17" s="3">
         <v>377267</v>
@@ -9875,7 +9876,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="6" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B18" s="3">
         <v>378104</v>
@@ -9883,7 +9884,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="6" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B19" s="3">
         <v>489413</v>
@@ -9891,7 +9892,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="6" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B20" s="3">
         <v>548641</v>
@@ -9899,7 +9900,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="6" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B21" s="3">
         <v>653514</v>
@@ -9907,7 +9908,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="6" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B22" s="3">
         <v>767044</v>
@@ -9915,7 +9916,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="6" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B23" s="3">
         <v>785247</v>
@@ -9923,7 +9924,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="6" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B24" s="3">
         <v>795715</v>
@@ -9931,7 +9932,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="6" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B25" s="3">
         <v>954238</v>
@@ -9939,7 +9940,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="6" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B26" s="3">
         <v>976802</v>
@@ -9947,7 +9948,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="6" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B27" s="3">
         <v>1028428</v>
@@ -9955,7 +9956,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="6" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B28" s="3">
         <v>1071359</v>
@@ -9963,7 +9964,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="6" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B29" s="3">
         <v>1138386</v>
@@ -9971,7 +9972,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="6" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B30" s="3">
         <v>1212038</v>
@@ -9979,7 +9980,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="6" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B31" s="3">
         <v>1278633</v>
@@ -9987,7 +9988,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="6" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B32" s="3">
         <v>1560320</v>
@@ -9995,7 +9996,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B33" s="3">
         <v>1646706</v>
@@ -10003,7 +10004,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="6" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B34" s="3">
         <v>1724953</v>
@@ -10011,7 +10012,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="6" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B35" s="3">
         <v>1758290</v>
@@ -10019,7 +10020,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="6" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B36" s="3">
         <v>1771888</v>
@@ -10027,7 +10028,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="6" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B37" s="3">
         <v>1796008</v>
@@ -10035,7 +10036,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="6" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B38" s="3">
         <v>1845243</v>
@@ -10043,7 +10044,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="6" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B39" s="3">
         <v>1960230</v>
@@ -10051,7 +10052,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="6" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B40" s="3">
         <v>1967351</v>
@@ -10059,7 +10060,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="6" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B41" s="3">
         <v>2043804</v>
@@ -10067,7 +10068,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="6" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B42" s="3">
         <v>2059245</v>
@@ -10075,7 +10076,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="6" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B43" s="3">
         <v>2132343</v>
@@ -10083,7 +10084,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="6" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B44" s="3">
         <v>2140583</v>
@@ -10091,7 +10092,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="6" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B45" s="3">
         <v>2330511</v>
@@ -10099,7 +10100,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="6" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B46" s="3">
         <v>2378245</v>
@@ -10107,7 +10108,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="6" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B47" s="3">
         <v>2454774</v>
@@ -10115,7 +10116,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="6" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B48" s="3">
         <v>2815834</v>
@@ -10123,7 +10124,7 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="6" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B49" s="3">
         <v>3164608</v>
@@ -10131,7 +10132,7 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="6" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B50" s="3">
         <v>3326331</v>
@@ -10139,7 +10140,7 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="6" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B51" s="3">
         <v>4155026</v>
@@ -10147,7 +10148,7 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="6" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B52" s="3">
         <v>5150111</v>
@@ -10155,7 +10156,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="6" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B53" s="3">
         <v>6002697</v>
@@ -10163,7 +10164,7 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B54" s="3">
         <v>8844170</v>
@@ -10171,7 +10172,7 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="6" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B55" s="3">
         <v>9760868</v>
@@ -10179,7 +10180,7 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="6" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B56" s="3">
         <v>1735995.5294117648</v>
@@ -10187,42 +10188,42 @@
     </row>
     <row r="62" spans="1:3">
       <c r="B62" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="C62" t="s">
         <v>589</v>
-      </c>
-      <c r="C62" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="B63" s="5" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C63" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="B64" s="5" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C64" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="66" spans="2:4">
       <c r="B66" s="5" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C66" t="s">
+        <v>617</v>
+      </c>
+      <c r="D66" t="s">
         <v>618</v>
-      </c>
-      <c r="D66" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="67" spans="2:4">
       <c r="B67" s="6" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C67" s="7">
         <v>20</v>
@@ -10233,7 +10234,7 @@
     </row>
     <row r="68" spans="2:4">
       <c r="B68" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C68" s="7">
         <v>19</v>
@@ -10244,7 +10245,7 @@
     </row>
     <row r="69" spans="2:4">
       <c r="B69" s="6" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C69" s="7">
         <v>18</v>
@@ -10255,7 +10256,7 @@
     </row>
     <row r="70" spans="2:4">
       <c r="B70" s="6" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C70" s="7">
         <v>17</v>
@@ -10266,7 +10267,7 @@
     </row>
     <row r="71" spans="2:4">
       <c r="B71" s="6" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C71" s="7">
         <v>16</v>
@@ -10277,7 +10278,7 @@
     </row>
     <row r="72" spans="2:4">
       <c r="B72" s="6" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C72" s="7">
         <v>15</v>
@@ -10288,7 +10289,7 @@
     </row>
     <row r="73" spans="2:4">
       <c r="B73" s="6" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C73" s="7">
         <v>14</v>
@@ -10299,7 +10300,7 @@
     </row>
     <row r="74" spans="2:4">
       <c r="B74" s="6" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C74" s="7">
         <v>13</v>
@@ -10310,7 +10311,7 @@
     </row>
     <row r="75" spans="2:4">
       <c r="B75" s="6" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C75" s="7">
         <v>12</v>
@@ -10321,7 +10322,7 @@
     </row>
     <row r="76" spans="2:4">
       <c r="B76" s="6" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C76" s="7">
         <v>11</v>
@@ -10332,7 +10333,7 @@
     </row>
     <row r="77" spans="2:4">
       <c r="B77" s="6" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C77" s="7">
         <v>10</v>
@@ -10343,7 +10344,7 @@
     </row>
     <row r="78" spans="2:4">
       <c r="B78" s="6" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C78" s="7">
         <v>9</v>
@@ -10354,7 +10355,7 @@
     </row>
     <row r="79" spans="2:4">
       <c r="B79" s="6" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C79" s="7">
         <v>8</v>
@@ -10365,7 +10366,7 @@
     </row>
     <row r="80" spans="2:4">
       <c r="B80" s="6" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C80" s="7">
         <v>7</v>
@@ -10376,7 +10377,7 @@
     </row>
     <row r="81" spans="2:4">
       <c r="B81" s="6" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C81" s="7">
         <v>6</v>
@@ -10387,7 +10388,7 @@
     </row>
     <row r="82" spans="2:4">
       <c r="B82" s="6" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C82" s="7">
         <v>5</v>
@@ -10398,7 +10399,7 @@
     </row>
     <row r="83" spans="2:4">
       <c r="B83" s="6" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C83" s="7">
         <v>4</v>
@@ -10409,7 +10410,7 @@
     </row>
     <row r="84" spans="2:4">
       <c r="B84" s="6" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C84" s="7">
         <v>3</v>
@@ -10420,7 +10421,7 @@
     </row>
     <row r="85" spans="2:4">
       <c r="B85" s="6" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C85" s="7">
         <v>2</v>
@@ -10431,7 +10432,7 @@
     </row>
     <row r="86" spans="2:4">
       <c r="B86" s="6" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C86" s="7">
         <v>1</v>
@@ -10442,7 +10443,7 @@
     </row>
     <row r="87" spans="2:4">
       <c r="B87" s="6" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C87" s="7">
         <v>20</v>
@@ -10453,42 +10454,42 @@
     </row>
     <row r="94" spans="2:4">
       <c r="B94" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="C94" t="s">
         <v>589</v>
-      </c>
-      <c r="C94" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="95" spans="2:4">
       <c r="B95" s="5" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C95" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="96" spans="2:4">
       <c r="B96" s="5" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C96" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="98" spans="2:4">
       <c r="B98" s="5" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C98" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D98" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="99" spans="2:4">
       <c r="B99" s="6" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C99" s="7">
         <v>19</v>
@@ -10499,7 +10500,7 @@
     </row>
     <row r="100" spans="2:4">
       <c r="B100" s="6" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C100" s="7">
         <v>18</v>
@@ -10510,7 +10511,7 @@
     </row>
     <row r="101" spans="2:4">
       <c r="B101" s="6" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C101" s="7">
         <v>17</v>
@@ -10521,7 +10522,7 @@
     </row>
     <row r="102" spans="2:4">
       <c r="B102" s="6" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C102" s="7">
         <v>16</v>
@@ -10532,7 +10533,7 @@
     </row>
     <row r="103" spans="2:4">
       <c r="B103" s="6" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C103" s="7">
         <v>14</v>
@@ -10543,7 +10544,7 @@
     </row>
     <row r="104" spans="2:4">
       <c r="B104" s="6" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C104" s="7">
         <v>13</v>
@@ -10554,7 +10555,7 @@
     </row>
     <row r="105" spans="2:4">
       <c r="B105" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C105" s="7">
         <v>12</v>
@@ -10565,7 +10566,7 @@
     </row>
     <row r="106" spans="2:4">
       <c r="B106" s="6" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C106" s="7">
         <v>11</v>
@@ -10576,7 +10577,7 @@
     </row>
     <row r="107" spans="2:4">
       <c r="B107" s="6" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C107" s="7">
         <v>10</v>
@@ -10587,7 +10588,7 @@
     </row>
     <row r="108" spans="2:4">
       <c r="B108" s="6" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C108" s="7">
         <v>9</v>
@@ -10598,7 +10599,7 @@
     </row>
     <row r="109" spans="2:4">
       <c r="B109" s="6" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C109" s="7">
         <v>8</v>
@@ -10609,7 +10610,7 @@
     </row>
     <row r="110" spans="2:4">
       <c r="B110" s="6" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C110" s="7">
         <v>7</v>
@@ -10620,7 +10621,7 @@
     </row>
     <row r="111" spans="2:4">
       <c r="B111" s="6" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C111" s="7">
         <v>6</v>
@@ -10631,7 +10632,7 @@
     </row>
     <row r="112" spans="2:4">
       <c r="B112" s="6" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C112" s="7">
         <v>5</v>
@@ -10642,7 +10643,7 @@
     </row>
     <row r="113" spans="2:4">
       <c r="B113" s="6" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C113" s="7">
         <v>4</v>
@@ -10653,7 +10654,7 @@
     </row>
     <row r="114" spans="2:4">
       <c r="B114" s="6" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C114" s="7">
         <v>2</v>
@@ -10664,7 +10665,7 @@
     </row>
     <row r="115" spans="2:4">
       <c r="B115" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C115" s="7">
         <v>1</v>
@@ -10675,7 +10676,7 @@
     </row>
     <row r="116" spans="2:4">
       <c r="B116" s="6" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C116" s="7">
         <v>19</v>
@@ -10715,7 +10716,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C1" t="s">
         <v>4</v>
@@ -10745,10 +10746,10 @@
         <v>464</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="N1" t="s">
         <v>1</v>
@@ -10921,7 +10922,7 @@
         <v>8.1</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L5" s="3">
         <v>4</v>
@@ -11414,7 +11415,7 @@
         <v>7.2</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="L16" s="3">
         <v>15</v>
@@ -11461,7 +11462,7 @@
         <v>7.1</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="L17" s="3">
         <v>16</v>
@@ -11675,7 +11676,7 @@
         <v>158</v>
       </c>
       <c r="G22" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H22" t="s">
         <v>489</v>
@@ -11684,16 +11685,16 @@
         <v>1967351</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="M22" s="3">
         <v>5</v>
       </c>
       <c r="N22" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="23" spans="1:15">
@@ -11716,16 +11717,16 @@
         <v>170</v>
       </c>
       <c r="G23" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="I23" s="3">
         <v>1724953</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="M23" s="3">
         <v>6</v>
@@ -11734,7 +11735,7 @@
         <v>490</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="24" spans="1:15">
@@ -11766,7 +11767,7 @@
         <v>6002697</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="M24" s="3">
         <v>7</v>
@@ -11807,7 +11808,7 @@
         <v>1771888</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="M25" s="3">
         <v>10</v>
@@ -11836,19 +11837,19 @@
         <v>291</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="G26" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H26" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="I26" s="3">
         <v>1646706</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="M26" s="3">
         <v>12</v>
@@ -11857,7 +11858,7 @@
         <v>491</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="27" spans="1:15">
@@ -11877,19 +11878,19 @@
         <v>291</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G27" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H27" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="I27" s="3">
         <v>1138386</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="M27" s="3">
         <v>13</v>
@@ -11898,7 +11899,7 @@
         <v>492</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="28" spans="1:15">
@@ -11930,7 +11931,7 @@
         <v>1560320</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M28" s="3">
         <v>14</v>
@@ -11947,7 +11948,7 @@
         <v>485</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
@@ -11962,25 +11963,25 @@
         <v>170</v>
       </c>
       <c r="G29" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H29" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="I29" s="3">
         <v>2140583</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="M29" s="3">
         <v>16</v>
       </c>
       <c r="N29" t="s">
-        <v>493</v>
+        <v>620</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="30" spans="1:15">
@@ -12012,7 +12013,7 @@
         <v>1796008</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="M30" s="3">
         <v>17</v>
@@ -12044,25 +12045,25 @@
         <v>167</v>
       </c>
       <c r="G31" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H31" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I31" s="3">
         <v>6319</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="M31" s="3">
         <v>18</v>
       </c>
       <c r="N31" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="32" spans="1:15">
@@ -12085,25 +12086,25 @@
         <v>184</v>
       </c>
       <c r="G32" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H32" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I32" s="3">
         <v>3326331</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="M32" s="3">
         <v>19</v>
       </c>
       <c r="N32" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="33" spans="1:15">
@@ -12321,7 +12322,7 @@
         <v>55</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C39" t="s">
         <v>11</v>
@@ -12461,7 +12462,7 @@
         <v>52</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C43" t="s">
         <v>11</v>
@@ -12563,7 +12564,7 @@
         <v>68</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C46" t="s">
         <v>11</v>
@@ -12668,7 +12669,7 @@
         <v>51</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C49" t="s">
         <v>11</v>
@@ -12773,7 +12774,7 @@
         <v>67</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C52" t="s">
         <v>11</v>
@@ -12913,7 +12914,7 @@
         <v>83</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C56" t="s">
         <v>11</v>
@@ -12948,7 +12949,7 @@
         <v>80</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C57" t="s">
         <v>11</v>
@@ -13053,7 +13054,7 @@
         <v>69</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C60" t="s">
         <v>11</v>
@@ -13158,7 +13159,7 @@
         <v>328</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C63" t="s">
         <v>11</v>
@@ -13333,7 +13334,7 @@
         <v>73</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C68" t="s">
         <v>11</v>
@@ -13473,7 +13474,7 @@
         <v>134</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C72" t="s">
         <v>11</v>
@@ -13508,7 +13509,7 @@
         <v>293</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C73" t="s">
         <v>11</v>
@@ -13578,7 +13579,7 @@
         <v>81</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C75" t="s">
         <v>11</v>
@@ -13893,7 +13894,7 @@
         <v>63</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C84" t="s">
         <v>11</v>
@@ -13928,7 +13929,7 @@
         <v>333</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C85" t="s">
         <v>11</v>
@@ -13963,7 +13964,7 @@
         <v>141</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C86" t="s">
         <v>11</v>
@@ -13998,7 +13999,7 @@
         <v>320</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C87" t="s">
         <v>11</v>
@@ -14033,7 +14034,7 @@
         <v>77</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C88" t="s">
         <v>11</v>
@@ -14068,7 +14069,7 @@
         <v>74</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C89" t="s">
         <v>11</v>
@@ -14103,7 +14104,7 @@
         <v>332</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C90" t="s">
         <v>11</v>

--- a/db/A7XLK-1405-TVSeries.xlsx
+++ b/db/A7XLK-1405-TVSeries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F78A8AF-8350-2A42-91FE-C627E5465764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE62A93-ECFA-7246-BFAD-CE22577C27DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1120" yWindow="1600" windowWidth="38780" windowHeight="17320" xr2:uid="{BAC94C6D-C196-2D4F-A2F2-89F0A182D671}"/>
+    <workbookView xWindow="3140" yWindow="4680" windowWidth="38780" windowHeight="17320" xr2:uid="{BAC94C6D-C196-2D4F-A2F2-89F0A182D671}"/>
   </bookViews>
   <sheets>
     <sheet name="今日電影" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="622">
   <si>
     <t>No</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1138,10 +1138,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>好好生活</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>上游</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2162,10 +2158,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>人民的財產/突圍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>靳东 闫妮 黄志忠 陈晓 秦岚</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2183,6 +2175,151 @@
   </si>
   <si>
     <t>D:05/05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>201</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>031</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>劉濤 林峯 蘆芳生 柴碧雲 張晨光 譚耀文 恬妞 徐嘉雯 白梓軒 倪虹潔 高宏亮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/162011.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-201.jpeg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/161808.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>突圍 *</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>星辰大海 *</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>好好生活 *</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>八角亭謎霧 *</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>094</t>
+  </si>
+  <si>
+    <t>-12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">段奕宏 郝蕾 祖峯 吳越 邢岷山 白宇帆 米拉 艾麗婭 溫崢嶸 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://www.gitube.co/vod/161339.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-135.jpeg</t>
+  </si>
+  <si>
+    <t>http://www.gitube.co/vod/155795.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>136</t>
+  </si>
+  <si>
+    <t>095</t>
+  </si>
+  <si>
+    <t>白鹿 王一哲 金晨 鄭湫泓 辣目洋子 赫雷 周陸啦 昌隆 黃馨瑤 黃宥明 張壘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-136.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-137.jpeg</t>
+  </si>
+  <si>
+    <t>137</t>
+  </si>
+  <si>
+    <t>096</t>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/155491.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我是真的爱你 *</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玉樓春 *</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">劉濤 杜淳 李念 王媛可 袁文康 王天辰 代旭 隋蘭 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对你的爱很美 *</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">張嘉益 沙溢 劉敏濤 陳美伊 姜冠南 宋丹丹 王紫璇 代文雯 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-138.jpeg</t>
+  </si>
+  <si>
+    <t>https://gimy.app/vod/155126.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-142-TVSeries/A7XLK-1405-TVSeries-139.jpeg</t>
+  </si>
+  <si>
+    <t>https://gimytv.com/v_8aQ.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>139</t>
+  </si>
+  <si>
+    <t>098</t>
+  </si>
+  <si>
+    <t>藍盈瑩 金晨 啜妮 隋源 王珞丹 韓庚 鄭業成 朱雨辰 楊旭文 王陽 劉凱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>北轍南轅 *</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2587,7 +2724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C0AA310-9C39-A04D-BB87-9521EAB5B98C}">
-  <dimension ref="A1:P94"/>
+  <dimension ref="A1:P100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.83203125" style="1"/>
@@ -2609,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C1" t="s">
         <v>4</v>
@@ -2633,19 +2770,19 @@
         <v>3</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="M1" s="3" t="s">
-        <v>532</v>
-      </c>
       <c r="N1" s="3" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="O1" t="s">
         <v>1</v>
@@ -2656,7 +2793,7 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
@@ -2674,10 +2811,10 @@
         <v>170</v>
       </c>
       <c r="G2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I2" s="3">
         <v>3164608</v>
@@ -2686,21 +2823,21 @@
         <v>8.6</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="L2" s="3">
         <v>1</v>
       </c>
       <c r="O2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
@@ -2718,10 +2855,10 @@
         <v>161</v>
       </c>
       <c r="G3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I3" s="3">
         <v>52300</v>
@@ -2730,21 +2867,21 @@
         <v>8.5</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="L3" s="3">
         <v>2</v>
       </c>
       <c r="O3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>49</v>
@@ -2759,13 +2896,13 @@
         <v>291</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="I4" s="3">
         <v>489413</v>
@@ -2774,16 +2911,16 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L4" s="3">
         <v>3</v>
       </c>
       <c r="O4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2818,7 +2955,7 @@
         <v>8.1</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="L5" s="3">
         <v>4</v>
@@ -2835,7 +2972,7 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>51</v>
@@ -2853,10 +2990,10 @@
         <v>161</v>
       </c>
       <c r="G6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I6" s="3">
         <v>95136</v>
@@ -2865,21 +3002,21 @@
         <v>7.9</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="L6" s="3">
         <v>5</v>
       </c>
       <c r="O6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>52</v>
@@ -2897,10 +3034,10 @@
         <v>170</v>
       </c>
       <c r="G7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I7" s="3">
         <v>767044</v>
@@ -2909,21 +3046,21 @@
         <v>7.8</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="L7" s="3">
         <v>6</v>
       </c>
       <c r="O7" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>53</v>
@@ -2941,10 +3078,10 @@
         <v>195</v>
       </c>
       <c r="G8" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I8" s="3">
         <v>378104</v>
@@ -2953,21 +3090,21 @@
         <v>7.8</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L8" s="3">
         <v>7</v>
       </c>
       <c r="O8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>54</v>
@@ -2985,10 +3122,10 @@
         <v>173</v>
       </c>
       <c r="G9" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="I9" s="3">
         <v>2330511</v>
@@ -2997,7 +3134,7 @@
         <v>7.6</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="L9" s="3">
         <v>8</v>
@@ -3006,15 +3143,15 @@
         <v>5</v>
       </c>
       <c r="O9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>55</v>
@@ -3032,10 +3169,10 @@
         <v>222</v>
       </c>
       <c r="G10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H10" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="I10" s="3">
         <v>548641</v>
@@ -3044,21 +3181,21 @@
         <v>7.6</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L10" s="3">
         <v>9</v>
       </c>
       <c r="O10" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>56</v>
@@ -3073,13 +3210,13 @@
         <v>291</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G11" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H11" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I11" s="3">
         <v>52113</v>
@@ -3088,21 +3225,21 @@
         <v>7.5</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="L11" s="3">
         <v>10</v>
       </c>
       <c r="O11" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>57</v>
@@ -3120,10 +3257,10 @@
         <v>158</v>
       </c>
       <c r="G12" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H12" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="I12" s="3">
         <v>134785</v>
@@ -3132,16 +3269,16 @@
         <v>7.5</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L12" s="3">
         <v>11</v>
       </c>
       <c r="O12" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -3176,7 +3313,7 @@
         <v>7.4</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="L13" s="3">
         <v>12</v>
@@ -3223,7 +3360,7 @@
         <v>7.4</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="L14" s="3">
         <v>13</v>
@@ -3240,7 +3377,7 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>60</v>
@@ -3255,13 +3392,13 @@
         <v>291</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G15" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H15" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="I15" s="3">
         <v>1278633</v>
@@ -3270,21 +3407,21 @@
         <v>7.3</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="L15" s="3">
         <v>14</v>
       </c>
       <c r="O15" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>61</v>
@@ -3302,10 +3439,10 @@
         <v>285</v>
       </c>
       <c r="G16" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H16" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="I16" s="3">
         <v>2043804</v>
@@ -3314,7 +3451,7 @@
         <v>7.2</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="L16" s="3">
         <v>15</v>
@@ -3323,10 +3460,10 @@
         <v>9</v>
       </c>
       <c r="O16" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -3361,7 +3498,7 @@
         <v>7.1</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="L17" s="3">
         <v>16</v>
@@ -3408,7 +3545,7 @@
         <v>7.1</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="L18" s="3">
         <v>17</v>
@@ -3422,7 +3559,7 @@
     </row>
     <row r="19" spans="1:16">
       <c r="A19" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>64</v>
@@ -3437,13 +3574,13 @@
         <v>291</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G19" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H19" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="I19" s="3">
         <v>785247</v>
@@ -3452,16 +3589,16 @@
         <v>7</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="L19" s="3">
         <v>18</v>
       </c>
       <c r="O19" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -3496,7 +3633,7 @@
         <v>7</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L20" s="3">
         <v>19</v>
@@ -3513,7 +3650,7 @@
     </row>
     <row r="21" spans="1:16">
       <c r="A21" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>66</v>
@@ -3528,13 +3665,13 @@
         <v>291</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G21" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H21" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="I21" s="3">
         <v>89338</v>
@@ -3543,21 +3680,21 @@
         <v>7</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="L21" s="3">
         <v>20</v>
       </c>
       <c r="O21" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="22" spans="1:16">
       <c r="A22" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>67</v>
@@ -3575,30 +3712,30 @@
         <v>158</v>
       </c>
       <c r="G22" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H22" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I22" s="3">
         <v>1967351</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="M22" s="3">
         <v>5</v>
       </c>
       <c r="O22" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="23" spans="1:16">
       <c r="A23" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>68</v>
@@ -3616,25 +3753,25 @@
         <v>170</v>
       </c>
       <c r="G23" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H23" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="I23" s="3">
         <v>1724953</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="M23" s="3">
         <v>6</v>
       </c>
       <c r="O23" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -3666,7 +3803,7 @@
         <v>6002697</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="M24" s="3">
         <v>7</v>
@@ -3680,7 +3817,7 @@
     </row>
     <row r="25" spans="1:16">
       <c r="A25" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>70</v>
@@ -3698,30 +3835,30 @@
         <v>173</v>
       </c>
       <c r="G25" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H25" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I25" s="3">
         <v>1771888</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="M25" s="3">
         <v>10</v>
       </c>
       <c r="O25" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="26" spans="1:16">
       <c r="A26" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>71</v>
@@ -3736,33 +3873,33 @@
         <v>291</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G26" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H26" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="I26" s="3">
         <v>1646706</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="M26" s="3">
         <v>12</v>
       </c>
       <c r="O26" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="27" spans="1:16">
       <c r="A27" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>72</v>
@@ -3777,28 +3914,28 @@
         <v>291</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G27" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H27" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="I27" s="3">
         <v>1138386</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M27" s="3">
         <v>13</v>
       </c>
       <c r="O27" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3830,7 +3967,7 @@
         <v>1560320</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="M28" s="3">
         <v>14</v>
@@ -3844,10 +3981,10 @@
     </row>
     <row r="29" spans="1:16">
       <c r="A29" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
@@ -3862,25 +3999,25 @@
         <v>170</v>
       </c>
       <c r="G29" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H29" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="I29" s="3">
         <v>2140583</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="M29" s="3">
         <v>16</v>
       </c>
       <c r="O29" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3912,7 +4049,7 @@
         <v>1796008</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="M30" s="3">
         <v>17</v>
@@ -3926,7 +4063,7 @@
     </row>
     <row r="31" spans="1:16">
       <c r="A31" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>75</v>
@@ -3944,30 +4081,30 @@
         <v>167</v>
       </c>
       <c r="G31" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H31" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="I31" s="3">
         <v>6319</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="M31" s="3">
         <v>18</v>
       </c>
       <c r="O31" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="32" spans="1:16">
       <c r="A32" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>76</v>
@@ -3985,33 +4122,33 @@
         <v>184</v>
       </c>
       <c r="G32" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H32" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I32" s="3">
         <v>3326331</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="M32" s="3">
         <v>19</v>
       </c>
       <c r="O32" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="33" spans="1:16">
       <c r="A33" s="1" t="s">
-        <v>75</v>
+        <v>582</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>77</v>
+        <v>583</v>
       </c>
       <c r="C33" t="s">
         <v>11</v>
@@ -4023,30 +4160,30 @@
         <v>291</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>230</v>
+        <v>268</v>
       </c>
       <c r="G33" t="s">
-        <v>231</v>
+        <v>584</v>
       </c>
       <c r="H33" t="s">
-        <v>112</v>
+        <v>589</v>
       </c>
       <c r="I33" s="3">
-        <v>9760868</v>
+        <v>261668</v>
       </c>
       <c r="O33" t="s">
-        <v>40</v>
+        <v>586</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>232</v>
+        <v>585</v>
       </c>
     </row>
     <row r="34" spans="1:16">
       <c r="A34" s="1" t="s">
-        <v>321</v>
+        <v>75</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C34" t="s">
         <v>11</v>
@@ -4058,30 +4195,30 @@
         <v>291</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>170</v>
+        <v>230</v>
       </c>
       <c r="G34" t="s">
-        <v>366</v>
+        <v>231</v>
       </c>
       <c r="H34" t="s">
-        <v>303</v>
+        <v>112</v>
       </c>
       <c r="I34" s="3">
-        <v>5150111</v>
+        <v>9760868</v>
       </c>
       <c r="O34" t="s">
-        <v>340</v>
+        <v>40</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>368</v>
+        <v>232</v>
       </c>
     </row>
     <row r="35" spans="1:16">
       <c r="A35" s="1" t="s">
-        <v>49</v>
+        <v>320</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C35" t="s">
         <v>11</v>
@@ -4093,33 +4230,33 @@
         <v>291</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="G35" t="s">
-        <v>162</v>
+        <v>365</v>
       </c>
       <c r="H35" t="s">
-        <v>86</v>
+        <v>302</v>
       </c>
       <c r="I35" s="3">
-        <v>2815834</v>
+        <v>5150111</v>
       </c>
       <c r="O35" t="s">
-        <v>16</v>
+        <v>339</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>163</v>
+        <v>367</v>
       </c>
     </row>
     <row r="36" spans="1:16">
       <c r="A36" s="1" t="s">
-        <v>315</v>
+        <v>49</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C36" t="s">
-        <v>350</v>
+        <v>11</v>
       </c>
       <c r="D36">
         <v>2021</v>
@@ -4128,33 +4265,33 @@
         <v>291</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>351</v>
+        <v>161</v>
       </c>
       <c r="G36" t="s">
-        <v>352</v>
+        <v>162</v>
       </c>
       <c r="H36" t="s">
-        <v>298</v>
+        <v>86</v>
       </c>
       <c r="I36" s="3">
-        <v>2535509</v>
+        <v>2815834</v>
       </c>
       <c r="O36" t="s">
-        <v>334</v>
+        <v>16</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>353</v>
+        <v>163</v>
       </c>
     </row>
     <row r="37" spans="1:16">
       <c r="A37" s="1" t="s">
-        <v>54</v>
+        <v>314</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C37" t="s">
-        <v>11</v>
+        <v>349</v>
       </c>
       <c r="D37">
         <v>2021</v>
@@ -4163,30 +4300,30 @@
         <v>291</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>173</v>
+        <v>350</v>
       </c>
       <c r="G37" t="s">
-        <v>174</v>
+        <v>351</v>
       </c>
       <c r="H37" t="s">
-        <v>91</v>
+        <v>298</v>
       </c>
       <c r="I37" s="3">
-        <v>2378245</v>
+        <v>2535509</v>
       </c>
       <c r="O37" t="s">
-        <v>21</v>
+        <v>333</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>175</v>
+        <v>352</v>
       </c>
     </row>
     <row r="38" spans="1:16">
       <c r="A38" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C38" t="s">
         <v>11</v>
@@ -4198,30 +4335,30 @@
         <v>291</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="G38" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I38" s="3">
-        <v>2059245</v>
+        <v>2378245</v>
       </c>
       <c r="O38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="39" spans="1:16">
       <c r="A39" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>535</v>
+        <v>82</v>
       </c>
       <c r="C39" t="s">
         <v>11</v>
@@ -4233,30 +4370,30 @@
         <v>291</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="G39" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H39" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I39" s="3">
-        <v>1960230</v>
+        <v>2059245</v>
       </c>
       <c r="O39" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40" spans="1:16">
       <c r="A40" s="1" t="s">
-        <v>136</v>
+        <v>55</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>83</v>
+        <v>534</v>
       </c>
       <c r="C40" t="s">
         <v>11</v>
@@ -4268,30 +4405,30 @@
         <v>291</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="G40" t="s">
-        <v>264</v>
+        <v>177</v>
       </c>
       <c r="H40" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="I40" s="3">
-        <v>1845243</v>
+        <v>1960230</v>
       </c>
       <c r="O40" t="s">
-        <v>148</v>
+        <v>22</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>265</v>
+        <v>178</v>
       </c>
     </row>
     <row r="41" spans="1:16">
       <c r="A41" s="1" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C41" t="s">
         <v>11</v>
@@ -4303,30 +4440,30 @@
         <v>291</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>282</v>
+        <v>158</v>
       </c>
       <c r="G41" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="H41" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="I41" s="3">
-        <v>1758290</v>
+        <v>1845243</v>
       </c>
       <c r="O41" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
     </row>
     <row r="42" spans="1:16">
       <c r="A42" s="1" t="s">
-        <v>58</v>
+        <v>143</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>133</v>
+        <v>84</v>
       </c>
       <c r="C42" t="s">
         <v>11</v>
@@ -4338,30 +4475,30 @@
         <v>291</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>184</v>
+        <v>282</v>
       </c>
       <c r="G42" t="s">
-        <v>185</v>
+        <v>281</v>
       </c>
       <c r="H42" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="I42" s="3">
-        <v>1212038</v>
+        <v>1758290</v>
       </c>
       <c r="O42" t="s">
-        <v>25</v>
+        <v>155</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>186</v>
+        <v>283</v>
       </c>
     </row>
     <row r="43" spans="1:16">
       <c r="A43" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>536</v>
+        <v>133</v>
       </c>
       <c r="C43" t="s">
         <v>11</v>
@@ -4373,27 +4510,30 @@
         <v>291</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>161</v>
+        <v>184</v>
+      </c>
+      <c r="G43" t="s">
+        <v>185</v>
       </c>
       <c r="H43" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="I43" s="3">
-        <v>976802</v>
+        <v>1212038</v>
       </c>
       <c r="O43" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
     </row>
     <row r="44" spans="1:16">
       <c r="A44" s="1" t="s">
-        <v>324</v>
+        <v>52</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>134</v>
+        <v>535</v>
       </c>
       <c r="C44" t="s">
         <v>11</v>
@@ -4405,30 +4545,27 @@
         <v>291</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="G44" t="s">
-        <v>375</v>
+        <v>161</v>
       </c>
       <c r="H44" t="s">
-        <v>306</v>
+        <v>89</v>
       </c>
       <c r="I44" s="3">
-        <v>954238</v>
+        <v>976802</v>
       </c>
       <c r="O44" t="s">
-        <v>374</v>
+        <v>19</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>376</v>
+        <v>169</v>
       </c>
     </row>
     <row r="45" spans="1:16">
       <c r="A45" s="1" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C45" t="s">
         <v>11</v>
@@ -4440,30 +4577,30 @@
         <v>291</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>358</v>
+        <v>173</v>
       </c>
       <c r="G45" t="s">
-        <v>357</v>
+        <v>374</v>
       </c>
       <c r="H45" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="I45" s="3">
-        <v>795715</v>
+        <v>954238</v>
       </c>
       <c r="O45" t="s">
-        <v>336</v>
+        <v>373</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>359</v>
+        <v>375</v>
       </c>
     </row>
     <row r="46" spans="1:16">
       <c r="A46" s="1" t="s">
-        <v>68</v>
+        <v>316</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>537</v>
+        <v>135</v>
       </c>
       <c r="C46" t="s">
         <v>11</v>
@@ -4475,33 +4612,33 @@
         <v>291</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>198</v>
+        <v>357</v>
       </c>
       <c r="G46" t="s">
-        <v>212</v>
+        <v>356</v>
       </c>
       <c r="H46" t="s">
-        <v>105</v>
+        <v>299</v>
       </c>
       <c r="I46" s="3">
-        <v>653514</v>
+        <v>795715</v>
       </c>
       <c r="O46" t="s">
-        <v>34</v>
+        <v>335</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>213</v>
+        <v>358</v>
       </c>
     </row>
     <row r="47" spans="1:16">
       <c r="A47" s="1" t="s">
-        <v>138</v>
+        <v>68</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>136</v>
+        <v>536</v>
       </c>
       <c r="C47" t="s">
-        <v>224</v>
+        <v>11</v>
       </c>
       <c r="D47">
         <v>2021</v>
@@ -4510,33 +4647,33 @@
         <v>291</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>268</v>
+        <v>198</v>
       </c>
       <c r="G47" t="s">
-        <v>269</v>
+        <v>212</v>
       </c>
       <c r="H47" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="I47" s="3">
-        <v>459883</v>
+        <v>653514</v>
       </c>
       <c r="O47" t="s">
-        <v>150</v>
+        <v>34</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>270</v>
+        <v>213</v>
       </c>
     </row>
     <row r="48" spans="1:16">
       <c r="A48" s="1" t="s">
-        <v>316</v>
+        <v>138</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C48" t="s">
-        <v>11</v>
+        <v>224</v>
       </c>
       <c r="D48">
         <v>2021</v>
@@ -4545,30 +4682,30 @@
         <v>291</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>355</v>
+        <v>268</v>
       </c>
       <c r="G48" t="s">
-        <v>354</v>
+        <v>269</v>
       </c>
       <c r="H48" t="s">
-        <v>299</v>
+        <v>126</v>
       </c>
       <c r="I48" s="3">
-        <v>377267</v>
+        <v>459883</v>
       </c>
       <c r="O48" t="s">
-        <v>335</v>
+        <v>150</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>356</v>
+        <v>270</v>
       </c>
     </row>
     <row r="49" spans="1:16">
       <c r="A49" s="1" t="s">
-        <v>51</v>
+        <v>315</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>538</v>
+        <v>137</v>
       </c>
       <c r="C49" t="s">
         <v>11</v>
@@ -4580,30 +4717,30 @@
         <v>291</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>167</v>
+        <v>354</v>
       </c>
       <c r="G49" t="s">
-        <v>168</v>
+        <v>353</v>
       </c>
       <c r="H49" t="s">
-        <v>87</v>
+        <v>590</v>
       </c>
       <c r="I49" s="3">
-        <v>303763</v>
+        <v>377267</v>
       </c>
       <c r="O49" t="s">
-        <v>18</v>
+        <v>334</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>166</v>
+        <v>355</v>
       </c>
     </row>
     <row r="50" spans="1:16">
       <c r="A50" s="1" t="s">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>138</v>
+        <v>537</v>
       </c>
       <c r="C50" t="s">
         <v>11</v>
@@ -4614,31 +4751,31 @@
       <c r="E50" t="s">
         <v>291</v>
       </c>
-      <c r="F50" s="1">
-        <v>-10</v>
+      <c r="F50" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="G50" t="s">
-        <v>13</v>
+        <v>168</v>
       </c>
       <c r="H50" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="I50" s="3">
-        <v>200612</v>
+        <v>303763</v>
       </c>
       <c r="O50" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="51" spans="1:16">
       <c r="A51" s="1" t="s">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C51" t="s">
         <v>11</v>
@@ -4649,31 +4786,31 @@
       <c r="E51" t="s">
         <v>291</v>
       </c>
-      <c r="F51" s="1" t="s">
-        <v>192</v>
+      <c r="F51" s="1">
+        <v>-10</v>
       </c>
       <c r="G51" t="s">
-        <v>193</v>
+        <v>13</v>
       </c>
       <c r="H51" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="I51" s="3">
-        <v>132204</v>
+        <v>200612</v>
       </c>
       <c r="O51" t="s">
-        <v>288</v>
+        <v>14</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>194</v>
+        <v>160</v>
       </c>
     </row>
     <row r="52" spans="1:16">
       <c r="A52" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>539</v>
+        <v>139</v>
       </c>
       <c r="C52" t="s">
         <v>11</v>
@@ -4685,30 +4822,30 @@
         <v>291</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G52" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="H52" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="I52" s="3">
-        <v>121479</v>
+        <v>132204</v>
       </c>
       <c r="O52" t="s">
-        <v>33</v>
+        <v>288</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
     </row>
     <row r="53" spans="1:16">
       <c r="A53" s="1" t="s">
-        <v>322</v>
+        <v>67</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>140</v>
+        <v>538</v>
       </c>
       <c r="C53" t="s">
         <v>11</v>
@@ -4720,30 +4857,30 @@
         <v>291</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="G53" t="s">
-        <v>370</v>
+        <v>210</v>
       </c>
       <c r="H53" t="s">
-        <v>304</v>
+        <v>104</v>
       </c>
       <c r="I53" s="3">
-        <v>98231</v>
+        <v>121479</v>
       </c>
       <c r="O53" t="s">
-        <v>369</v>
+        <v>33</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>371</v>
+        <v>211</v>
       </c>
     </row>
     <row r="54" spans="1:16">
       <c r="A54" s="1" t="s">
-        <v>137</v>
+        <v>321</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C54" t="s">
         <v>11</v>
@@ -4755,278 +4892,278 @@
         <v>291</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="G54" t="s">
-        <v>266</v>
+        <v>369</v>
       </c>
       <c r="H54" t="s">
-        <v>125</v>
+        <v>303</v>
       </c>
       <c r="I54" s="3">
-        <v>4524</v>
+        <v>98231</v>
       </c>
       <c r="O54" t="s">
-        <v>149</v>
+        <v>368</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>267</v>
+        <v>370</v>
       </c>
     </row>
     <row r="55" spans="1:16">
       <c r="A55" s="1" t="s">
-        <v>62</v>
+        <v>137</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C55" t="s">
         <v>11</v>
       </c>
       <c r="D55">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E55" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="G55" t="s">
-        <v>196</v>
+        <v>266</v>
       </c>
       <c r="H55" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="I55" s="3">
-        <v>7733587</v>
+        <v>4524</v>
       </c>
       <c r="O55" t="s">
-        <v>28</v>
+        <v>149</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>197</v>
+        <v>267</v>
       </c>
     </row>
     <row r="56" spans="1:16">
       <c r="A56" s="1" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>540</v>
+        <v>142</v>
       </c>
       <c r="C56" t="s">
         <v>11</v>
       </c>
       <c r="D56">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="E56" t="s">
         <v>292</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>253</v>
+        <v>195</v>
       </c>
       <c r="G56" t="s">
-        <v>252</v>
+        <v>196</v>
       </c>
       <c r="H56" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="I56" s="3">
-        <v>5275870</v>
+        <v>7733587</v>
       </c>
       <c r="O56" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>254</v>
+        <v>197</v>
       </c>
     </row>
     <row r="57" spans="1:16">
       <c r="A57" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C57" t="s">
         <v>11</v>
       </c>
       <c r="D57">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="E57" t="s">
         <v>292</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="G57" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="H57" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I57" s="3">
-        <v>5265895</v>
+        <v>5275870</v>
       </c>
       <c r="O57" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
     </row>
     <row r="58" spans="1:16">
       <c r="A58" s="1" t="s">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>143</v>
+        <v>540</v>
       </c>
       <c r="C58" t="s">
         <v>11</v>
       </c>
       <c r="D58">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="E58" t="s">
         <v>292</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>274</v>
+        <v>244</v>
       </c>
       <c r="G58" t="s">
-        <v>273</v>
+        <v>243</v>
       </c>
       <c r="H58" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="I58" s="3">
-        <v>4674495</v>
+        <v>5265895</v>
       </c>
       <c r="O58" t="s">
-        <v>152</v>
+        <v>45</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>275</v>
+        <v>245</v>
       </c>
     </row>
     <row r="59" spans="1:16">
       <c r="A59" s="1" t="s">
-        <v>327</v>
+        <v>140</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C59" t="s">
         <v>11</v>
       </c>
       <c r="D59">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="E59" t="s">
         <v>292</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>158</v>
+        <v>274</v>
       </c>
       <c r="G59" t="s">
-        <v>383</v>
+        <v>273</v>
       </c>
       <c r="H59" t="s">
-        <v>308</v>
+        <v>128</v>
       </c>
       <c r="I59" s="3">
-        <v>4655514</v>
+        <v>4674495</v>
       </c>
       <c r="O59" t="s">
-        <v>344</v>
+        <v>152</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>384</v>
+        <v>275</v>
       </c>
     </row>
     <row r="60" spans="1:16">
       <c r="A60" s="1" t="s">
-        <v>69</v>
+        <v>326</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>542</v>
+        <v>144</v>
       </c>
       <c r="C60" t="s">
         <v>11</v>
       </c>
       <c r="D60">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="E60" t="s">
         <v>292</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>214</v>
+        <v>158</v>
       </c>
       <c r="G60" t="s">
-        <v>215</v>
+        <v>382</v>
       </c>
       <c r="H60" t="s">
-        <v>106</v>
+        <v>307</v>
       </c>
       <c r="I60" s="3">
-        <v>4141267</v>
+        <v>4655514</v>
       </c>
       <c r="O60" t="s">
-        <v>35</v>
+        <v>343</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>216</v>
+        <v>383</v>
       </c>
     </row>
     <row r="61" spans="1:16">
       <c r="A61" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>316</v>
+        <v>541</v>
       </c>
       <c r="C61" t="s">
         <v>11</v>
       </c>
       <c r="D61">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="E61" t="s">
         <v>292</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="G61" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="H61" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I61" s="3">
-        <v>2991300</v>
+        <v>4141267</v>
       </c>
       <c r="O61" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="62" spans="1:16">
       <c r="A62" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C62" t="s">
-        <v>224</v>
+        <v>11</v>
       </c>
       <c r="D62">
         <v>2019</v>
@@ -5035,135 +5172,135 @@
         <v>292</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="G62" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="H62" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="I62" s="3">
-        <v>2563754</v>
+        <v>2991300</v>
       </c>
       <c r="O62" t="s">
-        <v>289</v>
+        <v>32</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
     </row>
     <row r="63" spans="1:16">
       <c r="A63" s="1" t="s">
-        <v>328</v>
+        <v>72</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>543</v>
+        <v>316</v>
       </c>
       <c r="C63" t="s">
-        <v>11</v>
+        <v>224</v>
       </c>
       <c r="D63">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="E63" t="s">
         <v>292</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>387</v>
+        <v>222</v>
       </c>
       <c r="G63" t="s">
-        <v>386</v>
+        <v>223</v>
       </c>
       <c r="H63" t="s">
-        <v>309</v>
+        <v>109</v>
       </c>
       <c r="I63" s="3">
-        <v>2400663</v>
+        <v>2563754</v>
       </c>
       <c r="O63" t="s">
-        <v>385</v>
+        <v>289</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>388</v>
+        <v>225</v>
       </c>
     </row>
     <row r="64" spans="1:16">
       <c r="A64" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>318</v>
+        <v>542</v>
       </c>
       <c r="C64" t="s">
         <v>11</v>
       </c>
       <c r="D64">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E64" t="s">
         <v>292</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="G64" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="H64" t="s">
-        <v>377</v>
+        <v>308</v>
       </c>
       <c r="I64" s="3">
-        <v>2340742</v>
+        <v>2400663</v>
       </c>
       <c r="O64" t="s">
-        <v>342</v>
+        <v>384</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
     </row>
     <row r="65" spans="1:16">
       <c r="A65" s="1" t="s">
-        <v>133</v>
+        <v>324</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C65" t="s">
         <v>11</v>
       </c>
       <c r="D65">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="E65" t="s">
         <v>292</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>258</v>
+        <v>378</v>
       </c>
       <c r="G65" t="s">
-        <v>257</v>
+        <v>377</v>
       </c>
       <c r="H65" t="s">
-        <v>121</v>
+        <v>376</v>
       </c>
       <c r="I65" s="3">
-        <v>1265188</v>
+        <v>2340742</v>
       </c>
       <c r="O65" t="s">
-        <v>145</v>
-      </c>
-      <c r="P65" t="s">
-        <v>259</v>
+        <v>341</v>
+      </c>
+      <c r="P65" s="2" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="66" spans="1:16">
       <c r="A66" s="1" t="s">
-        <v>84</v>
+        <v>133</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C66" t="s">
         <v>11</v>
@@ -5175,660 +5312,660 @@
         <v>292</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="G66" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H66" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I66" s="3">
-        <v>1259285</v>
+        <v>1265188</v>
       </c>
       <c r="O66" t="s">
-        <v>48</v>
-      </c>
-      <c r="P66" s="2" t="s">
-        <v>256</v>
+        <v>145</v>
+      </c>
+      <c r="P66" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="67" spans="1:16">
       <c r="A67" s="1" t="s">
-        <v>144</v>
+        <v>84</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C67" t="s">
         <v>11</v>
       </c>
       <c r="D67">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="E67" t="s">
         <v>292</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>285</v>
+        <v>230</v>
       </c>
       <c r="G67" t="s">
-        <v>284</v>
+        <v>255</v>
       </c>
       <c r="H67" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="I67" s="3">
-        <v>1218509</v>
+        <v>1259285</v>
       </c>
       <c r="O67" t="s">
-        <v>156</v>
+        <v>48</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>286</v>
+        <v>256</v>
       </c>
     </row>
     <row r="68" spans="1:16">
       <c r="A68" s="1" t="s">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>544</v>
+        <v>320</v>
       </c>
       <c r="C68" t="s">
         <v>11</v>
       </c>
       <c r="D68">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="E68" t="s">
         <v>292</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>204</v>
+        <v>285</v>
       </c>
       <c r="G68" t="s">
-        <v>226</v>
+        <v>284</v>
       </c>
       <c r="H68" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="I68" s="3">
-        <v>947291</v>
+        <v>1218509</v>
       </c>
       <c r="O68" t="s">
-        <v>38</v>
+        <v>156</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>227</v>
+        <v>286</v>
       </c>
     </row>
     <row r="69" spans="1:16">
       <c r="A69" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>322</v>
+        <v>543</v>
       </c>
       <c r="C69" t="s">
         <v>11</v>
       </c>
       <c r="D69">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="E69" t="s">
         <v>292</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>239</v>
+        <v>204</v>
       </c>
       <c r="G69" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="H69" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="I69" s="3">
-        <v>802315</v>
+        <v>947291</v>
       </c>
       <c r="O69" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
     </row>
     <row r="70" spans="1:16">
       <c r="A70" s="1" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C70" t="s">
         <v>11</v>
       </c>
       <c r="D70">
-        <v>2017</v>
+        <v>2011</v>
       </c>
       <c r="E70" t="s">
         <v>292</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="G70" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="H70" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="I70" s="3">
-        <v>617188</v>
+        <v>802315</v>
       </c>
       <c r="O70" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
     </row>
     <row r="71" spans="1:16">
       <c r="A71" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C71" t="s">
         <v>11</v>
       </c>
       <c r="D71">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="E71" t="s">
         <v>292</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="G71" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H71" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I71" s="3">
-        <v>613506</v>
+        <v>617188</v>
       </c>
       <c r="O71" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P71" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="72" spans="1:16">
       <c r="A72" s="1" t="s">
-        <v>134</v>
+        <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>545</v>
+        <v>323</v>
       </c>
       <c r="C72" t="s">
         <v>11</v>
       </c>
       <c r="D72">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E72" t="s">
         <v>292</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>247</v>
+        <v>189</v>
       </c>
       <c r="G72" t="s">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="H72" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="I72" s="3">
-        <v>587879</v>
+        <v>613506</v>
       </c>
       <c r="O72" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="P72" s="2" t="s">
-        <v>261</v>
+        <v>221</v>
       </c>
     </row>
     <row r="73" spans="1:16">
       <c r="A73" s="1" t="s">
-        <v>293</v>
+        <v>134</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C73" t="s">
         <v>11</v>
       </c>
       <c r="D73">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="E73" t="s">
         <v>292</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>207</v>
+        <v>247</v>
       </c>
       <c r="G73" t="s">
-        <v>295</v>
+        <v>260</v>
       </c>
       <c r="H73" t="s">
-        <v>294</v>
+        <v>122</v>
       </c>
       <c r="I73" s="3">
-        <v>562667</v>
+        <v>587879</v>
       </c>
       <c r="O73" t="s">
-        <v>297</v>
+        <v>146</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>296</v>
+        <v>261</v>
       </c>
     </row>
     <row r="74" spans="1:16">
       <c r="A74" s="1" t="s">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>325</v>
+        <v>545</v>
       </c>
       <c r="C74" t="s">
         <v>11</v>
       </c>
       <c r="D74">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="E74" t="s">
         <v>292</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="G74" t="s">
-        <v>250</v>
+        <v>295</v>
       </c>
       <c r="H74" t="s">
-        <v>249</v>
+        <v>294</v>
       </c>
       <c r="I74" s="3">
-        <v>552739</v>
+        <v>562667</v>
       </c>
       <c r="O74" t="s">
-        <v>46</v>
+        <v>297</v>
       </c>
       <c r="P74" s="2" t="s">
-        <v>251</v>
+        <v>296</v>
       </c>
     </row>
     <row r="75" spans="1:16">
       <c r="A75" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>547</v>
+        <v>324</v>
       </c>
       <c r="C75" t="s">
         <v>11</v>
       </c>
       <c r="D75">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E75" t="s">
         <v>292</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>247</v>
+        <v>195</v>
       </c>
       <c r="G75" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="H75" t="s">
-        <v>118</v>
+        <v>249</v>
       </c>
       <c r="I75" s="3">
-        <v>517958</v>
+        <v>552739</v>
       </c>
       <c r="O75" t="s">
-        <v>290</v>
+        <v>46</v>
       </c>
       <c r="P75" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="76" spans="1:16">
       <c r="A76" s="1" t="s">
-        <v>319</v>
+        <v>81</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>326</v>
+        <v>546</v>
       </c>
       <c r="C76" t="s">
         <v>11</v>
       </c>
       <c r="D76">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="E76" t="s">
         <v>292</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>198</v>
+        <v>247</v>
       </c>
       <c r="G76" t="s">
-        <v>363</v>
+        <v>246</v>
       </c>
       <c r="H76" t="s">
-        <v>362</v>
+        <v>118</v>
       </c>
       <c r="I76" s="3">
-        <v>483734</v>
+        <v>517958</v>
       </c>
       <c r="O76" t="s">
-        <v>338</v>
+        <v>290</v>
       </c>
       <c r="P76" s="2" t="s">
-        <v>364</v>
+        <v>248</v>
       </c>
     </row>
     <row r="77" spans="1:16">
       <c r="A77" s="1" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C77" t="s">
         <v>11</v>
       </c>
       <c r="D77">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="E77" t="s">
         <v>292</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="G77" t="s">
-        <v>391</v>
+        <v>362</v>
       </c>
       <c r="H77" t="s">
-        <v>311</v>
+        <v>361</v>
       </c>
       <c r="I77" s="3">
-        <v>470562</v>
+        <v>483734</v>
       </c>
       <c r="O77" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="P77" s="2" t="s">
-        <v>392</v>
+        <v>363</v>
       </c>
     </row>
     <row r="78" spans="1:16">
       <c r="A78" s="1" t="s">
-        <v>142</v>
+        <v>329</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C78" t="s">
         <v>11</v>
       </c>
       <c r="D78">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="E78" t="s">
         <v>292</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>277</v>
+        <v>207</v>
       </c>
       <c r="G78" t="s">
-        <v>279</v>
+        <v>390</v>
       </c>
       <c r="H78" t="s">
-        <v>130</v>
+        <v>310</v>
       </c>
       <c r="I78" s="3">
-        <v>349359</v>
+        <v>470562</v>
       </c>
       <c r="O78" t="s">
-        <v>154</v>
+        <v>345</v>
       </c>
       <c r="P78" s="2" t="s">
-        <v>280</v>
+        <v>391</v>
       </c>
     </row>
     <row r="79" spans="1:16">
       <c r="A79" s="1" t="s">
-        <v>64</v>
+        <v>142</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C79" t="s">
         <v>11</v>
       </c>
       <c r="D79">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="E79" t="s">
         <v>292</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>202</v>
+        <v>277</v>
       </c>
       <c r="G79" t="s">
-        <v>201</v>
+        <v>279</v>
       </c>
       <c r="H79" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I79" s="3">
-        <v>290313</v>
+        <v>349359</v>
       </c>
       <c r="O79" t="s">
-        <v>30</v>
+        <v>154</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>203</v>
+        <v>280</v>
       </c>
     </row>
     <row r="80" spans="1:16">
       <c r="A80" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C80" t="s">
         <v>11</v>
       </c>
       <c r="D80">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="E80" t="s">
         <v>292</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G80" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="H80" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I80" s="3">
-        <v>243599</v>
+        <v>290313</v>
       </c>
       <c r="O80" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P80" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="81" spans="1:16">
       <c r="A81" s="1" t="s">
-        <v>139</v>
+        <v>65</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C81" t="s">
         <v>11</v>
       </c>
       <c r="D81">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="E81" t="s">
         <v>292</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="G81" t="s">
-        <v>271</v>
+        <v>205</v>
       </c>
       <c r="H81" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I81" s="3">
-        <v>189629</v>
+        <v>243599</v>
       </c>
       <c r="O81" t="s">
-        <v>151</v>
+        <v>31</v>
       </c>
       <c r="P81" s="2" t="s">
-        <v>272</v>
+        <v>206</v>
       </c>
     </row>
     <row r="82" spans="1:16">
       <c r="A82" s="1" t="s">
-        <v>331</v>
+        <v>139</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C82" t="s">
         <v>11</v>
       </c>
       <c r="D82">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="E82" t="s">
         <v>292</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>247</v>
+        <v>198</v>
       </c>
       <c r="G82" t="s">
-        <v>393</v>
+        <v>271</v>
       </c>
       <c r="H82" t="s">
-        <v>312</v>
+        <v>127</v>
       </c>
       <c r="I82" s="3">
-        <v>154914</v>
+        <v>189629</v>
       </c>
       <c r="O82" t="s">
-        <v>347</v>
+        <v>151</v>
       </c>
       <c r="P82" s="2" t="s">
-        <v>394</v>
+        <v>272</v>
       </c>
     </row>
     <row r="83" spans="1:16">
       <c r="A83" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C83" t="s">
         <v>11</v>
       </c>
       <c r="D83">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E83" t="s">
         <v>292</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>173</v>
+        <v>247</v>
       </c>
       <c r="G83" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="H83" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I83" s="3">
-        <v>147091</v>
+        <v>154914</v>
       </c>
       <c r="O83" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
     </row>
     <row r="84" spans="1:16">
       <c r="A84" s="1" t="s">
-        <v>63</v>
+        <v>325</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>548</v>
+        <v>332</v>
       </c>
       <c r="C84" t="s">
         <v>11</v>
       </c>
       <c r="D84">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="E84" t="s">
         <v>292</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="G84" t="s">
-        <v>199</v>
+        <v>380</v>
       </c>
       <c r="H84" t="s">
-        <v>100</v>
+        <v>306</v>
       </c>
       <c r="I84" s="3">
-        <v>136424</v>
+        <v>147091</v>
       </c>
       <c r="O84" t="s">
-        <v>29</v>
+        <v>342</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>200</v>
+        <v>381</v>
       </c>
     </row>
     <row r="85" spans="1:16">
       <c r="A85" s="1" t="s">
-        <v>333</v>
+        <v>63</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C85" t="s">
         <v>11</v>
@@ -5840,65 +5977,65 @@
         <v>292</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>158</v>
+        <v>198</v>
       </c>
       <c r="G85" t="s">
-        <v>397</v>
+        <v>199</v>
       </c>
       <c r="H85" t="s">
-        <v>314</v>
+        <v>100</v>
       </c>
       <c r="I85" s="3">
-        <v>136234</v>
+        <v>136424</v>
       </c>
       <c r="O85" t="s">
-        <v>349</v>
+        <v>29</v>
       </c>
       <c r="P85" s="2" t="s">
-        <v>398</v>
+        <v>200</v>
       </c>
     </row>
     <row r="86" spans="1:16">
       <c r="A86" s="1" t="s">
-        <v>141</v>
+        <v>332</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C86" t="s">
         <v>11</v>
       </c>
       <c r="D86">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="E86" t="s">
         <v>292</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>277</v>
+        <v>158</v>
       </c>
       <c r="G86" t="s">
-        <v>276</v>
+        <v>396</v>
       </c>
       <c r="H86" t="s">
-        <v>129</v>
+        <v>313</v>
       </c>
       <c r="I86" s="3">
-        <v>99365</v>
+        <v>136234</v>
       </c>
       <c r="O86" t="s">
-        <v>153</v>
+        <v>348</v>
       </c>
       <c r="P86" s="2" t="s">
-        <v>278</v>
+        <v>397</v>
       </c>
     </row>
     <row r="87" spans="1:16">
       <c r="A87" s="1" t="s">
-        <v>320</v>
+        <v>141</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C87" t="s">
         <v>11</v>
@@ -5910,65 +6047,65 @@
         <v>292</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="G87" t="s">
-        <v>367</v>
+        <v>276</v>
       </c>
       <c r="H87" t="s">
-        <v>302</v>
+        <v>129</v>
       </c>
       <c r="I87" s="3">
-        <v>67758</v>
+        <v>99365</v>
       </c>
       <c r="O87" t="s">
-        <v>339</v>
+        <v>153</v>
       </c>
       <c r="P87" s="2" t="s">
-        <v>365</v>
+        <v>278</v>
       </c>
     </row>
     <row r="88" spans="1:16">
       <c r="A88" s="1" t="s">
-        <v>77</v>
+        <v>319</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C88" t="s">
         <v>11</v>
       </c>
       <c r="D88">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="E88" t="s">
         <v>292</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="G88" t="s">
-        <v>235</v>
+        <v>366</v>
       </c>
       <c r="H88" t="s">
-        <v>114</v>
+        <v>301</v>
       </c>
       <c r="I88" s="3">
-        <v>25178</v>
+        <v>67758</v>
       </c>
       <c r="O88" t="s">
-        <v>42</v>
+        <v>338</v>
       </c>
       <c r="P88" s="2" t="s">
-        <v>237</v>
+        <v>364</v>
       </c>
     </row>
     <row r="89" spans="1:16">
       <c r="A89" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C89" t="s">
         <v>11</v>
@@ -5980,106 +6117,100 @@
         <v>292</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>173</v>
+        <v>236</v>
       </c>
       <c r="G89" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="H89" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="I89" s="3">
-        <v>19483</v>
+        <v>25178</v>
       </c>
       <c r="O89" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P89" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
     </row>
     <row r="90" spans="1:16">
       <c r="A90" s="1" t="s">
-        <v>332</v>
+        <v>74</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C90" t="s">
         <v>11</v>
       </c>
       <c r="D90">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="E90" t="s">
         <v>292</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>396</v>
+        <v>173</v>
       </c>
       <c r="G90" t="s">
-        <v>395</v>
+        <v>228</v>
       </c>
       <c r="H90" t="s">
-        <v>313</v>
+        <v>111</v>
       </c>
       <c r="I90" s="3">
-        <v>15835</v>
+        <v>19483</v>
       </c>
       <c r="O90" t="s">
-        <v>348</v>
+        <v>39</v>
       </c>
       <c r="P90" s="2" t="s">
-        <v>399</v>
+        <v>229</v>
       </c>
     </row>
     <row r="91" spans="1:16">
       <c r="A91" s="1" t="s">
-        <v>556</v>
+        <v>331</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="C91" t="s">
         <v>11</v>
       </c>
       <c r="D91">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="E91" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>198</v>
+        <v>395</v>
       </c>
       <c r="G91" t="s">
-        <v>567</v>
+        <v>394</v>
       </c>
       <c r="H91" t="s">
-        <v>566</v>
+        <v>312</v>
       </c>
       <c r="I91" s="3">
-        <v>744361</v>
-      </c>
-      <c r="K91" s="4" t="s">
-        <v>573</v>
-      </c>
-      <c r="N91" s="3">
-        <v>1</v>
+        <v>15835</v>
       </c>
       <c r="O91" t="s">
-        <v>569</v>
+        <v>347</v>
       </c>
       <c r="P91" s="2" t="s">
-        <v>568</v>
+        <v>398</v>
       </c>
     </row>
     <row r="92" spans="1:16">
       <c r="A92" s="1" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C92" t="s">
         <v>11</v>
@@ -6091,30 +6222,36 @@
         <v>291</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="G92" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="H92" t="s">
-        <v>574</v>
+        <v>565</v>
+      </c>
+      <c r="I92" s="3">
+        <v>744361</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="N92" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>570</v>
+        <v>568</v>
+      </c>
+      <c r="P92" s="2" t="s">
+        <v>567</v>
       </c>
     </row>
     <row r="93" spans="1:16">
       <c r="A93" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C93" t="s">
         <v>11</v>
@@ -6126,30 +6263,30 @@
         <v>291</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>580</v>
+        <v>173</v>
       </c>
       <c r="G93" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="H93" t="s">
-        <v>575</v>
-      </c>
-      <c r="K93" s="5" t="s">
-        <v>582</v>
+        <v>573</v>
+      </c>
+      <c r="K93" s="4" t="s">
+        <v>579</v>
       </c>
       <c r="N93" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O93" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="94" spans="1:16">
       <c r="A94" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C94" t="s">
         <v>11</v>
@@ -6161,99 +6298,312 @@
         <v>291</v>
       </c>
       <c r="F94" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="G94" t="s">
+        <v>576</v>
+      </c>
+      <c r="H94" t="s">
+        <v>574</v>
+      </c>
+      <c r="K94" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="N94" s="3">
+        <v>3</v>
+      </c>
+      <c r="O94" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16">
+      <c r="A95" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="C95" t="s">
+        <v>11</v>
+      </c>
+      <c r="D95">
+        <v>2021</v>
+      </c>
+      <c r="E95" t="s">
+        <v>291</v>
+      </c>
+      <c r="F95" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="G94" t="s">
-        <v>579</v>
-      </c>
-      <c r="H94" t="s">
-        <v>578</v>
-      </c>
-      <c r="K94" s="5" t="s">
-        <v>583</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="G95" t="s">
+        <v>577</v>
+      </c>
+      <c r="H95" t="s">
+        <v>588</v>
+      </c>
+      <c r="I95" s="3">
+        <v>177237</v>
+      </c>
+      <c r="K95" s="5" t="s">
+        <v>581</v>
+      </c>
+      <c r="N95" s="3">
         <v>5</v>
       </c>
-      <c r="O94" t="s">
-        <v>572</v>
+      <c r="O95" t="s">
+        <v>571</v>
+      </c>
+      <c r="P95" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16">
+      <c r="A96" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="C96" t="s">
+        <v>11</v>
+      </c>
+      <c r="D96">
+        <v>2021</v>
+      </c>
+      <c r="E96" t="s">
+        <v>291</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G96" t="s">
+        <v>595</v>
+      </c>
+      <c r="H96" t="s">
+        <v>591</v>
+      </c>
+      <c r="I96" s="3">
+        <v>51449</v>
+      </c>
+      <c r="O96" t="s">
+        <v>597</v>
+      </c>
+      <c r="P96" s="2" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16">
+      <c r="A97" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="C97" t="s">
+        <v>11</v>
+      </c>
+      <c r="D97">
+        <v>2021</v>
+      </c>
+      <c r="E97" t="s">
+        <v>291</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G97" t="s">
+        <v>601</v>
+      </c>
+      <c r="H97" t="s">
+        <v>608</v>
+      </c>
+      <c r="I97" s="3">
+        <v>1393142</v>
+      </c>
+      <c r="O97" t="s">
+        <v>602</v>
+      </c>
+      <c r="P97" s="2" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16">
+      <c r="A98" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="C98" t="s">
+        <v>11</v>
+      </c>
+      <c r="D98">
+        <v>2021</v>
+      </c>
+      <c r="E98" t="s">
+        <v>291</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G98" t="s">
+        <v>609</v>
+      </c>
+      <c r="H98" t="s">
+        <v>607</v>
+      </c>
+      <c r="I98" s="3">
+        <v>768229</v>
+      </c>
+      <c r="O98" t="s">
+        <v>603</v>
+      </c>
+      <c r="P98" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16">
+      <c r="A99" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="C99" t="s">
+        <v>11</v>
+      </c>
+      <c r="D99">
+        <v>2021</v>
+      </c>
+      <c r="E99" t="s">
+        <v>291</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="G99" t="s">
+        <v>613</v>
+      </c>
+      <c r="H99" t="s">
+        <v>610</v>
+      </c>
+      <c r="I99" s="3">
+        <v>166812</v>
+      </c>
+      <c r="O99" t="s">
+        <v>614</v>
+      </c>
+      <c r="P99" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16">
+      <c r="A100" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="C100" t="s">
+        <v>11</v>
+      </c>
+      <c r="D100">
+        <v>2021</v>
+      </c>
+      <c r="E100" t="s">
+        <v>291</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="G100" t="s">
+        <v>620</v>
+      </c>
+      <c r="H100" t="s">
+        <v>621</v>
+      </c>
+      <c r="O100" t="s">
+        <v>616</v>
+      </c>
+      <c r="P100" s="2" t="s">
+        <v>617</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P90">
-    <sortCondition ref="B2:B90"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P91">
+    <sortCondition ref="B2:B91"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="P50" r:id="rId1" xr:uid="{725A3016-CC80-5F4A-B091-4E71BCFAD36B}"/>
+    <hyperlink ref="P51" r:id="rId1" xr:uid="{725A3016-CC80-5F4A-B091-4E71BCFAD36B}"/>
     <hyperlink ref="P13" r:id="rId2" xr:uid="{38F493C0-3185-604E-A3BD-AAB0EC5B83DF}"/>
-    <hyperlink ref="P35" r:id="rId3" xr:uid="{2E642780-E9D7-BF4B-9D23-FEBE51DDD0C9}"/>
+    <hyperlink ref="P36" r:id="rId3" xr:uid="{2E642780-E9D7-BF4B-9D23-FEBE51DDD0C9}"/>
     <hyperlink ref="P17" r:id="rId4" xr:uid="{5CF6DEF3-9028-3D4C-846C-DA2618807577}"/>
-    <hyperlink ref="P49" r:id="rId5" xr:uid="{A298B622-5340-5148-820B-D468159EA5BD}"/>
-    <hyperlink ref="P43" r:id="rId6" xr:uid="{EF9BC619-52CD-2D48-BE99-80BD81A8CD54}"/>
-    <hyperlink ref="P38" r:id="rId7" xr:uid="{0002A242-754F-5A40-86A8-5F7DBBEBB9D1}"/>
-    <hyperlink ref="P37" r:id="rId8" xr:uid="{085C9D3E-4AFA-FF48-AA1A-64ECF275D4C0}"/>
-    <hyperlink ref="P39" r:id="rId9" xr:uid="{118F4CA9-C4A7-F74E-8AFF-041FB2741717}"/>
+    <hyperlink ref="P50" r:id="rId5" xr:uid="{A298B622-5340-5148-820B-D468159EA5BD}"/>
+    <hyperlink ref="P44" r:id="rId6" xr:uid="{EF9BC619-52CD-2D48-BE99-80BD81A8CD54}"/>
+    <hyperlink ref="P39" r:id="rId7" xr:uid="{0002A242-754F-5A40-86A8-5F7DBBEBB9D1}"/>
+    <hyperlink ref="P38" r:id="rId8" xr:uid="{085C9D3E-4AFA-FF48-AA1A-64ECF275D4C0}"/>
+    <hyperlink ref="P40" r:id="rId9" xr:uid="{118F4CA9-C4A7-F74E-8AFF-041FB2741717}"/>
     <hyperlink ref="P20" r:id="rId10" xr:uid="{75687EB7-0A29-5C47-921B-954A17F06565}"/>
     <hyperlink ref="P14" r:id="rId11" xr:uid="{81B8E0D0-29DD-E74A-8CE3-1464ECDB131A}"/>
-    <hyperlink ref="P42" r:id="rId12" xr:uid="{5D4D2728-3F60-EE43-86DF-EE58ADBF8432}"/>
+    <hyperlink ref="P43" r:id="rId12" xr:uid="{5D4D2728-3F60-EE43-86DF-EE58ADBF8432}"/>
     <hyperlink ref="P18" r:id="rId13" xr:uid="{31C21087-E027-4542-80B2-C095CF193FA7}"/>
     <hyperlink ref="P30" r:id="rId14" xr:uid="{36CFF13A-82D4-9642-B07B-0C3E49B5D215}"/>
-    <hyperlink ref="P51" r:id="rId15" xr:uid="{DDDE99D5-3422-6549-8393-D5FC330D45B8}"/>
-    <hyperlink ref="P55" r:id="rId16" xr:uid="{9621A5D4-6BD1-984D-9C8C-2A89CFA54CFF}"/>
-    <hyperlink ref="P84" r:id="rId17" xr:uid="{CC87EE91-DF39-EA48-9614-33030270159C}"/>
-    <hyperlink ref="P79" r:id="rId18" xr:uid="{C4E1F448-AF1B-BC43-983F-FB439266392E}"/>
-    <hyperlink ref="P80" r:id="rId19" xr:uid="{17A665F7-B807-4640-B444-16CFE27D5FDF}"/>
-    <hyperlink ref="P61" r:id="rId20" xr:uid="{244C8E1D-D3A7-9549-9D73-8F4D984A6ACD}"/>
-    <hyperlink ref="P52" r:id="rId21" xr:uid="{135AB67A-502A-8A4D-B049-40F78987A6E4}"/>
-    <hyperlink ref="P46" r:id="rId22" xr:uid="{2EBEE3F8-DF57-0E4A-9FB8-2C6B08B9453B}"/>
-    <hyperlink ref="P60" r:id="rId23" xr:uid="{50C93161-BA50-264D-9EB0-FD96B5179BD3}"/>
-    <hyperlink ref="P70" r:id="rId24" xr:uid="{EB1586AB-126F-2B4B-AB36-6A028744AF76}"/>
-    <hyperlink ref="P71" r:id="rId25" xr:uid="{7C55426F-9022-8044-ACAA-5AEC9137C037}"/>
-    <hyperlink ref="P62" r:id="rId26" xr:uid="{AD424BE3-B862-2442-B3B2-5028AF918C6F}"/>
-    <hyperlink ref="P68" r:id="rId27" xr:uid="{2183D387-1FD2-324D-A080-BF2A14B2C266}"/>
-    <hyperlink ref="P89" r:id="rId28" xr:uid="{FDBD3899-8300-BE4F-B928-93EB7382FF06}"/>
-    <hyperlink ref="P33" r:id="rId29" xr:uid="{529C6D37-3C52-0C4C-8560-C27F3F7C2BCE}"/>
+    <hyperlink ref="P52" r:id="rId15" xr:uid="{DDDE99D5-3422-6549-8393-D5FC330D45B8}"/>
+    <hyperlink ref="P56" r:id="rId16" xr:uid="{9621A5D4-6BD1-984D-9C8C-2A89CFA54CFF}"/>
+    <hyperlink ref="P85" r:id="rId17" xr:uid="{CC87EE91-DF39-EA48-9614-33030270159C}"/>
+    <hyperlink ref="P80" r:id="rId18" xr:uid="{C4E1F448-AF1B-BC43-983F-FB439266392E}"/>
+    <hyperlink ref="P81" r:id="rId19" xr:uid="{17A665F7-B807-4640-B444-16CFE27D5FDF}"/>
+    <hyperlink ref="P62" r:id="rId20" xr:uid="{244C8E1D-D3A7-9549-9D73-8F4D984A6ACD}"/>
+    <hyperlink ref="P53" r:id="rId21" xr:uid="{135AB67A-502A-8A4D-B049-40F78987A6E4}"/>
+    <hyperlink ref="P47" r:id="rId22" xr:uid="{2EBEE3F8-DF57-0E4A-9FB8-2C6B08B9453B}"/>
+    <hyperlink ref="P61" r:id="rId23" xr:uid="{50C93161-BA50-264D-9EB0-FD96B5179BD3}"/>
+    <hyperlink ref="P71" r:id="rId24" xr:uid="{EB1586AB-126F-2B4B-AB36-6A028744AF76}"/>
+    <hyperlink ref="P72" r:id="rId25" xr:uid="{7C55426F-9022-8044-ACAA-5AEC9137C037}"/>
+    <hyperlink ref="P63" r:id="rId26" xr:uid="{AD424BE3-B862-2442-B3B2-5028AF918C6F}"/>
+    <hyperlink ref="P69" r:id="rId27" xr:uid="{2183D387-1FD2-324D-A080-BF2A14B2C266}"/>
+    <hyperlink ref="P90" r:id="rId28" xr:uid="{FDBD3899-8300-BE4F-B928-93EB7382FF06}"/>
+    <hyperlink ref="P34" r:id="rId29" xr:uid="{529C6D37-3C52-0C4C-8560-C27F3F7C2BCE}"/>
     <hyperlink ref="P5" r:id="rId30" xr:uid="{D004E2AA-6899-A547-B940-4CF0A68E6AE2}"/>
-    <hyperlink ref="P88" r:id="rId31" xr:uid="{2DA721C4-AB3A-EB48-85F9-525AB6A822AB}"/>
-    <hyperlink ref="P69" r:id="rId32" xr:uid="{72A6DA76-289B-1945-8072-DAECE2441387}"/>
+    <hyperlink ref="P89" r:id="rId31" xr:uid="{2DA721C4-AB3A-EB48-85F9-525AB6A822AB}"/>
+    <hyperlink ref="P70" r:id="rId32" xr:uid="{72A6DA76-289B-1945-8072-DAECE2441387}"/>
     <hyperlink ref="P24" r:id="rId33" xr:uid="{1ED33379-967F-8D43-85DD-BDDF4C65376C}"/>
-    <hyperlink ref="P57" r:id="rId34" xr:uid="{F704F2D4-3F11-614C-BFFC-5AA6E996A592}"/>
-    <hyperlink ref="P75" r:id="rId35" xr:uid="{5F94CB6B-2D0C-7C41-9363-23A9286E6D55}"/>
-    <hyperlink ref="P74" r:id="rId36" xr:uid="{02572C89-38D3-4B47-B603-D75FBB76E0BB}"/>
-    <hyperlink ref="P56" r:id="rId37" xr:uid="{96F331DE-1BF1-354F-9E54-FA8C80316EFB}"/>
-    <hyperlink ref="P66" r:id="rId38" xr:uid="{D40AF006-F71D-054C-BD53-C9CF18C19E2B}"/>
-    <hyperlink ref="P72" r:id="rId39" xr:uid="{D3ABB7B3-002B-9E42-A591-D3282F8D9EDC}"/>
+    <hyperlink ref="P58" r:id="rId34" xr:uid="{F704F2D4-3F11-614C-BFFC-5AA6E996A592}"/>
+    <hyperlink ref="P76" r:id="rId35" xr:uid="{5F94CB6B-2D0C-7C41-9363-23A9286E6D55}"/>
+    <hyperlink ref="P75" r:id="rId36" xr:uid="{02572C89-38D3-4B47-B603-D75FBB76E0BB}"/>
+    <hyperlink ref="P57" r:id="rId37" xr:uid="{96F331DE-1BF1-354F-9E54-FA8C80316EFB}"/>
+    <hyperlink ref="P67" r:id="rId38" xr:uid="{D40AF006-F71D-054C-BD53-C9CF18C19E2B}"/>
+    <hyperlink ref="P73" r:id="rId39" xr:uid="{D3ABB7B3-002B-9E42-A591-D3282F8D9EDC}"/>
     <hyperlink ref="P28" r:id="rId40" xr:uid="{F2CD1548-C098-164F-AE85-0E2D85DE116F}"/>
-    <hyperlink ref="P40" r:id="rId41" xr:uid="{81094FDB-D745-024E-BD73-D63401EE9AA2}"/>
-    <hyperlink ref="P54" r:id="rId42" xr:uid="{850F5B2D-3612-1E44-A230-B654A61C2B8F}"/>
-    <hyperlink ref="P47" r:id="rId43" xr:uid="{D84F734D-746E-B841-A450-F741C1E43856}"/>
-    <hyperlink ref="P81" r:id="rId44" xr:uid="{7870E1C9-1855-634F-8B01-0A6F56E1C8EC}"/>
-    <hyperlink ref="P58" r:id="rId45" xr:uid="{74E258E9-3406-444C-9382-59C9A5DD2D28}"/>
-    <hyperlink ref="P86" r:id="rId46" xr:uid="{22AFEECC-9483-CC40-B244-DB64D5BE611A}"/>
-    <hyperlink ref="P78" r:id="rId47" xr:uid="{3F60EBBC-9A66-404C-8F8D-E0FD74919AF5}"/>
-    <hyperlink ref="P41" r:id="rId48" xr:uid="{97FC090B-C1AF-3B40-8E1E-653AF871E0B8}"/>
-    <hyperlink ref="P67" r:id="rId49" xr:uid="{24271837-2997-A04B-B1A8-30D8EAA5AABF}"/>
-    <hyperlink ref="P73" r:id="rId50" xr:uid="{C6FE7874-DE1E-8744-8F7F-A7266A282BC7}"/>
-    <hyperlink ref="P36" r:id="rId51" xr:uid="{45D4B454-64FD-E043-9E1E-D98B915DA3C4}"/>
-    <hyperlink ref="P48" r:id="rId52" xr:uid="{592E8301-AD04-6A43-BE2C-DF1DCF4D0C8C}"/>
-    <hyperlink ref="P45" r:id="rId53" xr:uid="{AFFE99AD-C3BD-7D47-ADD2-0033AB1BD297}"/>
+    <hyperlink ref="P41" r:id="rId41" xr:uid="{81094FDB-D745-024E-BD73-D63401EE9AA2}"/>
+    <hyperlink ref="P55" r:id="rId42" xr:uid="{850F5B2D-3612-1E44-A230-B654A61C2B8F}"/>
+    <hyperlink ref="P48" r:id="rId43" xr:uid="{D84F734D-746E-B841-A450-F741C1E43856}"/>
+    <hyperlink ref="P82" r:id="rId44" xr:uid="{7870E1C9-1855-634F-8B01-0A6F56E1C8EC}"/>
+    <hyperlink ref="P59" r:id="rId45" xr:uid="{74E258E9-3406-444C-9382-59C9A5DD2D28}"/>
+    <hyperlink ref="P87" r:id="rId46" xr:uid="{22AFEECC-9483-CC40-B244-DB64D5BE611A}"/>
+    <hyperlink ref="P79" r:id="rId47" xr:uid="{3F60EBBC-9A66-404C-8F8D-E0FD74919AF5}"/>
+    <hyperlink ref="P42" r:id="rId48" xr:uid="{97FC090B-C1AF-3B40-8E1E-653AF871E0B8}"/>
+    <hyperlink ref="P68" r:id="rId49" xr:uid="{24271837-2997-A04B-B1A8-30D8EAA5AABF}"/>
+    <hyperlink ref="P74" r:id="rId50" xr:uid="{C6FE7874-DE1E-8744-8F7F-A7266A282BC7}"/>
+    <hyperlink ref="P37" r:id="rId51" xr:uid="{45D4B454-64FD-E043-9E1E-D98B915DA3C4}"/>
+    <hyperlink ref="P49" r:id="rId52" xr:uid="{592E8301-AD04-6A43-BE2C-DF1DCF4D0C8C}"/>
+    <hyperlink ref="P46" r:id="rId53" xr:uid="{AFFE99AD-C3BD-7D47-ADD2-0033AB1BD297}"/>
     <hyperlink ref="P8" r:id="rId54" xr:uid="{10637FCE-769F-EF46-AFAF-F312278F1225}"/>
-    <hyperlink ref="P76" r:id="rId55" xr:uid="{1E8D6F6E-5279-684F-9870-749B17340F35}"/>
-    <hyperlink ref="P87" r:id="rId56" xr:uid="{C19F506D-023C-1247-BE6A-C23960198C51}"/>
-    <hyperlink ref="P34" r:id="rId57" xr:uid="{3E64B722-3690-B44C-ABC4-059D3B71C8D7}"/>
-    <hyperlink ref="P53" r:id="rId58" xr:uid="{50C3436F-19AF-D74F-8E0A-E9F0AEF4EF7F}"/>
+    <hyperlink ref="P77" r:id="rId55" xr:uid="{1E8D6F6E-5279-684F-9870-749B17340F35}"/>
+    <hyperlink ref="P88" r:id="rId56" xr:uid="{C19F506D-023C-1247-BE6A-C23960198C51}"/>
+    <hyperlink ref="P35" r:id="rId57" xr:uid="{3E64B722-3690-B44C-ABC4-059D3B71C8D7}"/>
+    <hyperlink ref="P54" r:id="rId58" xr:uid="{50C3436F-19AF-D74F-8E0A-E9F0AEF4EF7F}"/>
     <hyperlink ref="P25" r:id="rId59" xr:uid="{A5BBD32C-6F92-A842-A00C-8F17A0710E00}"/>
-    <hyperlink ref="P44" r:id="rId60" xr:uid="{117A81C3-427C-DF49-BA81-BE00A024107F}"/>
-    <hyperlink ref="P64" r:id="rId61" xr:uid="{5E89FA9C-5C01-5342-876F-D8B51FE4E2B8}"/>
-    <hyperlink ref="P83" r:id="rId62" xr:uid="{AE06ADB0-CCC6-5E4F-AA64-084B6EC4EDA5}"/>
-    <hyperlink ref="P59" r:id="rId63" xr:uid="{C1BBF821-4DC8-5347-B6F0-96939C529BA4}"/>
-    <hyperlink ref="P63" r:id="rId64" xr:uid="{990812EE-4D67-A148-8354-137377C29D95}"/>
+    <hyperlink ref="P45" r:id="rId60" xr:uid="{117A81C3-427C-DF49-BA81-BE00A024107F}"/>
+    <hyperlink ref="P65" r:id="rId61" xr:uid="{5E89FA9C-5C01-5342-876F-D8B51FE4E2B8}"/>
+    <hyperlink ref="P84" r:id="rId62" xr:uid="{AE06ADB0-CCC6-5E4F-AA64-084B6EC4EDA5}"/>
+    <hyperlink ref="P60" r:id="rId63" xr:uid="{C1BBF821-4DC8-5347-B6F0-96939C529BA4}"/>
+    <hyperlink ref="P64" r:id="rId64" xr:uid="{990812EE-4D67-A148-8354-137377C29D95}"/>
     <hyperlink ref="P7" r:id="rId65" xr:uid="{9C8D9D49-3342-1D45-9490-372911350A58}"/>
-    <hyperlink ref="P77" r:id="rId66" xr:uid="{EFDE2707-AAFE-A445-930B-DB05A658CF11}"/>
-    <hyperlink ref="P82" r:id="rId67" xr:uid="{C4CFA4B9-7F0C-2D48-848B-F4855312250F}"/>
-    <hyperlink ref="P85" r:id="rId68" xr:uid="{2C92D437-B811-BA4F-A7A0-ECBD7F90C3E8}"/>
-    <hyperlink ref="P90" r:id="rId69" xr:uid="{1DA360B3-3EEC-0B4A-92B2-F41887D4DA99}"/>
+    <hyperlink ref="P78" r:id="rId66" xr:uid="{EFDE2707-AAFE-A445-930B-DB05A658CF11}"/>
+    <hyperlink ref="P83" r:id="rId67" xr:uid="{C4CFA4B9-7F0C-2D48-848B-F4855312250F}"/>
+    <hyperlink ref="P86" r:id="rId68" xr:uid="{2C92D437-B811-BA4F-A7A0-ECBD7F90C3E8}"/>
+    <hyperlink ref="P91" r:id="rId69" xr:uid="{1DA360B3-3EEC-0B4A-92B2-F41887D4DA99}"/>
     <hyperlink ref="P2" r:id="rId70" xr:uid="{53707DD5-6AE9-244D-BE8B-768805F672D6}"/>
     <hyperlink ref="P3" r:id="rId71" xr:uid="{36EBDC68-249C-1C48-AAF4-2B47231ACC4B}"/>
     <hyperlink ref="P4" r:id="rId72" xr:uid="{A1D0B6A6-8992-754F-A034-0A1E7D5B9BCB}"/>
@@ -6273,7 +6623,14 @@
     <hyperlink ref="P29" r:id="rId86" xr:uid="{E7621B53-08FB-B74A-A424-0441D515E519}"/>
     <hyperlink ref="P31" r:id="rId87" xr:uid="{5A433509-4F2A-A14A-A833-86760759B3D9}"/>
     <hyperlink ref="P32" r:id="rId88" xr:uid="{BB2B37DA-456D-874A-BDF1-8CD5A80F949B}"/>
-    <hyperlink ref="P91" r:id="rId89" xr:uid="{8A9992FB-9BED-B24F-BB67-58D1B7E4F16C}"/>
+    <hyperlink ref="P92" r:id="rId89" xr:uid="{8A9992FB-9BED-B24F-BB67-58D1B7E4F16C}"/>
+    <hyperlink ref="P33" r:id="rId90" xr:uid="{04415B44-4167-8E48-9712-E43324798AF2}"/>
+    <hyperlink ref="P95" r:id="rId91" xr:uid="{1A01B6C3-1D4E-B94D-AD91-D10C37B355BE}"/>
+    <hyperlink ref="P96" r:id="rId92" xr:uid="{EDC1E283-6211-A049-A833-36C3977DF17A}"/>
+    <hyperlink ref="P97" r:id="rId93" xr:uid="{35C674F0-4B7E-C948-A2CE-31FC7FB9A295}"/>
+    <hyperlink ref="P98" r:id="rId94" xr:uid="{931BE5D0-DD8E-5E46-9B6A-034AA06BBFDE}"/>
+    <hyperlink ref="P99" r:id="rId95" xr:uid="{A0245193-6CAC-3F4F-9F85-D15A44DF7AA4}"/>
+    <hyperlink ref="P100" r:id="rId96" xr:uid="{6CBE15CD-F619-5746-8884-3F066BF8F37A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-1405-TVSeries.xlsx
+++ b/db/A7XLK-1405-TVSeries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE62A93-ECFA-7246-BFAD-CE22577C27DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C41C3849-54FC-DF4E-86AC-2F0DF1FF0433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3140" yWindow="4680" windowWidth="38780" windowHeight="17320" xr2:uid="{BAC94C6D-C196-2D4F-A2F2-89F0A182D671}"/>
+    <workbookView xWindow="1080" yWindow="4680" windowWidth="38780" windowHeight="17320" xr2:uid="{BAC94C6D-C196-2D4F-A2F2-89F0A182D671}"/>
   </bookViews>
   <sheets>
     <sheet name="今日電影" sheetId="1" r:id="rId1"/>
@@ -1162,10 +1162,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>我的砍價女王</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>我的前半生</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1636,10 +1632,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>理想之城</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>孫儷 趙又廷 於和偉 陳明昊 高葉 李傳纓 張澍 李洪濤 趙君</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2210,10 +2202,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>好好生活 *</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>八角亭謎霧 *</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2320,6 +2308,18 @@
   </si>
   <si>
     <t>北轍南轅 *</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>理想之城 **</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>好好生活 **</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我的砍價女王 **</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2746,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C1" t="s">
         <v>4</v>
@@ -2770,19 +2770,19 @@
         <v>3</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="O1" t="s">
         <v>1</v>
@@ -2793,7 +2793,7 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
@@ -2811,10 +2811,10 @@
         <v>170</v>
       </c>
       <c r="G2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I2" s="3">
         <v>3164608</v>
@@ -2823,21 +2823,21 @@
         <v>8.6</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="L2" s="3">
         <v>1</v>
       </c>
       <c r="O2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
@@ -2855,10 +2855,10 @@
         <v>161</v>
       </c>
       <c r="G3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="I3" s="3">
         <v>52300</v>
@@ -2867,21 +2867,21 @@
         <v>8.5</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="L3" s="3">
         <v>2</v>
       </c>
       <c r="O3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>49</v>
@@ -2896,13 +2896,13 @@
         <v>291</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I4" s="3">
         <v>489413</v>
@@ -2911,16 +2911,16 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="L4" s="3">
         <v>3</v>
       </c>
       <c r="O4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2955,7 +2955,7 @@
         <v>8.1</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="L5" s="3">
         <v>4</v>
@@ -2972,7 +2972,7 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>51</v>
@@ -2990,10 +2990,10 @@
         <v>161</v>
       </c>
       <c r="G6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I6" s="3">
         <v>95136</v>
@@ -3002,21 +3002,21 @@
         <v>7.9</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="L6" s="3">
         <v>5</v>
       </c>
       <c r="O6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>52</v>
@@ -3034,10 +3034,10 @@
         <v>170</v>
       </c>
       <c r="G7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I7" s="3">
         <v>767044</v>
@@ -3046,21 +3046,21 @@
         <v>7.8</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L7" s="3">
         <v>6</v>
       </c>
       <c r="O7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>53</v>
@@ -3078,7 +3078,7 @@
         <v>195</v>
       </c>
       <c r="G8" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H8" t="s">
         <v>300</v>
@@ -3090,21 +3090,21 @@
         <v>7.8</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="L8" s="3">
         <v>7</v>
       </c>
       <c r="O8" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>54</v>
@@ -3122,10 +3122,10 @@
         <v>173</v>
       </c>
       <c r="G9" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="H9" t="s">
-        <v>437</v>
+        <v>619</v>
       </c>
       <c r="I9" s="3">
         <v>2330511</v>
@@ -3134,7 +3134,7 @@
         <v>7.6</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="L9" s="3">
         <v>8</v>
@@ -3143,15 +3143,15 @@
         <v>5</v>
       </c>
       <c r="O9" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>55</v>
@@ -3169,10 +3169,10 @@
         <v>222</v>
       </c>
       <c r="G10" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="H10" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="I10" s="3">
         <v>548641</v>
@@ -3181,21 +3181,21 @@
         <v>7.6</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="L10" s="3">
         <v>9</v>
       </c>
       <c r="O10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>56</v>
@@ -3210,13 +3210,13 @@
         <v>291</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G11" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="H11" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I11" s="3">
         <v>52113</v>
@@ -3225,21 +3225,21 @@
         <v>7.5</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="L11" s="3">
         <v>10</v>
       </c>
       <c r="O11" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>57</v>
@@ -3257,10 +3257,10 @@
         <v>158</v>
       </c>
       <c r="G12" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H12" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I12" s="3">
         <v>134785</v>
@@ -3269,16 +3269,16 @@
         <v>7.5</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L12" s="3">
         <v>11</v>
       </c>
       <c r="O12" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -3313,7 +3313,7 @@
         <v>7.4</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="L13" s="3">
         <v>12</v>
@@ -3360,7 +3360,7 @@
         <v>7.4</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="L14" s="3">
         <v>13</v>
@@ -3377,7 +3377,7 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>60</v>
@@ -3392,13 +3392,13 @@
         <v>291</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="G15" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="H15" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="I15" s="3">
         <v>1278633</v>
@@ -3407,21 +3407,21 @@
         <v>7.3</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="L15" s="3">
         <v>14</v>
       </c>
       <c r="O15" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>61</v>
@@ -3439,10 +3439,10 @@
         <v>285</v>
       </c>
       <c r="G16" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="H16" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I16" s="3">
         <v>2043804</v>
@@ -3451,7 +3451,7 @@
         <v>7.2</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="L16" s="3">
         <v>15</v>
@@ -3460,10 +3460,10 @@
         <v>9</v>
       </c>
       <c r="O16" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -3498,7 +3498,7 @@
         <v>7.1</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L17" s="3">
         <v>16</v>
@@ -3545,7 +3545,7 @@
         <v>7.1</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L18" s="3">
         <v>17</v>
@@ -3559,7 +3559,7 @@
     </row>
     <row r="19" spans="1:16">
       <c r="A19" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>64</v>
@@ -3574,13 +3574,13 @@
         <v>291</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G19" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="H19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="I19" s="3">
         <v>785247</v>
@@ -3589,16 +3589,16 @@
         <v>7</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="L19" s="3">
         <v>18</v>
       </c>
       <c r="O19" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -3633,7 +3633,7 @@
         <v>7</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L20" s="3">
         <v>19</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="21" spans="1:16">
       <c r="A21" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>66</v>
@@ -3665,13 +3665,13 @@
         <v>291</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G21" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H21" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="I21" s="3">
         <v>89338</v>
@@ -3680,21 +3680,21 @@
         <v>7</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="L21" s="3">
         <v>20</v>
       </c>
       <c r="O21" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="22" spans="1:16">
       <c r="A22" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>67</v>
@@ -3712,30 +3712,30 @@
         <v>158</v>
       </c>
       <c r="G22" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="H22" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="I22" s="3">
         <v>1967351</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="M22" s="3">
         <v>5</v>
       </c>
       <c r="O22" t="s">
+        <v>491</v>
+      </c>
+      <c r="P22" s="2" t="s">
         <v>493</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="23" spans="1:16">
       <c r="A23" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>68</v>
@@ -3753,25 +3753,25 @@
         <v>170</v>
       </c>
       <c r="G23" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="H23" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="I23" s="3">
         <v>1724953</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="M23" s="3">
         <v>6</v>
       </c>
       <c r="O23" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -3803,7 +3803,7 @@
         <v>6002697</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="M24" s="3">
         <v>7</v>
@@ -3817,7 +3817,7 @@
     </row>
     <row r="25" spans="1:16">
       <c r="A25" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>70</v>
@@ -3835,7 +3835,7 @@
         <v>173</v>
       </c>
       <c r="G25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H25" t="s">
         <v>304</v>
@@ -3844,21 +3844,21 @@
         <v>1771888</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="M25" s="3">
         <v>10</v>
       </c>
       <c r="O25" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="26" spans="1:16">
       <c r="A26" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>71</v>
@@ -3873,33 +3873,33 @@
         <v>291</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="G26" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="H26" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="I26" s="3">
         <v>1646706</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="M26" s="3">
         <v>12</v>
       </c>
       <c r="O26" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="27" spans="1:16">
       <c r="A27" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>72</v>
@@ -3914,28 +3914,28 @@
         <v>291</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="G27" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="H27" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="I27" s="3">
         <v>1138386</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="M27" s="3">
         <v>13</v>
       </c>
       <c r="O27" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3967,7 +3967,7 @@
         <v>1560320</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="M28" s="3">
         <v>14</v>
@@ -3981,10 +3981,10 @@
     </row>
     <row r="29" spans="1:16">
       <c r="A29" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
@@ -3999,25 +3999,25 @@
         <v>170</v>
       </c>
       <c r="G29" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H29" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="I29" s="3">
         <v>2140583</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="M29" s="3">
         <v>16</v>
       </c>
       <c r="O29" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -4049,7 +4049,7 @@
         <v>1796008</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="M30" s="3">
         <v>17</v>
@@ -4063,7 +4063,7 @@
     </row>
     <row r="31" spans="1:16">
       <c r="A31" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>75</v>
@@ -4081,30 +4081,30 @@
         <v>167</v>
       </c>
       <c r="G31" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H31" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="I31" s="3">
         <v>6319</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="M31" s="3">
         <v>18</v>
       </c>
       <c r="O31" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="32" spans="1:16">
       <c r="A32" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>76</v>
@@ -4122,33 +4122,33 @@
         <v>184</v>
       </c>
       <c r="G32" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="H32" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="I32" s="3">
         <v>3326331</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="M32" s="3">
         <v>19</v>
       </c>
       <c r="O32" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="33" spans="1:16">
       <c r="A33" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C33" t="s">
         <v>11</v>
@@ -4163,19 +4163,19 @@
         <v>268</v>
       </c>
       <c r="G33" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="H33" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="I33" s="3">
         <v>261668</v>
       </c>
       <c r="O33" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -4215,7 +4215,7 @@
     </row>
     <row r="35" spans="1:16">
       <c r="A35" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>78</v>
@@ -4233,7 +4233,7 @@
         <v>170</v>
       </c>
       <c r="G35" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H35" t="s">
         <v>302</v>
@@ -4242,10 +4242,10 @@
         <v>5150111</v>
       </c>
       <c r="O35" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -4285,13 +4285,13 @@
     </row>
     <row r="37" spans="1:16">
       <c r="A37" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C37" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D37">
         <v>2021</v>
@@ -4300,10 +4300,10 @@
         <v>291</v>
       </c>
       <c r="F37" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="G37" t="s">
         <v>350</v>
-      </c>
-      <c r="G37" t="s">
-        <v>351</v>
       </c>
       <c r="H37" t="s">
         <v>298</v>
@@ -4312,10 +4312,10 @@
         <v>2535509</v>
       </c>
       <c r="O37" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -4393,7 +4393,7 @@
         <v>55</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C40" t="s">
         <v>11</v>
@@ -4533,7 +4533,7 @@
         <v>52</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C44" t="s">
         <v>11</v>
@@ -4562,7 +4562,7 @@
     </row>
     <row r="45" spans="1:16">
       <c r="A45" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>134</v>
@@ -4580,24 +4580,24 @@
         <v>173</v>
       </c>
       <c r="G45" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H45" t="s">
-        <v>305</v>
+        <v>621</v>
       </c>
       <c r="I45" s="3">
         <v>954238</v>
       </c>
       <c r="O45" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="46" spans="1:16">
       <c r="A46" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>135</v>
@@ -4612,10 +4612,10 @@
         <v>291</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H46" t="s">
         <v>299</v>
@@ -4624,10 +4624,10 @@
         <v>795715</v>
       </c>
       <c r="O46" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4635,7 +4635,7 @@
         <v>68</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C47" t="s">
         <v>11</v>
@@ -4702,7 +4702,7 @@
     </row>
     <row r="49" spans="1:16">
       <c r="A49" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>137</v>
@@ -4717,22 +4717,22 @@
         <v>291</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G49" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H49" t="s">
-        <v>590</v>
+        <v>620</v>
       </c>
       <c r="I49" s="3">
         <v>377267</v>
       </c>
       <c r="O49" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4740,7 +4740,7 @@
         <v>51</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C50" t="s">
         <v>11</v>
@@ -4845,7 +4845,7 @@
         <v>67</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C53" t="s">
         <v>11</v>
@@ -4877,7 +4877,7 @@
     </row>
     <row r="54" spans="1:16">
       <c r="A54" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>140</v>
@@ -4895,7 +4895,7 @@
         <v>158</v>
       </c>
       <c r="G54" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H54" t="s">
         <v>303</v>
@@ -4904,10 +4904,10 @@
         <v>98231</v>
       </c>
       <c r="O54" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4985,7 +4985,7 @@
         <v>83</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C57" t="s">
         <v>11</v>
@@ -5020,7 +5020,7 @@
         <v>80</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C58" t="s">
         <v>11</v>
@@ -5087,7 +5087,7 @@
     </row>
     <row r="60" spans="1:16">
       <c r="A60" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>144</v>
@@ -5105,19 +5105,19 @@
         <v>158</v>
       </c>
       <c r="G60" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H60" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I60" s="3">
         <v>4655514</v>
       </c>
       <c r="O60" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -5125,7 +5125,7 @@
         <v>69</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C61" t="s">
         <v>11</v>
@@ -5160,7 +5160,7 @@
         <v>66</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C62" t="s">
         <v>11</v>
@@ -5195,7 +5195,7 @@
         <v>72</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C63" t="s">
         <v>224</v>
@@ -5227,10 +5227,10 @@
     </row>
     <row r="64" spans="1:16">
       <c r="A64" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C64" t="s">
         <v>11</v>
@@ -5242,30 +5242,30 @@
         <v>292</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G64" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H64" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="I64" s="3">
         <v>2400663</v>
       </c>
       <c r="O64" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="65" spans="1:16">
       <c r="A65" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C65" t="s">
         <v>11</v>
@@ -5277,22 +5277,22 @@
         <v>292</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G65" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H65" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I65" s="3">
         <v>2340742</v>
       </c>
       <c r="O65" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="P65" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -5300,7 +5300,7 @@
         <v>133</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C66" t="s">
         <v>11</v>
@@ -5335,7 +5335,7 @@
         <v>84</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C67" t="s">
         <v>11</v>
@@ -5370,7 +5370,7 @@
         <v>144</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C68" t="s">
         <v>11</v>
@@ -5405,7 +5405,7 @@
         <v>73</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C69" t="s">
         <v>11</v>
@@ -5440,7 +5440,7 @@
         <v>78</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C70" t="s">
         <v>11</v>
@@ -5475,7 +5475,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C71" t="s">
         <v>11</v>
@@ -5510,7 +5510,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C72" t="s">
         <v>11</v>
@@ -5545,7 +5545,7 @@
         <v>134</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C73" t="s">
         <v>11</v>
@@ -5580,7 +5580,7 @@
         <v>293</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C74" t="s">
         <v>11</v>
@@ -5615,7 +5615,7 @@
         <v>82</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C75" t="s">
         <v>11</v>
@@ -5650,7 +5650,7 @@
         <v>81</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C76" t="s">
         <v>11</v>
@@ -5682,10 +5682,10 @@
     </row>
     <row r="77" spans="1:16">
       <c r="A77" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C77" t="s">
         <v>11</v>
@@ -5700,27 +5700,27 @@
         <v>198</v>
       </c>
       <c r="G77" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H77" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I77" s="3">
         <v>483734</v>
       </c>
       <c r="O77" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="P77" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="78" spans="1:16">
       <c r="A78" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C78" t="s">
         <v>11</v>
@@ -5735,19 +5735,19 @@
         <v>207</v>
       </c>
       <c r="G78" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H78" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I78" s="3">
         <v>470562</v>
       </c>
       <c r="O78" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="P78" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5755,7 +5755,7 @@
         <v>142</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C79" t="s">
         <v>11</v>
@@ -5790,7 +5790,7 @@
         <v>64</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C80" t="s">
         <v>11</v>
@@ -5825,7 +5825,7 @@
         <v>65</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C81" t="s">
         <v>11</v>
@@ -5860,7 +5860,7 @@
         <v>139</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C82" t="s">
         <v>11</v>
@@ -5892,10 +5892,10 @@
     </row>
     <row r="83" spans="1:16">
       <c r="A83" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>331</v>
       </c>
       <c r="C83" t="s">
         <v>11</v>
@@ -5910,27 +5910,27 @@
         <v>247</v>
       </c>
       <c r="G83" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H83" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I83" s="3">
         <v>154914</v>
       </c>
       <c r="O83" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="84" spans="1:16">
       <c r="A84" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C84" t="s">
         <v>11</v>
@@ -5945,19 +5945,19 @@
         <v>173</v>
       </c>
       <c r="G84" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H84" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I84" s="3">
         <v>147091</v>
       </c>
       <c r="O84" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5965,7 +5965,7 @@
         <v>63</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C85" t="s">
         <v>11</v>
@@ -5997,10 +5997,10 @@
     </row>
     <row r="86" spans="1:16">
       <c r="A86" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C86" t="s">
         <v>11</v>
@@ -6015,19 +6015,19 @@
         <v>158</v>
       </c>
       <c r="G86" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H86" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I86" s="3">
         <v>136234</v>
       </c>
       <c r="O86" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="P86" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6035,7 +6035,7 @@
         <v>141</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C87" t="s">
         <v>11</v>
@@ -6067,10 +6067,10 @@
     </row>
     <row r="88" spans="1:16">
       <c r="A88" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C88" t="s">
         <v>11</v>
@@ -6085,7 +6085,7 @@
         <v>247</v>
       </c>
       <c r="G88" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H88" t="s">
         <v>301</v>
@@ -6094,10 +6094,10 @@
         <v>67758</v>
       </c>
       <c r="O88" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P88" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6105,7 +6105,7 @@
         <v>77</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C89" t="s">
         <v>11</v>
@@ -6140,7 +6140,7 @@
         <v>74</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C90" t="s">
         <v>11</v>
@@ -6172,10 +6172,10 @@
     </row>
     <row r="91" spans="1:16">
       <c r="A91" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C91" t="s">
         <v>11</v>
@@ -6187,30 +6187,30 @@
         <v>292</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G91" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H91" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I91" s="3">
         <v>15835</v>
       </c>
       <c r="O91" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="P91" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="92" spans="1:16">
       <c r="A92" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C92" t="s">
         <v>11</v>
@@ -6225,33 +6225,33 @@
         <v>198</v>
       </c>
       <c r="G92" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H92" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="I92" s="3">
         <v>744361</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="N92" s="3">
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="P92" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="93" spans="1:16">
       <c r="A93" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C93" t="s">
         <v>11</v>
@@ -6266,27 +6266,27 @@
         <v>173</v>
       </c>
       <c r="G93" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="H93" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="N93" s="3">
         <v>2</v>
       </c>
       <c r="O93" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="94" spans="1:16">
       <c r="A94" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C94" t="s">
         <v>11</v>
@@ -6298,30 +6298,30 @@
         <v>291</v>
       </c>
       <c r="F94" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="G94" t="s">
+        <v>574</v>
+      </c>
+      <c r="H94" t="s">
+        <v>572</v>
+      </c>
+      <c r="K94" s="5" t="s">
         <v>578</v>
-      </c>
-      <c r="G94" t="s">
-        <v>576</v>
-      </c>
-      <c r="H94" t="s">
-        <v>574</v>
-      </c>
-      <c r="K94" s="5" t="s">
-        <v>580</v>
       </c>
       <c r="N94" s="3">
         <v>3</v>
       </c>
       <c r="O94" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="95" spans="1:16">
       <c r="A95" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C95" t="s">
         <v>11</v>
@@ -6336,33 +6336,33 @@
         <v>189</v>
       </c>
       <c r="G95" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="H95" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="I95" s="3">
         <v>177237</v>
       </c>
       <c r="K95" s="5" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="N95" s="3">
         <v>5</v>
       </c>
       <c r="O95" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="P95" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="96" spans="1:16">
       <c r="A96" s="1" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="C96" t="s">
         <v>11</v>
@@ -6374,30 +6374,30 @@
         <v>291</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="G96" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="H96" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="I96" s="3">
         <v>51449</v>
       </c>
       <c r="O96" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="P96" s="2" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="97" spans="1:16">
       <c r="A97" s="1" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="C97" t="s">
         <v>11</v>
@@ -6412,27 +6412,27 @@
         <v>195</v>
       </c>
       <c r="G97" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="H97" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="I97" s="3">
         <v>1393142</v>
       </c>
       <c r="O97" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="P97" s="2" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="98" spans="1:16">
       <c r="A98" s="1" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="C98" t="s">
         <v>11</v>
@@ -6447,27 +6447,27 @@
         <v>173</v>
       </c>
       <c r="G98" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="H98" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="I98" s="3">
         <v>768229</v>
       </c>
       <c r="O98" t="s">
+        <v>600</v>
+      </c>
+      <c r="P98" s="2" t="s">
         <v>603</v>
-      </c>
-      <c r="P98" s="2" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="99" spans="1:16">
       <c r="A99" s="1" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="C99" t="s">
         <v>11</v>
@@ -6479,30 +6479,30 @@
         <v>291</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G99" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="H99" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="I99" s="3">
         <v>166812</v>
       </c>
       <c r="O99" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="P99" s="2" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="100" spans="1:16">
       <c r="A100" s="1" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C100" t="s">
         <v>11</v>
@@ -6514,19 +6514,19 @@
         <v>291</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="G100" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="H100" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="O100" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="P100" s="2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
   </sheetData>

--- a/db/A7XLK-1405-TVSeries.xlsx
+++ b/db/A7XLK-1405-TVSeries.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11010"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11114"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C41C3849-54FC-DF4E-86AC-2F0DF1FF0433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68A3E4F4-5E8C-A64C-AA1E-425BF81FF008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="4680" windowWidth="38780" windowHeight="17320" xr2:uid="{BAC94C6D-C196-2D4F-A2F2-89F0A182D671}"/>
   </bookViews>
@@ -2104,10 +2104,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>小捨得</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>宋佳 佟大爲 蔣欣 李佳航 張國立 劉楚恬 李一情 單禹豪</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2320,6 +2316,10 @@
   </si>
   <si>
     <t>我的砍價女王 **</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小捨得 **</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3125,7 +3125,7 @@
         <v>436</v>
       </c>
       <c r="H9" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I9" s="3">
         <v>2330511</v>
@@ -4145,10 +4145,10 @@
     </row>
     <row r="33" spans="1:16">
       <c r="A33" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>580</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>581</v>
       </c>
       <c r="C33" t="s">
         <v>11</v>
@@ -4163,19 +4163,19 @@
         <v>268</v>
       </c>
       <c r="G33" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H33" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="I33" s="3">
         <v>261668</v>
       </c>
       <c r="O33" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -4583,7 +4583,7 @@
         <v>373</v>
       </c>
       <c r="H45" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="I45" s="3">
         <v>954238</v>
@@ -4723,7 +4723,7 @@
         <v>352</v>
       </c>
       <c r="H49" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I49" s="3">
         <v>377267</v>
@@ -6225,25 +6225,25 @@
         <v>198</v>
       </c>
       <c r="G92" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H92" t="s">
-        <v>563</v>
+        <v>621</v>
       </c>
       <c r="I92" s="3">
         <v>744361</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="N92" s="3">
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="P92" s="2" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6266,19 +6266,19 @@
         <v>173</v>
       </c>
       <c r="G93" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H93" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="N93" s="3">
         <v>2</v>
       </c>
       <c r="O93" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6298,22 +6298,22 @@
         <v>291</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="G94" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H94" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="K94" s="5" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="N94" s="3">
         <v>3</v>
       </c>
       <c r="O94" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6336,33 +6336,33 @@
         <v>189</v>
       </c>
       <c r="G95" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H95" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="I95" s="3">
         <v>177237</v>
       </c>
       <c r="K95" s="5" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N95" s="3">
         <v>5</v>
       </c>
       <c r="O95" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="P95" s="2" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="96" spans="1:16">
       <c r="A96" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>589</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>590</v>
       </c>
       <c r="C96" t="s">
         <v>11</v>
@@ -6374,30 +6374,30 @@
         <v>291</v>
       </c>
       <c r="F96" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="G96" t="s">
         <v>591</v>
       </c>
-      <c r="G96" t="s">
-        <v>592</v>
-      </c>
       <c r="H96" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="I96" s="3">
         <v>51449</v>
       </c>
       <c r="O96" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="P96" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="97" spans="1:16">
       <c r="A97" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>596</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>597</v>
       </c>
       <c r="C97" t="s">
         <v>11</v>
@@ -6412,27 +6412,27 @@
         <v>195</v>
       </c>
       <c r="G97" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H97" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="I97" s="3">
         <v>1393142</v>
       </c>
       <c r="O97" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="P97" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="98" spans="1:16">
       <c r="A98" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>601</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>602</v>
       </c>
       <c r="C98" t="s">
         <v>11</v>
@@ -6447,27 +6447,27 @@
         <v>173</v>
       </c>
       <c r="G98" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H98" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="I98" s="3">
         <v>768229</v>
       </c>
       <c r="O98" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="P98" s="2" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="99" spans="1:16">
       <c r="A99" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>608</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>609</v>
       </c>
       <c r="C99" t="s">
         <v>11</v>
@@ -6482,27 +6482,27 @@
         <v>394</v>
       </c>
       <c r="G99" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H99" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I99" s="3">
         <v>166812</v>
       </c>
       <c r="O99" t="s">
+        <v>610</v>
+      </c>
+      <c r="P99" s="2" t="s">
         <v>611</v>
-      </c>
-      <c r="P99" s="2" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="100" spans="1:16">
       <c r="A100" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>615</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>616</v>
       </c>
       <c r="C100" t="s">
         <v>11</v>
@@ -6517,16 +6517,16 @@
         <v>511</v>
       </c>
       <c r="G100" t="s">
+        <v>616</v>
+      </c>
+      <c r="H100" t="s">
         <v>617</v>
       </c>
-      <c r="H100" t="s">
-        <v>618</v>
-      </c>
       <c r="O100" t="s">
+        <v>612</v>
+      </c>
+      <c r="P100" s="2" t="s">
         <v>613</v>
-      </c>
-      <c r="P100" s="2" t="s">
-        <v>614</v>
       </c>
     </row>
   </sheetData>
